--- a/credit_monthly_summary.xlsx
+++ b/credit_monthly_summary.xlsx
@@ -7,12 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Credit Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="debit summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="debit summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Credit Summary'!$A$2:$J$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'debit summary'!$A$1:$O$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'debit summary'!$A$1:$O$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -69,10 +67,10 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -443,481 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>CHASE #3444</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>BEGIN BALANCE</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>CASH / CHECK DEPOSIT</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>NORDSTROM</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>J JILL STORE 69 WA</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>AMAZON MARKETPLACE NA PA</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>AMAZON.COM</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL CREDIT</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>ENDING BALANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n">
-        <v>-227.5</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>-45.98</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>-248.04</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>-250.76</v>
-      </c>
-      <c r="H3" s="3">
-        <f>SUM(C3:G3)</f>
-        <v/>
-      </c>
-      <c r="I3" s="3">
-        <f>'debit summary'!B26</f>
-        <v/>
-      </c>
-      <c r="J3" s="3">
-        <f>B3+H3-I3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>FEB</t>
-        </is>
-      </c>
-      <c r="B4" s="3">
-        <f>J3</f>
-        <v/>
-      </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3">
-        <f>SUM(C4:G4)</f>
-        <v/>
-      </c>
-      <c r="I4" s="3">
-        <f>'debit summary'!C26</f>
-        <v/>
-      </c>
-      <c r="J4" s="3">
-        <f>B4+H4-I4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="B5" s="3">
-        <f>J4</f>
-        <v/>
-      </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3">
-        <f>SUM(C5:G5)</f>
-        <v/>
-      </c>
-      <c r="I5" s="3">
-        <f>'debit summary'!D26</f>
-        <v/>
-      </c>
-      <c r="J5" s="3">
-        <f>B5+H5-I5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>APR</t>
-        </is>
-      </c>
-      <c r="B6" s="3">
-        <f>J5</f>
-        <v/>
-      </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3">
-        <f>SUM(C6:G6)</f>
-        <v/>
-      </c>
-      <c r="I6" s="3">
-        <f>'debit summary'!E26</f>
-        <v/>
-      </c>
-      <c r="J6" s="3">
-        <f>B6+H6-I6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-      <c r="B7" s="3">
-        <f>J6</f>
-        <v/>
-      </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3">
-        <f>SUM(C7:G7)</f>
-        <v/>
-      </c>
-      <c r="I7" s="3">
-        <f>'debit summary'!F26</f>
-        <v/>
-      </c>
-      <c r="J7" s="3">
-        <f>B7+H7-I7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="B8" s="3">
-        <f>J7</f>
-        <v/>
-      </c>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3">
-        <f>SUM(C8:G8)</f>
-        <v/>
-      </c>
-      <c r="I8" s="3">
-        <f>'debit summary'!G26</f>
-        <v/>
-      </c>
-      <c r="J8" s="3">
-        <f>B8+H8-I8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="B9" s="3">
-        <f>J8</f>
-        <v/>
-      </c>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3">
-        <f>SUM(C9:G9)</f>
-        <v/>
-      </c>
-      <c r="I9" s="3">
-        <f>'debit summary'!H26</f>
-        <v/>
-      </c>
-      <c r="J9" s="3">
-        <f>B9+H9-I9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="B10" s="3">
-        <f>J9</f>
-        <v/>
-      </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3">
-        <f>SUM(C10:G10)</f>
-        <v/>
-      </c>
-      <c r="I10" s="3">
-        <f>'debit summary'!I26</f>
-        <v/>
-      </c>
-      <c r="J10" s="3">
-        <f>B10+H10-I10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="B11" s="3">
-        <f>J10</f>
-        <v/>
-      </c>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3">
-        <f>SUM(C11:G11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="3">
-        <f>'debit summary'!J26</f>
-        <v/>
-      </c>
-      <c r="J11" s="3">
-        <f>B11+H11-I11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="B12" s="3">
-        <f>J11</f>
-        <v/>
-      </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3">
-        <f>SUM(C12:G12)</f>
-        <v/>
-      </c>
-      <c r="I12" s="3">
-        <f>'debit summary'!K26</f>
-        <v/>
-      </c>
-      <c r="J12" s="3">
-        <f>B12+H12-I12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>NOV</t>
-        </is>
-      </c>
-      <c r="B13" s="3">
-        <f>J12</f>
-        <v/>
-      </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3">
-        <f>SUM(C13:G13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="3">
-        <f>'debit summary'!L26</f>
-        <v/>
-      </c>
-      <c r="J13" s="3">
-        <f>B13+H13-I13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>DEC</t>
-        </is>
-      </c>
-      <c r="B14" s="3">
-        <f>J13</f>
-        <v/>
-      </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3">
-        <f>SUM(C14:G14)</f>
-        <v/>
-      </c>
-      <c r="I14" s="3">
-        <f>'debit summary'!M26</f>
-        <v/>
-      </c>
-      <c r="J14" s="3">
-        <f>B14+H14-I14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3">
-        <f>SUM(C3:C14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="3">
-        <f>SUM(D3:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="3">
-        <f>SUM(E3:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="3">
-        <f>SUM(F3:F14)</f>
-        <v/>
-      </c>
-      <c r="G15" s="3">
-        <f>SUM(G3:G14)</f>
-        <v/>
-      </c>
-      <c r="H15" s="3">
-        <f>SUM(H3:H14)</f>
-        <v/>
-      </c>
-      <c r="I15" s="3">
-        <f>'debit summary'!N26</f>
-        <v/>
-      </c>
-      <c r="J15" s="3">
-        <f>J14</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:J15"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -938,93 +462,96 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Merchant</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>March</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>#000006632 WITHDRWL</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Prime*Zh8618Uz3 Amzn.Com/Bill WA</t>
         </is>
       </c>
       <c r="B2" s="3">
-        <f>-5000.00</f>
-        <v/>
-      </c>
-      <c r="C2" s="3" t="n"/>
+        <f>16.25</f>
+        <v/>
+      </c>
+      <c r="C2" s="3">
+        <f>16.25</f>
+        <v/>
+      </c>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
@@ -1039,19 +566,22 @@
         <f>SUM(B2:M2)</f>
         <v/>
       </c>
-      <c r="O2" s="1" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>% ARABICA THE GROVE Los Angeles CA</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon.Comseattlewa US</t>
         </is>
       </c>
       <c r="B3" s="3">
-        <f>14.00</f>
-        <v/>
-      </c>
-      <c r="C3" s="3" t="n"/>
+        <f>117.76</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>117.76</f>
+        <v/>
+      </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
@@ -1066,21 +596,21 @@
         <f>SUM(B3:M3)</f>
         <v/>
       </c>
-      <c r="O3" s="1" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>99 RANCH MARKET KENT WA</t>
-        </is>
-      </c>
-      <c r="B4" s="3">
-        <f>90.44</f>
-        <v/>
-      </c>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>BCD-WILSHIRE 0000 LOS ANGELES CA</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
+      <c r="E4" s="3">
+        <f>75.20</f>
+        <v/>
+      </c>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
@@ -1093,21 +623,21 @@
         <f>SUM(B4:M4)</f>
         <v/>
       </c>
-      <c r="O4" s="1" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>ACE PARKING LOT SEATTLE WA</t>
-        </is>
-      </c>
-      <c r="B5" s="3">
-        <f>18.00</f>
-        <v/>
-      </c>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>BROOKS BROTHERS CABAZON CA</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
+      <c r="E5" s="3">
+        <f>501.72</f>
+        <v/>
+      </c>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
@@ -1120,19 +650,22 @@
         <f>SUM(B5:M5)</f>
         <v/>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>BCD-IRVINE 0000 IRVINE CA</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Citi Card Onlinepayment</t>
         </is>
       </c>
       <c r="B6" s="3">
-        <f>72.41</f>
-        <v/>
-      </c>
-      <c r="C6" s="3" t="n"/>
+        <f>975.00+364.75+1400.00</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>975.00+364.75+1400.00</f>
+        <v/>
+      </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
@@ -1147,19 +680,22 @@
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
-      <c r="O6" s="1" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>BCD-WILSHIRE 0000 LOS ANGELES CA</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Credit One Bank Payment</t>
         </is>
       </c>
       <c r="B7" s="3">
-        <f>75.20+73.43</f>
-        <v/>
-      </c>
-      <c r="C7" s="3" t="n"/>
+        <f>817.29</f>
+        <v/>
+      </c>
+      <c r="C7" s="3">
+        <f>817.29</f>
+        <v/>
+      </c>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
@@ -1174,21 +710,21 @@
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
-      <c r="O7" s="1" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>BROOKS BROTHERS CABAZON CA</t>
-        </is>
-      </c>
-      <c r="B8" s="3">
-        <f>501.72</f>
-        <v/>
-      </c>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
+      <c r="E8" s="3">
+        <f>18.58</f>
+        <v/>
+      </c>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="n"/>
@@ -1201,21 +737,21 @@
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
-      <c r="O8" s="1" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>DIPTYQUE GROVE 930579840142026 LOS ANGELES CA</t>
-        </is>
-      </c>
-      <c r="B9" s="3">
-        <f>136.89</f>
-        <v/>
-      </c>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GANNI INC NEW YORK NY</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
+      <c r="E9" s="3">
+        <f>75.64</f>
+        <v/>
+      </c>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
@@ -1228,21 +764,21 @@
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
-      <c r="O9" s="1" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>ERMENEGILDO ZEGNA CORPORATION ALBANY NY</t>
-        </is>
-      </c>
-      <c r="B10" s="3">
-        <f>906.72</f>
-        <v/>
-      </c>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>H MART IRVINE INC 1822 IRVINE CA</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
+      <c r="E10" s="3">
+        <f>31.93</f>
+        <v/>
+      </c>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="3" t="n"/>
@@ -1255,21 +791,21 @@
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
-      <c r="O10" s="1" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
-        </is>
-      </c>
-      <c r="B11" s="3">
-        <f>18.58</f>
-        <v/>
-      </c>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>IN-N-OUT CABAZON CABAZON CA</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
+      <c r="E11" s="3">
+        <f>15.62</f>
+        <v/>
+      </c>
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n"/>
@@ -1282,19 +818,22 @@
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
-      <c r="O11" s="1" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>FT LEWIS COMMISSARY 000001222 FORT LEWIS WA</t>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Irs Usataxpymt</t>
         </is>
       </c>
       <c r="B12" s="3">
-        <f>98.94</f>
-        <v/>
-      </c>
-      <c r="C12" s="3" t="n"/>
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
+      <c r="C12" s="3">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
@@ -1309,19 +848,22 @@
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
-      <c r="O12" s="1" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>GANNI INC NEW YORK NY</t>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Kindercare Portland OR</t>
         </is>
       </c>
       <c r="B13" s="3">
-        <f>75.64</f>
-        <v/>
-      </c>
-      <c r="C13" s="3" t="n"/>
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
@@ -1336,21 +878,21 @@
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
-      <c r="O13" s="1" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>H MART IRVINE INC 1822 IRVINE CA</t>
-        </is>
-      </c>
-      <c r="B14" s="3">
-        <f>31.93</f>
-        <v/>
-      </c>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
+      <c r="E14" s="3">
+        <f>413.63</f>
+        <v/>
+      </c>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="3" t="n"/>
@@ -1363,19 +905,22 @@
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
-      <c r="O14" s="1" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IN-N-OUT CABAZON CABAZON CA</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Nys Dtf Pit Tax Paymnt</t>
         </is>
       </c>
       <c r="B15" s="3">
-        <f>15.62</f>
-        <v/>
-      </c>
-      <c r="C15" s="3" t="n"/>
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
+      <c r="C15" s="3">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
@@ -1390,21 +935,21 @@
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
-      <c r="O15" s="1" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>LAZ PARKING M17154 0000 LOS ANGELES CA</t>
-        </is>
-      </c>
-      <c r="B16" s="3">
-        <f>10.00</f>
-        <v/>
-      </c>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>PANDA EXPRESS TACOMA WA</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
+      <c r="E16" s="3">
+        <f>28.49</f>
+        <v/>
+      </c>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="3" t="n"/>
@@ -1417,19 +962,22 @@
         <f>SUM(B16:M16)</f>
         <v/>
       </c>
-      <c r="O16" s="1" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>MEI WA BAKERY 00-08043154247 KENT WA</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
         </is>
       </c>
       <c r="B17" s="3">
-        <f>20.80</f>
-        <v/>
-      </c>
-      <c r="C17" s="3" t="n"/>
+        <f>343.93</f>
+        <v/>
+      </c>
+      <c r="C17" s="3">
+        <f>343.93</f>
+        <v/>
+      </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
@@ -1444,19 +992,22 @@
         <f>SUM(B17:M17)</f>
         <v/>
       </c>
-      <c r="O17" s="1" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
         </is>
       </c>
       <c r="B18" s="3">
-        <f>413.63</f>
-        <v/>
-      </c>
-      <c r="C18" s="3" t="n"/>
+        <f>17.59</f>
+        <v/>
+      </c>
+      <c r="C18" s="3">
+        <f>17.59</f>
+        <v/>
+      </c>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
@@ -1471,19 +1022,22 @@
         <f>SUM(B18:M18)</f>
         <v/>
       </c>
-      <c r="O18" s="1" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>PANDA EXPRESS TACOMA WA</t>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
         </is>
       </c>
       <c r="B19" s="3">
-        <f>28.49</f>
-        <v/>
-      </c>
-      <c r="C19" s="3" t="n"/>
+        <f>152.14</f>
+        <v/>
+      </c>
+      <c r="C19" s="3">
+        <f>152.14</f>
+        <v/>
+      </c>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
@@ -1498,19 +1052,22 @@
         <f>SUM(B19:M19)</f>
         <v/>
       </c>
-      <c r="O19" s="1" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>SEA AIRPORT PARKING 0000 SEATTLE WA</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
         </is>
       </c>
       <c r="B20" s="3">
-        <f>98.00</f>
-        <v/>
-      </c>
-      <c r="C20" s="3" t="n"/>
+        <f>71.79</f>
+        <v/>
+      </c>
+      <c r="C20" s="3">
+        <f>71.79</f>
+        <v/>
+      </c>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
@@ -1525,19 +1082,22 @@
         <f>SUM(B20:M20)</f>
         <v/>
       </c>
-      <c r="O20" s="1" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>SP ALO-YOGA COMMERCE CA</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
         </is>
       </c>
       <c r="B21" s="3">
-        <f>282.52</f>
-        <v/>
-      </c>
-      <c r="C21" s="3" t="n"/>
+        <f>18.75</f>
+        <v/>
+      </c>
+      <c r="C21" s="3">
+        <f>18.75</f>
+        <v/>
+      </c>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
@@ -1552,19 +1112,22 @@
         <f>SUM(B21:M21)</f>
         <v/>
       </c>
-      <c r="O21" s="1" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>TAKASHIMA -IRVINE 0000 IRVINE CA</t>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
         </is>
       </c>
       <c r="B22" s="3">
-        <f>96.95</f>
-        <v/>
-      </c>
-      <c r="C22" s="3" t="n"/>
+        <f>50.03</f>
+        <v/>
+      </c>
+      <c r="C22" s="3">
+        <f>50.03</f>
+        <v/>
+      </c>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n"/>
@@ -1579,19 +1142,22 @@
         <f>SUM(B22:M22)</f>
         <v/>
       </c>
-      <c r="O22" s="1" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>TEMU.COM TEMU.COM DE</t>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*V25 Seattle WA</t>
         </is>
       </c>
       <c r="B23" s="3">
-        <f>19.48</f>
-        <v/>
-      </c>
-      <c r="C23" s="3" t="n"/>
+        <f>20.80</f>
+        <v/>
+      </c>
+      <c r="C23" s="3">
+        <f>20.80</f>
+        <v/>
+      </c>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n"/>
@@ -1606,19 +1172,22 @@
         <f>SUM(B23:M23)</f>
         <v/>
       </c>
-      <c r="O23" s="1" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>WHOLE FOODS MARKET/CHB 000010588 UNIVERSITY PL WA</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
         </is>
       </c>
       <c r="B24" s="3">
-        <f>7.51</f>
-        <v/>
-      </c>
-      <c r="C24" s="3" t="n"/>
+        <f>40.33</f>
+        <v/>
+      </c>
+      <c r="C24" s="3">
+        <f>40.33</f>
+        <v/>
+      </c>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
@@ -1633,23 +1202,22 @@
         <f>SUM(B24:M24)</f>
         <v/>
       </c>
-      <c r="O24" s="1" t="inlineStr">
-        <is>
-          <t>Grocery</t>
-        </is>
-      </c>
+      <c r="O24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Prog Casualty Ins Prem</t>
         </is>
       </c>
       <c r="B25" s="3">
-        <f>95.44+101.98+76.47</f>
-        <v/>
-      </c>
-      <c r="C25" s="3" t="n"/>
+        <f>930.52</f>
+        <v/>
+      </c>
+      <c r="C25" s="3">
+        <f>930.52</f>
+        <v/>
+      </c>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n"/>
@@ -1664,70 +1232,158 @@
         <f>SUM(B25:M25)</f>
         <v/>
       </c>
-      <c r="O25" s="1" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B26" s="3">
-        <f>SUM(B2:B25)</f>
-        <v/>
-      </c>
-      <c r="C26" s="3">
-        <f>SUM(C2:C25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="3">
-        <f>SUM(D2:D25)</f>
-        <v/>
-      </c>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>WHOLE FOODS MARKET/CHB 000010588 UNIVERSITY PL WA</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
       <c r="E26" s="3">
-        <f>SUM(E2:E25)</f>
-        <v/>
-      </c>
-      <c r="F26" s="3">
-        <f>SUM(F2:F25)</f>
-        <v/>
-      </c>
-      <c r="G26" s="3">
-        <f>SUM(G2:G25)</f>
-        <v/>
-      </c>
-      <c r="H26" s="3">
-        <f>SUM(H2:H25)</f>
-        <v/>
-      </c>
-      <c r="I26" s="3">
-        <f>SUM(I2:I25)</f>
-        <v/>
-      </c>
-      <c r="J26" s="3">
-        <f>SUM(J2:J25)</f>
-        <v/>
-      </c>
-      <c r="K26" s="3">
-        <f>SUM(K2:K25)</f>
-        <v/>
-      </c>
-      <c r="L26" s="3">
-        <f>SUM(L2:L25)</f>
-        <v/>
-      </c>
-      <c r="M26" s="3">
-        <f>SUM(M2:M25)</f>
-        <v/>
-      </c>
+        <f>7.51</f>
+        <v/>
+      </c>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="3" t="n"/>
+      <c r="M26" s="3" t="n"/>
       <c r="N26" s="3">
         <f>SUM(B26:M26)</f>
         <v/>
       </c>
-      <c r="O26" s="1" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3">
+        <f>95.44+101.98+76.47</f>
+        <v/>
+      </c>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3">
+        <f>SUM(B27:M27)</f>
+        <v/>
+      </c>
+      <c r="O27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Withdrawal Branch 0964 New York</t>
+        </is>
+      </c>
+      <c r="B28" s="3">
+        <f>3200.00</f>
+        <v/>
+      </c>
+      <c r="C28" s="3">
+        <f>3200.00</f>
+        <v/>
+      </c>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="n"/>
+      <c r="M28" s="3" t="n"/>
+      <c r="N28" s="3">
+        <f>SUM(B28:M28)</f>
+        <v/>
+      </c>
+      <c r="O28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B29" s="3">
+        <f>SUM(B2:B28)</f>
+        <v/>
+      </c>
+      <c r="C29" s="3">
+        <f>SUM(C2:C28)</f>
+        <v/>
+      </c>
+      <c r="D29" s="3">
+        <f>SUM(D2:D28)</f>
+        <v/>
+      </c>
+      <c r="E29" s="3">
+        <f>SUM(E2:E28)</f>
+        <v/>
+      </c>
+      <c r="F29" s="3">
+        <f>SUM(F2:F28)</f>
+        <v/>
+      </c>
+      <c r="G29" s="3">
+        <f>SUM(G2:G28)</f>
+        <v/>
+      </c>
+      <c r="H29" s="3">
+        <f>SUM(H2:H28)</f>
+        <v/>
+      </c>
+      <c r="I29" s="3">
+        <f>SUM(I2:I28)</f>
+        <v/>
+      </c>
+      <c r="J29" s="3">
+        <f>SUM(J2:J28)</f>
+        <v/>
+      </c>
+      <c r="K29" s="3">
+        <f>SUM(K2:K28)</f>
+        <v/>
+      </c>
+      <c r="L29" s="3">
+        <f>SUM(L2:L28)</f>
+        <v/>
+      </c>
+      <c r="M29" s="3">
+        <f>SUM(M2:M28)</f>
+        <v/>
+      </c>
+      <c r="N29" s="3">
+        <f>SUM(B29:M29)</f>
+        <v/>
+      </c>
+      <c r="O29" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O26"/>
+  <autoFilter ref="A1:O29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/credit_monthly_summary.xlsx
+++ b/credit_monthly_summary.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="debit summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Credit Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="debit summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'debit summary'!$A$1:$O$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Credit Summary'!$A$2:$S$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'debit summary'!$A$1:$O$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -67,10 +69,10 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -441,7 +443,696 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:S15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>CHASE #3444</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>BEGIN BALANCE</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CASH / CHECK DEPOSIT</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>NO1 SUSHI 88 CORKBBO ACH</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>VEOLIA WATER</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ORANGE &amp; ROCKLAND</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>WITHDRAWAL BRANCH 0964</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>BILL PAY:VEOLIA WATER NEW Y 200045 6BU1T6KR</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>BILL PAY:ORANGE &amp; ROCKLAND 136130 6BQ1P6KR</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>INTERNET TRF TO CLIENT-ADDED TRANSFER ACCOUNT</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>WITHDRAWAL BRANCH 0964 NEW YORK</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*NX6 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*9O5 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*SB8 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>NYS DTF PIT TAX PAYMNT</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL CREDIT</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>ENDING BALANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3">
+        <f>SUM(C3:P3)</f>
+        <v/>
+      </c>
+      <c r="R3" s="3">
+        <f>'debit summary'!B41</f>
+        <v/>
+      </c>
+      <c r="S3" s="3">
+        <f>B3+Q3-R3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>S3</f>
+        <v/>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3">
+        <f>SUM(C4:P4)</f>
+        <v/>
+      </c>
+      <c r="R4" s="3">
+        <f>'debit summary'!C41</f>
+        <v/>
+      </c>
+      <c r="S4" s="3">
+        <f>B4+Q4-R4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>S4</f>
+        <v/>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3">
+        <f>SUM(C5:P5)</f>
+        <v/>
+      </c>
+      <c r="R5" s="3">
+        <f>'debit summary'!D41</f>
+        <v/>
+      </c>
+      <c r="S5" s="3">
+        <f>B5+Q5-R5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>NOV</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>S5</f>
+        <v/>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3">
+        <f>SUM(C6:P6)</f>
+        <v/>
+      </c>
+      <c r="R6" s="3">
+        <f>'debit summary'!E41</f>
+        <v/>
+      </c>
+      <c r="S6" s="3">
+        <f>B6+Q6-R6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>S6</f>
+        <v/>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="n"/>
+      <c r="Q7" s="3">
+        <f>SUM(C7:P7)</f>
+        <v/>
+      </c>
+      <c r="R7" s="3">
+        <f>'debit summary'!F41</f>
+        <v/>
+      </c>
+      <c r="S7" s="3">
+        <f>B7+Q7-R7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>S7</f>
+        <v/>
+      </c>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>740</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q8" s="3">
+        <f>SUM(C8:P8)</f>
+        <v/>
+      </c>
+      <c r="R8" s="3">
+        <f>'debit summary'!G41</f>
+        <v/>
+      </c>
+      <c r="S8" s="3">
+        <f>B8+Q8-R8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>FEB</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>S8</f>
+        <v/>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="n"/>
+      <c r="Q9" s="3">
+        <f>SUM(C9:P9)</f>
+        <v/>
+      </c>
+      <c r="R9" s="3">
+        <f>'debit summary'!H41</f>
+        <v/>
+      </c>
+      <c r="S9" s="3">
+        <f>B9+Q9-R9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>S9</f>
+        <v/>
+      </c>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="n"/>
+      <c r="Q10" s="3">
+        <f>SUM(C10:P10)</f>
+        <v/>
+      </c>
+      <c r="R10" s="3">
+        <f>'debit summary'!I41</f>
+        <v/>
+      </c>
+      <c r="S10" s="3">
+        <f>B10+Q10-R10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>APR</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>S10</f>
+        <v/>
+      </c>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3">
+        <f>SUM(C11:P11)</f>
+        <v/>
+      </c>
+      <c r="R11" s="3">
+        <f>'debit summary'!J41</f>
+        <v/>
+      </c>
+      <c r="S11" s="3">
+        <f>B11+Q11-R11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>S11</f>
+        <v/>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="3" t="n"/>
+      <c r="Q12" s="3">
+        <f>SUM(C12:P12)</f>
+        <v/>
+      </c>
+      <c r="R12" s="3">
+        <f>'debit summary'!K41</f>
+        <v/>
+      </c>
+      <c r="S12" s="3">
+        <f>B12+Q12-R12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>JUN</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>S12</f>
+        <v/>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="n"/>
+      <c r="Q13" s="3">
+        <f>SUM(C13:P13)</f>
+        <v/>
+      </c>
+      <c r="R13" s="3">
+        <f>'debit summary'!L41</f>
+        <v/>
+      </c>
+      <c r="S13" s="3">
+        <f>B13+Q13-R13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>S13</f>
+        <v/>
+      </c>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3" t="n"/>
+      <c r="O14" s="3" t="n"/>
+      <c r="P14" s="3" t="n"/>
+      <c r="Q14" s="3">
+        <f>SUM(C14:P14)</f>
+        <v/>
+      </c>
+      <c r="R14" s="3">
+        <f>'debit summary'!M41</f>
+        <v/>
+      </c>
+      <c r="S14" s="3">
+        <f>B14+Q14-R14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3">
+        <f>SUM(C3:C14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="3">
+        <f>SUM(D3:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="3">
+        <f>SUM(E3:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="3">
+        <f>SUM(F3:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="3">
+        <f>SUM(G3:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="3">
+        <f>SUM(H3:H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="3">
+        <f>SUM(I3:I14)</f>
+        <v/>
+      </c>
+      <c r="J15" s="3">
+        <f>SUM(J3:J14)</f>
+        <v/>
+      </c>
+      <c r="K15" s="3">
+        <f>SUM(K3:K14)</f>
+        <v/>
+      </c>
+      <c r="L15" s="3">
+        <f>SUM(L3:L14)</f>
+        <v/>
+      </c>
+      <c r="M15" s="3">
+        <f>SUM(M3:M14)</f>
+        <v/>
+      </c>
+      <c r="N15" s="3">
+        <f>SUM(N3:N14)</f>
+        <v/>
+      </c>
+      <c r="O15" s="3">
+        <f>SUM(O3:O14)</f>
+        <v/>
+      </c>
+      <c r="P15" s="3">
+        <f>SUM(P3:P14)</f>
+        <v/>
+      </c>
+      <c r="Q15" s="3">
+        <f>SUM(Q3:Q14)</f>
+        <v/>
+      </c>
+      <c r="R15" s="3">
+        <f>'debit summary'!N41</f>
+        <v/>
+      </c>
+      <c r="S15" s="3">
+        <f>S14</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:S15"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -462,96 +1153,90 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Merchant</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>NOV</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>FEB</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>APR</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>JUN</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Prime*Zh8618Uz3 Amzn.Com/Bill WA</t>
-        </is>
-      </c>
-      <c r="B2" s="3">
-        <f>16.25</f>
-        <v/>
-      </c>
-      <c r="C2" s="3">
-        <f>16.25</f>
-        <v/>
-      </c>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>434 / Nys Commission</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
@@ -566,22 +1251,20 @@
         <f>SUM(B2:M2)</f>
         <v/>
       </c>
-      <c r="O2" s="2" t="inlineStr"/>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>GERCORY</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Amazon.Comseattlewa US</t>
-        </is>
-      </c>
-      <c r="B3" s="3">
-        <f>117.76</f>
-        <v/>
-      </c>
-      <c r="C3" s="3">
-        <f>117.76</f>
-        <v/>
-      </c>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Amazon Prime*Zh8618Uz3 Amzn.Com/Bill WA</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
@@ -596,21 +1279,22 @@
         <f>SUM(B3:M3)</f>
         <v/>
       </c>
-      <c r="O3" s="2" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>GERCORY</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>BCD-WILSHIRE 0000 LOS ANGELES CA</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Amazon.Com*N22Fjseattlewa US</t>
         </is>
       </c>
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3">
-        <f>75.20</f>
-        <v/>
-      </c>
+      <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
@@ -623,21 +1307,22 @@
         <f>SUM(B4:M4)</f>
         <v/>
       </c>
-      <c r="O4" s="2" t="inlineStr"/>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>GERCORY</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>BROOKS BROTHERS CABAZON CA</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Amazon.Comseattlewa US</t>
         </is>
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3">
-        <f>501.72</f>
-        <v/>
-      </c>
+      <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
@@ -650,22 +1335,20 @@
         <f>SUM(B5:M5)</f>
         <v/>
       </c>
-      <c r="O5" s="2" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>GERCORY</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Citi Card Onlinepayment</t>
-        </is>
-      </c>
-      <c r="B6" s="3">
-        <f>975.00+364.75+1400.00</f>
-        <v/>
-      </c>
-      <c r="C6" s="3">
-        <f>975.00+364.75+1400.00</f>
-        <v/>
-      </c>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Amex Epayment ACH Pmt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
@@ -680,22 +1363,20 @@
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
-      <c r="O6" s="2" t="inlineStr"/>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>GERCORY</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Credit One Bank Payment</t>
-        </is>
-      </c>
-      <c r="B7" s="3">
-        <f>817.29</f>
-        <v/>
-      </c>
-      <c r="C7" s="3">
-        <f>817.29</f>
-        <v/>
-      </c>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Arrow Bank Na Web Pmt</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
@@ -710,21 +1391,22 @@
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
-      <c r="O7" s="2" t="inlineStr"/>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>GERCORY</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Bill Pay:Associated Mutual 210061 Ubq1P6Kr</t>
         </is>
       </c>
       <c r="B8" s="3" t="n"/>
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3">
-        <f>18.58</f>
-        <v/>
-      </c>
+      <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="n"/>
@@ -737,21 +1419,22 @@
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
-      <c r="O8" s="2" t="inlineStr"/>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>GERCORY</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>GANNI INC NEW YORK NY</t>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
         </is>
       </c>
       <c r="B9" s="3" t="n"/>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3">
-        <f>75.64</f>
-        <v/>
-      </c>
+      <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
@@ -764,22 +1447,26 @@
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
-      <c r="O9" s="2" t="inlineStr"/>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>H MART IRVINE INC 1822 IRVINE CA</t>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
         </is>
       </c>
       <c r="B10" s="3" t="n"/>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3">
-        <f>31.93</f>
-        <v/>
-      </c>
-      <c r="F10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3">
+        <f>350.00</f>
+        <v/>
+      </c>
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
@@ -791,21 +1478,22 @@
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
-      <c r="O10" s="2" t="inlineStr"/>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>IN-N-OUT CABAZON CABAZON CA</t>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Bill Pay:Orange &amp; Rockland 879293 5Bq1P6Kr</t>
         </is>
       </c>
       <c r="B11" s="3" t="n"/>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3">
-        <f>15.62</f>
-        <v/>
-      </c>
+      <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n"/>
@@ -818,25 +1506,26 @@
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
-      <c r="O11" s="2" t="inlineStr"/>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Irs Usataxpymt</t>
-        </is>
-      </c>
-      <c r="B12" s="3">
-        <f>800.00+800.00</f>
-        <v/>
-      </c>
-      <c r="C12" s="3">
-        <f>800.00+800.00</f>
-        <v/>
-      </c>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
+      <c r="F12" s="3">
+        <f>300.00</f>
+        <v/>
+      </c>
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="3" t="n"/>
@@ -848,22 +1537,20 @@
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
-      <c r="O12" s="2" t="inlineStr"/>
+      <c r="O12" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Kindercare Portland OR</t>
-        </is>
-      </c>
-      <c r="B13" s="3">
-        <f>490.00+120.00</f>
-        <v/>
-      </c>
-      <c r="C13" s="3">
-        <f>490.00+120.00</f>
-        <v/>
-      </c>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Bill Pay:Veolia Water New Y 200054 Hbu1T6Kr</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
@@ -878,21 +1565,22 @@
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
-      <c r="O13" s="2" t="inlineStr"/>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Citi Card Onlinepayment</t>
         </is>
       </c>
       <c r="B14" s="3" t="n"/>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3">
-        <f>413.63</f>
-        <v/>
-      </c>
+      <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="3" t="n"/>
@@ -905,22 +1593,20 @@
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
-      <c r="O14" s="2" t="inlineStr"/>
+      <c r="O14" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Nys Dtf Pit Tax Paymnt</t>
-        </is>
-      </c>
-      <c r="B15" s="3">
-        <f>200.00+200.00</f>
-        <v/>
-      </c>
-      <c r="C15" s="3">
-        <f>200.00+200.00</f>
-        <v/>
-      </c>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Credit One Bank Payment</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
@@ -935,21 +1621,22 @@
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
-      <c r="O15" s="2" t="inlineStr"/>
+      <c r="O15" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>PANDA EXPRESS TACOMA WA</t>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Discover Bank Net/Mobile</t>
         </is>
       </c>
       <c r="B16" s="3" t="n"/>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3">
-        <f>28.49</f>
-        <v/>
-      </c>
+      <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="3" t="n"/>
@@ -962,22 +1649,20 @@
         <f>SUM(B16:M16)</f>
         <v/>
       </c>
-      <c r="O16" s="2" t="inlineStr"/>
+      <c r="O16" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B17" s="3">
-        <f>343.93</f>
-        <v/>
-      </c>
-      <c r="C17" s="3">
-        <f>343.93</f>
-        <v/>
-      </c>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
@@ -992,22 +1677,20 @@
         <f>SUM(B17:M17)</f>
         <v/>
       </c>
-      <c r="O17" s="2" t="inlineStr"/>
+      <c r="O17" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B18" s="3">
-        <f>17.59</f>
-        <v/>
-      </c>
-      <c r="C18" s="3">
-        <f>17.59</f>
-        <v/>
-      </c>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Huntington Banksil Payment</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
@@ -1022,25 +1705,26 @@
         <f>SUM(B18:M18)</f>
         <v/>
       </c>
-      <c r="O18" s="2" t="inlineStr"/>
+      <c r="O18" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B19" s="3">
-        <f>152.14</f>
-        <v/>
-      </c>
-      <c r="C19" s="3">
-        <f>152.14</f>
-        <v/>
-      </c>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Internet Trf To Client-Added Transfer Account</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
+      <c r="F19" s="3">
+        <f>740.00</f>
+        <v/>
+      </c>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n"/>
@@ -1052,22 +1736,20 @@
         <f>SUM(B19:M19)</f>
         <v/>
       </c>
-      <c r="O19" s="2" t="inlineStr"/>
+      <c r="O19" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B20" s="3">
-        <f>71.79</f>
-        <v/>
-      </c>
-      <c r="C20" s="3">
-        <f>71.79</f>
-        <v/>
-      </c>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Irs Usataxpymt</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
@@ -1082,22 +1764,20 @@
         <f>SUM(B20:M20)</f>
         <v/>
       </c>
-      <c r="O20" s="2" t="inlineStr"/>
+      <c r="O20" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B21" s="3">
-        <f>18.75</f>
-        <v/>
-      </c>
-      <c r="C21" s="3">
-        <f>18.75</f>
-        <v/>
-      </c>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Kindercare Portland OR</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
@@ -1112,22 +1792,20 @@
         <f>SUM(B21:M21)</f>
         <v/>
       </c>
-      <c r="O21" s="2" t="inlineStr"/>
+      <c r="O21" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B22" s="3">
-        <f>50.03</f>
-        <v/>
-      </c>
-      <c r="C22" s="3">
-        <f>50.03</f>
-        <v/>
-      </c>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>No1 Sushi 88 Corkbbo ACH</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n"/>
@@ -1142,22 +1820,20 @@
         <f>SUM(B22:M22)</f>
         <v/>
       </c>
-      <c r="O22" s="2" t="inlineStr"/>
+      <c r="O22" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*V25 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B23" s="3">
-        <f>20.80</f>
-        <v/>
-      </c>
-      <c r="C23" s="3">
-        <f>20.80</f>
-        <v/>
-      </c>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n"/>
@@ -1172,25 +1848,26 @@
         <f>SUM(B23:M23)</f>
         <v/>
       </c>
-      <c r="O23" s="2" t="inlineStr"/>
+      <c r="O23" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B24" s="3">
-        <f>40.33</f>
-        <v/>
-      </c>
-      <c r="C24" s="3">
-        <f>40.33</f>
-        <v/>
-      </c>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Nys Dtf Pit Tax Paymnt</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
+      <c r="F24" s="3">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="n"/>
@@ -1202,22 +1879,20 @@
         <f>SUM(B24:M24)</f>
         <v/>
       </c>
-      <c r="O24" s="2" t="inlineStr"/>
+      <c r="O24" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Prog Casualty Ins Prem</t>
-        </is>
-      </c>
-      <c r="B25" s="3">
-        <f>930.52</f>
-        <v/>
-      </c>
-      <c r="C25" s="3">
-        <f>930.52</f>
-        <v/>
-      </c>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>PANDA EXPRESS TACOMA WA</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n"/>
@@ -1232,21 +1907,22 @@
         <f>SUM(B25:M25)</f>
         <v/>
       </c>
-      <c r="O25" s="2" t="inlineStr"/>
+      <c r="O25" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>WHOLE FOODS MARKET/CHB 000010588 UNIVERSITY PL WA</t>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Paypal Inst Xfer</t>
         </is>
       </c>
       <c r="B26" s="3" t="n"/>
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3">
-        <f>7.51</f>
-        <v/>
-      </c>
+      <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n"/>
       <c r="G26" s="3" t="n"/>
       <c r="H26" s="3" t="n"/>
@@ -1259,26 +1935,26 @@
         <f>SUM(B26:M26)</f>
         <v/>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>Grocery</t>
+      <c r="O26" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*9O5 Seattle WA</t>
         </is>
       </c>
       <c r="B27" s="3" t="n"/>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3">
-        <f>95.44+101.98+76.47</f>
-        <v/>
-      </c>
-      <c r="F27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3">
+        <f>26.57</f>
+        <v/>
+      </c>
       <c r="G27" s="3" t="n"/>
       <c r="H27" s="3" t="n"/>
       <c r="I27" s="3" t="n"/>
@@ -1290,22 +1966,20 @@
         <f>SUM(B27:M27)</f>
         <v/>
       </c>
-      <c r="O27" s="2" t="inlineStr"/>
+      <c r="O27" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Withdrawal Branch 0964 New York</t>
-        </is>
-      </c>
-      <c r="B28" s="3">
-        <f>3200.00</f>
-        <v/>
-      </c>
-      <c r="C28" s="3">
-        <f>3200.00</f>
-        <v/>
-      </c>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n"/>
@@ -1320,70 +1994,419 @@
         <f>SUM(B28:M28)</f>
         <v/>
       </c>
-      <c r="O28" s="2" t="inlineStr"/>
+      <c r="O28" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B29" s="3">
-        <f>SUM(B2:B28)</f>
-        <v/>
-      </c>
-      <c r="C29" s="3">
-        <f>SUM(C2:C28)</f>
-        <v/>
-      </c>
-      <c r="D29" s="3">
-        <f>SUM(D2:D28)</f>
-        <v/>
-      </c>
-      <c r="E29" s="3">
-        <f>SUM(E2:E28)</f>
-        <v/>
-      </c>
-      <c r="F29" s="3">
-        <f>SUM(F2:F28)</f>
-        <v/>
-      </c>
-      <c r="G29" s="3">
-        <f>SUM(G2:G28)</f>
-        <v/>
-      </c>
-      <c r="H29" s="3">
-        <f>SUM(H2:H28)</f>
-        <v/>
-      </c>
-      <c r="I29" s="3">
-        <f>SUM(I2:I28)</f>
-        <v/>
-      </c>
-      <c r="J29" s="3">
-        <f>SUM(J2:J28)</f>
-        <v/>
-      </c>
-      <c r="K29" s="3">
-        <f>SUM(K2:K28)</f>
-        <v/>
-      </c>
-      <c r="L29" s="3">
-        <f>SUM(L2:L28)</f>
-        <v/>
-      </c>
-      <c r="M29" s="3">
-        <f>SUM(M2:M28)</f>
-        <v/>
-      </c>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
       <c r="N29" s="3">
         <f>SUM(B29:M29)</f>
         <v/>
       </c>
-      <c r="O29" s="2" t="inlineStr"/>
+      <c r="O29" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="3">
+        <f>SUM(B30:M30)</f>
+        <v/>
+      </c>
+      <c r="O30" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3">
+        <f>SUM(B31:M31)</f>
+        <v/>
+      </c>
+      <c r="O31" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Nx6 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3">
+        <f>75.40</f>
+        <v/>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="n"/>
+      <c r="M32" s="3" t="n"/>
+      <c r="N32" s="3">
+        <f>SUM(B32:M32)</f>
+        <v/>
+      </c>
+      <c r="O32" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3">
+        <f>18.75</f>
+        <v/>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3">
+        <f>SUM(B33:M33)</f>
+        <v/>
+      </c>
+      <c r="O33" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="3" t="n"/>
+      <c r="K34" s="3" t="n"/>
+      <c r="L34" s="3" t="n"/>
+      <c r="M34" s="3" t="n"/>
+      <c r="N34" s="3">
+        <f>SUM(B34:M34)</f>
+        <v/>
+      </c>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*V25 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3">
+        <f>SUM(B35:M35)</f>
+        <v/>
+      </c>
+      <c r="O35" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Yr6 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+      <c r="I36" s="3" t="n"/>
+      <c r="J36" s="3" t="n"/>
+      <c r="K36" s="3" t="n"/>
+      <c r="L36" s="3" t="n"/>
+      <c r="M36" s="3" t="n"/>
+      <c r="N36" s="3">
+        <f>SUM(B36:M36)</f>
+        <v/>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="n"/>
+      <c r="L37" s="3" t="n"/>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3">
+        <f>SUM(B37:M37)</f>
+        <v/>
+      </c>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Prog Casualty Ins Prem</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+      <c r="I38" s="3" t="n"/>
+      <c r="J38" s="3" t="n"/>
+      <c r="K38" s="3" t="n"/>
+      <c r="L38" s="3" t="n"/>
+      <c r="M38" s="3" t="n"/>
+      <c r="N38" s="3">
+        <f>SUM(B38:M38)</f>
+        <v/>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3">
+        <f>SUM(B39:M39)</f>
+        <v/>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Withdrawal Branch 0964 New York</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3">
+        <f>1000.00</f>
+        <v/>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="n"/>
+      <c r="J40" s="3" t="n"/>
+      <c r="K40" s="3" t="n"/>
+      <c r="L40" s="3" t="n"/>
+      <c r="M40" s="3" t="n"/>
+      <c r="N40" s="3">
+        <f>SUM(B40:M40)</f>
+        <v/>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B41" s="3">
+        <f>SUM(B2:B40)</f>
+        <v/>
+      </c>
+      <c r="C41" s="3">
+        <f>SUM(C2:C40)</f>
+        <v/>
+      </c>
+      <c r="D41" s="3">
+        <f>SUM(D2:D40)</f>
+        <v/>
+      </c>
+      <c r="E41" s="3">
+        <f>SUM(E2:E40)</f>
+        <v/>
+      </c>
+      <c r="F41" s="3">
+        <f>SUM(F2:F40)</f>
+        <v/>
+      </c>
+      <c r="G41" s="3">
+        <f>SUM(G2:G40)</f>
+        <v/>
+      </c>
+      <c r="H41" s="3">
+        <f>SUM(H2:H40)</f>
+        <v/>
+      </c>
+      <c r="I41" s="3">
+        <f>SUM(I2:I40)</f>
+        <v/>
+      </c>
+      <c r="J41" s="3">
+        <f>SUM(J2:J40)</f>
+        <v/>
+      </c>
+      <c r="K41" s="3">
+        <f>SUM(K2:K40)</f>
+        <v/>
+      </c>
+      <c r="L41" s="3">
+        <f>SUM(L2:L40)</f>
+        <v/>
+      </c>
+      <c r="M41" s="3">
+        <f>SUM(M2:M40)</f>
+        <v/>
+      </c>
+      <c r="N41" s="3">
+        <f>SUM(B41:M41)</f>
+        <v/>
+      </c>
+      <c r="O41" s="1" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O29"/>
+  <autoFilter ref="A1:O41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/credit_monthly_summary.xlsx
+++ b/credit_monthly_summary.xlsx
@@ -2,19 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="1" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Credit Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="debit summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CHASE #3444" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CHASE DETIAL#3444" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="AMEX #5533" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="CHASE CC#5235" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Credit Summary'!$A$2:$S$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'debit summary'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHASE #3444'!$A$2:$S$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CHASE DETIAL#3444'!$A$1:$O$41</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -30,7 +32,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -51,23 +55,81 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00000000"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="00000000"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="00000000"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="00000000"/>
+        <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -78,9 +140,21 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -447,27 +521,1923 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="2" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>CHASE #3444</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="7" t="n"/>
+      <c r="G1" s="7" t="n"/>
+      <c r="H1" s="7" t="n"/>
+      <c r="I1" s="7" t="n"/>
+      <c r="J1" s="7" t="n"/>
+      <c r="K1" s="7" t="n"/>
+      <c r="L1" s="7" t="n"/>
+      <c r="M1" s="7" t="n"/>
+      <c r="N1" s="7" t="n"/>
+      <c r="O1" s="7" t="n"/>
+      <c r="P1" s="7" t="n"/>
+      <c r="Q1" s="7" t="n"/>
+      <c r="R1" s="7" t="n"/>
+      <c r="S1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>BEGIN BALANCE</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CASH / CHECK DEPOSIT</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>NO1 SUSHI 88 CORKBBO ACH</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>VEOLIA WATER</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ORANGE &amp; ROCKLAND</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>WITHDRAWAL BRANCH 0964</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>AMAZON</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>BILL PAY:VEOLIA WATER NEW Y 200045 6BU1T6KR</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>BILL PAY:ORANGE &amp; ROCKLAND 136130 6BQ1P6KR</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>INTERNET TRF TO CLIENT-ADDED TRANSFER ACCOUNT</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>WITHDRAWAL BRANCH 0964 NEW YORK</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*NX6 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*9O5 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*SB8 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>NYS DTF PIT TAX PAYMNT</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL CREDIT</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>DEBIT</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>ENDING BALANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3">
+        <f>SUM(C3:P3)</f>
+        <v/>
+      </c>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3">
+        <f>B3+Q3-R3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>S3</f>
+        <v/>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3">
+        <f>SUM(C4:P4)</f>
+        <v/>
+      </c>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3">
+        <f>B4+Q4-R4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>S4</f>
+        <v/>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3">
+        <f>SUM(C5:P5)</f>
+        <v/>
+      </c>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3">
+        <f>B5+Q5-R5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>NOV</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>S5</f>
+        <v/>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3">
+        <f>SUM(C6:P6)</f>
+        <v/>
+      </c>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3">
+        <f>B6+Q6-R6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>S6</f>
+        <v/>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="n"/>
+      <c r="Q7" s="3">
+        <f>SUM(C7:P7)</f>
+        <v/>
+      </c>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="3">
+        <f>B7+Q7-R7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>S7</f>
+        <v/>
+      </c>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="n"/>
+      <c r="Q8" s="3">
+        <f>SUM(C8:P8)</f>
+        <v/>
+      </c>
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" s="3">
+        <f>B8+Q8-R8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>FEB</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>S8</f>
+        <v/>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="n"/>
+      <c r="Q9" s="3">
+        <f>SUM(C9:P9)</f>
+        <v/>
+      </c>
+      <c r="R9" s="3" t="n"/>
+      <c r="S9" s="3">
+        <f>B9+Q9-R9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>S9</f>
+        <v/>
+      </c>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="n"/>
+      <c r="Q10" s="3">
+        <f>SUM(C10:P10)</f>
+        <v/>
+      </c>
+      <c r="R10" s="3" t="n"/>
+      <c r="S10" s="3">
+        <f>B10+Q10-R10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>APR</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>S10</f>
+        <v/>
+      </c>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3">
+        <f>SUM(C11:P11)</f>
+        <v/>
+      </c>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3">
+        <f>B11+Q11-R11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>S11</f>
+        <v/>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="3" t="n"/>
+      <c r="Q12" s="3">
+        <f>SUM(C12:P12)</f>
+        <v/>
+      </c>
+      <c r="R12" s="3" t="n"/>
+      <c r="S12" s="3">
+        <f>B12+Q12-R12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>JUN</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>S12</f>
+        <v/>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="n"/>
+      <c r="Q13" s="3">
+        <f>SUM(C13:P13)</f>
+        <v/>
+      </c>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" s="3">
+        <f>B13+Q13-R13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>S13</f>
+        <v/>
+      </c>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3" t="n"/>
+      <c r="O14" s="3" t="n"/>
+      <c r="P14" s="3" t="n"/>
+      <c r="Q14" s="3">
+        <f>SUM(C14:P14)</f>
+        <v/>
+      </c>
+      <c r="R14" s="3" t="n"/>
+      <c r="S14" s="3">
+        <f>B14+Q14-R14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3">
+        <f>SUM(C3:C14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="3">
+        <f>SUM(D3:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="3">
+        <f>SUM(E3:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="3">
+        <f>SUM(F3:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="3">
+        <f>SUM(G3:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="3">
+        <f>SUM(H3:H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="3">
+        <f>SUM(I3:I14)</f>
+        <v/>
+      </c>
+      <c r="J15" s="3">
+        <f>SUM(J3:J14)</f>
+        <v/>
+      </c>
+      <c r="K15" s="3">
+        <f>SUM(K3:K14)</f>
+        <v/>
+      </c>
+      <c r="L15" s="3">
+        <f>SUM(L3:L14)</f>
+        <v/>
+      </c>
+      <c r="M15" s="3">
+        <f>SUM(M3:M14)</f>
+        <v/>
+      </c>
+      <c r="N15" s="3">
+        <f>SUM(N3:N14)</f>
+        <v/>
+      </c>
+      <c r="O15" s="3">
+        <f>SUM(O3:O14)</f>
+        <v/>
+      </c>
+      <c r="P15" s="3">
+        <f>SUM(P3:P14)</f>
+        <v/>
+      </c>
+      <c r="Q15" s="3">
+        <f>SUM(Q3:Q14)</f>
+        <v/>
+      </c>
+      <c r="R15" s="3">
+        <f>SUM(R3:R14)</f>
+        <v/>
+      </c>
+      <c r="S15" s="3">
+        <f>S14</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:S15"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>AUG</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>NOV</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>FEB</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>APR</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>JUN</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>434 / Nys Commission</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3">
+        <f>SUM(B2:M2)</f>
+        <v/>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>GERCORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Amazon Prime*Zh8618Uz3 Amzn.Com/Bill WA</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3">
+        <f>SUM(B3:M3)</f>
+        <v/>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>GERCORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Amazon.Com*N22Fjseattlewa US</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3">
+        <f>SUM(B4:M4)</f>
+        <v/>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>GERCORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Amazon.Comseattlewa US</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3">
+        <f>SUM(B5:M5)</f>
+        <v/>
+      </c>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>GERCORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Amex Epayment ACH Pmt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3">
+        <f>SUM(B6:M6)</f>
+        <v/>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>GERCORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Arrow Bank Na Web Pmt</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3">
+        <f>SUM(B7:M7)</f>
+        <v/>
+      </c>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>GERCORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Bill Pay:Associated Mutual 210061 Ubq1P6Kr</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3">
+        <f>SUM(B8:M8)</f>
+        <v/>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>GERCORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3">
+        <f>SUM(B9:M9)</f>
+        <v/>
+      </c>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3">
+        <f>SUM(B10:M10)</f>
+        <v/>
+      </c>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Bill Pay:Orange &amp; Rockland 879293 5Bq1P6Kr</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3">
+        <f>SUM(B11:M11)</f>
+        <v/>
+      </c>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3">
+        <f>SUM(B12:M12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Bill Pay:Veolia Water New Y 200054 Hbu1T6Kr</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3">
+        <f>SUM(B13:M13)</f>
+        <v/>
+      </c>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Citi Card Onlinepayment</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3">
+        <f>SUM(B14:M14)</f>
+        <v/>
+      </c>
+      <c r="O14" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Credit One Bank Payment</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3">
+        <f>SUM(B15:M15)</f>
+        <v/>
+      </c>
+      <c r="O15" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Discover Bank Net/Mobile</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3">
+        <f>SUM(B16:M16)</f>
+        <v/>
+      </c>
+      <c r="O16" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3">
+        <f>SUM(B17:M17)</f>
+        <v/>
+      </c>
+      <c r="O17" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Huntington Banksil Payment</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
+      <c r="N18" s="3">
+        <f>SUM(B18:M18)</f>
+        <v/>
+      </c>
+      <c r="O18" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Internet Trf To Client-Added Transfer Account</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3">
+        <f>SUM(B19:M19)</f>
+        <v/>
+      </c>
+      <c r="O19" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Irs Usataxpymt</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
+      <c r="N20" s="3">
+        <f>SUM(B20:M20)</f>
+        <v/>
+      </c>
+      <c r="O20" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Kindercare Portland OR</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3">
+        <f>SUM(B21:M21)</f>
+        <v/>
+      </c>
+      <c r="O21" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>No1 Sushi 88 Corkbbo ACH</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="n"/>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
+      <c r="N22" s="3">
+        <f>SUM(B22:M22)</f>
+        <v/>
+      </c>
+      <c r="O22" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3">
+        <f>SUM(B23:M23)</f>
+        <v/>
+      </c>
+      <c r="O23" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Nys Dtf Pit Tax Paymnt</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="n"/>
+      <c r="M24" s="3" t="n"/>
+      <c r="N24" s="3">
+        <f>SUM(B24:M24)</f>
+        <v/>
+      </c>
+      <c r="O24" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>PANDA EXPRESS TACOMA WA</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="3">
+        <f>SUM(B25:M25)</f>
+        <v/>
+      </c>
+      <c r="O25" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Paypal Inst Xfer</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="3" t="n"/>
+      <c r="M26" s="3" t="n"/>
+      <c r="N26" s="3">
+        <f>SUM(B26:M26)</f>
+        <v/>
+      </c>
+      <c r="O26" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*9O5 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3">
+        <f>SUM(B27:M27)</f>
+        <v/>
+      </c>
+      <c r="O27" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="n"/>
+      <c r="M28" s="3" t="n"/>
+      <c r="N28" s="3">
+        <f>SUM(B28:M28)</f>
+        <v/>
+      </c>
+      <c r="O28" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3">
+        <f>SUM(B29:M29)</f>
+        <v/>
+      </c>
+      <c r="O29" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="3">
+        <f>SUM(B30:M30)</f>
+        <v/>
+      </c>
+      <c r="O30" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3">
+        <f>SUM(B31:M31)</f>
+        <v/>
+      </c>
+      <c r="O31" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Nx6 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="n"/>
+      <c r="M32" s="3" t="n"/>
+      <c r="N32" s="3">
+        <f>SUM(B32:M32)</f>
+        <v/>
+      </c>
+      <c r="O32" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3">
+        <f>SUM(B33:M33)</f>
+        <v/>
+      </c>
+      <c r="O33" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="3" t="n"/>
+      <c r="K34" s="3" t="n"/>
+      <c r="L34" s="3" t="n"/>
+      <c r="M34" s="3" t="n"/>
+      <c r="N34" s="3">
+        <f>SUM(B34:M34)</f>
+        <v/>
+      </c>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*V25 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3">
+        <f>SUM(B35:M35)</f>
+        <v/>
+      </c>
+      <c r="O35" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Yr6 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+      <c r="I36" s="3" t="n"/>
+      <c r="J36" s="3" t="n"/>
+      <c r="K36" s="3" t="n"/>
+      <c r="L36" s="3" t="n"/>
+      <c r="M36" s="3" t="n"/>
+      <c r="N36" s="3">
+        <f>SUM(B36:M36)</f>
+        <v/>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="n"/>
+      <c r="L37" s="3" t="n"/>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3">
+        <f>SUM(B37:M37)</f>
+        <v/>
+      </c>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Prog Casualty Ins Prem</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+      <c r="I38" s="3" t="n"/>
+      <c r="J38" s="3" t="n"/>
+      <c r="K38" s="3" t="n"/>
+      <c r="L38" s="3" t="n"/>
+      <c r="M38" s="3" t="n"/>
+      <c r="N38" s="3">
+        <f>SUM(B38:M38)</f>
+        <v/>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3">
+        <f>SUM(B39:M39)</f>
+        <v/>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Withdrawal Branch 0964 New York</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="n"/>
+      <c r="J40" s="3" t="n"/>
+      <c r="K40" s="3" t="n"/>
+      <c r="L40" s="3" t="n"/>
+      <c r="M40" s="3" t="n"/>
+      <c r="N40" s="3">
+        <f>SUM(B40:M40)</f>
+        <v/>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>discover Bank Net/Mobile</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="n"/>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3">
+        <f>SUM(B41:M41)</f>
+        <v/>
+      </c>
+      <c r="O41" s="1" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B42" s="9">
+        <f>SUM(B2:B41)</f>
+        <v/>
+      </c>
+      <c r="C42" s="9">
+        <f>SUM(C2:C41)</f>
+        <v/>
+      </c>
+      <c r="D42" s="9">
+        <f>SUM(D2:D41)</f>
+        <v/>
+      </c>
+      <c r="E42" s="9">
+        <f>SUM(E2:E41)</f>
+        <v/>
+      </c>
+      <c r="F42" s="9">
+        <f>SUM(F2:F41)</f>
+        <v/>
+      </c>
+      <c r="G42" s="9">
+        <f>SUM(G2:G41)</f>
+        <v/>
+      </c>
+      <c r="H42" s="9">
+        <f>SUM(H2:H41)</f>
+        <v/>
+      </c>
+      <c r="I42" s="9">
+        <f>SUM(I2:I41)</f>
+        <v/>
+      </c>
+      <c r="J42" s="9">
+        <f>SUM(J2:J41)</f>
+        <v/>
+      </c>
+      <c r="K42" s="9">
+        <f>SUM(K2:K41)</f>
+        <v/>
+      </c>
+      <c r="L42" s="9">
+        <f>SUM(L2:L41)</f>
+        <v/>
+      </c>
+      <c r="M42" s="9">
+        <f>SUM(M2:M41)</f>
+        <v/>
+      </c>
+      <c r="N42" s="9">
+        <f>SUM(B42:M42)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O41"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="15.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22.140625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="27.7109375" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="14.85546875" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="21.7109375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="27.5703125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="9.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="47.42578125" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="47.7109375" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="50.85546875" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="38.28515625" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="40.85546875" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="40.7109375" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="40.42578125" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="24.7109375" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="24.7109375" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="24.7109375" bestFit="1" customWidth="1" min="18" max="18"/>
+    <col width="24.7109375" bestFit="1" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
       <c r="A1" s="1" t="n"/>
       <c r="B1" s="2" t="inlineStr">
         <is>
@@ -491,8 +2461,11 @@
       <c r="Q1" s="1" t="n"/>
       <c r="R1" s="1" t="n"/>
       <c r="S1" s="1" t="n"/>
-    </row>
-    <row r="2" ht="24" customHeight="1">
+      <c r="T1" s="1" t="n"/>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="n"/>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -571,15 +2544,30 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
+          <t>KINDERCARE PORTLAND OR</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>AMAZON PRIME*ZH8618UZ3 AMZN.COM/BILL WA</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>IRS USATAXPYMT</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
           <t>TOTAL CREDIT</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>ENDING BALANCE</t>
         </is>
@@ -608,16 +2596,16 @@
       <c r="N3" s="3" t="n"/>
       <c r="O3" s="3" t="n"/>
       <c r="P3" s="3" t="n"/>
-      <c r="Q3" s="3">
-        <f>SUM(C3:P3)</f>
-        <v/>
-      </c>
-      <c r="R3" s="3">
-        <f>'debit summary'!B41</f>
-        <v/>
-      </c>
-      <c r="S3" s="3">
-        <f>B3+Q3-R3</f>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="n"/>
+      <c r="T3" s="3">
+        <f>SUM(C3:S3)</f>
+        <v/>
+      </c>
+      <c r="U3" s="3" t="n"/>
+      <c r="V3" s="3">
+        <f>B3+T3-U3</f>
         <v/>
       </c>
     </row>
@@ -645,16 +2633,16 @@
       <c r="N4" s="3" t="n"/>
       <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3">
-        <f>SUM(C4:P4)</f>
-        <v/>
-      </c>
-      <c r="R4" s="3">
-        <f>'debit summary'!C41</f>
-        <v/>
-      </c>
-      <c r="S4" s="3">
-        <f>B4+Q4-R4</f>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3">
+        <f>SUM(C4:S4)</f>
+        <v/>
+      </c>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3">
+        <f>B4+T4-U4</f>
         <v/>
       </c>
     </row>
@@ -682,16 +2670,16 @@
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3">
-        <f>SUM(C5:P5)</f>
-        <v/>
-      </c>
-      <c r="R5" s="3">
-        <f>'debit summary'!D41</f>
-        <v/>
-      </c>
-      <c r="S5" s="3">
-        <f>B5+Q5-R5</f>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3">
+        <f>SUM(C5:S5)</f>
+        <v/>
+      </c>
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="3">
+        <f>B5+T5-U5</f>
         <v/>
       </c>
     </row>
@@ -706,29 +2694,65 @@
         <v/>
       </c>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
+      <c r="D6" s="3">
+        <f>4000.00</f>
+        <v/>
+      </c>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="n"/>
+      <c r="I6" s="3">
+        <f>300.00</f>
+        <v/>
+      </c>
+      <c r="J6" s="3">
+        <f>350.00</f>
+        <v/>
+      </c>
+      <c r="K6" s="3">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
+      <c r="L6" s="3">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
+      <c r="M6" s="3">
+        <f>75.40</f>
+        <v/>
+      </c>
+      <c r="N6" s="3">
+        <f>26.57</f>
+        <v/>
+      </c>
+      <c r="O6" s="3">
+        <f>18.75</f>
+        <v/>
+      </c>
+      <c r="P6" s="3">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
       <c r="Q6" s="3">
-        <f>SUM(C6:P6)</f>
+        <f>490.00</f>
         <v/>
       </c>
       <c r="R6" s="3">
-        <f>'debit summary'!E41</f>
+        <f>16.25</f>
         <v/>
       </c>
       <c r="S6" s="3">
-        <f>B6+Q6-R6</f>
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
+      <c r="T6" s="3">
+        <f>SUM(C6:S6)</f>
+        <v/>
+      </c>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3">
+        <f>B6+T6-U6</f>
         <v/>
       </c>
     </row>
@@ -756,16 +2780,16 @@
       <c r="N7" s="3" t="n"/>
       <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="n"/>
-      <c r="Q7" s="3">
-        <f>SUM(C7:P7)</f>
-        <v/>
-      </c>
-      <c r="R7" s="3">
-        <f>'debit summary'!F41</f>
-        <v/>
-      </c>
-      <c r="S7" s="3">
-        <f>B7+Q7-R7</f>
+      <c r="Q7" s="3" t="n"/>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="3">
+        <f>SUM(C7:S7)</f>
+        <v/>
+      </c>
+      <c r="U7" s="3" t="n"/>
+      <c r="V7" s="3">
+        <f>B7+T7-U7</f>
         <v/>
       </c>
     </row>
@@ -785,40 +2809,24 @@
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>350</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>740</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>26.57</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="Q8" s="3">
-        <f>SUM(C8:P8)</f>
-        <v/>
-      </c>
-      <c r="R8" s="3">
-        <f>'debit summary'!G41</f>
-        <v/>
-      </c>
-      <c r="S8" s="3">
-        <f>B8+Q8-R8</f>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="n"/>
+      <c r="Q8" s="3" t="n"/>
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" s="3" t="n"/>
+      <c r="T8" s="3">
+        <f>SUM(C8:S8)</f>
+        <v/>
+      </c>
+      <c r="U8" s="3" t="n"/>
+      <c r="V8" s="3">
+        <f>B8+T8-U8</f>
         <v/>
       </c>
     </row>
@@ -846,16 +2854,16 @@
       <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="n"/>
-      <c r="Q9" s="3">
-        <f>SUM(C9:P9)</f>
-        <v/>
-      </c>
-      <c r="R9" s="3">
-        <f>'debit summary'!H41</f>
-        <v/>
-      </c>
-      <c r="S9" s="3">
-        <f>B9+Q9-R9</f>
+      <c r="Q9" s="3" t="n"/>
+      <c r="R9" s="3" t="n"/>
+      <c r="S9" s="3" t="n"/>
+      <c r="T9" s="3">
+        <f>SUM(C9:S9)</f>
+        <v/>
+      </c>
+      <c r="U9" s="3" t="n"/>
+      <c r="V9" s="3">
+        <f>B9+T9-U9</f>
         <v/>
       </c>
     </row>
@@ -883,16 +2891,16 @@
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="n"/>
       <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3">
-        <f>SUM(C10:P10)</f>
-        <v/>
-      </c>
-      <c r="R10" s="3">
-        <f>'debit summary'!I41</f>
-        <v/>
-      </c>
-      <c r="S10" s="3">
-        <f>B10+Q10-R10</f>
+      <c r="Q10" s="3" t="n"/>
+      <c r="R10" s="3" t="n"/>
+      <c r="S10" s="3" t="n"/>
+      <c r="T10" s="3">
+        <f>SUM(C10:S10)</f>
+        <v/>
+      </c>
+      <c r="U10" s="3" t="n"/>
+      <c r="V10" s="3">
+        <f>B10+T10-U10</f>
         <v/>
       </c>
     </row>
@@ -920,16 +2928,16 @@
       <c r="N11" s="3" t="n"/>
       <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="3">
-        <f>SUM(C11:P11)</f>
-        <v/>
-      </c>
-      <c r="R11" s="3">
-        <f>'debit summary'!J41</f>
-        <v/>
-      </c>
-      <c r="S11" s="3">
-        <f>B11+Q11-R11</f>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3" t="n"/>
+      <c r="T11" s="3">
+        <f>SUM(C11:S11)</f>
+        <v/>
+      </c>
+      <c r="U11" s="3" t="n"/>
+      <c r="V11" s="3">
+        <f>B11+T11-U11</f>
         <v/>
       </c>
     </row>
@@ -957,16 +2965,16 @@
       <c r="N12" s="3" t="n"/>
       <c r="O12" s="3" t="n"/>
       <c r="P12" s="3" t="n"/>
-      <c r="Q12" s="3">
-        <f>SUM(C12:P12)</f>
-        <v/>
-      </c>
-      <c r="R12" s="3">
-        <f>'debit summary'!K41</f>
-        <v/>
-      </c>
-      <c r="S12" s="3">
-        <f>B12+Q12-R12</f>
+      <c r="Q12" s="3" t="n"/>
+      <c r="R12" s="3" t="n"/>
+      <c r="S12" s="3" t="n"/>
+      <c r="T12" s="3">
+        <f>SUM(C12:S12)</f>
+        <v/>
+      </c>
+      <c r="U12" s="3" t="n"/>
+      <c r="V12" s="3">
+        <f>B12+T12-U12</f>
         <v/>
       </c>
     </row>
@@ -994,16 +3002,16 @@
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="3" t="n"/>
       <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="3">
-        <f>SUM(C13:P13)</f>
-        <v/>
-      </c>
-      <c r="R13" s="3">
-        <f>'debit summary'!L41</f>
-        <v/>
-      </c>
-      <c r="S13" s="3">
-        <f>B13+Q13-R13</f>
+      <c r="Q13" s="3" t="n"/>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" s="3" t="n"/>
+      <c r="T13" s="3">
+        <f>SUM(C13:S13)</f>
+        <v/>
+      </c>
+      <c r="U13" s="3" t="n"/>
+      <c r="V13" s="3">
+        <f>B13+T13-U13</f>
         <v/>
       </c>
     </row>
@@ -1031,16 +3039,16 @@
       <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="n"/>
       <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3">
-        <f>SUM(C14:P14)</f>
-        <v/>
-      </c>
-      <c r="R14" s="3">
-        <f>'debit summary'!M41</f>
-        <v/>
-      </c>
-      <c r="S14" s="3">
-        <f>B14+Q14-R14</f>
+      <c r="Q14" s="3" t="n"/>
+      <c r="R14" s="3" t="n"/>
+      <c r="S14" s="3" t="n"/>
+      <c r="T14" s="3">
+        <f>SUM(C14:S14)</f>
+        <v/>
+      </c>
+      <c r="U14" s="3" t="n"/>
+      <c r="V14" s="3">
+        <f>B14+T14-U14</f>
         <v/>
       </c>
     </row>
@@ -1112,21 +3120,32 @@
         <v/>
       </c>
       <c r="R15" s="3">
-        <f>'debit summary'!N41</f>
+        <f>SUM(R3:R14)</f>
         <v/>
       </c>
       <c r="S15" s="3">
-        <f>S14</f>
+        <f>SUM(S3:S14)</f>
+        <v/>
+      </c>
+      <c r="T15" s="3">
+        <f>SUM(T3:T14)</f>
+        <v/>
+      </c>
+      <c r="U15" s="3">
+        <f>SUM(U3:U14)</f>
+        <v/>
+      </c>
+      <c r="V15" s="3">
+        <f>V14</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S15"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1135,21 +3154,18 @@
   <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="50.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="5.140625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="5" bestFit="1" customWidth="1" min="3" max="4"/>
+    <col width="5.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="8.140625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="5" bestFit="1" customWidth="1" min="7" max="8"/>
+    <col width="5.5703125" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="5" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="5.42578125" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="5" bestFit="1" customWidth="1" min="12" max="13"/>
+    <col width="8.140625" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="15.5703125" bestFit="1" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1270,7 +3286,10 @@
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
+      <c r="I3" s="3">
+        <f>16.25</f>
+        <v/>
+      </c>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
@@ -1463,13 +3482,13 @@
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3">
-        <f>350.00</f>
-        <v/>
-      </c>
+      <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
+      <c r="I10" s="3">
+        <f>350.00</f>
+        <v/>
+      </c>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n"/>
@@ -1522,13 +3541,13 @@
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3">
-        <f>300.00</f>
-        <v/>
-      </c>
+      <c r="F12" s="3" t="n"/>
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
+      <c r="I12" s="3">
+        <f>300.00</f>
+        <v/>
+      </c>
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="n"/>
@@ -1721,13 +3740,13 @@
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3">
-        <f>740.00</f>
-        <v/>
-      </c>
+      <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
+      <c r="I19" s="3">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="n"/>
       <c r="L19" s="3" t="n"/>
@@ -1755,7 +3774,10 @@
       <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
+      <c r="I20" s="3">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="n"/>
       <c r="L20" s="3" t="n"/>
@@ -1783,7 +3805,10 @@
       <c r="F21" s="3" t="n"/>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
+      <c r="I21" s="3">
+        <f>490.00</f>
+        <v/>
+      </c>
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="n"/>
@@ -1811,7 +3836,10 @@
       <c r="F22" s="3" t="n"/>
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
+      <c r="I22" s="3">
+        <f>4000.00</f>
+        <v/>
+      </c>
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="n"/>
       <c r="L22" s="3" t="n"/>
@@ -1864,13 +3892,13 @@
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3">
-        <f>200.00+200.00</f>
-        <v/>
-      </c>
+      <c r="F24" s="3" t="n"/>
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
+      <c r="I24" s="3">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="n"/>
@@ -1951,13 +3979,13 @@
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3">
-        <f>26.57</f>
-        <v/>
-      </c>
+      <c r="F27" s="3" t="n"/>
       <c r="G27" s="3" t="n"/>
       <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
+      <c r="I27" s="3">
+        <f>26.57</f>
+        <v/>
+      </c>
       <c r="J27" s="3" t="n"/>
       <c r="K27" s="3" t="n"/>
       <c r="L27" s="3" t="n"/>
@@ -2094,13 +4122,13 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3">
-        <f>75.40</f>
-        <v/>
-      </c>
+      <c r="F32" s="3" t="n"/>
       <c r="G32" s="3" t="n"/>
       <c r="H32" s="3" t="n"/>
-      <c r="I32" s="3" t="n"/>
+      <c r="I32" s="3">
+        <f>75.40</f>
+        <v/>
+      </c>
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n"/>
@@ -2125,13 +4153,13 @@
       <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3">
-        <f>18.75</f>
-        <v/>
-      </c>
+      <c r="F33" s="3" t="n"/>
       <c r="G33" s="3" t="n"/>
       <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
+      <c r="I33" s="3">
+        <f>18.75</f>
+        <v/>
+      </c>
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="n"/>
       <c r="L33" s="3" t="n"/>
@@ -2324,13 +4352,13 @@
       <c r="C40" s="3" t="n"/>
       <c r="D40" s="3" t="n"/>
       <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3">
-        <f>1000.00</f>
-        <v/>
-      </c>
+      <c r="F40" s="3" t="n"/>
       <c r="G40" s="3" t="n"/>
       <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
+      <c r="I40" s="3">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="n"/>
@@ -2403,10 +4431,22 @@
         <f>SUM(B41:M41)</f>
         <v/>
       </c>
-      <c r="O41" s="1" t="inlineStr"/>
+      <c r="O41" s="1" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O41"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/credit_monthly_summary.xlsx
+++ b/credit_monthly_summary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="1" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="3" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="CHASE #3444" sheetId="1" state="visible" r:id="rId1"/>
@@ -45,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -60,19 +60,6 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -140,18 +127,16 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -525,118 +510,118 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>CHASE #3444</t>
         </is>
       </c>
-      <c r="B1" s="7" t="n"/>
-      <c r="C1" s="7" t="n"/>
-      <c r="D1" s="7" t="n"/>
-      <c r="E1" s="7" t="n"/>
-      <c r="F1" s="7" t="n"/>
-      <c r="G1" s="7" t="n"/>
-      <c r="H1" s="7" t="n"/>
-      <c r="I1" s="7" t="n"/>
-      <c r="J1" s="7" t="n"/>
-      <c r="K1" s="7" t="n"/>
-      <c r="L1" s="7" t="n"/>
-      <c r="M1" s="7" t="n"/>
-      <c r="N1" s="7" t="n"/>
-      <c r="O1" s="7" t="n"/>
-      <c r="P1" s="7" t="n"/>
-      <c r="Q1" s="7" t="n"/>
-      <c r="R1" s="7" t="n"/>
-      <c r="S1" s="8" t="n"/>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="8" t="n"/>
+      <c r="K1" s="8" t="n"/>
+      <c r="L1" s="8" t="n"/>
+      <c r="M1" s="8" t="n"/>
+      <c r="N1" s="8" t="n"/>
+      <c r="O1" s="8" t="n"/>
+      <c r="P1" s="8" t="n"/>
+      <c r="Q1" s="8" t="n"/>
+      <c r="R1" s="8" t="n"/>
+      <c r="S1" s="9" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="n"/>
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>BEGIN BALANCE</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>CASH / CHECK DEPOSIT</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>NO1 SUSHI 88 CORKBBO ACH</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>VEOLIA WATER</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>ORANGE &amp; ROCKLAND</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>WITHDRAWAL BRANCH 0964</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>AMAZON</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>BILL PAY:VEOLIA WATER NEW Y 200045 6BU1T6KR</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>BILL PAY:ORANGE &amp; ROCKLAND 136130 6BQ1P6KR</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>INTERNET TRF TO CLIENT-ADDED TRANSFER ACCOUNT</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>WITHDRAWAL BRANCH 0964 NEW YORK</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>POS MAC AMAZON.COM*NX6 SEATTLE WA</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>POS MAC AMAZON.COM*9O5 SEATTLE WA</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" s="6" t="inlineStr">
         <is>
           <t>POS MAC AMAZON.COM*SB8 SEATTLE WA</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" s="6" t="inlineStr">
         <is>
           <t>NYS DTF PIT TAX PAYMNT</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q2" s="6" t="inlineStr">
         <is>
           <t>TOTAL CREDIT</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="S2" s="6" t="inlineStr">
         <is>
           <t>ENDING BALANCE</t>
         </is>
@@ -1150,77 +1135,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Merchant</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>OCT</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>DEC</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
@@ -1245,7 +1230,7 @@
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="3" t="n"/>
       <c r="N2" s="3">
-        <f>SUM(B2:M2)</f>
+        <f>SUM(B2,C2,D2,E2,F2,G2,H2,I2,J2,K2,L2,M2)</f>
         <v/>
       </c>
       <c r="O2" s="1" t="inlineStr">
@@ -1273,7 +1258,7 @@
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
       <c r="N3" s="3">
-        <f>SUM(B3:M3)</f>
+        <f>SUM(B3,C3,D3,E3,F3,G3,H3,I3,J3,K3,L3,M3)</f>
         <v/>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -1301,7 +1286,7 @@
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
       <c r="N4" s="3">
-        <f>SUM(B4:M4)</f>
+        <f>SUM(B4,C4,D4,E4,F4,G4,H4,I4,J4,K4,L4,M4)</f>
         <v/>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -1329,7 +1314,7 @@
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
       <c r="N5" s="3">
-        <f>SUM(B5:M5)</f>
+        <f>SUM(B5,C5,D5,E5,F5,G5,H5,I5,J5,K5,L5,M5)</f>
         <v/>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -1357,7 +1342,7 @@
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="n"/>
       <c r="N6" s="3">
-        <f>SUM(B6:M6)</f>
+        <f>SUM(B6,C6,D6,E6,F6,G6,H6,I6,J6,K6,L6,M6)</f>
         <v/>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -1385,7 +1370,7 @@
       <c r="L7" s="3" t="n"/>
       <c r="M7" s="3" t="n"/>
       <c r="N7" s="3">
-        <f>SUM(B7:M7)</f>
+        <f>SUM(B7,C7,D7,E7,F7,G7,H7,I7,J7,K7,L7,M7)</f>
         <v/>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -1413,7 +1398,7 @@
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n"/>
       <c r="N8" s="3">
-        <f>SUM(B8:M8)</f>
+        <f>SUM(B8,C8,D8,E8,F8,G8,H8,I8,J8,K8,L8,M8)</f>
         <v/>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -1441,7 +1426,7 @@
       <c r="L9" s="3" t="n"/>
       <c r="M9" s="3" t="n"/>
       <c r="N9" s="3">
-        <f>SUM(B9:M9)</f>
+        <f>SUM(B9,C9,D9,E9,F9,G9,H9,I9,J9,K9,L9,M9)</f>
         <v/>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1469,7 +1454,7 @@
       <c r="L10" s="3" t="n"/>
       <c r="M10" s="3" t="n"/>
       <c r="N10" s="3">
-        <f>SUM(B10:M10)</f>
+        <f>SUM(B10,C10,D10,E10,F10,G10,H10,I10,J10,K10,L10,M10)</f>
         <v/>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1497,7 +1482,7 @@
       <c r="L11" s="3" t="n"/>
       <c r="M11" s="3" t="n"/>
       <c r="N11" s="3">
-        <f>SUM(B11:M11)</f>
+        <f>SUM(B11,C11,D11,E11,F11,G11,H11,I11,J11,K11,L11,M11)</f>
         <v/>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1525,7 +1510,7 @@
       <c r="L12" s="3" t="n"/>
       <c r="M12" s="3" t="n"/>
       <c r="N12" s="3">
-        <f>SUM(B12:M12)</f>
+        <f>SUM(B12,C12,D12,E12,F12,G12,H12,I12,J12,K12,L12,M12)</f>
         <v/>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1553,7 +1538,7 @@
       <c r="L13" s="3" t="n"/>
       <c r="M13" s="3" t="n"/>
       <c r="N13" s="3">
-        <f>SUM(B13:M13)</f>
+        <f>SUM(B13,C13,D13,E13,F13,G13,H13,I13,J13,K13,L13,M13)</f>
         <v/>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1581,7 +1566,7 @@
       <c r="L14" s="3" t="n"/>
       <c r="M14" s="3" t="n"/>
       <c r="N14" s="3">
-        <f>SUM(B14:M14)</f>
+        <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,J14,K14,L14,M14)</f>
         <v/>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1609,7 +1594,7 @@
       <c r="L15" s="3" t="n"/>
       <c r="M15" s="3" t="n"/>
       <c r="N15" s="3">
-        <f>SUM(B15:M15)</f>
+        <f>SUM(B15,C15,D15,E15,F15,G15,H15,I15,J15,K15,L15,M15)</f>
         <v/>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1637,7 +1622,7 @@
       <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="n"/>
       <c r="N16" s="3">
-        <f>SUM(B16:M16)</f>
+        <f>SUM(B16,C16,D16,E16,F16,G16,H16,I16,J16,K16,L16,M16)</f>
         <v/>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1665,7 +1650,7 @@
       <c r="L17" s="3" t="n"/>
       <c r="M17" s="3" t="n"/>
       <c r="N17" s="3">
-        <f>SUM(B17:M17)</f>
+        <f>SUM(B17,C17,D17,E17,F17,G17,H17,I17,J17,K17,L17,M17)</f>
         <v/>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1693,7 +1678,7 @@
       <c r="L18" s="3" t="n"/>
       <c r="M18" s="3" t="n"/>
       <c r="N18" s="3">
-        <f>SUM(B18:M18)</f>
+        <f>SUM(B18,C18,D18,E18,F18,G18,H18,I18,J18,K18,L18,M18)</f>
         <v/>
       </c>
       <c r="O18" s="1" t="inlineStr">
@@ -1721,7 +1706,7 @@
       <c r="L19" s="3" t="n"/>
       <c r="M19" s="3" t="n"/>
       <c r="N19" s="3">
-        <f>SUM(B19:M19)</f>
+        <f>SUM(B19,C19,D19,E19,F19,G19,H19,I19,J19,K19,L19,M19)</f>
         <v/>
       </c>
       <c r="O19" s="1" t="inlineStr">
@@ -1749,7 +1734,7 @@
       <c r="L20" s="3" t="n"/>
       <c r="M20" s="3" t="n"/>
       <c r="N20" s="3">
-        <f>SUM(B20:M20)</f>
+        <f>SUM(B20,C20,D20,E20,F20,G20,H20,I20,J20,K20,L20,M20)</f>
         <v/>
       </c>
       <c r="O20" s="1" t="inlineStr">
@@ -1777,7 +1762,7 @@
       <c r="L21" s="3" t="n"/>
       <c r="M21" s="3" t="n"/>
       <c r="N21" s="3">
-        <f>SUM(B21:M21)</f>
+        <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,J21,K21,L21,M21)</f>
         <v/>
       </c>
       <c r="O21" s="1" t="inlineStr">
@@ -1805,7 +1790,7 @@
       <c r="L22" s="3" t="n"/>
       <c r="M22" s="3" t="n"/>
       <c r="N22" s="3">
-        <f>SUM(B22:M22)</f>
+        <f>SUM(B22,C22,D22,E22,F22,G22,H22,I22,J22,K22,L22,M22)</f>
         <v/>
       </c>
       <c r="O22" s="1" t="inlineStr">
@@ -1833,7 +1818,7 @@
       <c r="L23" s="3" t="n"/>
       <c r="M23" s="3" t="n"/>
       <c r="N23" s="3">
-        <f>SUM(B23:M23)</f>
+        <f>SUM(B23,C23,D23,E23,F23,G23,H23,I23,J23,K23,L23,M23)</f>
         <v/>
       </c>
       <c r="O23" s="1" t="inlineStr">
@@ -1861,7 +1846,7 @@
       <c r="L24" s="3" t="n"/>
       <c r="M24" s="3" t="n"/>
       <c r="N24" s="3">
-        <f>SUM(B24:M24)</f>
+        <f>SUM(B24,C24,D24,E24,F24,G24,H24,I24,J24,K24,L24,M24)</f>
         <v/>
       </c>
       <c r="O24" s="1" t="inlineStr">
@@ -1889,7 +1874,7 @@
       <c r="L25" s="3" t="n"/>
       <c r="M25" s="3" t="n"/>
       <c r="N25" s="3">
-        <f>SUM(B25:M25)</f>
+        <f>SUM(B25,C25,D25,E25,F25,G25,H25,I25,J25,K25,L25,M25)</f>
         <v/>
       </c>
       <c r="O25" s="1" t="inlineStr">
@@ -1917,7 +1902,7 @@
       <c r="L26" s="3" t="n"/>
       <c r="M26" s="3" t="n"/>
       <c r="N26" s="3">
-        <f>SUM(B26:M26)</f>
+        <f>SUM(B26,C26,D26,E26,F26,G26,H26,I26,J26,K26,L26,M26)</f>
         <v/>
       </c>
       <c r="O26" s="1" t="inlineStr">
@@ -1945,7 +1930,7 @@
       <c r="L27" s="3" t="n"/>
       <c r="M27" s="3" t="n"/>
       <c r="N27" s="3">
-        <f>SUM(B27:M27)</f>
+        <f>SUM(B27,C27,D27,E27,F27,G27,H27,I27,J27,K27,L27,M27)</f>
         <v/>
       </c>
       <c r="O27" s="1" t="inlineStr">
@@ -1973,7 +1958,7 @@
       <c r="L28" s="3" t="n"/>
       <c r="M28" s="3" t="n"/>
       <c r="N28" s="3">
-        <f>SUM(B28:M28)</f>
+        <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,J28,K28,L28,M28)</f>
         <v/>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -2001,7 +1986,7 @@
       <c r="L29" s="3" t="n"/>
       <c r="M29" s="3" t="n"/>
       <c r="N29" s="3">
-        <f>SUM(B29:M29)</f>
+        <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29)</f>
         <v/>
       </c>
       <c r="O29" s="1" t="inlineStr">
@@ -2029,7 +2014,7 @@
       <c r="L30" s="3" t="n"/>
       <c r="M30" s="3" t="n"/>
       <c r="N30" s="3">
-        <f>SUM(B30:M30)</f>
+        <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30)</f>
         <v/>
       </c>
       <c r="O30" s="1" t="inlineStr">
@@ -2057,7 +2042,7 @@
       <c r="L31" s="3" t="n"/>
       <c r="M31" s="3" t="n"/>
       <c r="N31" s="3">
-        <f>SUM(B31:M31)</f>
+        <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31)</f>
         <v/>
       </c>
       <c r="O31" s="1" t="inlineStr">
@@ -2085,7 +2070,7 @@
       <c r="L32" s="3" t="n"/>
       <c r="M32" s="3" t="n"/>
       <c r="N32" s="3">
-        <f>SUM(B32:M32)</f>
+        <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32)</f>
         <v/>
       </c>
       <c r="O32" s="1" t="inlineStr">
@@ -2113,7 +2098,7 @@
       <c r="L33" s="3" t="n"/>
       <c r="M33" s="3" t="n"/>
       <c r="N33" s="3">
-        <f>SUM(B33:M33)</f>
+        <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33)</f>
         <v/>
       </c>
       <c r="O33" s="1" t="inlineStr">
@@ -2141,7 +2126,7 @@
       <c r="L34" s="3" t="n"/>
       <c r="M34" s="3" t="n"/>
       <c r="N34" s="3">
-        <f>SUM(B34:M34)</f>
+        <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,J34,K34,L34,M34)</f>
         <v/>
       </c>
       <c r="O34" s="1" t="inlineStr">
@@ -2169,7 +2154,7 @@
       <c r="L35" s="3" t="n"/>
       <c r="M35" s="3" t="n"/>
       <c r="N35" s="3">
-        <f>SUM(B35:M35)</f>
+        <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,J35,K35,L35,M35)</f>
         <v/>
       </c>
       <c r="O35" s="1" t="inlineStr">
@@ -2197,7 +2182,7 @@
       <c r="L36" s="3" t="n"/>
       <c r="M36" s="3" t="n"/>
       <c r="N36" s="3">
-        <f>SUM(B36:M36)</f>
+        <f>SUM(B36,C36,D36,E36,F36,G36,H36,I36,J36,K36,L36,M36)</f>
         <v/>
       </c>
       <c r="O36" s="1" t="inlineStr">
@@ -2225,7 +2210,7 @@
       <c r="L37" s="3" t="n"/>
       <c r="M37" s="3" t="n"/>
       <c r="N37" s="3">
-        <f>SUM(B37:M37)</f>
+        <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,J37,K37,L37,M37)</f>
         <v/>
       </c>
       <c r="O37" s="1" t="inlineStr">
@@ -2253,7 +2238,7 @@
       <c r="L38" s="3" t="n"/>
       <c r="M38" s="3" t="n"/>
       <c r="N38" s="3">
-        <f>SUM(B38:M38)</f>
+        <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38)</f>
         <v/>
       </c>
       <c r="O38" s="1" t="inlineStr">
@@ -2281,7 +2266,7 @@
       <c r="L39" s="3" t="n"/>
       <c r="M39" s="3" t="n"/>
       <c r="N39" s="3">
-        <f>SUM(B39:M39)</f>
+        <f>SUM(B39,C39,D39,E39,F39,G39,H39,I39,J39,K39,L39,M39)</f>
         <v/>
       </c>
       <c r="O39" s="1" t="inlineStr">
@@ -2309,7 +2294,7 @@
       <c r="L40" s="3" t="n"/>
       <c r="M40" s="3" t="n"/>
       <c r="N40" s="3">
-        <f>SUM(B40:M40)</f>
+        <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,J40,K40,L40,M40)</f>
         <v/>
       </c>
       <c r="O40" s="1" t="inlineStr">
@@ -2337,7 +2322,7 @@
       <c r="L41" s="3" t="n"/>
       <c r="M41" s="3" t="n"/>
       <c r="N41" s="3">
-        <f>SUM(B41:M41)</f>
+        <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41)</f>
         <v/>
       </c>
       <c r="O41" s="1" t="n"/>
@@ -2348,56 +2333,56 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B42" s="9">
+      <c r="B42" s="5">
         <f>SUM(B2:B41)</f>
         <v/>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="5">
         <f>SUM(C2:C41)</f>
         <v/>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="5">
         <f>SUM(D2:D41)</f>
         <v/>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="5">
         <f>SUM(E2:E41)</f>
         <v/>
       </c>
-      <c r="F42" s="9">
+      <c r="F42" s="5">
         <f>SUM(F2:F41)</f>
         <v/>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="5">
         <f>SUM(G2:G41)</f>
         <v/>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="5">
         <f>SUM(H2:H41)</f>
         <v/>
       </c>
-      <c r="I42" s="9">
+      <c r="I42" s="5">
         <f>SUM(I2:I41)</f>
         <v/>
       </c>
-      <c r="J42" s="9">
+      <c r="J42" s="5">
         <f>SUM(J2:J41)</f>
         <v/>
       </c>
-      <c r="K42" s="9">
+      <c r="K42" s="5">
         <f>SUM(K2:K41)</f>
         <v/>
       </c>
-      <c r="L42" s="9">
+      <c r="L42" s="5">
         <f>SUM(L2:L41)</f>
         <v/>
       </c>
-      <c r="M42" s="9">
+      <c r="M42" s="5">
         <f>SUM(M2:M41)</f>
         <v/>
       </c>
-      <c r="N42" s="9">
-        <f>SUM(B42:M42)</f>
+      <c r="N42" s="5">
+        <f>SUM(B42,C42,D42,E42,F42,G42,H42,I42,J42,K42,L42,M42)</f>
         <v/>
       </c>
     </row>
@@ -2413,7 +2398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2432,14 +2417,14 @@
     <col width="40.7109375" bestFit="1" customWidth="1" min="14" max="14"/>
     <col width="40.42578125" bestFit="1" customWidth="1" min="15" max="15"/>
     <col width="24.7109375" bestFit="1" customWidth="1" min="16" max="16"/>
-    <col width="24.7109375" bestFit="1" customWidth="1" min="17" max="17"/>
-    <col width="24.7109375" bestFit="1" customWidth="1" min="18" max="18"/>
-    <col width="24.7109375" bestFit="1" customWidth="1" min="19" max="19"/>
+    <col width="13.85546875" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="8.140625" bestFit="1" customWidth="1" min="18" max="18"/>
+    <col width="17.42578125" bestFit="1" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>CHASE #3444</t>
         </is>
@@ -2461,113 +2446,95 @@
       <c r="Q1" s="1" t="n"/>
       <c r="R1" s="1" t="n"/>
       <c r="S1" s="1" t="n"/>
-      <c r="T1" s="1" t="n"/>
-      <c r="U1" s="1" t="n"/>
-      <c r="V1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="n"/>
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>BEGIN BALANCE</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>CASH / CHECK DEPOSIT</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>NO1 SUSHI 88 CORKBBO ACH</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>VEOLIA WATER</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>ORANGE &amp; ROCKLAND</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>WITHDRAWAL BRANCH 0964</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>AMAZON</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>BILL PAY:VEOLIA WATER NEW Y 200045 6BU1T6KR</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>BILL PAY:ORANGE &amp; ROCKLAND 136130 6BQ1P6KR</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>INTERNET TRF TO CLIENT-ADDED TRANSFER ACCOUNT</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>WITHDRAWAL BRANCH 0964 NEW YORK</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>POS MAC AMAZON.COM*NX6 SEATTLE WA</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>POS MAC AMAZON.COM*9O5 SEATTLE WA</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" s="6" t="inlineStr">
         <is>
           <t>POS MAC AMAZON.COM*SB8 SEATTLE WA</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" s="6" t="inlineStr">
         <is>
           <t>NYS DTF PIT TAX PAYMNT</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>KINDERCARE PORTLAND OR</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>AMAZON PRIME*ZH8618UZ3 AMZN.COM/BILL WA</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>IRS USATAXPYMT</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="Q2" s="6" t="inlineStr">
         <is>
           <t>TOTAL CREDIT</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="S2" s="6" t="inlineStr">
         <is>
           <t>ENDING BALANCE</t>
         </is>
@@ -2596,16 +2563,13 @@
       <c r="N3" s="3" t="n"/>
       <c r="O3" s="3" t="n"/>
       <c r="P3" s="3" t="n"/>
-      <c r="Q3" s="3" t="n"/>
+      <c r="Q3" s="3">
+        <f>SUM(C3:P3)</f>
+        <v/>
+      </c>
       <c r="R3" s="3" t="n"/>
-      <c r="S3" s="3" t="n"/>
-      <c r="T3" s="3">
-        <f>SUM(C3:S3)</f>
-        <v/>
-      </c>
-      <c r="U3" s="3" t="n"/>
-      <c r="V3" s="3">
-        <f>B3+T3-U3</f>
+      <c r="S3" s="3">
+        <f>B3+Q3-R3</f>
         <v/>
       </c>
     </row>
@@ -2633,16 +2597,13 @@
       <c r="N4" s="3" t="n"/>
       <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3" t="n"/>
+      <c r="Q4" s="3">
+        <f>SUM(C4:P4)</f>
+        <v/>
+      </c>
       <c r="R4" s="3" t="n"/>
-      <c r="S4" s="3" t="n"/>
-      <c r="T4" s="3">
-        <f>SUM(C4:S4)</f>
-        <v/>
-      </c>
-      <c r="U4" s="3" t="n"/>
-      <c r="V4" s="3">
-        <f>B4+T4-U4</f>
+      <c r="S4" s="3">
+        <f>B4+Q4-R4</f>
         <v/>
       </c>
     </row>
@@ -2670,16 +2631,13 @@
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="n"/>
+      <c r="Q5" s="3">
+        <f>SUM(C5:P5)</f>
+        <v/>
+      </c>
       <c r="R5" s="3" t="n"/>
-      <c r="S5" s="3" t="n"/>
-      <c r="T5" s="3">
-        <f>SUM(C5:S5)</f>
-        <v/>
-      </c>
-      <c r="U5" s="3" t="n"/>
-      <c r="V5" s="3">
-        <f>B5+T5-U5</f>
+      <c r="S5" s="3">
+        <f>B5+Q5-R5</f>
         <v/>
       </c>
     </row>
@@ -2694,65 +2652,26 @@
         <v/>
       </c>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3">
-        <f>4000.00</f>
-        <v/>
-      </c>
+      <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3">
-        <f>300.00</f>
-        <v/>
-      </c>
-      <c r="J6" s="3">
-        <f>350.00</f>
-        <v/>
-      </c>
-      <c r="K6" s="3">
-        <f>385.77+740.00</f>
-        <v/>
-      </c>
-      <c r="L6" s="3">
-        <f>1000.00+3200.00</f>
-        <v/>
-      </c>
-      <c r="M6" s="3">
-        <f>75.40</f>
-        <v/>
-      </c>
-      <c r="N6" s="3">
-        <f>26.57</f>
-        <v/>
-      </c>
-      <c r="O6" s="3">
-        <f>18.75</f>
-        <v/>
-      </c>
-      <c r="P6" s="3">
-        <f>200.00+200.00</f>
-        <v/>
-      </c>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
       <c r="Q6" s="3">
-        <f>490.00</f>
-        <v/>
-      </c>
-      <c r="R6" s="3">
-        <f>16.25</f>
-        <v/>
-      </c>
+        <f>SUM(C6:P6)</f>
+        <v/>
+      </c>
+      <c r="R6" s="3" t="n"/>
       <c r="S6" s="3">
-        <f>800.00+800.00</f>
-        <v/>
-      </c>
-      <c r="T6" s="3">
-        <f>SUM(C6:S6)</f>
-        <v/>
-      </c>
-      <c r="U6" s="3" t="n"/>
-      <c r="V6" s="3">
-        <f>B6+T6-U6</f>
+        <f>B6+Q6-R6</f>
         <v/>
       </c>
     </row>
@@ -2780,16 +2699,13 @@
       <c r="N7" s="3" t="n"/>
       <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="n"/>
-      <c r="Q7" s="3" t="n"/>
+      <c r="Q7" s="3">
+        <f>SUM(C7:P7)</f>
+        <v/>
+      </c>
       <c r="R7" s="3" t="n"/>
-      <c r="S7" s="3" t="n"/>
-      <c r="T7" s="3">
-        <f>SUM(C7:S7)</f>
-        <v/>
-      </c>
-      <c r="U7" s="3" t="n"/>
-      <c r="V7" s="3">
-        <f>B7+T7-U7</f>
+      <c r="S7" s="3">
+        <f>B7+Q7-R7</f>
         <v/>
       </c>
     </row>
@@ -2817,16 +2733,13 @@
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="n"/>
       <c r="P8" s="3" t="n"/>
-      <c r="Q8" s="3" t="n"/>
+      <c r="Q8" s="3">
+        <f>SUM(C8:P8)</f>
+        <v/>
+      </c>
       <c r="R8" s="3" t="n"/>
-      <c r="S8" s="3" t="n"/>
-      <c r="T8" s="3">
-        <f>SUM(C8:S8)</f>
-        <v/>
-      </c>
-      <c r="U8" s="3" t="n"/>
-      <c r="V8" s="3">
-        <f>B8+T8-U8</f>
+      <c r="S8" s="3">
+        <f>B8+Q8-R8</f>
         <v/>
       </c>
     </row>
@@ -2854,16 +2767,13 @@
       <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="n"/>
-      <c r="Q9" s="3" t="n"/>
+      <c r="Q9" s="3">
+        <f>SUM(C9:P9)</f>
+        <v/>
+      </c>
       <c r="R9" s="3" t="n"/>
-      <c r="S9" s="3" t="n"/>
-      <c r="T9" s="3">
-        <f>SUM(C9:S9)</f>
-        <v/>
-      </c>
-      <c r="U9" s="3" t="n"/>
-      <c r="V9" s="3">
-        <f>B9+T9-U9</f>
+      <c r="S9" s="3">
+        <f>B9+Q9-R9</f>
         <v/>
       </c>
     </row>
@@ -2891,16 +2801,13 @@
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="n"/>
       <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3" t="n"/>
+      <c r="Q10" s="3">
+        <f>SUM(C10:P10)</f>
+        <v/>
+      </c>
       <c r="R10" s="3" t="n"/>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3">
-        <f>SUM(C10:S10)</f>
-        <v/>
-      </c>
-      <c r="U10" s="3" t="n"/>
-      <c r="V10" s="3">
-        <f>B10+T10-U10</f>
+      <c r="S10" s="3">
+        <f>B10+Q10-R10</f>
         <v/>
       </c>
     </row>
@@ -2928,16 +2835,13 @@
       <c r="N11" s="3" t="n"/>
       <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="3" t="n"/>
+      <c r="Q11" s="3">
+        <f>SUM(C11:P11)</f>
+        <v/>
+      </c>
       <c r="R11" s="3" t="n"/>
-      <c r="S11" s="3" t="n"/>
-      <c r="T11" s="3">
-        <f>SUM(C11:S11)</f>
-        <v/>
-      </c>
-      <c r="U11" s="3" t="n"/>
-      <c r="V11" s="3">
-        <f>B11+T11-U11</f>
+      <c r="S11" s="3">
+        <f>B11+Q11-R11</f>
         <v/>
       </c>
     </row>
@@ -2965,16 +2869,13 @@
       <c r="N12" s="3" t="n"/>
       <c r="O12" s="3" t="n"/>
       <c r="P12" s="3" t="n"/>
-      <c r="Q12" s="3" t="n"/>
+      <c r="Q12" s="3">
+        <f>SUM(C12:P12)</f>
+        <v/>
+      </c>
       <c r="R12" s="3" t="n"/>
-      <c r="S12" s="3" t="n"/>
-      <c r="T12" s="3">
-        <f>SUM(C12:S12)</f>
-        <v/>
-      </c>
-      <c r="U12" s="3" t="n"/>
-      <c r="V12" s="3">
-        <f>B12+T12-U12</f>
+      <c r="S12" s="3">
+        <f>B12+Q12-R12</f>
         <v/>
       </c>
     </row>
@@ -3002,16 +2903,13 @@
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="3" t="n"/>
       <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="3" t="n"/>
+      <c r="Q13" s="3">
+        <f>SUM(C13:P13)</f>
+        <v/>
+      </c>
       <c r="R13" s="3" t="n"/>
-      <c r="S13" s="3" t="n"/>
-      <c r="T13" s="3">
-        <f>SUM(C13:S13)</f>
-        <v/>
-      </c>
-      <c r="U13" s="3" t="n"/>
-      <c r="V13" s="3">
-        <f>B13+T13-U13</f>
+      <c r="S13" s="3">
+        <f>B13+Q13-R13</f>
         <v/>
       </c>
     </row>
@@ -3039,16 +2937,13 @@
       <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="n"/>
       <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="n"/>
+      <c r="Q14" s="3">
+        <f>SUM(C14:P14)</f>
+        <v/>
+      </c>
       <c r="R14" s="3" t="n"/>
-      <c r="S14" s="3" t="n"/>
-      <c r="T14" s="3">
-        <f>SUM(C14:S14)</f>
-        <v/>
-      </c>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3">
-        <f>B14+T14-U14</f>
+      <c r="S14" s="3">
+        <f>B14+Q14-R14</f>
         <v/>
       </c>
     </row>
@@ -3124,19 +3019,7 @@
         <v/>
       </c>
       <c r="S15" s="3">
-        <f>SUM(S3:S14)</f>
-        <v/>
-      </c>
-      <c r="T15" s="3">
-        <f>SUM(T3:T14)</f>
-        <v/>
-      </c>
-      <c r="U15" s="3">
-        <f>SUM(U3:U14)</f>
-        <v/>
-      </c>
-      <c r="V15" s="3">
-        <f>V14</f>
+        <f>S14</f>
         <v/>
       </c>
     </row>
@@ -3151,7 +3034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3164,85 +3047,92 @@
     <col width="5" bestFit="1" customWidth="1" min="10" max="10"/>
     <col width="5.42578125" bestFit="1" customWidth="1" min="11" max="11"/>
     <col width="5" bestFit="1" customWidth="1" min="12" max="13"/>
-    <col width="8.140625" bestFit="1" customWidth="1" min="14" max="14"/>
-    <col width="15.5703125" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="6.28515625" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="8.140625" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="15.5703125" bestFit="1" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Merchant</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>OCT</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>DEC</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="4" t="n">
+        <v>46234</v>
+      </c>
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
+      </c>
+      <c r="Q1" s="7" t="n">
+        <v>46240</v>
       </c>
     </row>
     <row r="2">
@@ -3263,11 +3153,12 @@
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3">
-        <f>SUM(B2:M2)</f>
-        <v/>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="N2" s="3" t="n"/>
+      <c r="O2" s="3">
+        <f>SUM(B2,C2,D2,E2,F2,G2,H2,I2,J2,K2,L2,M2,N2,Q2)</f>
+        <v/>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -3285,23 +3176,31 @@
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3">
+      <c r="H3" s="3">
         <f>16.25</f>
         <v/>
       </c>
+      <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
       <c r="N3" s="3">
-        <f>SUM(B3:M3)</f>
-        <v/>
-      </c>
-      <c r="O3" s="1" t="inlineStr">
+        <f>16.25</f>
+        <v/>
+      </c>
+      <c r="O3" s="3">
+        <f>SUM(B3,C3,D3,E3,F3,G3,H3,I3,J3,K3,L3,M3,N3,Q3)</f>
+        <v/>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
+      </c>
+      <c r="Q3" s="5">
+        <f>16.25</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -3322,11 +3221,12 @@
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3">
-        <f>SUM(B4:M4)</f>
-        <v/>
-      </c>
-      <c r="O4" s="1" t="inlineStr">
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3">
+        <f>SUM(B4,C4,D4,E4,F4,G4,H4,I4,J4,K4,L4,M4,N4,Q4)</f>
+        <v/>
+      </c>
+      <c r="P4" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -3350,11 +3250,12 @@
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3">
-        <f>SUM(B5:M5)</f>
-        <v/>
-      </c>
-      <c r="O5" s="1" t="inlineStr">
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3">
+        <f>SUM(B5,C5,D5,E5,F5,G5,H5,I5,J5,K5,L5,M5,N5,Q5)</f>
+        <v/>
+      </c>
+      <c r="P5" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -3378,11 +3279,12 @@
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3">
-        <f>SUM(B6:M6)</f>
-        <v/>
-      </c>
-      <c r="O6" s="1" t="inlineStr">
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3">
+        <f>SUM(B6,C6,D6,E6,F6,G6,H6,I6,J6,K6,L6,M6,N6,Q6)</f>
+        <v/>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -3406,11 +3308,12 @@
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
       <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3">
-        <f>SUM(B7:M7)</f>
-        <v/>
-      </c>
-      <c r="O7" s="1" t="inlineStr">
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3">
+        <f>SUM(B7,C7,D7,E7,F7,G7,H7,I7,J7,K7,L7,M7,N7,Q7)</f>
+        <v/>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -3434,11 +3337,12 @@
       <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3">
-        <f>SUM(B8:M8)</f>
-        <v/>
-      </c>
-      <c r="O8" s="1" t="inlineStr">
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3">
+        <f>SUM(B8,C8,D8,E8,F8,G8,H8,I8,J8,K8,L8,M8,N8,Q8)</f>
+        <v/>
+      </c>
+      <c r="P8" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -3462,11 +3366,12 @@
       <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n"/>
       <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3">
-        <f>SUM(B9:M9)</f>
-        <v/>
-      </c>
-      <c r="O9" s="1" t="inlineStr">
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3">
+        <f>SUM(B9,C9,D9,E9,F9,G9,H9,I9,J9,K9,L9,M9,N9,Q9)</f>
+        <v/>
+      </c>
+      <c r="P9" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -3484,23 +3389,31 @@
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3">
+      <c r="H10" s="3">
         <f>350.00</f>
         <v/>
       </c>
+      <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n"/>
       <c r="M10" s="3" t="n"/>
       <c r="N10" s="3">
-        <f>SUM(B10:M10)</f>
-        <v/>
-      </c>
-      <c r="O10" s="1" t="inlineStr">
+        <f>350.00</f>
+        <v/>
+      </c>
+      <c r="O10" s="3">
+        <f>SUM(B10,C10,D10,E10,F10,G10,H10,I10,J10,K10,L10,M10,N10,Q10)</f>
+        <v/>
+      </c>
+      <c r="P10" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
+      </c>
+      <c r="Q10" s="5">
+        <f>350.00</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -3521,11 +3434,12 @@
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n"/>
       <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3">
-        <f>SUM(B11:M11)</f>
-        <v/>
-      </c>
-      <c r="O11" s="1" t="inlineStr">
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3">
+        <f>SUM(B11,C11,D11,E11,F11,G11,H11,I11,J11,K11,L11,M11,N11,Q11)</f>
+        <v/>
+      </c>
+      <c r="P11" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -3543,23 +3457,31 @@
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
       <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3">
+      <c r="H12" s="3">
         <f>300.00</f>
         <v/>
       </c>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="n"/>
       <c r="M12" s="3" t="n"/>
       <c r="N12" s="3">
-        <f>SUM(B12:M12)</f>
-        <v/>
-      </c>
-      <c r="O12" s="1" t="inlineStr">
+        <f>300.00</f>
+        <v/>
+      </c>
+      <c r="O12" s="3">
+        <f>SUM(B12,C12,D12,E12,F12,G12,H12,I12,J12,K12,L12,M12,N12,Q12)</f>
+        <v/>
+      </c>
+      <c r="P12" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
+      </c>
+      <c r="Q12" s="5">
+        <f>300.00</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -3580,11 +3502,12 @@
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="n"/>
       <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3">
-        <f>SUM(B13:M13)</f>
-        <v/>
-      </c>
-      <c r="O13" s="1" t="inlineStr">
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3">
+        <f>SUM(B13,C13,D13,E13,F13,G13,H13,I13,J13,K13,L13,M13,N13,Q13)</f>
+        <v/>
+      </c>
+      <c r="P13" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -3602,20 +3525,31 @@
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
+      <c r="H14" s="3">
+        <f>975.00</f>
+        <v/>
+      </c>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="n"/>
       <c r="L14" s="3" t="n"/>
       <c r="M14" s="3" t="n"/>
       <c r="N14" s="3">
-        <f>SUM(B14:M14)</f>
-        <v/>
-      </c>
-      <c r="O14" s="1" t="inlineStr">
+        <f>975.00</f>
+        <v/>
+      </c>
+      <c r="O14" s="3">
+        <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,J14,K14,L14,M14,N14,Q14)</f>
+        <v/>
+      </c>
+      <c r="P14" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
+      </c>
+      <c r="Q14" s="5">
+        <f>975.00</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -3630,20 +3564,31 @@
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
+      <c r="H15" s="3">
+        <f>817.29</f>
+        <v/>
+      </c>
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="n"/>
       <c r="M15" s="3" t="n"/>
       <c r="N15" s="3">
-        <f>SUM(B15:M15)</f>
-        <v/>
-      </c>
-      <c r="O15" s="1" t="inlineStr">
+        <f>817.29</f>
+        <v/>
+      </c>
+      <c r="O15" s="3">
+        <f>SUM(B15,C15,D15,E15,F15,G15,H15,I15,J15,K15,L15,M15,N15,Q15)</f>
+        <v/>
+      </c>
+      <c r="P15" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
+      </c>
+      <c r="Q15" s="5">
+        <f>817.29</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -3664,11 +3609,12 @@
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3">
-        <f>SUM(B16:M16)</f>
-        <v/>
-      </c>
-      <c r="O16" s="1" t="inlineStr">
+      <c r="N16" s="3" t="n"/>
+      <c r="O16" s="3">
+        <f>SUM(B16,C16,D16,E16,F16,G16,H16,I16,J16,K16,L16,M16,N16,Q16)</f>
+        <v/>
+      </c>
+      <c r="P16" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -3692,11 +3638,12 @@
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="n"/>
       <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3">
-        <f>SUM(B17:M17)</f>
-        <v/>
-      </c>
-      <c r="O17" s="1" t="inlineStr">
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3">
+        <f>SUM(B17,C17,D17,E17,F17,G17,H17,I17,J17,K17,L17,M17,N17,Q17)</f>
+        <v/>
+      </c>
+      <c r="P17" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -3720,11 +3667,12 @@
       <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="n"/>
       <c r="M18" s="3" t="n"/>
-      <c r="N18" s="3">
-        <f>SUM(B18:M18)</f>
-        <v/>
-      </c>
-      <c r="O18" s="1" t="inlineStr">
+      <c r="N18" s="3" t="n"/>
+      <c r="O18" s="3">
+        <f>SUM(B18,C18,D18,E18,F18,G18,H18,I18,J18,K18,L18,M18,N18,Q18)</f>
+        <v/>
+      </c>
+      <c r="P18" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -3742,23 +3690,31 @@
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3">
+      <c r="H19" s="3">
         <f>385.77+740.00</f>
         <v/>
       </c>
+      <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="n"/>
       <c r="L19" s="3" t="n"/>
       <c r="M19" s="3" t="n"/>
       <c r="N19" s="3">
-        <f>SUM(B19:M19)</f>
-        <v/>
-      </c>
-      <c r="O19" s="1" t="inlineStr">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
+      <c r="O19" s="3">
+        <f>SUM(B19,C19,D19,E19,F19,G19,H19,I19,J19,K19,L19,M19,N19,Q19)</f>
+        <v/>
+      </c>
+      <c r="P19" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
+      </c>
+      <c r="Q19" s="5">
+        <f>385.77+740.00</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -3773,23 +3729,31 @@
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3">
+      <c r="H20" s="3">
         <f>800.00+800.00</f>
         <v/>
       </c>
+      <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="n"/>
       <c r="L20" s="3" t="n"/>
       <c r="M20" s="3" t="n"/>
       <c r="N20" s="3">
-        <f>SUM(B20:M20)</f>
-        <v/>
-      </c>
-      <c r="O20" s="1" t="inlineStr">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
+      <c r="O20" s="3">
+        <f>SUM(B20,C20,D20,E20,F20,G20,H20,I20,J20,K20,L20,M20,N20,Q20)</f>
+        <v/>
+      </c>
+      <c r="P20" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
+      </c>
+      <c r="Q20" s="5">
+        <f>800.00+800.00</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -3804,23 +3768,31 @@
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
       <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3">
-        <f>490.00</f>
-        <v/>
-      </c>
+      <c r="H21" s="3">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
+      <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="n"/>
       <c r="M21" s="3" t="n"/>
       <c r="N21" s="3">
-        <f>SUM(B21:M21)</f>
-        <v/>
-      </c>
-      <c r="O21" s="1" t="inlineStr">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
+      <c r="O21" s="3">
+        <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,J21,K21,L21,M21,N21,Q21)</f>
+        <v/>
+      </c>
+      <c r="P21" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
+      </c>
+      <c r="Q21" s="5">
+        <f>490.00+120.00</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -3835,23 +3807,31 @@
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n"/>
       <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3">
+      <c r="H22" s="3">
         <f>4000.00</f>
         <v/>
       </c>
+      <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="n"/>
       <c r="L22" s="3" t="n"/>
       <c r="M22" s="3" t="n"/>
       <c r="N22" s="3">
-        <f>SUM(B22:M22)</f>
-        <v/>
-      </c>
-      <c r="O22" s="1" t="inlineStr">
+        <f>4000.00</f>
+        <v/>
+      </c>
+      <c r="O22" s="3">
+        <f>SUM(B22,C22,D22,E22,F22,G22,H22,I22,J22,K22,L22,M22,N22,Q22)</f>
+        <v/>
+      </c>
+      <c r="P22" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
+      </c>
+      <c r="Q22" s="5">
+        <f>4000.00</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -3872,11 +3852,12 @@
       <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="n"/>
       <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3">
-        <f>SUM(B23:M23)</f>
-        <v/>
-      </c>
-      <c r="O23" s="1" t="inlineStr">
+      <c r="N23" s="3" t="n"/>
+      <c r="O23" s="3">
+        <f>SUM(B23,C23,D23,E23,F23,G23,H23,I23,J23,K23,L23,M23,N23,Q23)</f>
+        <v/>
+      </c>
+      <c r="P23" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -3894,23 +3875,31 @@
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3">
+      <c r="H24" s="3">
         <f>200.00+200.00</f>
         <v/>
       </c>
+      <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="n"/>
       <c r="M24" s="3" t="n"/>
       <c r="N24" s="3">
-        <f>SUM(B24:M24)</f>
-        <v/>
-      </c>
-      <c r="O24" s="1" t="inlineStr">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
+      <c r="O24" s="3">
+        <f>SUM(B24,C24,D24,E24,F24,G24,H24,I24,J24,K24,L24,M24,N24,Q24)</f>
+        <v/>
+      </c>
+      <c r="P24" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
+      </c>
+      <c r="Q24" s="5">
+        <f>200.00+200.00</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -3931,11 +3920,12 @@
       <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="n"/>
       <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3">
-        <f>SUM(B25:M25)</f>
-        <v/>
-      </c>
-      <c r="O25" s="1" t="inlineStr">
+      <c r="N25" s="3" t="n"/>
+      <c r="O25" s="3">
+        <f>SUM(B25,C25,D25,E25,F25,G25,H25,I25,J25,K25,L25,M25,N25,Q25)</f>
+        <v/>
+      </c>
+      <c r="P25" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -3959,11 +3949,12 @@
       <c r="K26" s="3" t="n"/>
       <c r="L26" s="3" t="n"/>
       <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3">
-        <f>SUM(B26:M26)</f>
-        <v/>
-      </c>
-      <c r="O26" s="1" t="inlineStr">
+      <c r="N26" s="3" t="n"/>
+      <c r="O26" s="3">
+        <f>SUM(B26,C26,D26,E26,F26,G26,H26,I26,J26,K26,L26,M26,N26,Q26)</f>
+        <v/>
+      </c>
+      <c r="P26" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -3981,23 +3972,31 @@
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n"/>
       <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3">
+      <c r="H27" s="3">
         <f>26.57</f>
         <v/>
       </c>
+      <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n"/>
       <c r="K27" s="3" t="n"/>
       <c r="L27" s="3" t="n"/>
       <c r="M27" s="3" t="n"/>
       <c r="N27" s="3">
-        <f>SUM(B27:M27)</f>
-        <v/>
-      </c>
-      <c r="O27" s="1" t="inlineStr">
+        <f>26.57</f>
+        <v/>
+      </c>
+      <c r="O27" s="3">
+        <f>SUM(B27,C27,D27,E27,F27,G27,H27,I27,J27,K27,L27,M27,N27,Q27)</f>
+        <v/>
+      </c>
+      <c r="P27" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
+      </c>
+      <c r="Q27" s="5">
+        <f>26.57</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -4018,11 +4017,12 @@
       <c r="K28" s="3" t="n"/>
       <c r="L28" s="3" t="n"/>
       <c r="M28" s="3" t="n"/>
-      <c r="N28" s="3">
-        <f>SUM(B28:M28)</f>
-        <v/>
-      </c>
-      <c r="O28" s="1" t="inlineStr">
+      <c r="N28" s="3" t="n"/>
+      <c r="O28" s="3">
+        <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,J28,K28,L28,M28,N28,Q28)</f>
+        <v/>
+      </c>
+      <c r="P28" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -4046,11 +4046,12 @@
       <c r="K29" s="3" t="n"/>
       <c r="L29" s="3" t="n"/>
       <c r="M29" s="3" t="n"/>
-      <c r="N29" s="3">
-        <f>SUM(B29:M29)</f>
-        <v/>
-      </c>
-      <c r="O29" s="1" t="inlineStr">
+      <c r="N29" s="3" t="n"/>
+      <c r="O29" s="3">
+        <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29,N29,Q29)</f>
+        <v/>
+      </c>
+      <c r="P29" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -4074,11 +4075,12 @@
       <c r="K30" s="3" t="n"/>
       <c r="L30" s="3" t="n"/>
       <c r="M30" s="3" t="n"/>
-      <c r="N30" s="3">
-        <f>SUM(B30:M30)</f>
-        <v/>
-      </c>
-      <c r="O30" s="1" t="inlineStr">
+      <c r="N30" s="3" t="n"/>
+      <c r="O30" s="3">
+        <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30,N30,Q30)</f>
+        <v/>
+      </c>
+      <c r="P30" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -4102,11 +4104,12 @@
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="n"/>
       <c r="M31" s="3" t="n"/>
-      <c r="N31" s="3">
-        <f>SUM(B31:M31)</f>
-        <v/>
-      </c>
-      <c r="O31" s="1" t="inlineStr">
+      <c r="N31" s="3" t="n"/>
+      <c r="O31" s="3">
+        <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31,N31,Q31)</f>
+        <v/>
+      </c>
+      <c r="P31" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -4124,23 +4127,31 @@
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n"/>
       <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="3">
+      <c r="H32" s="3">
         <f>75.40</f>
         <v/>
       </c>
+      <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n"/>
       <c r="M32" s="3" t="n"/>
       <c r="N32" s="3">
-        <f>SUM(B32:M32)</f>
-        <v/>
-      </c>
-      <c r="O32" s="1" t="inlineStr">
+        <f>75.40</f>
+        <v/>
+      </c>
+      <c r="O32" s="3">
+        <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32,N32,Q32)</f>
+        <v/>
+      </c>
+      <c r="P32" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
+      </c>
+      <c r="Q32" s="5">
+        <f>75.40</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -4155,23 +4166,31 @@
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
       <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3">
+      <c r="H33" s="3">
         <f>18.75</f>
         <v/>
       </c>
+      <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="n"/>
       <c r="L33" s="3" t="n"/>
       <c r="M33" s="3" t="n"/>
       <c r="N33" s="3">
-        <f>SUM(B33:M33)</f>
-        <v/>
-      </c>
-      <c r="O33" s="1" t="inlineStr">
+        <f>18.75</f>
+        <v/>
+      </c>
+      <c r="O33" s="3">
+        <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33,N33,Q33)</f>
+        <v/>
+      </c>
+      <c r="P33" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
+      </c>
+      <c r="Q33" s="5">
+        <f>18.75</f>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -4192,11 +4211,12 @@
       <c r="K34" s="3" t="n"/>
       <c r="L34" s="3" t="n"/>
       <c r="M34" s="3" t="n"/>
-      <c r="N34" s="3">
-        <f>SUM(B34:M34)</f>
-        <v/>
-      </c>
-      <c r="O34" s="1" t="inlineStr">
+      <c r="N34" s="3" t="n"/>
+      <c r="O34" s="3">
+        <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,J34,K34,L34,M34,N34,Q34)</f>
+        <v/>
+      </c>
+      <c r="P34" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -4220,11 +4240,12 @@
       <c r="K35" s="3" t="n"/>
       <c r="L35" s="3" t="n"/>
       <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3">
-        <f>SUM(B35:M35)</f>
-        <v/>
-      </c>
-      <c r="O35" s="1" t="inlineStr">
+      <c r="N35" s="3" t="n"/>
+      <c r="O35" s="3">
+        <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,J35,K35,L35,M35,N35,Q35)</f>
+        <v/>
+      </c>
+      <c r="P35" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -4248,11 +4269,12 @@
       <c r="K36" s="3" t="n"/>
       <c r="L36" s="3" t="n"/>
       <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3">
-        <f>SUM(B36:M36)</f>
-        <v/>
-      </c>
-      <c r="O36" s="1" t="inlineStr">
+      <c r="N36" s="3" t="n"/>
+      <c r="O36" s="3">
+        <f>SUM(B36,C36,D36,E36,F36,G36,H36,I36,J36,K36,L36,M36,N36,Q36)</f>
+        <v/>
+      </c>
+      <c r="P36" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -4276,11 +4298,12 @@
       <c r="K37" s="3" t="n"/>
       <c r="L37" s="3" t="n"/>
       <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3">
-        <f>SUM(B37:M37)</f>
-        <v/>
-      </c>
-      <c r="O37" s="1" t="inlineStr">
+      <c r="N37" s="3" t="n"/>
+      <c r="O37" s="3">
+        <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,J37,K37,L37,M37,N37,Q37)</f>
+        <v/>
+      </c>
+      <c r="P37" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -4298,20 +4321,31 @@
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n"/>
       <c r="G38" s="3" t="n"/>
-      <c r="H38" s="3" t="n"/>
+      <c r="H38" s="3">
+        <f>930.52</f>
+        <v/>
+      </c>
       <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="n"/>
       <c r="M38" s="3" t="n"/>
       <c r="N38" s="3">
-        <f>SUM(B38:M38)</f>
-        <v/>
-      </c>
-      <c r="O38" s="1" t="inlineStr">
+        <f>930.52</f>
+        <v/>
+      </c>
+      <c r="O38" s="3">
+        <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38,N38,Q38)</f>
+        <v/>
+      </c>
+      <c r="P38" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
+      </c>
+      <c r="Q38" s="5">
+        <f>930.52</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -4332,11 +4366,12 @@
       <c r="K39" s="3" t="n"/>
       <c r="L39" s="3" t="n"/>
       <c r="M39" s="3" t="n"/>
-      <c r="N39" s="3">
-        <f>SUM(B39:M39)</f>
-        <v/>
-      </c>
-      <c r="O39" s="1" t="inlineStr">
+      <c r="N39" s="3" t="n"/>
+      <c r="O39" s="3">
+        <f>SUM(B39,C39,D39,E39,F39,G39,H39,I39,J39,K39,L39,M39,N39,Q39)</f>
+        <v/>
+      </c>
+      <c r="P39" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -4354,23 +4389,31 @@
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
       <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3">
+      <c r="H40" s="3">
         <f>1000.00+3200.00</f>
         <v/>
       </c>
+      <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="n"/>
       <c r="M40" s="3" t="n"/>
       <c r="N40" s="3">
-        <f>SUM(B40:M40)</f>
-        <v/>
-      </c>
-      <c r="O40" s="1" t="inlineStr">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
+      <c r="O40" s="3">
+        <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,J40,K40,L40,M40,N40,Q40)</f>
+        <v/>
+      </c>
+      <c r="P40" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
+      </c>
+      <c r="Q40" s="5">
+        <f>1000.00+3200.00</f>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -4428,10 +4471,18 @@
         <v/>
       </c>
       <c r="N41" s="3">
-        <f>SUM(B41:M41)</f>
-        <v/>
-      </c>
-      <c r="O41" s="1" t="n"/>
+        <f>SUM(N2:N40)</f>
+        <v/>
+      </c>
+      <c r="O41" s="3">
+        <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41,N41,Q41)</f>
+        <v/>
+      </c>
+      <c r="P41" s="1" t="n"/>
+      <c r="Q41" s="5">
+        <f>SUM(Q2:Q40)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/credit_monthly_summary.xlsx
+++ b/credit_monthly_summary.xlsx
@@ -121,9 +121,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -135,6 +132,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -510,7 +510,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>CHASE #3444</t>
         </is>
@@ -535,93 +535,93 @@
       <c r="S1" s="9" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="6" t="n"/>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="n"/>
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>BEGIN BALANCE</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>CASH / CHECK DEPOSIT</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>NO1 SUSHI 88 CORKBBO ACH</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>VEOLIA WATER</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>ORANGE &amp; ROCKLAND</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>WITHDRAWAL BRANCH 0964</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>AMAZON</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>BILL PAY:VEOLIA WATER NEW Y 200045 6BU1T6KR</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>BILL PAY:ORANGE &amp; ROCKLAND 136130 6BQ1P6KR</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>INTERNET TRF TO CLIENT-ADDED TRANSFER ACCOUNT</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>WITHDRAWAL BRANCH 0964 NEW YORK</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>POS MAC AMAZON.COM*NX6 SEATTLE WA</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>POS MAC AMAZON.COM*9O5 SEATTLE WA</t>
         </is>
       </c>
-      <c r="O2" s="6" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>POS MAC AMAZON.COM*SB8 SEATTLE WA</t>
         </is>
       </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>NYS DTF PIT TAX PAYMNT</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>TOTAL CREDIT</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="S2" s="6" t="inlineStr">
+      <c r="S2" s="7" t="inlineStr">
         <is>
           <t>ENDING BALANCE</t>
         </is>
@@ -633,29 +633,29 @@
           <t>AUG</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
-      <c r="P3" s="3" t="n"/>
-      <c r="Q3" s="3">
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2">
         <f>SUM(C3:P3)</f>
         <v/>
       </c>
-      <c r="R3" s="3" t="n"/>
-      <c r="S3" s="3">
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2">
         <f>B3+Q3-R3</f>
         <v/>
       </c>
@@ -666,30 +666,30 @@
           <t>SEP</t>
         </is>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <f>S3</f>
         <v/>
       </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="n"/>
-      <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3">
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2">
         <f>SUM(C4:P4)</f>
         <v/>
       </c>
-      <c r="R4" s="3" t="n"/>
-      <c r="S4" s="3">
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2">
         <f>B4+Q4-R4</f>
         <v/>
       </c>
@@ -700,30 +700,30 @@
           <t>OCT</t>
         </is>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <f>S4</f>
         <v/>
       </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3">
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
+      <c r="P5" s="2" t="n"/>
+      <c r="Q5" s="2">
         <f>SUM(C5:P5)</f>
         <v/>
       </c>
-      <c r="R5" s="3" t="n"/>
-      <c r="S5" s="3">
+      <c r="R5" s="2" t="n"/>
+      <c r="S5" s="2">
         <f>B5+Q5-R5</f>
         <v/>
       </c>
@@ -734,30 +734,30 @@
           <t>NOV</t>
         </is>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <f>S5</f>
         <v/>
       </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="n"/>
-      <c r="Q6" s="3">
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2">
         <f>SUM(C6:P6)</f>
         <v/>
       </c>
-      <c r="R6" s="3" t="n"/>
-      <c r="S6" s="3">
+      <c r="R6" s="2" t="n"/>
+      <c r="S6" s="2">
         <f>B6+Q6-R6</f>
         <v/>
       </c>
@@ -768,30 +768,30 @@
           <t>DEC</t>
         </is>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <f>S6</f>
         <v/>
       </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
-      <c r="P7" s="3" t="n"/>
-      <c r="Q7" s="3">
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="n"/>
+      <c r="Q7" s="2">
         <f>SUM(C7:P7)</f>
         <v/>
       </c>
-      <c r="R7" s="3" t="n"/>
-      <c r="S7" s="3">
+      <c r="R7" s="2" t="n"/>
+      <c r="S7" s="2">
         <f>B7+Q7-R7</f>
         <v/>
       </c>
@@ -802,30 +802,30 @@
           <t>JAN</t>
         </is>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <f>S7</f>
         <v/>
       </c>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
-      <c r="P8" s="3" t="n"/>
-      <c r="Q8" s="3">
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2">
         <f>SUM(C8:P8)</f>
         <v/>
       </c>
-      <c r="R8" s="3" t="n"/>
-      <c r="S8" s="3">
+      <c r="R8" s="2" t="n"/>
+      <c r="S8" s="2">
         <f>B8+Q8-R8</f>
         <v/>
       </c>
@@ -836,30 +836,30 @@
           <t>FEB</t>
         </is>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <f>S8</f>
         <v/>
       </c>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
-      <c r="P9" s="3" t="n"/>
-      <c r="Q9" s="3">
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
+      <c r="P9" s="2" t="n"/>
+      <c r="Q9" s="2">
         <f>SUM(C9:P9)</f>
         <v/>
       </c>
-      <c r="R9" s="3" t="n"/>
-      <c r="S9" s="3">
+      <c r="R9" s="2" t="n"/>
+      <c r="S9" s="2">
         <f>B9+Q9-R9</f>
         <v/>
       </c>
@@ -870,30 +870,30 @@
           <t>MAR</t>
         </is>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <f>S9</f>
         <v/>
       </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3">
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
+      <c r="P10" s="2" t="n"/>
+      <c r="Q10" s="2">
         <f>SUM(C10:P10)</f>
         <v/>
       </c>
-      <c r="R10" s="3" t="n"/>
-      <c r="S10" s="3">
+      <c r="R10" s="2" t="n"/>
+      <c r="S10" s="2">
         <f>B10+Q10-R10</f>
         <v/>
       </c>
@@ -904,30 +904,30 @@
           <t>APR</t>
         </is>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <f>S10</f>
         <v/>
       </c>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="3">
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="n"/>
+      <c r="Q11" s="2">
         <f>SUM(C11:P11)</f>
         <v/>
       </c>
-      <c r="R11" s="3" t="n"/>
-      <c r="S11" s="3">
+      <c r="R11" s="2" t="n"/>
+      <c r="S11" s="2">
         <f>B11+Q11-R11</f>
         <v/>
       </c>
@@ -938,30 +938,30 @@
           <t>MAY</t>
         </is>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <f>S11</f>
         <v/>
       </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="n"/>
-      <c r="P12" s="3" t="n"/>
-      <c r="Q12" s="3">
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n"/>
+      <c r="Q12" s="2">
         <f>SUM(C12:P12)</f>
         <v/>
       </c>
-      <c r="R12" s="3" t="n"/>
-      <c r="S12" s="3">
+      <c r="R12" s="2" t="n"/>
+      <c r="S12" s="2">
         <f>B12+Q12-R12</f>
         <v/>
       </c>
@@ -972,30 +972,30 @@
           <t>JUN</t>
         </is>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <f>S12</f>
         <v/>
       </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="n"/>
-      <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="3">
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="n"/>
+      <c r="Q13" s="2">
         <f>SUM(C13:P13)</f>
         <v/>
       </c>
-      <c r="R13" s="3" t="n"/>
-      <c r="S13" s="3">
+      <c r="R13" s="2" t="n"/>
+      <c r="S13" s="2">
         <f>B13+Q13-R13</f>
         <v/>
       </c>
@@ -1006,30 +1006,30 @@
           <t>JUL</t>
         </is>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <f>S13</f>
         <v/>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3">
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="n"/>
+      <c r="Q14" s="2">
         <f>SUM(C14:P14)</f>
         <v/>
       </c>
-      <c r="R14" s="3" t="n"/>
-      <c r="S14" s="3">
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2">
         <f>B14+Q14-R14</f>
         <v/>
       </c>
@@ -1040,72 +1040,72 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3">
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2">
         <f>SUM(C3:C14)</f>
         <v/>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2">
         <f>SUM(D3:D14)</f>
         <v/>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <f>SUM(E3:E14)</f>
         <v/>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <f>SUM(F3:F14)</f>
         <v/>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <f>SUM(G3:G14)</f>
         <v/>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <f>SUM(H3:H14)</f>
         <v/>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="2">
         <f>SUM(I3:I14)</f>
         <v/>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="2">
         <f>SUM(J3:J14)</f>
         <v/>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="2">
         <f>SUM(K3:K14)</f>
         <v/>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="2">
         <f>SUM(L3:L14)</f>
         <v/>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="2">
         <f>SUM(M3:M14)</f>
         <v/>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="2">
         <f>SUM(N3:N14)</f>
         <v/>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="2">
         <f>SUM(O3:O14)</f>
         <v/>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="2">
         <f>SUM(P3:P14)</f>
         <v/>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="2">
         <f>SUM(Q3:Q14)</f>
         <v/>
       </c>
-      <c r="R15" s="3">
+      <c r="R15" s="2">
         <f>SUM(R3:R14)</f>
         <v/>
       </c>
-      <c r="S15" s="3">
+      <c r="S15" s="2">
         <f>S14</f>
         <v/>
       </c>
@@ -1135,77 +1135,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Merchant</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>OCT</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>DEC</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="N1" s="6" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="O1" s="6" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
@@ -1217,19 +1217,19 @@
           <t>434 / Nys Commission</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3">
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2">
         <f>SUM(B2,C2,D2,E2,F2,G2,H2,I2,J2,K2,L2,M2)</f>
         <v/>
       </c>
@@ -1245,19 +1245,19 @@
           <t>Amazon Prime*Zh8618Uz3 Amzn.Com/Bill WA</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2">
         <f>SUM(B3,C3,D3,E3,F3,G3,H3,I3,J3,K3,L3,M3)</f>
         <v/>
       </c>
@@ -1273,19 +1273,19 @@
           <t>Amazon.Com*N22Fjseattlewa US</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2">
         <f>SUM(B4,C4,D4,E4,F4,G4,H4,I4,J4,K4,L4,M4)</f>
         <v/>
       </c>
@@ -1301,19 +1301,19 @@
           <t>Amazon.Comseattlewa US</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2">
         <f>SUM(B5,C5,D5,E5,F5,G5,H5,I5,J5,K5,L5,M5)</f>
         <v/>
       </c>
@@ -1329,19 +1329,19 @@
           <t>Amex Epayment ACH Pmt</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2">
         <f>SUM(B6,C6,D6,E6,F6,G6,H6,I6,J6,K6,L6,M6)</f>
         <v/>
       </c>
@@ -1357,19 +1357,19 @@
           <t>Arrow Bank Na Web Pmt</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2">
         <f>SUM(B7,C7,D7,E7,F7,G7,H7,I7,J7,K7,L7,M7)</f>
         <v/>
       </c>
@@ -1385,19 +1385,19 @@
           <t>Bill Pay:Associated Mutual 210061 Ubq1P6Kr</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2">
         <f>SUM(B8,C8,D8,E8,F8,G8,H8,I8,J8,K8,L8,M8)</f>
         <v/>
       </c>
@@ -1413,19 +1413,19 @@
           <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2">
         <f>SUM(B9,C9,D9,E9,F9,G9,H9,I9,J9,K9,L9,M9)</f>
         <v/>
       </c>
@@ -1441,19 +1441,19 @@
           <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2">
         <f>SUM(B10,C10,D10,E10,F10,G10,H10,I10,J10,K10,L10,M10)</f>
         <v/>
       </c>
@@ -1469,19 +1469,19 @@
           <t>Bill Pay:Orange &amp; Rockland 879293 5Bq1P6Kr</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3">
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2">
         <f>SUM(B11,C11,D11,E11,F11,G11,H11,I11,J11,K11,L11,M11)</f>
         <v/>
       </c>
@@ -1497,19 +1497,19 @@
           <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3">
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2">
         <f>SUM(B12,C12,D12,E12,F12,G12,H12,I12,J12,K12,L12,M12)</f>
         <v/>
       </c>
@@ -1525,19 +1525,19 @@
           <t>Bill Pay:Veolia Water New Y 200054 Hbu1T6Kr</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2">
         <f>SUM(B13,C13,D13,E13,F13,G13,H13,I13,J13,K13,L13,M13)</f>
         <v/>
       </c>
@@ -1553,19 +1553,19 @@
           <t>Citi Card Onlinepayment</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2">
         <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,J14,K14,L14,M14)</f>
         <v/>
       </c>
@@ -1581,19 +1581,19 @@
           <t>Credit One Bank Payment</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
-      <c r="N15" s="3">
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2">
         <f>SUM(B15,C15,D15,E15,F15,G15,H15,I15,J15,K15,L15,M15)</f>
         <v/>
       </c>
@@ -1609,19 +1609,19 @@
           <t>Discover Bank Net/Mobile</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2">
         <f>SUM(B16,C16,D16,E16,F16,G16,H16,I16,J16,K16,L16,M16)</f>
         <v/>
       </c>
@@ -1637,19 +1637,19 @@
           <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3">
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2">
         <f>SUM(B17,C17,D17,E17,F17,G17,H17,I17,J17,K17,L17,M17)</f>
         <v/>
       </c>
@@ -1665,19 +1665,19 @@
           <t>Huntington Banksil Payment</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n"/>
-      <c r="N18" s="3">
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2">
         <f>SUM(B18,C18,D18,E18,F18,G18,H18,I18,J18,K18,L18,M18)</f>
         <v/>
       </c>
@@ -1693,19 +1693,19 @@
           <t>Internet Trf To Client-Added Transfer Account</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3">
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2">
         <f>SUM(B19,C19,D19,E19,F19,G19,H19,I19,J19,K19,L19,M19)</f>
         <v/>
       </c>
@@ -1721,19 +1721,19 @@
           <t>Irs Usataxpymt</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3" t="n"/>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3">
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2">
         <f>SUM(B20,C20,D20,E20,F20,G20,H20,I20,J20,K20,L20,M20)</f>
         <v/>
       </c>
@@ -1749,19 +1749,19 @@
           <t>Kindercare Portland OR</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3">
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2">
         <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,J21,K21,L21,M21)</f>
         <v/>
       </c>
@@ -1777,19 +1777,19 @@
           <t>No1 Sushi 88 Corkbbo ACH</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3">
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2">
         <f>SUM(B22,C22,D22,E22,F22,G22,H22,I22,J22,K22,L22,M22)</f>
         <v/>
       </c>
@@ -1805,19 +1805,19 @@
           <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3">
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2">
         <f>SUM(B23,C23,D23,E23,F23,G23,H23,I23,J23,K23,L23,M23)</f>
         <v/>
       </c>
@@ -1833,19 +1833,19 @@
           <t>Nys Dtf Pit Tax Paymnt</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n"/>
-      <c r="M24" s="3" t="n"/>
-      <c r="N24" s="3">
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2">
         <f>SUM(B24,C24,D24,E24,F24,G24,H24,I24,J24,K24,L24,M24)</f>
         <v/>
       </c>
@@ -1861,19 +1861,19 @@
           <t>PANDA EXPRESS TACOMA WA</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3">
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2">
         <f>SUM(B25,C25,D25,E25,F25,G25,H25,I25,J25,K25,L25,M25)</f>
         <v/>
       </c>
@@ -1889,19 +1889,19 @@
           <t>Paypal Inst Xfer</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="n"/>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3">
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2">
         <f>SUM(B26,C26,D26,E26,F26,G26,H26,I26,J26,K26,L26,M26)</f>
         <v/>
       </c>
@@ -1917,19 +1917,19 @@
           <t>POS Mac Amazon.Com*9O5 Seattle WA</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="3" t="n"/>
-      <c r="N27" s="3">
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2">
         <f>SUM(B27,C27,D27,E27,F27,G27,H27,I27,J27,K27,L27,M27)</f>
         <v/>
       </c>
@@ -1945,19 +1945,19 @@
           <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="n"/>
-      <c r="L28" s="3" t="n"/>
-      <c r="M28" s="3" t="n"/>
-      <c r="N28" s="3">
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2">
         <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,J28,K28,L28,M28)</f>
         <v/>
       </c>
@@ -1973,19 +1973,19 @@
           <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
-      <c r="N29" s="3">
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2">
         <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29)</f>
         <v/>
       </c>
@@ -2001,19 +2001,19 @@
           <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="3" t="n"/>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="3">
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2">
         <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30)</f>
         <v/>
       </c>
@@ -2029,19 +2029,19 @@
           <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="n"/>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="3">
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2">
         <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31)</f>
         <v/>
       </c>
@@ -2057,19 +2057,19 @@
           <t>POS Mac Amazon.Com*Nx6 Seattle WA</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="3" t="n"/>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n"/>
-      <c r="M32" s="3" t="n"/>
-      <c r="N32" s="3">
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2">
         <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32)</f>
         <v/>
       </c>
@@ -2085,19 +2085,19 @@
           <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3">
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2">
         <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33)</f>
         <v/>
       </c>
@@ -2113,19 +2113,19 @@
           <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="3" t="n"/>
-      <c r="K34" s="3" t="n"/>
-      <c r="L34" s="3" t="n"/>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="3">
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2">
         <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,J34,K34,L34,M34)</f>
         <v/>
       </c>
@@ -2141,19 +2141,19 @@
           <t>POS Mac Amazon.Com*V25 Seattle WA</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="n"/>
-      <c r="J35" s="3" t="n"/>
-      <c r="K35" s="3" t="n"/>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3">
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2">
         <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,J35,K35,L35,M35)</f>
         <v/>
       </c>
@@ -2169,19 +2169,19 @@
           <t>POS Mac Amazon.Com*Yr6 Seattle WA</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="n"/>
-      <c r="J36" s="3" t="n"/>
-      <c r="K36" s="3" t="n"/>
-      <c r="L36" s="3" t="n"/>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3">
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2">
         <f>SUM(B36,C36,D36,E36,F36,G36,H36,I36,J36,K36,L36,M36)</f>
         <v/>
       </c>
@@ -2197,19 +2197,19 @@
           <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
-      <c r="I37" s="3" t="n"/>
-      <c r="J37" s="3" t="n"/>
-      <c r="K37" s="3" t="n"/>
-      <c r="L37" s="3" t="n"/>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3">
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2">
         <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,J37,K37,L37,M37)</f>
         <v/>
       </c>
@@ -2225,19 +2225,19 @@
           <t>Prog Casualty Ins Prem</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="n"/>
-      <c r="H38" s="3" t="n"/>
-      <c r="I38" s="3" t="n"/>
-      <c r="J38" s="3" t="n"/>
-      <c r="K38" s="3" t="n"/>
-      <c r="L38" s="3" t="n"/>
-      <c r="M38" s="3" t="n"/>
-      <c r="N38" s="3">
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2">
         <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38)</f>
         <v/>
       </c>
@@ -2253,19 +2253,19 @@
           <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
-      <c r="E39" s="3" t="n"/>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="3" t="n"/>
-      <c r="H39" s="3" t="n"/>
-      <c r="I39" s="3" t="n"/>
-      <c r="J39" s="3" t="n"/>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n"/>
-      <c r="M39" s="3" t="n"/>
-      <c r="N39" s="3">
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2">
         <f>SUM(B39,C39,D39,E39,F39,G39,H39,I39,J39,K39,L39,M39)</f>
         <v/>
       </c>
@@ -2281,19 +2281,19 @@
           <t>Withdrawal Branch 0964 New York</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
-      <c r="J40" s="3" t="n"/>
-      <c r="K40" s="3" t="n"/>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="3" t="n"/>
-      <c r="N40" s="3">
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2">
         <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,J40,K40,L40,M40)</f>
         <v/>
       </c>
@@ -2309,19 +2309,19 @@
           <t>discover Bank Net/Mobile</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="n"/>
-      <c r="K41" s="3" t="n"/>
-      <c r="L41" s="3" t="n"/>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3">
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2">
         <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41)</f>
         <v/>
       </c>
@@ -2333,55 +2333,55 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="4">
         <f>SUM(B2:B41)</f>
         <v/>
       </c>
-      <c r="C42" s="5">
+      <c r="C42" s="4">
         <f>SUM(C2:C41)</f>
         <v/>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="4">
         <f>SUM(D2:D41)</f>
         <v/>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="4">
         <f>SUM(E2:E41)</f>
         <v/>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="4">
         <f>SUM(F2:F41)</f>
         <v/>
       </c>
-      <c r="G42" s="5">
+      <c r="G42" s="4">
         <f>SUM(G2:G41)</f>
         <v/>
       </c>
-      <c r="H42" s="5">
+      <c r="H42" s="4">
         <f>SUM(H2:H41)</f>
         <v/>
       </c>
-      <c r="I42" s="5">
+      <c r="I42" s="4">
         <f>SUM(I2:I41)</f>
         <v/>
       </c>
-      <c r="J42" s="5">
+      <c r="J42" s="4">
         <f>SUM(J2:J41)</f>
         <v/>
       </c>
-      <c r="K42" s="5">
+      <c r="K42" s="4">
         <f>SUM(K2:K41)</f>
         <v/>
       </c>
-      <c r="L42" s="5">
+      <c r="L42" s="4">
         <f>SUM(L2:L41)</f>
         <v/>
       </c>
-      <c r="M42" s="5">
+      <c r="M42" s="4">
         <f>SUM(M2:M41)</f>
         <v/>
       </c>
-      <c r="N42" s="5">
+      <c r="N42" s="4">
         <f>SUM(B42,C42,D42,E42,F42,G42,H42,I42,J42,K42,L42,M42)</f>
         <v/>
       </c>
@@ -2424,7 +2424,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>CHASE #3444</t>
         </is>
@@ -2448,93 +2448,93 @@
       <c r="S1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="n"/>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="n"/>
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>BEGIN BALANCE</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>CASH / CHECK DEPOSIT</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>NO1 SUSHI 88 CORKBBO ACH</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>VEOLIA WATER</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>ORANGE &amp; ROCKLAND</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>WITHDRAWAL BRANCH 0964</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>AMAZON</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>BILL PAY:VEOLIA WATER NEW Y 200045 6BU1T6KR</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>BILL PAY:ORANGE &amp; ROCKLAND 136130 6BQ1P6KR</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>INTERNET TRF TO CLIENT-ADDED TRANSFER ACCOUNT</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>WITHDRAWAL BRANCH 0964 NEW YORK</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>POS MAC AMAZON.COM*NX6 SEATTLE WA</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>POS MAC AMAZON.COM*9O5 SEATTLE WA</t>
         </is>
       </c>
-      <c r="O2" s="6" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>POS MAC AMAZON.COM*SB8 SEATTLE WA</t>
         </is>
       </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>NYS DTF PIT TAX PAYMNT</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>TOTAL CREDIT</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="S2" s="6" t="inlineStr">
+      <c r="S2" s="7" t="inlineStr">
         <is>
           <t>ENDING BALANCE</t>
         </is>
@@ -2546,29 +2546,29 @@
           <t>AUG</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
-      <c r="P3" s="3" t="n"/>
-      <c r="Q3" s="3">
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2">
         <f>SUM(C3:P3)</f>
         <v/>
       </c>
-      <c r="R3" s="3" t="n"/>
-      <c r="S3" s="3">
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2">
         <f>B3+Q3-R3</f>
         <v/>
       </c>
@@ -2579,30 +2579,30 @@
           <t>SEP</t>
         </is>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <f>S3</f>
         <v/>
       </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="n"/>
-      <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3">
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2">
         <f>SUM(C4:P4)</f>
         <v/>
       </c>
-      <c r="R4" s="3" t="n"/>
-      <c r="S4" s="3">
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2">
         <f>B4+Q4-R4</f>
         <v/>
       </c>
@@ -2613,30 +2613,30 @@
           <t>OCT</t>
         </is>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <f>S4</f>
         <v/>
       </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3">
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
+      <c r="P5" s="2" t="n"/>
+      <c r="Q5" s="2">
         <f>SUM(C5:P5)</f>
         <v/>
       </c>
-      <c r="R5" s="3" t="n"/>
-      <c r="S5" s="3">
+      <c r="R5" s="2" t="n"/>
+      <c r="S5" s="2">
         <f>B5+Q5-R5</f>
         <v/>
       </c>
@@ -2647,30 +2647,30 @@
           <t>NOV</t>
         </is>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <f>S5</f>
         <v/>
       </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="n"/>
-      <c r="Q6" s="3">
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2">
         <f>SUM(C6:P6)</f>
         <v/>
       </c>
-      <c r="R6" s="3" t="n"/>
-      <c r="S6" s="3">
+      <c r="R6" s="2" t="n"/>
+      <c r="S6" s="2">
         <f>B6+Q6-R6</f>
         <v/>
       </c>
@@ -2681,30 +2681,30 @@
           <t>DEC</t>
         </is>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <f>S6</f>
         <v/>
       </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
-      <c r="P7" s="3" t="n"/>
-      <c r="Q7" s="3">
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="n"/>
+      <c r="Q7" s="2">
         <f>SUM(C7:P7)</f>
         <v/>
       </c>
-      <c r="R7" s="3" t="n"/>
-      <c r="S7" s="3">
+      <c r="R7" s="2" t="n"/>
+      <c r="S7" s="2">
         <f>B7+Q7-R7</f>
         <v/>
       </c>
@@ -2715,30 +2715,30 @@
           <t>JAN</t>
         </is>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <f>S7</f>
         <v/>
       </c>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
-      <c r="P8" s="3" t="n"/>
-      <c r="Q8" s="3">
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2">
         <f>SUM(C8:P8)</f>
         <v/>
       </c>
-      <c r="R8" s="3" t="n"/>
-      <c r="S8" s="3">
+      <c r="R8" s="2" t="n"/>
+      <c r="S8" s="2">
         <f>B8+Q8-R8</f>
         <v/>
       </c>
@@ -2749,30 +2749,30 @@
           <t>FEB</t>
         </is>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <f>S8</f>
         <v/>
       </c>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
-      <c r="P9" s="3" t="n"/>
-      <c r="Q9" s="3">
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
+      <c r="P9" s="2" t="n"/>
+      <c r="Q9" s="2">
         <f>SUM(C9:P9)</f>
         <v/>
       </c>
-      <c r="R9" s="3" t="n"/>
-      <c r="S9" s="3">
+      <c r="R9" s="2" t="n"/>
+      <c r="S9" s="2">
         <f>B9+Q9-R9</f>
         <v/>
       </c>
@@ -2783,30 +2783,30 @@
           <t>MAR</t>
         </is>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <f>S9</f>
         <v/>
       </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3">
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
+      <c r="P10" s="2" t="n"/>
+      <c r="Q10" s="2">
         <f>SUM(C10:P10)</f>
         <v/>
       </c>
-      <c r="R10" s="3" t="n"/>
-      <c r="S10" s="3">
+      <c r="R10" s="2" t="n"/>
+      <c r="S10" s="2">
         <f>B10+Q10-R10</f>
         <v/>
       </c>
@@ -2817,30 +2817,30 @@
           <t>APR</t>
         </is>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <f>S10</f>
         <v/>
       </c>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="3">
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="n"/>
+      <c r="Q11" s="2">
         <f>SUM(C11:P11)</f>
         <v/>
       </c>
-      <c r="R11" s="3" t="n"/>
-      <c r="S11" s="3">
+      <c r="R11" s="2" t="n"/>
+      <c r="S11" s="2">
         <f>B11+Q11-R11</f>
         <v/>
       </c>
@@ -2851,30 +2851,30 @@
           <t>MAY</t>
         </is>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <f>S11</f>
         <v/>
       </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="n"/>
-      <c r="P12" s="3" t="n"/>
-      <c r="Q12" s="3">
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n"/>
+      <c r="Q12" s="2">
         <f>SUM(C12:P12)</f>
         <v/>
       </c>
-      <c r="R12" s="3" t="n"/>
-      <c r="S12" s="3">
+      <c r="R12" s="2" t="n"/>
+      <c r="S12" s="2">
         <f>B12+Q12-R12</f>
         <v/>
       </c>
@@ -2885,30 +2885,30 @@
           <t>JUN</t>
         </is>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <f>S12</f>
         <v/>
       </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="n"/>
-      <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="3">
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="n"/>
+      <c r="Q13" s="2">
         <f>SUM(C13:P13)</f>
         <v/>
       </c>
-      <c r="R13" s="3" t="n"/>
-      <c r="S13" s="3">
+      <c r="R13" s="2" t="n"/>
+      <c r="S13" s="2">
         <f>B13+Q13-R13</f>
         <v/>
       </c>
@@ -2919,30 +2919,30 @@
           <t>JUL</t>
         </is>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <f>S13</f>
         <v/>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3">
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="n"/>
+      <c r="Q14" s="2">
         <f>SUM(C14:P14)</f>
         <v/>
       </c>
-      <c r="R14" s="3" t="n"/>
-      <c r="S14" s="3">
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2">
         <f>B14+Q14-R14</f>
         <v/>
       </c>
@@ -2953,72 +2953,72 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3">
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2">
         <f>SUM(C3:C14)</f>
         <v/>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2">
         <f>SUM(D3:D14)</f>
         <v/>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <f>SUM(E3:E14)</f>
         <v/>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <f>SUM(F3:F14)</f>
         <v/>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <f>SUM(G3:G14)</f>
         <v/>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <f>SUM(H3:H14)</f>
         <v/>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="2">
         <f>SUM(I3:I14)</f>
         <v/>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="2">
         <f>SUM(J3:J14)</f>
         <v/>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="2">
         <f>SUM(K3:K14)</f>
         <v/>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="2">
         <f>SUM(L3:L14)</f>
         <v/>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="2">
         <f>SUM(M3:M14)</f>
         <v/>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="2">
         <f>SUM(N3:N14)</f>
         <v/>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="2">
         <f>SUM(O3:O14)</f>
         <v/>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="2">
         <f>SUM(P3:P14)</f>
         <v/>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="2">
         <f>SUM(Q3:Q14)</f>
         <v/>
       </c>
-      <c r="R15" s="3">
+      <c r="R15" s="2">
         <f>SUM(R3:R14)</f>
         <v/>
       </c>
-      <c r="S15" s="3">
+      <c r="S15" s="2">
         <f>S14</f>
         <v/>
       </c>
@@ -3053,85 +3053,85 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Merchant</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>OCT</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>DEC</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="N1" s="4" t="n">
+      <c r="N1" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="O1" s="6" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="P1" s="6" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="n">
+      <c r="Q1" s="6" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -3141,20 +3141,20 @@
           <t>434 / Nys Commission</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n"/>
-      <c r="O2" s="3">
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2">
         <f>SUM(B2,C2,D2,E2,F2,G2,H2,I2,J2,K2,L2,M2,N2,Q2)</f>
         <v/>
       </c>
@@ -3170,26 +3170,20 @@
           <t>Amazon Prime*Zh8618Uz3 Amzn.Com/Bill WA</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3">
-        <f>16.25</f>
-        <v/>
-      </c>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3">
-        <f>16.25</f>
-        <v/>
-      </c>
-      <c r="O3" s="3">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2">
         <f>SUM(B3,C3,D3,E3,F3,G3,H3,I3,J3,K3,L3,M3,N3,Q3)</f>
         <v/>
       </c>
@@ -3197,10 +3191,6 @@
         <is>
           <t>GERCORY</t>
         </is>
-      </c>
-      <c r="Q3" s="5">
-        <f>16.25</f>
-        <v/>
       </c>
     </row>
     <row r="4">
@@ -3209,20 +3199,20 @@
           <t>Amazon.Com*N22Fjseattlewa US</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2">
         <f>SUM(B4,C4,D4,E4,F4,G4,H4,I4,J4,K4,L4,M4,N4,Q4)</f>
         <v/>
       </c>
@@ -3238,20 +3228,20 @@
           <t>Amazon.Comseattlewa US</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2">
         <f>SUM(B5,C5,D5,E5,F5,G5,H5,I5,J5,K5,L5,M5,N5,Q5)</f>
         <v/>
       </c>
@@ -3267,20 +3257,20 @@
           <t>Amex Epayment ACH Pmt</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2">
         <f>SUM(B6,C6,D6,E6,F6,G6,H6,I6,J6,K6,L6,M6,N6,Q6)</f>
         <v/>
       </c>
@@ -3296,20 +3286,20 @@
           <t>Arrow Bank Na Web Pmt</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2">
         <f>SUM(B7,C7,D7,E7,F7,G7,H7,I7,J7,K7,L7,M7,N7,Q7)</f>
         <v/>
       </c>
@@ -3325,20 +3315,20 @@
           <t>Bill Pay:Associated Mutual 210061 Ubq1P6Kr</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2">
         <f>SUM(B8,C8,D8,E8,F8,G8,H8,I8,J8,K8,L8,M8,N8,Q8)</f>
         <v/>
       </c>
@@ -3354,20 +3344,20 @@
           <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2">
         <f>SUM(B9,C9,D9,E9,F9,G9,H9,I9,J9,K9,L9,M9,N9,Q9)</f>
         <v/>
       </c>
@@ -3383,26 +3373,20 @@
           <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3">
-        <f>350.00</f>
-        <v/>
-      </c>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3">
-        <f>350.00</f>
-        <v/>
-      </c>
-      <c r="O10" s="3">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2">
         <f>SUM(B10,C10,D10,E10,F10,G10,H10,I10,J10,K10,L10,M10,N10,Q10)</f>
         <v/>
       </c>
@@ -3410,10 +3394,6 @@
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
-      </c>
-      <c r="Q10" s="5">
-        <f>350.00</f>
-        <v/>
       </c>
     </row>
     <row r="11">
@@ -3422,20 +3402,20 @@
           <t>Bill Pay:Orange &amp; Rockland 879293 5Bq1P6Kr</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3">
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2">
         <f>SUM(B11,C11,D11,E11,F11,G11,H11,I11,J11,K11,L11,M11,N11,Q11)</f>
         <v/>
       </c>
@@ -3451,26 +3431,20 @@
           <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3">
-        <f>300.00</f>
-        <v/>
-      </c>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3">
-        <f>300.00</f>
-        <v/>
-      </c>
-      <c r="O12" s="3">
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2">
         <f>SUM(B12,C12,D12,E12,F12,G12,H12,I12,J12,K12,L12,M12,N12,Q12)</f>
         <v/>
       </c>
@@ -3478,10 +3452,6 @@
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
-      </c>
-      <c r="Q12" s="5">
-        <f>300.00</f>
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -3490,20 +3460,20 @@
           <t>Bill Pay:Veolia Water New Y 200054 Hbu1T6Kr</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2">
         <f>SUM(B13,C13,D13,E13,F13,G13,H13,I13,J13,K13,L13,M13,N13,Q13)</f>
         <v/>
       </c>
@@ -3519,26 +3489,20 @@
           <t>Citi Card Onlinepayment</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3">
-        <f>975.00</f>
-        <v/>
-      </c>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3">
-        <f>975.00</f>
-        <v/>
-      </c>
-      <c r="O14" s="3">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2">
         <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,J14,K14,L14,M14,N14,Q14)</f>
         <v/>
       </c>
@@ -3546,10 +3510,6 @@
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
-      </c>
-      <c r="Q14" s="5">
-        <f>975.00</f>
-        <v/>
       </c>
     </row>
     <row r="15">
@@ -3558,26 +3518,20 @@
           <t>Credit One Bank Payment</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3">
-        <f>817.29</f>
-        <v/>
-      </c>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
-      <c r="N15" s="3">
-        <f>817.29</f>
-        <v/>
-      </c>
-      <c r="O15" s="3">
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2">
         <f>SUM(B15,C15,D15,E15,F15,G15,H15,I15,J15,K15,L15,M15,N15,Q15)</f>
         <v/>
       </c>
@@ -3585,10 +3539,6 @@
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
-      </c>
-      <c r="Q15" s="5">
-        <f>817.29</f>
-        <v/>
       </c>
     </row>
     <row r="16">
@@ -3597,20 +3547,20 @@
           <t>Discover Bank Net/Mobile</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2">
         <f>SUM(B16,C16,D16,E16,F16,G16,H16,I16,J16,K16,L16,M16,N16,Q16)</f>
         <v/>
       </c>
@@ -3626,20 +3576,20 @@
           <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3">
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2">
         <f>SUM(B17,C17,D17,E17,F17,G17,H17,I17,J17,K17,L17,M17,N17,Q17)</f>
         <v/>
       </c>
@@ -3655,20 +3605,20 @@
           <t>Huntington Banksil Payment</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n"/>
-      <c r="N18" s="3" t="n"/>
-      <c r="O18" s="3">
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2">
         <f>SUM(B18,C18,D18,E18,F18,G18,H18,I18,J18,K18,L18,M18,N18,Q18)</f>
         <v/>
       </c>
@@ -3684,26 +3634,20 @@
           <t>Internet Trf To Client-Added Transfer Account</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3">
-        <f>385.77+740.00</f>
-        <v/>
-      </c>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3">
-        <f>385.77+740.00</f>
-        <v/>
-      </c>
-      <c r="O19" s="3">
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2">
         <f>SUM(B19,C19,D19,E19,F19,G19,H19,I19,J19,K19,L19,M19,N19,Q19)</f>
         <v/>
       </c>
@@ -3711,10 +3655,6 @@
         <is>
           <t>MEALS</t>
         </is>
-      </c>
-      <c r="Q19" s="5">
-        <f>385.77+740.00</f>
-        <v/>
       </c>
     </row>
     <row r="20">
@@ -3723,26 +3663,20 @@
           <t>Irs Usataxpymt</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3">
-        <f>800.00+800.00</f>
-        <v/>
-      </c>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3" t="n"/>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3">
-        <f>800.00+800.00</f>
-        <v/>
-      </c>
-      <c r="O20" s="3">
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2">
         <f>SUM(B20,C20,D20,E20,F20,G20,H20,I20,J20,K20,L20,M20,N20,Q20)</f>
         <v/>
       </c>
@@ -3750,10 +3684,6 @@
         <is>
           <t>MEALS</t>
         </is>
-      </c>
-      <c r="Q20" s="5">
-        <f>800.00+800.00</f>
-        <v/>
       </c>
     </row>
     <row r="21">
@@ -3762,26 +3692,20 @@
           <t>Kindercare Portland OR</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3">
-        <f>490.00+120.00</f>
-        <v/>
-      </c>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3">
-        <f>490.00+120.00</f>
-        <v/>
-      </c>
-      <c r="O21" s="3">
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2">
         <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,J21,K21,L21,M21,N21,Q21)</f>
         <v/>
       </c>
@@ -3789,10 +3713,6 @@
         <is>
           <t>MEALS</t>
         </is>
-      </c>
-      <c r="Q21" s="5">
-        <f>490.00+120.00</f>
-        <v/>
       </c>
     </row>
     <row r="22">
@@ -3801,26 +3721,20 @@
           <t>No1 Sushi 88 Corkbbo ACH</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3">
-        <f>4000.00</f>
-        <v/>
-      </c>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3">
-        <f>4000.00</f>
-        <v/>
-      </c>
-      <c r="O22" s="3">
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2">
         <f>SUM(B22,C22,D22,E22,F22,G22,H22,I22,J22,K22,L22,M22,N22,Q22)</f>
         <v/>
       </c>
@@ -3828,10 +3742,6 @@
         <is>
           <t>MEALS</t>
         </is>
-      </c>
-      <c r="Q22" s="5">
-        <f>4000.00</f>
-        <v/>
       </c>
     </row>
     <row r="23">
@@ -3840,20 +3750,20 @@
           <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n"/>
-      <c r="O23" s="3">
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2">
         <f>SUM(B23,C23,D23,E23,F23,G23,H23,I23,J23,K23,L23,M23,N23,Q23)</f>
         <v/>
       </c>
@@ -3869,26 +3779,20 @@
           <t>Nys Dtf Pit Tax Paymnt</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3">
-        <f>200.00+200.00</f>
-        <v/>
-      </c>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n"/>
-      <c r="M24" s="3" t="n"/>
-      <c r="N24" s="3">
-        <f>200.00+200.00</f>
-        <v/>
-      </c>
-      <c r="O24" s="3">
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2">
         <f>SUM(B24,C24,D24,E24,F24,G24,H24,I24,J24,K24,L24,M24,N24,Q24)</f>
         <v/>
       </c>
@@ -3896,10 +3800,6 @@
         <is>
           <t>MEALS</t>
         </is>
-      </c>
-      <c r="Q24" s="5">
-        <f>200.00+200.00</f>
-        <v/>
       </c>
     </row>
     <row r="25">
@@ -3908,20 +3808,20 @@
           <t>PANDA EXPRESS TACOMA WA</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3">
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2">
         <f>SUM(B25,C25,D25,E25,F25,G25,H25,I25,J25,K25,L25,M25,N25,Q25)</f>
         <v/>
       </c>
@@ -3937,20 +3837,20 @@
           <t>Paypal Inst Xfer</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="n"/>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
-      <c r="O26" s="3">
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2">
         <f>SUM(B26,C26,D26,E26,F26,G26,H26,I26,J26,K26,L26,M26,N26,Q26)</f>
         <v/>
       </c>
@@ -3966,26 +3866,20 @@
           <t>POS Mac Amazon.Com*9O5 Seattle WA</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3">
-        <f>26.57</f>
-        <v/>
-      </c>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="3" t="n"/>
-      <c r="N27" s="3">
-        <f>26.57</f>
-        <v/>
-      </c>
-      <c r="O27" s="3">
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2">
         <f>SUM(B27,C27,D27,E27,F27,G27,H27,I27,J27,K27,L27,M27,N27,Q27)</f>
         <v/>
       </c>
@@ -3993,10 +3887,6 @@
         <is>
           <t>MEALS</t>
         </is>
-      </c>
-      <c r="Q27" s="5">
-        <f>26.57</f>
-        <v/>
       </c>
     </row>
     <row r="28">
@@ -4005,20 +3895,20 @@
           <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="n"/>
-      <c r="L28" s="3" t="n"/>
-      <c r="M28" s="3" t="n"/>
-      <c r="N28" s="3" t="n"/>
-      <c r="O28" s="3">
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2">
         <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,J28,K28,L28,M28,N28,Q28)</f>
         <v/>
       </c>
@@ -4034,20 +3924,20 @@
           <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
-      <c r="N29" s="3" t="n"/>
-      <c r="O29" s="3">
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2">
         <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29,N29,Q29)</f>
         <v/>
       </c>
@@ -4063,20 +3953,20 @@
           <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="3" t="n"/>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="3" t="n"/>
-      <c r="O30" s="3">
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2">
         <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30,N30,Q30)</f>
         <v/>
       </c>
@@ -4092,20 +3982,20 @@
           <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="n"/>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="3">
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2">
         <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31,N31,Q31)</f>
         <v/>
       </c>
@@ -4121,26 +4011,20 @@
           <t>POS Mac Amazon.Com*Nx6 Seattle WA</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3">
-        <f>75.40</f>
-        <v/>
-      </c>
-      <c r="I32" s="3" t="n"/>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n"/>
-      <c r="M32" s="3" t="n"/>
-      <c r="N32" s="3">
-        <f>75.40</f>
-        <v/>
-      </c>
-      <c r="O32" s="3">
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2">
         <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32,N32,Q32)</f>
         <v/>
       </c>
@@ -4148,10 +4032,6 @@
         <is>
           <t>SUPPLY</t>
         </is>
-      </c>
-      <c r="Q32" s="5">
-        <f>75.40</f>
-        <v/>
       </c>
     </row>
     <row r="33">
@@ -4160,26 +4040,20 @@
           <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3">
-        <f>18.75</f>
-        <v/>
-      </c>
-      <c r="I33" s="3" t="n"/>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3">
-        <f>18.75</f>
-        <v/>
-      </c>
-      <c r="O33" s="3">
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2">
         <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33,N33,Q33)</f>
         <v/>
       </c>
@@ -4187,10 +4061,6 @@
         <is>
           <t>SUPPLY</t>
         </is>
-      </c>
-      <c r="Q33" s="5">
-        <f>18.75</f>
-        <v/>
       </c>
     </row>
     <row r="34">
@@ -4199,20 +4069,20 @@
           <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="3" t="n"/>
-      <c r="K34" s="3" t="n"/>
-      <c r="L34" s="3" t="n"/>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="3" t="n"/>
-      <c r="O34" s="3">
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2">
         <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,J34,K34,L34,M34,N34,Q34)</f>
         <v/>
       </c>
@@ -4228,20 +4098,20 @@
           <t>POS Mac Amazon.Com*V25 Seattle WA</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="n"/>
-      <c r="J35" s="3" t="n"/>
-      <c r="K35" s="3" t="n"/>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="n"/>
-      <c r="O35" s="3">
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2">
         <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,J35,K35,L35,M35,N35,Q35)</f>
         <v/>
       </c>
@@ -4257,20 +4127,20 @@
           <t>POS Mac Amazon.Com*Yr6 Seattle WA</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="n"/>
-      <c r="J36" s="3" t="n"/>
-      <c r="K36" s="3" t="n"/>
-      <c r="L36" s="3" t="n"/>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3" t="n"/>
-      <c r="O36" s="3">
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2">
         <f>SUM(B36,C36,D36,E36,F36,G36,H36,I36,J36,K36,L36,M36,N36,Q36)</f>
         <v/>
       </c>
@@ -4286,20 +4156,20 @@
           <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
-      <c r="I37" s="3" t="n"/>
-      <c r="J37" s="3" t="n"/>
-      <c r="K37" s="3" t="n"/>
-      <c r="L37" s="3" t="n"/>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
-      <c r="O37" s="3">
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2">
         <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,J37,K37,L37,M37,N37,Q37)</f>
         <v/>
       </c>
@@ -4315,26 +4185,20 @@
           <t>Prog Casualty Ins Prem</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="n"/>
-      <c r="H38" s="3">
-        <f>930.52</f>
-        <v/>
-      </c>
-      <c r="I38" s="3" t="n"/>
-      <c r="J38" s="3" t="n"/>
-      <c r="K38" s="3" t="n"/>
-      <c r="L38" s="3" t="n"/>
-      <c r="M38" s="3" t="n"/>
-      <c r="N38" s="3">
-        <f>930.52</f>
-        <v/>
-      </c>
-      <c r="O38" s="3">
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2">
         <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38,N38,Q38)</f>
         <v/>
       </c>
@@ -4342,10 +4206,6 @@
         <is>
           <t>SUPPLY</t>
         </is>
-      </c>
-      <c r="Q38" s="5">
-        <f>930.52</f>
-        <v/>
       </c>
     </row>
     <row r="39">
@@ -4354,20 +4214,20 @@
           <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
-      <c r="E39" s="3" t="n"/>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="3" t="n"/>
-      <c r="H39" s="3" t="n"/>
-      <c r="I39" s="3" t="n"/>
-      <c r="J39" s="3" t="n"/>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n"/>
-      <c r="M39" s="3" t="n"/>
-      <c r="N39" s="3" t="n"/>
-      <c r="O39" s="3">
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2">
         <f>SUM(B39,C39,D39,E39,F39,G39,H39,I39,J39,K39,L39,M39,N39,Q39)</f>
         <v/>
       </c>
@@ -4383,26 +4243,20 @@
           <t>Withdrawal Branch 0964 New York</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3">
-        <f>1000.00+3200.00</f>
-        <v/>
-      </c>
-      <c r="I40" s="3" t="n"/>
-      <c r="J40" s="3" t="n"/>
-      <c r="K40" s="3" t="n"/>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="3" t="n"/>
-      <c r="N40" s="3">
-        <f>1000.00+3200.00</f>
-        <v/>
-      </c>
-      <c r="O40" s="3">
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2">
         <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,J40,K40,L40,M40,N40,Q40)</f>
         <v/>
       </c>
@@ -4410,10 +4264,6 @@
         <is>
           <t>SUPPLY</t>
         </is>
-      </c>
-      <c r="Q40" s="5">
-        <f>1000.00+3200.00</f>
-        <v/>
       </c>
     </row>
     <row r="41">
@@ -4422,64 +4272,64 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B41" s="3">
+      <c r="B41" s="2">
         <f>SUM(B2:B40)</f>
         <v/>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="2">
         <f>SUM(C2:C40)</f>
         <v/>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="2">
         <f>SUM(D2:D40)</f>
         <v/>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="2">
         <f>SUM(E2:E40)</f>
         <v/>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="2">
         <f>SUM(F2:F40)</f>
         <v/>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="2">
         <f>SUM(G2:G40)</f>
         <v/>
       </c>
-      <c r="H41" s="3">
+      <c r="H41" s="2">
         <f>SUM(H2:H40)</f>
         <v/>
       </c>
-      <c r="I41" s="3">
+      <c r="I41" s="2">
         <f>SUM(I2:I40)</f>
         <v/>
       </c>
-      <c r="J41" s="3">
+      <c r="J41" s="2">
         <f>SUM(J2:J40)</f>
         <v/>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="2">
         <f>SUM(K2:K40)</f>
         <v/>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="2">
         <f>SUM(L2:L40)</f>
         <v/>
       </c>
-      <c r="M41" s="3">
+      <c r="M41" s="2">
         <f>SUM(M2:M40)</f>
         <v/>
       </c>
-      <c r="N41" s="3">
+      <c r="N41" s="2">
         <f>SUM(N2:N40)</f>
         <v/>
       </c>
-      <c r="O41" s="3">
+      <c r="O41" s="2">
         <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41,N41,Q41)</f>
         <v/>
       </c>
       <c r="P41" s="1" t="n"/>
-      <c r="Q41" s="5">
+      <c r="Q41" s="4">
         <f>SUM(Q2:Q40)</f>
         <v/>
       </c>
@@ -4497,7 +4347,9 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1"/>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/credit_monthly_summary.xlsx
+++ b/credit_monthly_summary.xlsx
@@ -3,14 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="3" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="2" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="CHASE #3444" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="CHASE DETIAL#3444" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="AMEX #5533" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CHASE CC#5235" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="CHASE CC#5235" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHASE #3444'!$A$2:$S$15</definedName>
@@ -128,10 +127,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2398,658 +2397,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="15.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22.140625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="27.7109375" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="14.85546875" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="21.7109375" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="27.5703125" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="9.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="47.42578125" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="47.7109375" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="50.85546875" bestFit="1" customWidth="1" min="11" max="11"/>
-    <col width="38.28515625" bestFit="1" customWidth="1" min="12" max="12"/>
-    <col width="40.85546875" bestFit="1" customWidth="1" min="13" max="13"/>
-    <col width="40.7109375" bestFit="1" customWidth="1" min="14" max="14"/>
-    <col width="40.42578125" bestFit="1" customWidth="1" min="15" max="15"/>
-    <col width="24.7109375" bestFit="1" customWidth="1" min="16" max="16"/>
-    <col width="13.85546875" bestFit="1" customWidth="1" min="17" max="17"/>
-    <col width="8.140625" bestFit="1" customWidth="1" min="18" max="18"/>
-    <col width="17.42578125" bestFit="1" customWidth="1" min="19" max="19"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>CHASE #3444</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="n"/>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
-      <c r="Q1" s="1" t="n"/>
-      <c r="R1" s="1" t="n"/>
-      <c r="S1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="n"/>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>BEGIN BALANCE</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>CASH / CHECK DEPOSIT</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>NO1 SUSHI 88 CORKBBO ACH</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>VEOLIA WATER</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>ORANGE &amp; ROCKLAND</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>WITHDRAWAL BRANCH 0964</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>BILL PAY:VEOLIA WATER NEW Y 200045 6BU1T6KR</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>BILL PAY:ORANGE &amp; ROCKLAND 136130 6BQ1P6KR</t>
-        </is>
-      </c>
-      <c r="K2" s="7" t="inlineStr">
-        <is>
-          <t>INTERNET TRF TO CLIENT-ADDED TRANSFER ACCOUNT</t>
-        </is>
-      </c>
-      <c r="L2" s="7" t="inlineStr">
-        <is>
-          <t>WITHDRAWAL BRANCH 0964 NEW YORK</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="inlineStr">
-        <is>
-          <t>POS MAC AMAZON.COM*NX6 SEATTLE WA</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="inlineStr">
-        <is>
-          <t>POS MAC AMAZON.COM*9O5 SEATTLE WA</t>
-        </is>
-      </c>
-      <c r="O2" s="7" t="inlineStr">
-        <is>
-          <t>POS MAC AMAZON.COM*SB8 SEATTLE WA</t>
-        </is>
-      </c>
-      <c r="P2" s="7" t="inlineStr">
-        <is>
-          <t>NYS DTF PIT TAX PAYMNT</t>
-        </is>
-      </c>
-      <c r="Q2" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL CREDIT</t>
-        </is>
-      </c>
-      <c r="R2" s="7" t="inlineStr">
-        <is>
-          <t>DEBIT</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>ENDING BALANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2">
-        <f>SUM(C3:P3)</f>
-        <v/>
-      </c>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2">
-        <f>B3+Q3-R3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="B4" s="2">
-        <f>S3</f>
-        <v/>
-      </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
-      <c r="P4" s="2" t="n"/>
-      <c r="Q4" s="2">
-        <f>SUM(C4:P4)</f>
-        <v/>
-      </c>
-      <c r="R4" s="2" t="n"/>
-      <c r="S4" s="2">
-        <f>B4+Q4-R4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="B5" s="2">
-        <f>S4</f>
-        <v/>
-      </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n"/>
-      <c r="Q5" s="2">
-        <f>SUM(C5:P5)</f>
-        <v/>
-      </c>
-      <c r="R5" s="2" t="n"/>
-      <c r="S5" s="2">
-        <f>B5+Q5-R5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>NOV</t>
-        </is>
-      </c>
-      <c r="B6" s="2">
-        <f>S5</f>
-        <v/>
-      </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2">
-        <f>SUM(C6:P6)</f>
-        <v/>
-      </c>
-      <c r="R6" s="2" t="n"/>
-      <c r="S6" s="2">
-        <f>B6+Q6-R6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>DEC</t>
-        </is>
-      </c>
-      <c r="B7" s="2">
-        <f>S6</f>
-        <v/>
-      </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="n"/>
-      <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2" t="n"/>
-      <c r="P7" s="2" t="n"/>
-      <c r="Q7" s="2">
-        <f>SUM(C7:P7)</f>
-        <v/>
-      </c>
-      <c r="R7" s="2" t="n"/>
-      <c r="S7" s="2">
-        <f>B7+Q7-R7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="B8" s="2">
-        <f>S7</f>
-        <v/>
-      </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
-      <c r="P8" s="2" t="n"/>
-      <c r="Q8" s="2">
-        <f>SUM(C8:P8)</f>
-        <v/>
-      </c>
-      <c r="R8" s="2" t="n"/>
-      <c r="S8" s="2">
-        <f>B8+Q8-R8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>FEB</t>
-        </is>
-      </c>
-      <c r="B9" s="2">
-        <f>S8</f>
-        <v/>
-      </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
-      <c r="P9" s="2" t="n"/>
-      <c r="Q9" s="2">
-        <f>SUM(C9:P9)</f>
-        <v/>
-      </c>
-      <c r="R9" s="2" t="n"/>
-      <c r="S9" s="2">
-        <f>B9+Q9-R9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="B10" s="2">
-        <f>S9</f>
-        <v/>
-      </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2">
-        <f>SUM(C10:P10)</f>
-        <v/>
-      </c>
-      <c r="R10" s="2" t="n"/>
-      <c r="S10" s="2">
-        <f>B10+Q10-R10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>APR</t>
-        </is>
-      </c>
-      <c r="B11" s="2">
-        <f>S10</f>
-        <v/>
-      </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n"/>
-      <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2">
-        <f>SUM(C11:P11)</f>
-        <v/>
-      </c>
-      <c r="R11" s="2" t="n"/>
-      <c r="S11" s="2">
-        <f>B11+Q11-R11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-      <c r="B12" s="2">
-        <f>S11</f>
-        <v/>
-      </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
-      <c r="P12" s="2" t="n"/>
-      <c r="Q12" s="2">
-        <f>SUM(C12:P12)</f>
-        <v/>
-      </c>
-      <c r="R12" s="2" t="n"/>
-      <c r="S12" s="2">
-        <f>B12+Q12-R12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="B13" s="2">
-        <f>S12</f>
-        <v/>
-      </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="n"/>
-      <c r="Q13" s="2">
-        <f>SUM(C13:P13)</f>
-        <v/>
-      </c>
-      <c r="R13" s="2" t="n"/>
-      <c r="S13" s="2">
-        <f>B13+Q13-R13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="B14" s="2">
-        <f>S13</f>
-        <v/>
-      </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2">
-        <f>SUM(C14:P14)</f>
-        <v/>
-      </c>
-      <c r="R14" s="2" t="n"/>
-      <c r="S14" s="2">
-        <f>B14+Q14-R14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2">
-        <f>SUM(C3:C14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="2">
-        <f>SUM(D3:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="2">
-        <f>SUM(E3:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="2">
-        <f>SUM(F3:F14)</f>
-        <v/>
-      </c>
-      <c r="G15" s="2">
-        <f>SUM(G3:G14)</f>
-        <v/>
-      </c>
-      <c r="H15" s="2">
-        <f>SUM(H3:H14)</f>
-        <v/>
-      </c>
-      <c r="I15" s="2">
-        <f>SUM(I3:I14)</f>
-        <v/>
-      </c>
-      <c r="J15" s="2">
-        <f>SUM(J3:J14)</f>
-        <v/>
-      </c>
-      <c r="K15" s="2">
-        <f>SUM(K3:K14)</f>
-        <v/>
-      </c>
-      <c r="L15" s="2">
-        <f>SUM(L3:L14)</f>
-        <v/>
-      </c>
-      <c r="M15" s="2">
-        <f>SUM(M3:M14)</f>
-        <v/>
-      </c>
-      <c r="N15" s="2">
-        <f>SUM(N3:N14)</f>
-        <v/>
-      </c>
-      <c r="O15" s="2">
-        <f>SUM(O3:O14)</f>
-        <v/>
-      </c>
-      <c r="P15" s="2">
-        <f>SUM(P3:P14)</f>
-        <v/>
-      </c>
-      <c r="Q15" s="2">
-        <f>SUM(Q3:Q14)</f>
-        <v/>
-      </c>
-      <c r="R15" s="2">
-        <f>SUM(R3:R14)</f>
-        <v/>
-      </c>
-      <c r="S15" s="2">
-        <f>S14</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="5.140625" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="5" bestFit="1" customWidth="1" min="3" max="4"/>
     <col width="5.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="8.140625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="5" bestFit="1" customWidth="1" min="7" max="8"/>
+    <col width="5" bestFit="1" customWidth="1" min="6" max="8"/>
     <col width="5.5703125" bestFit="1" customWidth="1" min="9" max="9"/>
     <col width="5" bestFit="1" customWidth="1" min="10" max="10"/>
     <col width="5.42578125" bestFit="1" customWidth="1" min="11" max="11"/>
-    <col width="5" bestFit="1" customWidth="1" min="12" max="13"/>
-    <col width="6.28515625" bestFit="1" customWidth="1" min="14" max="14"/>
-    <col width="8.140625" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="5" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="9.28515625" bestFit="1" customWidth="1" min="13" max="15"/>
     <col width="15.5703125" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="9.28515625" bestFit="1" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3131,7 +2493,7 @@
           <t>Category</t>
         </is>
       </c>
-      <c r="Q1" s="6" t="n">
+      <c r="Q1" s="5" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -3181,8 +2543,14 @@
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
+      <c r="M3" s="2">
+        <f>16.25</f>
+        <v/>
+      </c>
+      <c r="N3" s="2">
+        <f>16.25</f>
+        <v/>
+      </c>
       <c r="O3" s="2">
         <f>SUM(B3,C3,D3,E3,F3,G3,H3,I3,J3,K3,L3,M3,N3,Q3)</f>
         <v/>
@@ -3192,11 +2560,15 @@
           <t>GERCORY</t>
         </is>
       </c>
+      <c r="Q3" s="4">
+        <f>16.25</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Amazon.Com*N22Fjseattlewa US</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -3210,8 +2582,14 @@
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
+      <c r="M4" s="2">
+        <f>117.76+26.57+343.93+17.59+152.14+71.79+75.40+18.75+50.03+20.80+40.33</f>
+        <v/>
+      </c>
+      <c r="N4" s="2">
+        <f>117.76+26.57+343.93+17.59+152.14+71.79+75.40+18.75+50.03+20.80+40.33</f>
+        <v/>
+      </c>
       <c r="O4" s="2">
         <f>SUM(B4,C4,D4,E4,F4,G4,H4,I4,J4,K4,L4,M4,N4,Q4)</f>
         <v/>
@@ -3221,11 +2599,15 @@
           <t>GERCORY</t>
         </is>
       </c>
+      <c r="Q4">
+        <f>117.76+26.57+343.93+17.59+152.14+71.79+75.40+18.75+50.03+20.80+40.33</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Amazon.Comseattlewa US</t>
+          <t>Amex Epayment ACH Pmt</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
@@ -3254,7 +2636,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Amex Epayment ACH Pmt</t>
+          <t>Arrow Bank Na Web Pmt</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -3283,7 +2665,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Arrow Bank Na Web Pmt</t>
+          <t>Bill Pay:Associated Mutual 210061 Ubq1P6Kr</t>
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
@@ -3312,7 +2694,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Associated Mutual 210061 Ubq1P6Kr</t>
+          <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
@@ -3334,14 +2716,14 @@
       </c>
       <c r="P8" s="1" t="inlineStr">
         <is>
-          <t>GERCORY</t>
+          <t>OFFICE EXPENSE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
+          <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
@@ -3355,8 +2737,14 @@
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
+      <c r="M9" s="2">
+        <f>350</f>
+        <v/>
+      </c>
+      <c r="N9" s="2">
+        <f>350</f>
+        <v/>
+      </c>
       <c r="O9" s="2">
         <f>SUM(B9,C9,D9,E9,F9,G9,H9,I9,J9,K9,L9,M9,N9,Q9)</f>
         <v/>
@@ -3366,11 +2754,15 @@
           <t>OFFICE EXPENSE</t>
         </is>
       </c>
+      <c r="Q9" s="4">
+        <f>350</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
+          <t>Bill Pay:Orange &amp; Rockland 879293 5Bq1P6Kr</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -3399,7 +2791,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Orange &amp; Rockland 879293 5Bq1P6Kr</t>
+          <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -3413,8 +2805,14 @@
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="n"/>
+      <c r="M11" s="2">
+        <f>300</f>
+        <v/>
+      </c>
+      <c r="N11" s="2">
+        <f>300</f>
+        <v/>
+      </c>
       <c r="O11" s="2">
         <f>SUM(B11,C11,D11,E11,F11,G11,H11,I11,J11,K11,L11,M11,N11,Q11)</f>
         <v/>
@@ -3424,11 +2822,15 @@
           <t>OFFICE EXPENSE</t>
         </is>
       </c>
+      <c r="Q11" s="4">
+        <f>300</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
+          <t>Bill Pay:Veolia Water New Y 200054 Hbu1T6Kr</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -3457,7 +2859,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Veolia Water New Y 200054 Hbu1T6Kr</t>
+          <t>Citi Card Onlinepayment</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -3471,8 +2873,14 @@
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
+      <c r="M13" s="2">
+        <f>975+364.75</f>
+        <v/>
+      </c>
+      <c r="N13" s="2">
+        <f>975+364.75</f>
+        <v/>
+      </c>
       <c r="O13" s="2">
         <f>SUM(B13,C13,D13,E13,F13,G13,H13,I13,J13,K13,L13,M13,N13,Q13)</f>
         <v/>
@@ -3482,11 +2890,15 @@
           <t>OFFICE EXPENSE</t>
         </is>
       </c>
+      <c r="Q13" s="4">
+        <f>975+364.75</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Citi Card Onlinepayment</t>
+          <t>Credit One Bank Payment</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -3500,8 +2912,14 @@
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
+      <c r="M14" s="2">
+        <f>817.29</f>
+        <v/>
+      </c>
+      <c r="N14" s="2">
+        <f>817.29</f>
+        <v/>
+      </c>
       <c r="O14" s="2">
         <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,J14,K14,L14,M14,N14,Q14)</f>
         <v/>
@@ -3511,11 +2929,15 @@
           <t>OFFICE EXPENSE</t>
         </is>
       </c>
+      <c r="Q14" s="4">
+        <f>817.29</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Credit One Bank Payment</t>
+          <t>Discover Bank Net/Mobile</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
@@ -3544,7 +2966,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Discover Bank Net/Mobile</t>
+          <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -3573,7 +2995,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
+          <t>Huntington Banksil Payment</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
@@ -3595,14 +3017,14 @@
       </c>
       <c r="P17" s="1" t="inlineStr">
         <is>
-          <t>OFFICE EXPENSE</t>
+          <t>MEALS</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Huntington Banksil Payment</t>
+          <t>Internet Trf To Client-Added Transfer Account</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -3616,8 +3038,14 @@
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
+      <c r="M18" s="2">
+        <f>385.77+740</f>
+        <v/>
+      </c>
+      <c r="N18" s="2">
+        <f>385.77+740</f>
+        <v/>
+      </c>
       <c r="O18" s="2">
         <f>SUM(B18,C18,D18,E18,F18,G18,H18,I18,J18,K18,L18,M18,N18,Q18)</f>
         <v/>
@@ -3627,11 +3055,15 @@
           <t>MEALS</t>
         </is>
       </c>
+      <c r="Q18" s="4">
+        <f>385.77+740</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Internet Trf To Client-Added Transfer Account</t>
+          <t>Irs Usataxpymt</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
@@ -3645,8 +3077,14 @@
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
+      <c r="M19" s="2">
+        <f>800+800</f>
+        <v/>
+      </c>
+      <c r="N19" s="2">
+        <f>800+800</f>
+        <v/>
+      </c>
       <c r="O19" s="2">
         <f>SUM(B19,C19,D19,E19,F19,G19,H19,I19,J19,K19,L19,M19,N19,Q19)</f>
         <v/>
@@ -3656,11 +3094,15 @@
           <t>MEALS</t>
         </is>
       </c>
+      <c r="Q19" s="4">
+        <f>800+800</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Irs Usataxpymt</t>
+          <t>Kindercare Portland OR</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
@@ -3674,8 +3116,14 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n"/>
+      <c r="M20" s="2">
+        <f>490+120</f>
+        <v/>
+      </c>
+      <c r="N20" s="2">
+        <f>490+120</f>
+        <v/>
+      </c>
       <c r="O20" s="2">
         <f>SUM(B20,C20,D20,E20,F20,G20,H20,I20,J20,K20,L20,M20,N20,Q20)</f>
         <v/>
@@ -3685,11 +3133,15 @@
           <t>MEALS</t>
         </is>
       </c>
+      <c r="Q20" s="4">
+        <f>490+120</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Kindercare Portland OR</t>
+          <t>No1 Sushi 88 Corkbbo ACH</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
@@ -3703,8 +3155,14 @@
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="n"/>
-      <c r="N21" s="2" t="n"/>
+      <c r="M21" s="2">
+        <f>4000</f>
+        <v/>
+      </c>
+      <c r="N21" s="2">
+        <f>4000</f>
+        <v/>
+      </c>
       <c r="O21" s="2">
         <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,J21,K21,L21,M21,N21,Q21)</f>
         <v/>
@@ -3714,11 +3172,15 @@
           <t>MEALS</t>
         </is>
       </c>
+      <c r="Q21" s="4">
+        <f>4000</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>No1 Sushi 88 Corkbbo ACH</t>
+          <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
@@ -3747,7 +3209,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
+          <t>Nys Dtf Pit Tax Paymnt</t>
         </is>
       </c>
       <c r="B23" s="2" t="n"/>
@@ -3761,8 +3223,14 @@
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="n"/>
-      <c r="N23" s="2" t="n"/>
+      <c r="M23" s="2">
+        <f>200+200</f>
+        <v/>
+      </c>
+      <c r="N23" s="2">
+        <f>200+200</f>
+        <v/>
+      </c>
       <c r="O23" s="2">
         <f>SUM(B23,C23,D23,E23,F23,G23,H23,I23,J23,K23,L23,M23,N23,Q23)</f>
         <v/>
@@ -3772,11 +3240,15 @@
           <t>MEALS</t>
         </is>
       </c>
+      <c r="Q23" s="4">
+        <f>200+200</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Nys Dtf Pit Tax Paymnt</t>
+          <t>PANDA EXPRESS TACOMA WA</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
@@ -3805,7 +3277,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>PANDA EXPRESS TACOMA WA</t>
+          <t>Paypal Inst Xfer</t>
         </is>
       </c>
       <c r="B25" s="2" t="n"/>
@@ -3834,7 +3306,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Paypal Inst Xfer</t>
+          <t>Prog Casualty Ins Prem</t>
         </is>
       </c>
       <c r="B26" s="2" t="n"/>
@@ -3848,22 +3320,32 @@
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
-      <c r="M26" s="2" t="n"/>
-      <c r="N26" s="2" t="n"/>
+      <c r="M26" s="2">
+        <f>930.52</f>
+        <v/>
+      </c>
+      <c r="N26" s="2">
+        <f>930.52</f>
+        <v/>
+      </c>
       <c r="O26" s="2">
         <f>SUM(B26,C26,D26,E26,F26,G26,H26,I26,J26,K26,L26,M26,N26,Q26)</f>
         <v/>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
-          <t>MEALS</t>
-        </is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="Q26" s="4">
+        <f>930.52</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*9O5 Seattle WA</t>
+          <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
         </is>
       </c>
       <c r="B27" s="2" t="n"/>
@@ -3885,14 +3367,14 @@
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
-          <t>MEALS</t>
+          <t>SUPPLY</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
+          <t>Withdrawal Branch 0964 New York</t>
         </is>
       </c>
       <c r="B28" s="2" t="n"/>
@@ -3906,431 +3388,278 @@
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="n"/>
-      <c r="N28" s="2" t="n"/>
+      <c r="M28" s="2">
+        <f>1000+3200</f>
+        <v/>
+      </c>
+      <c r="N28" s="2">
+        <f>1000+3200</f>
+        <v/>
+      </c>
       <c r="O28" s="2">
         <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,J28,K28,L28,M28,N28,Q28)</f>
         <v/>
       </c>
       <c r="P28" s="1" t="inlineStr">
         <is>
-          <t>MEALS</t>
-        </is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="Q28" s="4">
+        <f>1000+3200</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="n"/>
-      <c r="N29" s="2" t="n"/>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B29" s="2">
+        <f>SUM(B2:B28)</f>
+        <v/>
+      </c>
+      <c r="C29" s="2">
+        <f>SUM(C2:C28)</f>
+        <v/>
+      </c>
+      <c r="D29" s="2">
+        <f>SUM(D2:D28)</f>
+        <v/>
+      </c>
+      <c r="E29" s="2">
+        <f>SUM(E2:E28)</f>
+        <v/>
+      </c>
+      <c r="F29" s="2">
+        <f>SUM(F2:F28)</f>
+        <v/>
+      </c>
+      <c r="G29" s="2">
+        <f>SUM(G2:G28)</f>
+        <v/>
+      </c>
+      <c r="H29" s="2">
+        <f>SUM(H2:H28)</f>
+        <v/>
+      </c>
+      <c r="I29" s="2">
+        <f>SUM(I2:I28)</f>
+        <v/>
+      </c>
+      <c r="J29" s="2">
+        <f>SUM(J2:J28)</f>
+        <v/>
+      </c>
+      <c r="K29" s="2">
+        <f>SUM(K2:K28)</f>
+        <v/>
+      </c>
+      <c r="L29" s="2">
+        <f>SUM(L2:L28)</f>
+        <v/>
+      </c>
+      <c r="M29" s="2">
+        <f>SUM(M2:M28)</f>
+        <v/>
+      </c>
+      <c r="N29" s="2">
+        <f>SUM(N2:N28)</f>
+        <v/>
+      </c>
       <c r="O29" s="2">
         <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29,N29,Q29)</f>
         <v/>
       </c>
-      <c r="P29" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2">
-        <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30,N30,Q30)</f>
-        <v/>
-      </c>
-      <c r="P30" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
+      <c r="P29" s="1" t="n"/>
+      <c r="Q29" s="4">
+        <f>SUM(Q2:Q28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2">
-        <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31,N31,Q31)</f>
-        <v/>
-      </c>
-      <c r="P31" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BEGIN</t>
+        </is>
+      </c>
+      <c r="B31">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C31">
+        <f>B46</f>
+        <v/>
+      </c>
+      <c r="D31">
+        <f>C46</f>
+        <v/>
+      </c>
+      <c r="E31">
+        <f>D46</f>
+        <v/>
+      </c>
+      <c r="F31">
+        <f>E46</f>
+        <v/>
+      </c>
+      <c r="G31">
+        <f>F46</f>
+        <v/>
+      </c>
+      <c r="H31">
+        <f>G46</f>
+        <v/>
+      </c>
+      <c r="I31">
+        <f>H46</f>
+        <v/>
+      </c>
+      <c r="J31">
+        <f>I46</f>
+        <v/>
+      </c>
+      <c r="K31">
+        <f>J46</f>
+        <v/>
+      </c>
+      <c r="L31">
+        <f>K46</f>
+        <v/>
+      </c>
+      <c r="M31">
+        <f>L46</f>
+        <v/>
+      </c>
+      <c r="N31">
+        <f>M46</f>
+        <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Nx6 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2">
-        <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32,N32,Q32)</f>
-        <v/>
-      </c>
-      <c r="P32" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="B32" s="4">
+        <f>B41</f>
+        <v/>
+      </c>
+      <c r="C32" s="4">
+        <f>C41</f>
+        <v/>
+      </c>
+      <c r="D32" s="4">
+        <f>D41</f>
+        <v/>
+      </c>
+      <c r="E32" s="4">
+        <f>E41</f>
+        <v/>
+      </c>
+      <c r="F32" s="4">
+        <f>F41</f>
+        <v/>
+      </c>
+      <c r="G32" s="4">
+        <f>G41</f>
+        <v/>
+      </c>
+      <c r="H32" s="4">
+        <f>H41</f>
+        <v/>
+      </c>
+      <c r="I32" s="4">
+        <f>I41</f>
+        <v/>
+      </c>
+      <c r="J32" s="4">
+        <f>J41</f>
+        <v/>
+      </c>
+      <c r="K32" s="4">
+        <f>K41</f>
+        <v/>
+      </c>
+      <c r="L32" s="4">
+        <f>L41</f>
+        <v/>
+      </c>
+      <c r="M32" s="4">
+        <f>M41</f>
+        <v/>
+      </c>
+      <c r="N32" s="4">
+        <f>N41</f>
+        <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
-      <c r="N33" s="2" t="n"/>
-      <c r="O33" s="2">
-        <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33,N33,Q33)</f>
-        <v/>
-      </c>
-      <c r="P33" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LESS</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2">
-        <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,J34,K34,L34,M34,N34,Q34)</f>
-        <v/>
-      </c>
-      <c r="P34" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*V25 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
-      <c r="N35" s="2" t="n"/>
-      <c r="O35" s="2">
-        <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,J35,K35,L35,M35,N35,Q35)</f>
-        <v/>
-      </c>
-      <c r="P35" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Yr6 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="n"/>
-      <c r="O36" s="2">
-        <f>SUM(B36,C36,D36,E36,F36,G36,H36,I36,J36,K36,L36,M36,N36,Q36)</f>
-        <v/>
-      </c>
-      <c r="P36" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="n"/>
-      <c r="N37" s="2" t="n"/>
-      <c r="O37" s="2">
-        <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,J37,K37,L37,M37,N37,Q37)</f>
-        <v/>
-      </c>
-      <c r="P37" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Prog Casualty Ins Prem</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n"/>
-      <c r="N38" s="2" t="n"/>
-      <c r="O38" s="2">
-        <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38,N38,Q38)</f>
-        <v/>
-      </c>
-      <c r="P38" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="n"/>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2">
-        <f>SUM(B39,C39,D39,E39,F39,G39,H39,I39,J39,K39,L39,M39,N39,Q39)</f>
-        <v/>
-      </c>
-      <c r="P39" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Withdrawal Branch 0964 New York</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="n"/>
-      <c r="N40" s="2" t="n"/>
-      <c r="O40" s="2">
-        <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,J40,K40,L40,M40,N40,Q40)</f>
-        <v/>
-      </c>
-      <c r="P40" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B41" s="2">
-        <f>SUM(B2:B40)</f>
-        <v/>
-      </c>
-      <c r="C41" s="2">
-        <f>SUM(C2:C40)</f>
-        <v/>
-      </c>
-      <c r="D41" s="2">
-        <f>SUM(D2:D40)</f>
-        <v/>
-      </c>
-      <c r="E41" s="2">
-        <f>SUM(E2:E40)</f>
-        <v/>
-      </c>
-      <c r="F41" s="2">
-        <f>SUM(F2:F40)</f>
-        <v/>
-      </c>
-      <c r="G41" s="2">
-        <f>SUM(G2:G40)</f>
-        <v/>
-      </c>
-      <c r="H41" s="2">
-        <f>SUM(H2:H40)</f>
-        <v/>
-      </c>
-      <c r="I41" s="2">
-        <f>SUM(I2:I40)</f>
-        <v/>
-      </c>
-      <c r="J41" s="2">
-        <f>SUM(J2:J40)</f>
-        <v/>
-      </c>
-      <c r="K41" s="2">
-        <f>SUM(K2:K40)</f>
-        <v/>
-      </c>
-      <c r="L41" s="2">
-        <f>SUM(L2:L40)</f>
-        <v/>
-      </c>
-      <c r="M41" s="2">
-        <f>SUM(M2:M40)</f>
-        <v/>
-      </c>
-      <c r="N41" s="2">
-        <f>SUM(N2:N40)</f>
-        <v/>
-      </c>
-      <c r="O41" s="2">
-        <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41,N41,Q41)</f>
-        <v/>
-      </c>
-      <c r="P41" s="1" t="n"/>
-      <c r="Q41" s="4">
-        <f>SUM(Q2:Q40)</f>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ENDING`</t>
+        </is>
+      </c>
+      <c r="B34" s="4">
+        <f>B43+B44-B45</f>
+        <v/>
+      </c>
+      <c r="C34" s="4">
+        <f>C43+C44-C45</f>
+        <v/>
+      </c>
+      <c r="D34" s="4">
+        <f>D43+D44-D45</f>
+        <v/>
+      </c>
+      <c r="E34" s="4">
+        <f>E43+E44-E45</f>
+        <v/>
+      </c>
+      <c r="F34" s="4">
+        <f>F43+F44-F45</f>
+        <v/>
+      </c>
+      <c r="G34" s="4">
+        <f>G43+G44-G45</f>
+        <v/>
+      </c>
+      <c r="H34" s="4">
+        <f>H43+H44-H45</f>
+        <v/>
+      </c>
+      <c r="I34" s="4">
+        <f>I43+I44-I45</f>
+        <v/>
+      </c>
+      <c r="J34" s="4">
+        <f>J43+J44-J45</f>
+        <v/>
+      </c>
+      <c r="K34" s="4">
+        <f>K43+K44-K45</f>
+        <v/>
+      </c>
+      <c r="L34" s="4">
+        <f>L43+L44-L45</f>
+        <v/>
+      </c>
+      <c r="M34" s="4">
+        <f>M43+M44-M45</f>
+        <v/>
+      </c>
+      <c r="N34" s="4">
+        <f>N43+N44-N45</f>
         <v/>
       </c>
     </row>
@@ -4339,7 +3668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4347,9 +3676,7 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1"/>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/credit_monthly_summary.xlsx
+++ b/credit_monthly_summary.xlsx
@@ -1124,7 +1124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1246,7 +1246,10 @@
       </c>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
+      <c r="D3" s="2">
+        <f>16.25</f>
+        <v/>
+      </c>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
@@ -1269,12 +1272,18 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Amazon.Com*N22Fjseattlewa US</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
+      <c r="C4" s="2">
+        <f>26.57+75.40+18.75</f>
+        <v/>
+      </c>
+      <c r="D4" s="2">
+        <f>117.76+343.93+17.59+152.14+71.79+50.03+20.80+40.33</f>
+        <v/>
+      </c>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
@@ -1297,7 +1306,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Amazon.Comseattlewa US</t>
+          <t>Amex Epayment ACH Pmt</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
@@ -1325,7 +1334,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Amex Epayment ACH Pmt</t>
+          <t>Arrow Bank Na Web Pmt</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -1353,7 +1362,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Arrow Bank Na Web Pmt</t>
+          <t>Bill Pay:Associated Mutual 210061 Ubq1P6Kr</t>
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
@@ -1381,7 +1390,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Associated Mutual 210061 Ubq1P6Kr</t>
+          <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
@@ -1402,18 +1411,21 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>GERCORY</t>
+          <t>OFFICE EXPENSE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
+          <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
+      <c r="C9" s="2">
+        <f>350</f>
+        <v/>
+      </c>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
@@ -1437,7 +1449,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
+          <t>Bill Pay:Orange &amp; Rockland 879293 5Bq1P6Kr</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -1465,11 +1477,14 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Orange &amp; Rockland 879293 5Bq1P6Kr</t>
+          <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
+      <c r="C11" s="2">
+        <f>300</f>
+        <v/>
+      </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n"/>
@@ -1493,7 +1508,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
+          <t>Bill Pay:Veolia Water New Y 200054 Hbu1T6Kr</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -1521,12 +1536,15 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Veolia Water New Y 200054 Hbu1T6Kr</t>
+          <t>Citi Card Onlinepayment</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
+      <c r="D13" s="2">
+        <f>975</f>
+        <v/>
+      </c>
       <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
@@ -1549,12 +1567,15 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Citi Card Onlinepayment</t>
+          <t>Credit One Bank Payment</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
+      <c r="D14" s="2">
+        <f>817.29</f>
+        <v/>
+      </c>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
@@ -1577,7 +1598,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Credit One Bank Payment</t>
+          <t>Discover Bank Net/Mobile</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
@@ -1605,7 +1626,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Discover Bank Net/Mobile</t>
+          <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -1633,7 +1654,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
+          <t>Huntington Banksil Payment</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
@@ -1654,18 +1675,21 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>OFFICE EXPENSE</t>
+          <t>MEALS</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Huntington Banksil Payment</t>
+          <t>Internet Trf To Client-Added Transfer Account</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
+      <c r="C18" s="2">
+        <f>385.77+740</f>
+        <v/>
+      </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
@@ -1689,12 +1713,15 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Internet Trf To Client-Added Transfer Account</t>
+          <t>Irs Usataxpymt</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
+      <c r="D19" s="2">
+        <f>800+800</f>
+        <v/>
+      </c>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
@@ -1717,12 +1744,15 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Irs Usataxpymt</t>
+          <t>Kindercare Portland OR</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
+      <c r="D20" s="2">
+        <f>490+120</f>
+        <v/>
+      </c>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
@@ -1745,11 +1775,14 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Kindercare Portland OR</t>
+          <t>No1 Sushi 88 Corkbbo ACH</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
+      <c r="C21" s="2">
+        <f>4000</f>
+        <v/>
+      </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
@@ -1773,7 +1806,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>No1 Sushi 88 Corkbbo ACH</t>
+          <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
@@ -1801,12 +1834,15 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
+          <t>Nys Dtf Pit Tax Paymnt</t>
         </is>
       </c>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
+      <c r="D23" s="2">
+        <f>200+200</f>
+        <v/>
+      </c>
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
@@ -1829,7 +1865,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Nys Dtf Pit Tax Paymnt</t>
+          <t>PANDA EXPRESS TACOMA WA</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
@@ -1857,7 +1893,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>PANDA EXPRESS TACOMA WA</t>
+          <t>Paypal Inst Xfer</t>
         </is>
       </c>
       <c r="B25" s="2" t="n"/>
@@ -1885,12 +1921,15 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Paypal Inst Xfer</t>
+          <t>Prog Casualty Ins Prem</t>
         </is>
       </c>
       <c r="B26" s="2" t="n"/>
       <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
+      <c r="D26" s="2">
+        <f>930.52</f>
+        <v/>
+      </c>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
@@ -1906,14 +1945,14 @@
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>MEALS</t>
+          <t>SUPPLY</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*9O5 Seattle WA</t>
+          <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
         </is>
       </c>
       <c r="B27" s="2" t="n"/>
@@ -1934,19 +1973,25 @@
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>MEALS</t>
+          <t>SUPPLY</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
+          <t>Withdrawal Branch 0964 New York</t>
         </is>
       </c>
       <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
+      <c r="C28" s="2">
+        <f>1000</f>
+        <v/>
+      </c>
+      <c r="D28" s="2">
+        <f>3200</f>
+        <v/>
+      </c>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
@@ -1962,426 +2007,66 @@
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>MEALS</t>
+          <t>SUPPLY</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="n"/>
-      <c r="N29" s="2">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B29" s="4">
+        <f>SUM(B2:B28)</f>
+        <v/>
+      </c>
+      <c r="C29" s="4">
+        <f>SUM(C2:C28)</f>
+        <v/>
+      </c>
+      <c r="D29" s="4">
+        <f>SUM(D2:D28)</f>
+        <v/>
+      </c>
+      <c r="E29" s="4">
+        <f>SUM(E2:E28)</f>
+        <v/>
+      </c>
+      <c r="F29" s="4">
+        <f>SUM(F2:F28)</f>
+        <v/>
+      </c>
+      <c r="G29" s="4">
+        <f>SUM(G2:G28)</f>
+        <v/>
+      </c>
+      <c r="H29" s="4">
+        <f>SUM(H2:H28)</f>
+        <v/>
+      </c>
+      <c r="I29" s="4">
+        <f>SUM(I2:I28)</f>
+        <v/>
+      </c>
+      <c r="J29" s="4">
+        <f>SUM(J2:J28)</f>
+        <v/>
+      </c>
+      <c r="K29" s="4">
+        <f>SUM(K2:K28)</f>
+        <v/>
+      </c>
+      <c r="L29" s="4">
+        <f>SUM(L2:L28)</f>
+        <v/>
+      </c>
+      <c r="M29" s="4">
+        <f>SUM(M2:M28)</f>
+        <v/>
+      </c>
+      <c r="N29" s="4">
         <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29)</f>
-        <v/>
-      </c>
-      <c r="O29" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2">
-        <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30)</f>
-        <v/>
-      </c>
-      <c r="O30" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2">
-        <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31)</f>
-        <v/>
-      </c>
-      <c r="O31" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Nx6 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2">
-        <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32)</f>
-        <v/>
-      </c>
-      <c r="O32" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
-      <c r="N33" s="2">
-        <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33)</f>
-        <v/>
-      </c>
-      <c r="O33" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2">
-        <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,J34,K34,L34,M34)</f>
-        <v/>
-      </c>
-      <c r="O34" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*V25 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
-      <c r="N35" s="2">
-        <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,J35,K35,L35,M35)</f>
-        <v/>
-      </c>
-      <c r="O35" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Yr6 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2">
-        <f>SUM(B36,C36,D36,E36,F36,G36,H36,I36,J36,K36,L36,M36)</f>
-        <v/>
-      </c>
-      <c r="O36" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="n"/>
-      <c r="N37" s="2">
-        <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,J37,K37,L37,M37)</f>
-        <v/>
-      </c>
-      <c r="O37" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Prog Casualty Ins Prem</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n"/>
-      <c r="N38" s="2">
-        <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38)</f>
-        <v/>
-      </c>
-      <c r="O38" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="n"/>
-      <c r="N39" s="2">
-        <f>SUM(B39,C39,D39,E39,F39,G39,H39,I39,J39,K39,L39,M39)</f>
-        <v/>
-      </c>
-      <c r="O39" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Withdrawal Branch 0964 New York</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="n"/>
-      <c r="N40" s="2">
-        <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,J40,K40,L40,M40)</f>
-        <v/>
-      </c>
-      <c r="O40" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>discover Bank Net/Mobile</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
-      <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2">
-        <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41)</f>
-        <v/>
-      </c>
-      <c r="O41" s="1" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B42" s="4">
-        <f>SUM(B2:B41)</f>
-        <v/>
-      </c>
-      <c r="C42" s="4">
-        <f>SUM(C2:C41)</f>
-        <v/>
-      </c>
-      <c r="D42" s="4">
-        <f>SUM(D2:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="4">
-        <f>SUM(E2:E41)</f>
-        <v/>
-      </c>
-      <c r="F42" s="4">
-        <f>SUM(F2:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="4">
-        <f>SUM(G2:G41)</f>
-        <v/>
-      </c>
-      <c r="H42" s="4">
-        <f>SUM(H2:H41)</f>
-        <v/>
-      </c>
-      <c r="I42" s="4">
-        <f>SUM(I2:I41)</f>
-        <v/>
-      </c>
-      <c r="J42" s="4">
-        <f>SUM(J2:J41)</f>
-        <v/>
-      </c>
-      <c r="K42" s="4">
-        <f>SUM(K2:K41)</f>
-        <v/>
-      </c>
-      <c r="L42" s="4">
-        <f>SUM(L2:L41)</f>
-        <v/>
-      </c>
-      <c r="M42" s="4">
-        <f>SUM(M2:M41)</f>
-        <v/>
-      </c>
-      <c r="N42" s="4">
-        <f>SUM(B42,C42,D42,E42,F42,G42,H42,I42,J42,K42,L42,M42)</f>
         <v/>
       </c>
     </row>
@@ -2543,14 +2228,8 @@
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2">
-        <f>16.25</f>
-        <v/>
-      </c>
-      <c r="N3" s="2">
-        <f>16.25</f>
-        <v/>
-      </c>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
       <c r="O3" s="2">
         <f>SUM(B3,C3,D3,E3,F3,G3,H3,I3,J3,K3,L3,M3,N3,Q3)</f>
         <v/>
@@ -2583,13 +2262,10 @@
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2">
-        <f>117.76+26.57+343.93+17.59+152.14+71.79+75.40+18.75+50.03+20.80+40.33</f>
-        <v/>
-      </c>
-      <c r="N4" s="2">
-        <f>117.76+26.57+343.93+17.59+152.14+71.79+75.40+18.75+50.03+20.80+40.33</f>
-        <v/>
-      </c>
+        <f>109.43+343.93+17.59+152.14+71.79+50.03+20.80+13.79+40.33</f>
+        <v/>
+      </c>
+      <c r="N4" s="2" t="n"/>
       <c r="O4" s="2">
         <f>SUM(B4,C4,D4,E4,F4,G4,H4,I4,J4,K4,L4,M4,N4,Q4)</f>
         <v/>
@@ -2599,8 +2275,8 @@
           <t>GERCORY</t>
         </is>
       </c>
-      <c r="Q4">
-        <f>117.76+26.57+343.93+17.59+152.14+71.79+75.40+18.75+50.03+20.80+40.33</f>
+      <c r="Q4" s="4">
+        <f>109.43+117.76+26.57+343.93+17.59+152.14+71.79+18.75+50.03+20.80+13.79+40.33</f>
         <v/>
       </c>
     </row>
@@ -2621,7 +2297,10 @@
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
+      <c r="M5" s="2">
+        <f>1000</f>
+        <v/>
+      </c>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="2">
         <f>SUM(B5,C5,D5,E5,F5,G5,H5,I5,J5,K5,L5,M5,N5,Q5)</f>
@@ -2631,6 +2310,10 @@
         <is>
           <t>GERCORY</t>
         </is>
+      </c>
+      <c r="Q5" s="4">
+        <f>1000</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -2650,7 +2333,10 @@
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n"/>
+      <c r="M6" s="2">
+        <f>703</f>
+        <v/>
+      </c>
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2">
         <f>SUM(B6,C6,D6,E6,F6,G6,H6,I6,J6,K6,L6,M6,N6,Q6)</f>
@@ -2660,6 +2346,10 @@
         <is>
           <t>GERCORY</t>
         </is>
+      </c>
+      <c r="Q6" s="4">
+        <f>703</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -2708,7 +2398,10 @@
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n"/>
+      <c r="M8" s="2">
+        <f>578</f>
+        <v/>
+      </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2">
         <f>SUM(B8,C8,D8,E8,F8,G8,H8,I8,J8,K8,L8,M8,N8,Q8)</f>
@@ -2718,6 +2411,10 @@
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
+      </c>
+      <c r="Q8" s="4">
+        <f>578</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -2737,14 +2434,8 @@
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2">
-        <f>350</f>
-        <v/>
-      </c>
-      <c r="N9" s="2">
-        <f>350</f>
-        <v/>
-      </c>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
       <c r="O9" s="2">
         <f>SUM(B9,C9,D9,E9,F9,G9,H9,I9,J9,K9,L9,M9,N9,Q9)</f>
         <v/>
@@ -2753,10 +2444,6 @@
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
-      </c>
-      <c r="Q9" s="4">
-        <f>350</f>
-        <v/>
       </c>
     </row>
     <row r="10">
@@ -2805,14 +2492,8 @@
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2">
-        <f>300</f>
-        <v/>
-      </c>
-      <c r="N11" s="2">
-        <f>300</f>
-        <v/>
-      </c>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
       <c r="O11" s="2">
         <f>SUM(B11,C11,D11,E11,F11,G11,H11,I11,J11,K11,L11,M11,N11,Q11)</f>
         <v/>
@@ -2821,10 +2502,6 @@
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
-      </c>
-      <c r="Q11" s="4">
-        <f>300</f>
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -2874,13 +2551,10 @@
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2">
-        <f>975+364.75</f>
-        <v/>
-      </c>
-      <c r="N13" s="2">
-        <f>975+364.75</f>
-        <v/>
-      </c>
+        <f>364.75+1400</f>
+        <v/>
+      </c>
+      <c r="N13" s="2" t="n"/>
       <c r="O13" s="2">
         <f>SUM(B13,C13,D13,E13,F13,G13,H13,I13,J13,K13,L13,M13,N13,Q13)</f>
         <v/>
@@ -2891,7 +2565,7 @@
         </is>
       </c>
       <c r="Q13" s="4">
-        <f>975+364.75</f>
+        <f>975+364.75+1400</f>
         <v/>
       </c>
     </row>
@@ -2912,14 +2586,8 @@
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2">
-        <f>817.29</f>
-        <v/>
-      </c>
-      <c r="N14" s="2">
-        <f>817.29</f>
-        <v/>
-      </c>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
       <c r="O14" s="2">
         <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,J14,K14,L14,M14,N14,Q14)</f>
         <v/>
@@ -3009,7 +2677,10 @@
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
+      <c r="M17" s="2">
+        <f>900</f>
+        <v/>
+      </c>
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="2">
         <f>SUM(B17,C17,D17,E17,F17,G17,H17,I17,J17,K17,L17,M17,N17,Q17)</f>
@@ -3019,6 +2690,10 @@
         <is>
           <t>MEALS</t>
         </is>
+      </c>
+      <c r="Q17" s="4">
+        <f>900</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -3039,13 +2714,10 @@
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2">
-        <f>385.77+740</f>
-        <v/>
-      </c>
-      <c r="N18" s="2">
-        <f>385.77+740</f>
-        <v/>
-      </c>
+        <f>453</f>
+        <v/>
+      </c>
+      <c r="N18" s="2" t="n"/>
       <c r="O18" s="2">
         <f>SUM(B18,C18,D18,E18,F18,G18,H18,I18,J18,K18,L18,M18,N18,Q18)</f>
         <v/>
@@ -3056,7 +2728,7 @@
         </is>
       </c>
       <c r="Q18" s="4">
-        <f>385.77+740</f>
+        <f>453</f>
         <v/>
       </c>
     </row>
@@ -3077,14 +2749,8 @@
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2">
-        <f>800+800</f>
-        <v/>
-      </c>
-      <c r="N19" s="2">
-        <f>800+800</f>
-        <v/>
-      </c>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
       <c r="O19" s="2">
         <f>SUM(B19,C19,D19,E19,F19,G19,H19,I19,J19,K19,L19,M19,N19,Q19)</f>
         <v/>
@@ -3116,14 +2782,8 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2">
-        <f>490+120</f>
-        <v/>
-      </c>
-      <c r="N20" s="2">
-        <f>490+120</f>
-        <v/>
-      </c>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
       <c r="O20" s="2">
         <f>SUM(B20,C20,D20,E20,F20,G20,H20,I20,J20,K20,L20,M20,N20,Q20)</f>
         <v/>
@@ -3159,10 +2819,7 @@
         <f>4000</f>
         <v/>
       </c>
-      <c r="N21" s="2">
-        <f>4000</f>
-        <v/>
-      </c>
+      <c r="N21" s="2" t="n"/>
       <c r="O21" s="2">
         <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,J21,K21,L21,M21,N21,Q21)</f>
         <v/>
@@ -3171,10 +2828,6 @@
         <is>
           <t>MEALS</t>
         </is>
-      </c>
-      <c r="Q21" s="4">
-        <f>4000</f>
-        <v/>
       </c>
     </row>
     <row r="22">
@@ -3223,14 +2876,8 @@
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2">
-        <f>200+200</f>
-        <v/>
-      </c>
-      <c r="N23" s="2">
-        <f>200+200</f>
-        <v/>
-      </c>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
       <c r="O23" s="2">
         <f>SUM(B23,C23,D23,E23,F23,G23,H23,I23,J23,K23,L23,M23,N23,Q23)</f>
         <v/>
@@ -3320,14 +2967,8 @@
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
-      <c r="M26" s="2">
-        <f>930.52</f>
-        <v/>
-      </c>
-      <c r="N26" s="2">
-        <f>930.52</f>
-        <v/>
-      </c>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
       <c r="O26" s="2">
         <f>SUM(B26,C26,D26,E26,F26,G26,H26,I26,J26,K26,L26,M26,N26,Q26)</f>
         <v/>
@@ -3389,13 +3030,10 @@
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2">
-        <f>1000+3200</f>
-        <v/>
-      </c>
-      <c r="N28" s="2">
-        <f>1000+3200</f>
-        <v/>
-      </c>
+        <f>3800</f>
+        <v/>
+      </c>
+      <c r="N28" s="2" t="n"/>
       <c r="O28" s="2">
         <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,J28,K28,L28,M28,N28,Q28)</f>
         <v/>
@@ -3406,7 +3044,7 @@
         </is>
       </c>
       <c r="Q28" s="4">
-        <f>1000+3200</f>
+        <f>3200+3800</f>
         <v/>
       </c>
     </row>
@@ -3478,7 +3116,6 @@
         <v/>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>

--- a/credit_monthly_summary.xlsx
+++ b/credit_monthly_summary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="2" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="2" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="CHASE #3444" sheetId="1" state="visible" r:id="rId1"/>
@@ -115,15 +115,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -136,6 +133,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,128 +512,130 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>CHASE #3444</t>
         </is>
       </c>
-      <c r="B1" s="8" t="n"/>
-      <c r="C1" s="8" t="n"/>
-      <c r="D1" s="8" t="n"/>
-      <c r="E1" s="8" t="n"/>
-      <c r="F1" s="8" t="n"/>
-      <c r="G1" s="8" t="n"/>
-      <c r="H1" s="8" t="n"/>
-      <c r="I1" s="8" t="n"/>
-      <c r="J1" s="8" t="n"/>
-      <c r="K1" s="8" t="n"/>
-      <c r="L1" s="8" t="n"/>
-      <c r="M1" s="8" t="n"/>
-      <c r="N1" s="8" t="n"/>
-      <c r="O1" s="8" t="n"/>
-      <c r="P1" s="8" t="n"/>
-      <c r="Q1" s="8" t="n"/>
-      <c r="R1" s="8" t="n"/>
-      <c r="S1" s="9" t="n"/>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="7" t="n"/>
+      <c r="G1" s="7" t="n"/>
+      <c r="H1" s="7" t="n"/>
+      <c r="I1" s="7" t="n"/>
+      <c r="J1" s="7" t="n"/>
+      <c r="K1" s="7" t="n"/>
+      <c r="L1" s="7" t="n"/>
+      <c r="M1" s="7" t="n"/>
+      <c r="N1" s="7" t="n"/>
+      <c r="O1" s="7" t="n"/>
+      <c r="P1" s="7" t="n"/>
+      <c r="Q1" s="7" t="n"/>
+      <c r="R1" s="7" t="n"/>
+      <c r="S1" s="8" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="7" t="n"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>MONTH</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>BEGIN BALANCE</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>CASH / CHECK DEPOSIT</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>NO1 SUSHI 88 CORKBBO ACH</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>VEOLIA WATER</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>ORANGE &amp; ROCKLAND</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>WITHDRAWAL BRANCH 0964</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>AMAZON</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>BILL PAY:VEOLIA WATER NEW Y 200045 6BU1T6KR</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>BILL PAY:ORANGE &amp; ROCKLAND 136130 6BQ1P6KR</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>INTERNET TRF TO CLIENT-ADDED TRANSFER ACCOUNT</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>WITHDRAWAL BRANCH 0964 NEW YORK</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>POS MAC AMAZON.COM*NX6 SEATTLE WA</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>POS MAC AMAZON.COM*9O5 SEATTLE WA</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="O2" s="6" t="inlineStr">
         <is>
           <t>POS MAC AMAZON.COM*SB8 SEATTLE WA</t>
         </is>
       </c>
-      <c r="P2" s="7" t="inlineStr">
+      <c r="P2" s="6" t="inlineStr">
         <is>
           <t>NYS DTF PIT TAX PAYMNT</t>
         </is>
       </c>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="Q2" s="6" t="inlineStr">
         <is>
           <t>TOTAL CREDIT</t>
         </is>
       </c>
-      <c r="R2" s="7" t="inlineStr">
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
+      <c r="S2" s="6" t="inlineStr">
         <is>
           <t>ENDING BALANCE</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>AUG</t>
-        </is>
+      <c r="A3" s="9" t="n">
+        <v>45383</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>0</v>
@@ -660,10 +665,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
+      <c r="A4" s="9" t="n">
+        <v>45413</v>
       </c>
       <c r="B4" s="2">
         <f>S3</f>
@@ -694,10 +697,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
+      <c r="A5" s="9" t="n">
+        <v>45444</v>
       </c>
       <c r="B5" s="2">
         <f>S4</f>
@@ -728,10 +729,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>NOV</t>
-        </is>
+      <c r="A6" s="9" t="n">
+        <v>45474</v>
       </c>
       <c r="B6" s="2">
         <f>S5</f>
@@ -762,10 +761,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>DEC</t>
-        </is>
+      <c r="A7" s="9" t="n">
+        <v>45505</v>
       </c>
       <c r="B7" s="2">
         <f>S6</f>
@@ -796,10 +793,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
+      <c r="A8" s="9" t="n">
+        <v>45536</v>
       </c>
       <c r="B8" s="2">
         <f>S7</f>
@@ -830,10 +825,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>FEB</t>
-        </is>
+      <c r="A9" s="9" t="n">
+        <v>45566</v>
       </c>
       <c r="B9" s="2">
         <f>S8</f>
@@ -864,10 +857,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
+      <c r="A10" s="9" t="n">
+        <v>45597</v>
       </c>
       <c r="B10" s="2">
         <f>S9</f>
@@ -898,10 +889,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>APR</t>
-        </is>
+      <c r="A11" s="9" t="n">
+        <v>45627</v>
       </c>
       <c r="B11" s="2">
         <f>S10</f>
@@ -932,10 +921,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
+      <c r="A12" s="9" t="n">
+        <v>45658</v>
       </c>
       <c r="B12" s="2">
         <f>S11</f>
@@ -966,10 +953,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>JUN</t>
-        </is>
+      <c r="A13" s="9" t="n">
+        <v>45689</v>
       </c>
       <c r="B13" s="2">
         <f>S12</f>
@@ -1000,10 +985,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
+      <c r="A14" s="9" t="n">
+        <v>45717</v>
       </c>
       <c r="B14" s="2">
         <f>S13</f>
@@ -1124,7 +1107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1134,77 +1117,65 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Merchant</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>NOV</t>
-        </is>
-      </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>DEC</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>FEB</t>
-        </is>
-      </c>
-      <c r="I1" s="7" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="J1" s="7" t="inlineStr">
-        <is>
-          <t>APR</t>
-        </is>
-      </c>
-      <c r="K1" s="7" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-      <c r="L1" s="7" t="inlineStr">
-        <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="M1" s="7" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="B1" s="10">
+        <f>'CHASE #3444'!A3</f>
+        <v/>
+      </c>
+      <c r="C1" s="10">
+        <f>'CHASE #3444'!A4</f>
+        <v/>
+      </c>
+      <c r="D1" s="10">
+        <f>'CHASE #3444'!A5</f>
+        <v/>
+      </c>
+      <c r="E1" s="10">
+        <f>'CHASE #3444'!A6</f>
+        <v/>
+      </c>
+      <c r="F1" s="10">
+        <f>'CHASE #3444'!A7</f>
+        <v/>
+      </c>
+      <c r="G1" s="10">
+        <f>'CHASE #3444'!A8</f>
+        <v/>
+      </c>
+      <c r="H1" s="10">
+        <f>'CHASE #3444'!A9</f>
+        <v/>
+      </c>
+      <c r="I1" s="10">
+        <f>'CHASE #3444'!A10</f>
+        <v/>
+      </c>
+      <c r="J1" s="10">
+        <f>'CHASE #3444'!A11</f>
+        <v/>
+      </c>
+      <c r="K1" s="10">
+        <f>'CHASE #3444'!A12</f>
+        <v/>
+      </c>
+      <c r="L1" s="10">
+        <f>'CHASE #3444'!A13</f>
+        <v/>
+      </c>
+      <c r="M1" s="10">
+        <f>'CHASE #3444'!A14</f>
+        <v/>
+      </c>
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
@@ -1246,10 +1217,7 @@
       </c>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2">
-        <f>16.25</f>
-        <v/>
-      </c>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
@@ -1272,18 +1240,12 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Amazon.Com*N22Fjseattlewa US</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2">
-        <f>26.57+75.40+18.75</f>
-        <v/>
-      </c>
-      <c r="D4" s="2">
-        <f>117.76+343.93+17.59+152.14+71.79+50.03+20.80+40.33</f>
-        <v/>
-      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
@@ -1306,7 +1268,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Amex Epayment ACH Pmt</t>
+          <t>Amazon.Comseattlewa US</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
@@ -1334,7 +1296,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Arrow Bank Na Web Pmt</t>
+          <t>Amex Epayment ACH Pmt</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -1362,7 +1324,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Associated Mutual 210061 Ubq1P6Kr</t>
+          <t>Arrow Bank Na Web Pmt</t>
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
@@ -1390,7 +1352,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
+          <t>Bill Pay:Associated Mutual 210061 Ubq1P6Kr</t>
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
@@ -1411,21 +1373,18 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>OFFICE EXPENSE</t>
+          <t>GERCORY</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
+          <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2">
-        <f>350</f>
-        <v/>
-      </c>
+      <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
@@ -1449,7 +1408,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Orange &amp; Rockland 879293 5Bq1P6Kr</t>
+          <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -1477,14 +1436,11 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
+          <t>Bill Pay:Orange &amp; Rockland 879293 5Bq1P6Kr</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2">
-        <f>300</f>
-        <v/>
-      </c>
+      <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n"/>
@@ -1508,7 +1464,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Veolia Water New Y 200054 Hbu1T6Kr</t>
+          <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -1536,15 +1492,12 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Citi Card Onlinepayment</t>
+          <t>Bill Pay:Veolia Water New Y 200054 Hbu1T6Kr</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2">
-        <f>975</f>
-        <v/>
-      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
@@ -1567,15 +1520,12 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Credit One Bank Payment</t>
+          <t>Citi Card Onlinepayment</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2">
-        <f>817.29</f>
-        <v/>
-      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
@@ -1598,7 +1548,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Discover Bank Net/Mobile</t>
+          <t>Credit One Bank Payment</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
@@ -1626,7 +1576,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
+          <t>Discover Bank Net/Mobile</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -1654,7 +1604,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Huntington Banksil Payment</t>
+          <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
@@ -1675,21 +1625,18 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>MEALS</t>
+          <t>OFFICE EXPENSE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Internet Trf To Client-Added Transfer Account</t>
+          <t>Huntington Banksil Payment</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2">
-        <f>385.77+740</f>
-        <v/>
-      </c>
+      <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
@@ -1713,15 +1660,12 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Irs Usataxpymt</t>
+          <t>Internet Trf To Client-Added Transfer Account</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2">
-        <f>800+800</f>
-        <v/>
-      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
@@ -1744,15 +1688,12 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Kindercare Portland OR</t>
+          <t>Irs Usataxpymt</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2">
-        <f>490+120</f>
-        <v/>
-      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
@@ -1775,14 +1716,11 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>No1 Sushi 88 Corkbbo ACH</t>
+          <t>Kindercare Portland OR</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2">
-        <f>4000</f>
-        <v/>
-      </c>
+      <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
@@ -1806,7 +1744,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
+          <t>No1 Sushi 88 Corkbbo ACH</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
@@ -1834,15 +1772,12 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Nys Dtf Pit Tax Paymnt</t>
+          <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
         </is>
       </c>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2">
-        <f>200+200</f>
-        <v/>
-      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
@@ -1865,7 +1800,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>PANDA EXPRESS TACOMA WA</t>
+          <t>Nys Dtf Pit Tax Paymnt</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
@@ -1893,7 +1828,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Paypal Inst Xfer</t>
+          <t>PANDA EXPRESS TACOMA WA</t>
         </is>
       </c>
       <c r="B25" s="2" t="n"/>
@@ -1921,15 +1856,12 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Prog Casualty Ins Prem</t>
+          <t>Paypal Inst Xfer</t>
         </is>
       </c>
       <c r="B26" s="2" t="n"/>
       <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2">
-        <f>930.52</f>
-        <v/>
-      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
@@ -1945,14 +1877,14 @@
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>MEALS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
+          <t>POS Mac Amazon.Com*9O5 Seattle WA</t>
         </is>
       </c>
       <c r="B27" s="2" t="n"/>
@@ -1973,25 +1905,19 @@
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>MEALS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Withdrawal Branch 0964 New York</t>
+          <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
         </is>
       </c>
       <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2">
-        <f>1000</f>
-        <v/>
-      </c>
-      <c r="D28" s="2">
-        <f>3200</f>
-        <v/>
-      </c>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
@@ -2007,66 +1933,426 @@
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
+          <t>MEALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2">
+        <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29)</f>
+        <v/>
+      </c>
+      <c r="O29" s="1" t="inlineStr">
+        <is>
           <t>SUPPLY</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2">
+        <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30)</f>
+        <v/>
+      </c>
+      <c r="O30" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2">
+        <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31)</f>
+        <v/>
+      </c>
+      <c r="O31" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Nx6 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2">
+        <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32)</f>
+        <v/>
+      </c>
+      <c r="O32" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2">
+        <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33)</f>
+        <v/>
+      </c>
+      <c r="O33" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2">
+        <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,J34,K34,L34,M34)</f>
+        <v/>
+      </c>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*V25 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2">
+        <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,J35,K35,L35,M35)</f>
+        <v/>
+      </c>
+      <c r="O35" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Yr6 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2">
+        <f>SUM(B36,C36,D36,E36,F36,G36,H36,I36,J36,K36,L36,M36)</f>
+        <v/>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2">
+        <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,J37,K37,L37,M37)</f>
+        <v/>
+      </c>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Prog Casualty Ins Prem</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2">
+        <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38)</f>
+        <v/>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2">
+        <f>SUM(B39,C39,D39,E39,F39,G39,H39,I39,J39,K39,L39,M39)</f>
+        <v/>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Withdrawal Branch 0964 New York</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2">
+        <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,J40,K40,L40,M40)</f>
+        <v/>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>discover Bank Net/Mobile</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2">
+        <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41)</f>
+        <v/>
+      </c>
+      <c r="O41" s="1" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B29" s="4">
-        <f>SUM(B2:B28)</f>
-        <v/>
-      </c>
-      <c r="C29" s="4">
-        <f>SUM(C2:C28)</f>
-        <v/>
-      </c>
-      <c r="D29" s="4">
-        <f>SUM(D2:D28)</f>
-        <v/>
-      </c>
-      <c r="E29" s="4">
-        <f>SUM(E2:E28)</f>
-        <v/>
-      </c>
-      <c r="F29" s="4">
-        <f>SUM(F2:F28)</f>
-        <v/>
-      </c>
-      <c r="G29" s="4">
-        <f>SUM(G2:G28)</f>
-        <v/>
-      </c>
-      <c r="H29" s="4">
-        <f>SUM(H2:H28)</f>
-        <v/>
-      </c>
-      <c r="I29" s="4">
-        <f>SUM(I2:I28)</f>
-        <v/>
-      </c>
-      <c r="J29" s="4">
-        <f>SUM(J2:J28)</f>
-        <v/>
-      </c>
-      <c r="K29" s="4">
-        <f>SUM(K2:K28)</f>
-        <v/>
-      </c>
-      <c r="L29" s="4">
-        <f>SUM(L2:L28)</f>
-        <v/>
-      </c>
-      <c r="M29" s="4">
-        <f>SUM(M2:M28)</f>
-        <v/>
-      </c>
-      <c r="N29" s="4">
-        <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29)</f>
+      <c r="B42" s="3">
+        <f>SUM(B2:B41)</f>
+        <v/>
+      </c>
+      <c r="C42" s="3">
+        <f>SUM(C2:C41)</f>
+        <v/>
+      </c>
+      <c r="D42" s="3">
+        <f>SUM(D2:D41)</f>
+        <v/>
+      </c>
+      <c r="E42" s="3">
+        <f>SUM(E2:E41)</f>
+        <v/>
+      </c>
+      <c r="F42" s="3">
+        <f>SUM(F2:F41)</f>
+        <v/>
+      </c>
+      <c r="G42" s="3">
+        <f>SUM(G2:G41)</f>
+        <v/>
+      </c>
+      <c r="H42" s="3">
+        <f>SUM(H2:H41)</f>
+        <v/>
+      </c>
+      <c r="I42" s="3">
+        <f>SUM(I2:I41)</f>
+        <v/>
+      </c>
+      <c r="J42" s="3">
+        <f>SUM(J2:J41)</f>
+        <v/>
+      </c>
+      <c r="K42" s="3">
+        <f>SUM(K2:K41)</f>
+        <v/>
+      </c>
+      <c r="L42" s="3">
+        <f>SUM(L2:L41)</f>
+        <v/>
+      </c>
+      <c r="M42" s="3">
+        <f>SUM(M2:M41)</f>
+        <v/>
+      </c>
+      <c r="N42" s="3">
+        <f>SUM(B42,C42,D42,E42,F42,G42,H42,I42,J42,K42,L42,M42)</f>
         <v/>
       </c>
     </row>
@@ -2082,103 +2368,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="5.140625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="5" bestFit="1" customWidth="1" min="3" max="4"/>
-    <col width="5.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="5" bestFit="1" customWidth="1" min="6" max="8"/>
-    <col width="5.5703125" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="5" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="5.42578125" bestFit="1" customWidth="1" min="11" max="11"/>
-    <col width="5" bestFit="1" customWidth="1" min="12" max="12"/>
-    <col width="9.28515625" bestFit="1" customWidth="1" min="13" max="15"/>
+    <col width="7.140625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="7.85546875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="7" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="6.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="7.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="7.140625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="7" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="7.5703125" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="7.28515625" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="6.85546875" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="7.140625" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="7.7109375" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="7.140625" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="5.7109375" bestFit="1" customWidth="1" min="15" max="15"/>
     <col width="15.5703125" bestFit="1" customWidth="1" min="16" max="16"/>
-    <col width="9.28515625" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="6.28515625" bestFit="1" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Merchant</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>AUG</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>NOV</t>
-        </is>
-      </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>DEC</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>FEB</t>
-        </is>
-      </c>
-      <c r="I1" s="7" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="J1" s="7" t="inlineStr">
-        <is>
-          <t>APR</t>
-        </is>
-      </c>
-      <c r="K1" s="7" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-      <c r="L1" s="7" t="inlineStr">
-        <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="M1" s="7" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="n">
-        <v>46234</v>
-      </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="B1" s="10" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C1" s="10" t="n">
+        <v>45778</v>
+      </c>
+      <c r="D1" s="10" t="n">
+        <v>45809</v>
+      </c>
+      <c r="E1" s="10" t="n">
+        <v>45839</v>
+      </c>
+      <c r="F1" s="10" t="n">
+        <v>45870</v>
+      </c>
+      <c r="G1" s="10" t="n">
+        <v>45901</v>
+      </c>
+      <c r="H1" s="10" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I1" s="10" t="n">
+        <v>45962</v>
+      </c>
+      <c r="J1" s="10" t="n">
+        <v>45992</v>
+      </c>
+      <c r="K1" s="10" t="n">
+        <v>46023</v>
+      </c>
+      <c r="L1" s="10" t="n">
+        <v>46054</v>
+      </c>
+      <c r="M1" s="10" t="n">
+        <v>46082</v>
+      </c>
+      <c r="N1" s="10" t="n">
+        <v>46113</v>
+      </c>
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="P1" s="7" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="n">
+      <c r="Q1" s="4" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -2239,15 +2506,11 @@
           <t>GERCORY</t>
         </is>
       </c>
-      <c r="Q3" s="4">
-        <f>16.25</f>
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Amazon.Com*N22Fjseattlewa US</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -2261,10 +2524,7 @@
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2">
-        <f>109.43+343.93+17.59+152.14+71.79+50.03+20.80+13.79+40.33</f>
-        <v/>
-      </c>
+      <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
       <c r="O4" s="2">
         <f>SUM(B4,C4,D4,E4,F4,G4,H4,I4,J4,K4,L4,M4,N4,Q4)</f>
@@ -2275,15 +2535,11 @@
           <t>GERCORY</t>
         </is>
       </c>
-      <c r="Q4" s="4">
-        <f>109.43+117.76+26.57+343.93+17.59+152.14+71.79+18.75+50.03+20.80+13.79+40.33</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Amex Epayment ACH Pmt</t>
+          <t>Amazon.Comseattlewa US</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
@@ -2297,10 +2553,7 @@
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2">
-        <f>1000</f>
-        <v/>
-      </c>
+      <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="2">
         <f>SUM(B5,C5,D5,E5,F5,G5,H5,I5,J5,K5,L5,M5,N5,Q5)</f>
@@ -2311,15 +2564,11 @@
           <t>GERCORY</t>
         </is>
       </c>
-      <c r="Q5" s="4">
-        <f>1000</f>
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Arrow Bank Na Web Pmt</t>
+          <t>Amex Epayment ACH Pmt</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -2333,10 +2582,7 @@
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2">
-        <f>703</f>
-        <v/>
-      </c>
+      <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2">
         <f>SUM(B6,C6,D6,E6,F6,G6,H6,I6,J6,K6,L6,M6,N6,Q6)</f>
@@ -2347,15 +2593,11 @@
           <t>GERCORY</t>
         </is>
       </c>
-      <c r="Q6" s="4">
-        <f>703</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Associated Mutual 210061 Ubq1P6Kr</t>
+          <t>Arrow Bank Na Web Pmt</t>
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
@@ -2384,7 +2626,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
+          <t>Bill Pay:Associated Mutual 210061 Ubq1P6Kr</t>
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
@@ -2398,10 +2640,7 @@
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2">
-        <f>578</f>
-        <v/>
-      </c>
+      <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2">
         <f>SUM(B8,C8,D8,E8,F8,G8,H8,I8,J8,K8,L8,M8,N8,Q8)</f>
@@ -2409,18 +2648,14 @@
       </c>
       <c r="P8" s="1" t="inlineStr">
         <is>
-          <t>OFFICE EXPENSE</t>
-        </is>
-      </c>
-      <c r="Q8" s="4">
-        <f>578</f>
-        <v/>
+          <t>GERCORY</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
+          <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
@@ -2449,7 +2684,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Orange &amp; Rockland 879293 5Bq1P6Kr</t>
+          <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -2478,7 +2713,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
+          <t>Bill Pay:Orange &amp; Rockland 879293 5Bq1P6Kr</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -2507,7 +2742,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Veolia Water New Y 200054 Hbu1T6Kr</t>
+          <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -2536,7 +2771,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Citi Card Onlinepayment</t>
+          <t>Bill Pay:Veolia Water New Y 200054 Hbu1T6Kr</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -2550,10 +2785,7 @@
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2">
-        <f>364.75+1400</f>
-        <v/>
-      </c>
+      <c r="M13" s="2" t="n"/>
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2">
         <f>SUM(B13,C13,D13,E13,F13,G13,H13,I13,J13,K13,L13,M13,N13,Q13)</f>
@@ -2564,15 +2796,11 @@
           <t>OFFICE EXPENSE</t>
         </is>
       </c>
-      <c r="Q13" s="4">
-        <f>975+364.75+1400</f>
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Credit One Bank Payment</t>
+          <t>Citi Card Onlinepayment</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -2597,15 +2825,11 @@
           <t>OFFICE EXPENSE</t>
         </is>
       </c>
-      <c r="Q14" s="4">
-        <f>817.29</f>
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Discover Bank Net/Mobile</t>
+          <t>Credit One Bank Payment</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
@@ -2634,7 +2858,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
+          <t>Discover Bank Net/Mobile</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -2663,7 +2887,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Huntington Banksil Payment</t>
+          <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
@@ -2677,10 +2901,7 @@
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2">
-        <f>900</f>
-        <v/>
-      </c>
+      <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="2">
         <f>SUM(B17,C17,D17,E17,F17,G17,H17,I17,J17,K17,L17,M17,N17,Q17)</f>
@@ -2688,18 +2909,14 @@
       </c>
       <c r="P17" s="1" t="inlineStr">
         <is>
-          <t>MEALS</t>
-        </is>
-      </c>
-      <c r="Q17" s="4">
-        <f>900</f>
-        <v/>
+          <t>OFFICE EXPENSE</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Internet Trf To Client-Added Transfer Account</t>
+          <t>Huntington Banksil Payment</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -2713,10 +2930,7 @@
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2">
-        <f>453</f>
-        <v/>
-      </c>
+      <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2">
         <f>SUM(B18,C18,D18,E18,F18,G18,H18,I18,J18,K18,L18,M18,N18,Q18)</f>
@@ -2727,15 +2941,11 @@
           <t>MEALS</t>
         </is>
       </c>
-      <c r="Q18" s="4">
-        <f>453</f>
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Irs Usataxpymt</t>
+          <t>Internet Trf To Client-Added Transfer Account</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
@@ -2760,15 +2970,11 @@
           <t>MEALS</t>
         </is>
       </c>
-      <c r="Q19" s="4">
-        <f>800+800</f>
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Kindercare Portland OR</t>
+          <t>Irs Usataxpymt</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
@@ -2793,15 +2999,11 @@
           <t>MEALS</t>
         </is>
       </c>
-      <c r="Q20" s="4">
-        <f>490+120</f>
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>No1 Sushi 88 Corkbbo ACH</t>
+          <t>Kindercare Portland OR</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
@@ -2815,10 +3017,7 @@
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2">
-        <f>4000</f>
-        <v/>
-      </c>
+      <c r="M21" s="2" t="n"/>
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2">
         <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,J21,K21,L21,M21,N21,Q21)</f>
@@ -2833,7 +3032,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
+          <t>No1 Sushi 88 Corkbbo ACH</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
@@ -2862,7 +3061,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Nys Dtf Pit Tax Paymnt</t>
+          <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
         </is>
       </c>
       <c r="B23" s="2" t="n"/>
@@ -2887,15 +3086,11 @@
           <t>MEALS</t>
         </is>
       </c>
-      <c r="Q23" s="4">
-        <f>200+200</f>
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>PANDA EXPRESS TACOMA WA</t>
+          <t>Nys Dtf Pit Tax Paymnt</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
@@ -2924,7 +3119,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Paypal Inst Xfer</t>
+          <t>PANDA EXPRESS TACOMA WA</t>
         </is>
       </c>
       <c r="B25" s="2" t="n"/>
@@ -2953,7 +3148,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Prog Casualty Ins Prem</t>
+          <t>Paypal Inst Xfer</t>
         </is>
       </c>
       <c r="B26" s="2" t="n"/>
@@ -2975,18 +3170,14 @@
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="Q26" s="4">
-        <f>930.52</f>
-        <v/>
+          <t>MEALS</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
+          <t>POS Mac Amazon.Com*9O5 Seattle WA</t>
         </is>
       </c>
       <c r="B27" s="2" t="n"/>
@@ -3008,14 +3199,14 @@
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>MEALS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Withdrawal Branch 0964 New York</t>
+          <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
         </is>
       </c>
       <c r="B28" s="2" t="n"/>
@@ -3029,10 +3220,7 @@
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2">
-        <f>3800</f>
-        <v/>
-      </c>
+      <c r="M28" s="2" t="n"/>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2">
         <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,J28,K28,L28,M28,N28,Q28)</f>
@@ -3040,262 +3228,607 @@
       </c>
       <c r="P28" s="1" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
-        </is>
-      </c>
-      <c r="Q28" s="4">
-        <f>3200+3800</f>
-        <v/>
+          <t>MEALS</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B29" s="2">
-        <f>SUM(B2:B28)</f>
-        <v/>
-      </c>
-      <c r="C29" s="2">
-        <f>SUM(C2:C28)</f>
-        <v/>
-      </c>
-      <c r="D29" s="2">
-        <f>SUM(D2:D28)</f>
-        <v/>
-      </c>
-      <c r="E29" s="2">
-        <f>SUM(E2:E28)</f>
-        <v/>
-      </c>
-      <c r="F29" s="2">
-        <f>SUM(F2:F28)</f>
-        <v/>
-      </c>
-      <c r="G29" s="2">
-        <f>SUM(G2:G28)</f>
-        <v/>
-      </c>
-      <c r="H29" s="2">
-        <f>SUM(H2:H28)</f>
-        <v/>
-      </c>
-      <c r="I29" s="2">
-        <f>SUM(I2:I28)</f>
-        <v/>
-      </c>
-      <c r="J29" s="2">
-        <f>SUM(J2:J28)</f>
-        <v/>
-      </c>
-      <c r="K29" s="2">
-        <f>SUM(K2:K28)</f>
-        <v/>
-      </c>
-      <c r="L29" s="2">
-        <f>SUM(L2:L28)</f>
-        <v/>
-      </c>
-      <c r="M29" s="2">
-        <f>SUM(M2:M28)</f>
-        <v/>
-      </c>
-      <c r="N29" s="2">
-        <f>SUM(N2:N28)</f>
-        <v/>
-      </c>
+          <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
       <c r="O29" s="2">
         <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29,N29,Q29)</f>
         <v/>
       </c>
-      <c r="P29" s="1" t="n"/>
-      <c r="Q29" s="4">
-        <f>SUM(Q2:Q28)</f>
-        <v/>
+      <c r="P29" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2">
+        <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30,N30,Q30)</f>
+        <v/>
+      </c>
+      <c r="P30" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2">
+        <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31,N31,Q31)</f>
+        <v/>
+      </c>
+      <c r="P31" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Nx6 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2">
+        <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32,N32,Q32)</f>
+        <v/>
+      </c>
+      <c r="P32" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2">
+        <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33,N33,Q33)</f>
+        <v/>
+      </c>
+      <c r="P33" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2">
+        <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,J34,K34,L34,M34,N34,Q34)</f>
+        <v/>
+      </c>
+      <c r="P34" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*V25 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2">
+        <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,J35,K35,L35,M35,N35,Q35)</f>
+        <v/>
+      </c>
+      <c r="P35" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Yr6 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2">
+        <f>SUM(B36,C36,D36,E36,F36,G36,H36,I36,J36,K36,L36,M36,N36,Q36)</f>
+        <v/>
+      </c>
+      <c r="P36" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2">
+        <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,J37,K37,L37,M37,N37,Q37)</f>
+        <v/>
+      </c>
+      <c r="P37" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Prog Casualty Ins Prem</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2">
+        <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38,N38,Q38)</f>
+        <v/>
+      </c>
+      <c r="P38" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2">
+        <f>SUM(B39,C39,D39,E39,F39,G39,H39,I39,J39,K39,L39,M39,N39,Q39)</f>
+        <v/>
+      </c>
+      <c r="P39" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Withdrawal Branch 0964 New York</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2">
+        <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,J40,K40,L40,M40,N40,Q40)</f>
+        <v/>
+      </c>
+      <c r="P40" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B41" s="2">
+        <f>SUM(B2:B40)</f>
+        <v/>
+      </c>
+      <c r="C41" s="2">
+        <f>SUM(C2:C40)</f>
+        <v/>
+      </c>
+      <c r="D41" s="2">
+        <f>SUM(D2:D40)</f>
+        <v/>
+      </c>
+      <c r="E41" s="2">
+        <f>SUM(E2:E40)</f>
+        <v/>
+      </c>
+      <c r="F41" s="2">
+        <f>SUM(F2:F40)</f>
+        <v/>
+      </c>
+      <c r="G41" s="2">
+        <f>SUM(G2:G40)</f>
+        <v/>
+      </c>
+      <c r="H41" s="2">
+        <f>SUM(H2:H40)</f>
+        <v/>
+      </c>
+      <c r="I41" s="2">
+        <f>SUM(I2:I40)</f>
+        <v/>
+      </c>
+      <c r="J41" s="2">
+        <f>SUM(J2:J40)</f>
+        <v/>
+      </c>
+      <c r="K41" s="2">
+        <f>SUM(K2:K40)</f>
+        <v/>
+      </c>
+      <c r="L41" s="2">
+        <f>SUM(L2:L40)</f>
+        <v/>
+      </c>
+      <c r="M41" s="2">
+        <f>SUM(M2:M40)</f>
+        <v/>
+      </c>
+      <c r="N41" s="2">
+        <f>SUM(N2:N40)</f>
+        <v/>
+      </c>
+      <c r="O41" s="2">
+        <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41,N41,Q41)</f>
+        <v/>
+      </c>
+      <c r="P41" s="1" t="n"/>
+      <c r="Q41" s="3">
+        <f>SUM(Q2:Q40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>BEGIN</t>
         </is>
       </c>
-      <c r="B31">
+      <c r="B43">
         <f>0</f>
         <v/>
       </c>
-      <c r="C31">
+      <c r="C43">
         <f>B46</f>
         <v/>
       </c>
-      <c r="D31">
+      <c r="D43">
         <f>C46</f>
         <v/>
       </c>
-      <c r="E31">
+      <c r="E43">
         <f>D46</f>
         <v/>
       </c>
-      <c r="F31">
+      <c r="F43">
         <f>E46</f>
         <v/>
       </c>
-      <c r="G31">
+      <c r="G43">
         <f>F46</f>
         <v/>
       </c>
-      <c r="H31">
+      <c r="H43">
         <f>G46</f>
         <v/>
       </c>
-      <c r="I31">
+      <c r="I43">
         <f>H46</f>
         <v/>
       </c>
-      <c r="J31">
+      <c r="J43">
         <f>I46</f>
         <v/>
       </c>
-      <c r="K31">
+      <c r="K43">
         <f>J46</f>
         <v/>
       </c>
-      <c r="L31">
+      <c r="L43">
         <f>K46</f>
         <v/>
       </c>
-      <c r="M31">
+      <c r="M43">
         <f>L46</f>
         <v/>
       </c>
-      <c r="N31">
+      <c r="N43">
         <f>M46</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="B32" s="4">
+      <c r="B44" s="3">
         <f>B41</f>
         <v/>
       </c>
-      <c r="C32" s="4">
+      <c r="C44" s="3">
         <f>C41</f>
         <v/>
       </c>
-      <c r="D32" s="4">
+      <c r="D44" s="3">
         <f>D41</f>
         <v/>
       </c>
-      <c r="E32" s="4">
+      <c r="E44" s="3">
         <f>E41</f>
         <v/>
       </c>
-      <c r="F32" s="4">
+      <c r="F44" s="3">
         <f>F41</f>
         <v/>
       </c>
-      <c r="G32" s="4">
+      <c r="G44" s="3">
         <f>G41</f>
         <v/>
       </c>
-      <c r="H32" s="4">
+      <c r="H44" s="3">
         <f>H41</f>
         <v/>
       </c>
-      <c r="I32" s="4">
+      <c r="I44" s="3">
         <f>I41</f>
         <v/>
       </c>
-      <c r="J32" s="4">
+      <c r="J44" s="3">
         <f>J41</f>
         <v/>
       </c>
-      <c r="K32" s="4">
+      <c r="K44" s="3">
         <f>K41</f>
         <v/>
       </c>
-      <c r="L32" s="4">
+      <c r="L44" s="3">
         <f>L41</f>
         <v/>
       </c>
-      <c r="M32" s="4">
+      <c r="M44" s="3">
         <f>M41</f>
         <v/>
       </c>
-      <c r="N32" s="4">
+      <c r="N44" s="3">
         <f>N41</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>LESS</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>ENDING`</t>
         </is>
       </c>
-      <c r="B34" s="4">
+      <c r="B46" s="3">
         <f>B43+B44-B45</f>
         <v/>
       </c>
-      <c r="C34" s="4">
+      <c r="C46" s="3">
         <f>C43+C44-C45</f>
         <v/>
       </c>
-      <c r="D34" s="4">
+      <c r="D46" s="3">
         <f>D43+D44-D45</f>
         <v/>
       </c>
-      <c r="E34" s="4">
+      <c r="E46" s="3">
         <f>E43+E44-E45</f>
         <v/>
       </c>
-      <c r="F34" s="4">
+      <c r="F46" s="3">
         <f>F43+F44-F45</f>
         <v/>
       </c>
-      <c r="G34" s="4">
+      <c r="G46" s="3">
         <f>G43+G44-G45</f>
         <v/>
       </c>
-      <c r="H34" s="4">
+      <c r="H46" s="3">
         <f>H43+H44-H45</f>
         <v/>
       </c>
-      <c r="I34" s="4">
+      <c r="I46" s="3">
         <f>I43+I44-I45</f>
         <v/>
       </c>
-      <c r="J34" s="4">
+      <c r="J46" s="3">
         <f>J43+J44-J45</f>
         <v/>
       </c>
-      <c r="K34" s="4">
+      <c r="K46" s="3">
         <f>K43+K44-K45</f>
         <v/>
       </c>
-      <c r="L34" s="4">
+      <c r="L46" s="3">
         <f>L43+L44-L45</f>
         <v/>
       </c>
-      <c r="M34" s="4">
+      <c r="M46" s="3">
         <f>M43+M44-M45</f>
         <v/>
       </c>
-      <c r="N34" s="4">
+      <c r="N46" s="3">
         <f>N43+N44-N45</f>
         <v/>
       </c>
@@ -3313,7 +3846,9 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1"/>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/credit_monthly_summary.xlsx
+++ b/credit_monthly_summary.xlsx
@@ -1107,7 +1107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2274,85 +2274,61 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>discover Bank Net/Mobile</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
-      <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B41" s="3">
+        <f>SUM(B2:B40)</f>
+        <v/>
+      </c>
+      <c r="C41" s="3">
+        <f>SUM(C2:C40)</f>
+        <v/>
+      </c>
+      <c r="D41" s="3">
+        <f>SUM(D2:D40)</f>
+        <v/>
+      </c>
+      <c r="E41" s="3">
+        <f>SUM(E2:E40)</f>
+        <v/>
+      </c>
+      <c r="F41" s="3">
+        <f>SUM(F2:F40)</f>
+        <v/>
+      </c>
+      <c r="G41" s="3">
+        <f>SUM(G2:G40)</f>
+        <v/>
+      </c>
+      <c r="H41" s="3">
+        <f>SUM(H2:H40)</f>
+        <v/>
+      </c>
+      <c r="I41" s="3">
+        <f>SUM(I2:I40)</f>
+        <v/>
+      </c>
+      <c r="J41" s="3">
+        <f>SUM(J2:J40)</f>
+        <v/>
+      </c>
+      <c r="K41" s="3">
+        <f>SUM(K2:K40)</f>
+        <v/>
+      </c>
+      <c r="L41" s="3">
+        <f>SUM(L2:L40)</f>
+        <v/>
+      </c>
+      <c r="M41" s="3">
+        <f>SUM(M2:M40)</f>
+        <v/>
+      </c>
+      <c r="N41" s="3">
         <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41)</f>
-        <v/>
-      </c>
-      <c r="O41" s="1" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B42" s="3">
-        <f>SUM(B2:B41)</f>
-        <v/>
-      </c>
-      <c r="C42" s="3">
-        <f>SUM(C2:C41)</f>
-        <v/>
-      </c>
-      <c r="D42" s="3">
-        <f>SUM(D2:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="3">
-        <f>SUM(E2:E41)</f>
-        <v/>
-      </c>
-      <c r="F42" s="3">
-        <f>SUM(F2:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="3">
-        <f>SUM(G2:G41)</f>
-        <v/>
-      </c>
-      <c r="H42" s="3">
-        <f>SUM(H2:H41)</f>
-        <v/>
-      </c>
-      <c r="I42" s="3">
-        <f>SUM(I2:I41)</f>
-        <v/>
-      </c>
-      <c r="J42" s="3">
-        <f>SUM(J2:J41)</f>
-        <v/>
-      </c>
-      <c r="K42" s="3">
-        <f>SUM(K2:K41)</f>
-        <v/>
-      </c>
-      <c r="L42" s="3">
-        <f>SUM(L2:L41)</f>
-        <v/>
-      </c>
-      <c r="M42" s="3">
-        <f>SUM(M2:M41)</f>
-        <v/>
-      </c>
-      <c r="N42" s="3">
-        <f>SUM(B42,C42,D42,E42,F42,G42,H42,I42,J42,K42,L42,M42)</f>
         <v/>
       </c>
     </row>
@@ -2469,7 +2445,7 @@
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2">
-        <f>SUM(B2,C2,D2,E2,F2,G2,H2,I2,J2,K2,L2,M2,N2,Q2)</f>
+        <f>SUM(B2:M2)</f>
         <v/>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -2498,7 +2474,7 @@
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2">
-        <f>SUM(B3,C3,D3,E3,F3,G3,H3,I3,J3,K3,L3,M3,N3,Q3)</f>
+        <f>SUM(B3:M3)</f>
         <v/>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -2527,7 +2503,7 @@
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
       <c r="O4" s="2">
-        <f>SUM(B4,C4,D4,E4,F4,G4,H4,I4,J4,K4,L4,M4,N4,Q4)</f>
+        <f>SUM(B4:M4)</f>
         <v/>
       </c>
       <c r="P4" s="1" t="inlineStr">
@@ -2556,7 +2532,7 @@
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="2">
-        <f>SUM(B5,C5,D5,E5,F5,G5,H5,I5,J5,K5,L5,M5,N5,Q5)</f>
+        <f>SUM(B5:M5)</f>
         <v/>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -2585,7 +2561,7 @@
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2">
-        <f>SUM(B6,C6,D6,E6,F6,G6,H6,I6,J6,K6,L6,M6,N6,Q6)</f>
+        <f>SUM(B6:M6)</f>
         <v/>
       </c>
       <c r="P6" s="1" t="inlineStr">
@@ -2614,7 +2590,7 @@
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2">
-        <f>SUM(B7,C7,D7,E7,F7,G7,H7,I7,J7,K7,L7,M7,N7,Q7)</f>
+        <f>SUM(B7:M7)</f>
         <v/>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -2643,7 +2619,7 @@
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2">
-        <f>SUM(B8,C8,D8,E8,F8,G8,H8,I8,J8,K8,L8,M8,N8,Q8)</f>
+        <f>SUM(B8:M8)</f>
         <v/>
       </c>
       <c r="P8" s="1" t="inlineStr">
@@ -2672,7 +2648,7 @@
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2">
-        <f>SUM(B9,C9,D9,E9,F9,G9,H9,I9,J9,K9,L9,M9,N9,Q9)</f>
+        <f>SUM(B9:M9)</f>
         <v/>
       </c>
       <c r="P9" s="1" t="inlineStr">
@@ -2701,7 +2677,7 @@
       <c r="M10" s="2" t="n"/>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2">
-        <f>SUM(B10,C10,D10,E10,F10,G10,H10,I10,J10,K10,L10,M10,N10,Q10)</f>
+        <f>SUM(B10:M10)</f>
         <v/>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -2730,7 +2706,7 @@
       <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2">
-        <f>SUM(B11,C11,D11,E11,F11,G11,H11,I11,J11,K11,L11,M11,N11,Q11)</f>
+        <f>SUM(B11:M11)</f>
         <v/>
       </c>
       <c r="P11" s="1" t="inlineStr">
@@ -2759,7 +2735,7 @@
       <c r="M12" s="2" t="n"/>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2">
-        <f>SUM(B12,C12,D12,E12,F12,G12,H12,I12,J12,K12,L12,M12,N12,Q12)</f>
+        <f>SUM(B12:M12)</f>
         <v/>
       </c>
       <c r="P12" s="1" t="inlineStr">
@@ -2788,7 +2764,7 @@
       <c r="M13" s="2" t="n"/>
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2">
-        <f>SUM(B13,C13,D13,E13,F13,G13,H13,I13,J13,K13,L13,M13,N13,Q13)</f>
+        <f>SUM(B13:M13)</f>
         <v/>
       </c>
       <c r="P13" s="1" t="inlineStr">
@@ -2817,7 +2793,7 @@
       <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2">
-        <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,J14,K14,L14,M14,N14,Q14)</f>
+        <f>SUM(B14:M14)</f>
         <v/>
       </c>
       <c r="P14" s="1" t="inlineStr">
@@ -2846,7 +2822,7 @@
       <c r="M15" s="2" t="n"/>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2">
-        <f>SUM(B15,C15,D15,E15,F15,G15,H15,I15,J15,K15,L15,M15,N15,Q15)</f>
+        <f>SUM(B15:M15)</f>
         <v/>
       </c>
       <c r="P15" s="1" t="inlineStr">
@@ -2875,7 +2851,7 @@
       <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2">
-        <f>SUM(B16,C16,D16,E16,F16,G16,H16,I16,J16,K16,L16,M16,N16,Q16)</f>
+        <f>SUM(B16:M16)</f>
         <v/>
       </c>
       <c r="P16" s="1" t="inlineStr">
@@ -2904,7 +2880,7 @@
       <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="2">
-        <f>SUM(B17,C17,D17,E17,F17,G17,H17,I17,J17,K17,L17,M17,N17,Q17)</f>
+        <f>SUM(B17:M17)</f>
         <v/>
       </c>
       <c r="P17" s="1" t="inlineStr">
@@ -2933,7 +2909,7 @@
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2">
-        <f>SUM(B18,C18,D18,E18,F18,G18,H18,I18,J18,K18,L18,M18,N18,Q18)</f>
+        <f>SUM(B18:M18)</f>
         <v/>
       </c>
       <c r="P18" s="1" t="inlineStr">
@@ -2962,7 +2938,7 @@
       <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2">
-        <f>SUM(B19,C19,D19,E19,F19,G19,H19,I19,J19,K19,L19,M19,N19,Q19)</f>
+        <f>SUM(B19:M19)</f>
         <v/>
       </c>
       <c r="P19" s="1" t="inlineStr">
@@ -2991,7 +2967,7 @@
       <c r="M20" s="2" t="n"/>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2">
-        <f>SUM(B20,C20,D20,E20,F20,G20,H20,I20,J20,K20,L20,M20,N20,Q20)</f>
+        <f>SUM(B20:M20)</f>
         <v/>
       </c>
       <c r="P20" s="1" t="inlineStr">
@@ -3020,7 +2996,7 @@
       <c r="M21" s="2" t="n"/>
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2">
-        <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,J21,K21,L21,M21,N21,Q21)</f>
+        <f>SUM(B21:M21)</f>
         <v/>
       </c>
       <c r="P21" s="1" t="inlineStr">
@@ -3049,7 +3025,7 @@
       <c r="M22" s="2" t="n"/>
       <c r="N22" s="2" t="n"/>
       <c r="O22" s="2">
-        <f>SUM(B22,C22,D22,E22,F22,G22,H22,I22,J22,K22,L22,M22,N22,Q22)</f>
+        <f>SUM(B22:M22)</f>
         <v/>
       </c>
       <c r="P22" s="1" t="inlineStr">
@@ -3078,7 +3054,7 @@
       <c r="M23" s="2" t="n"/>
       <c r="N23" s="2" t="n"/>
       <c r="O23" s="2">
-        <f>SUM(B23,C23,D23,E23,F23,G23,H23,I23,J23,K23,L23,M23,N23,Q23)</f>
+        <f>SUM(B23:M23)</f>
         <v/>
       </c>
       <c r="P23" s="1" t="inlineStr">
@@ -3107,7 +3083,7 @@
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2">
-        <f>SUM(B24,C24,D24,E24,F24,G24,H24,I24,J24,K24,L24,M24,N24,Q24)</f>
+        <f>SUM(B24:M24)</f>
         <v/>
       </c>
       <c r="P24" s="1" t="inlineStr">
@@ -3136,7 +3112,7 @@
       <c r="M25" s="2" t="n"/>
       <c r="N25" s="2" t="n"/>
       <c r="O25" s="2">
-        <f>SUM(B25,C25,D25,E25,F25,G25,H25,I25,J25,K25,L25,M25,N25,Q25)</f>
+        <f>SUM(B25:M25)</f>
         <v/>
       </c>
       <c r="P25" s="1" t="inlineStr">
@@ -3165,7 +3141,7 @@
       <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="n"/>
       <c r="O26" s="2">
-        <f>SUM(B26,C26,D26,E26,F26,G26,H26,I26,J26,K26,L26,M26,N26,Q26)</f>
+        <f>SUM(B26:M26)</f>
         <v/>
       </c>
       <c r="P26" s="1" t="inlineStr">
@@ -3194,7 +3170,7 @@
       <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2">
-        <f>SUM(B27,C27,D27,E27,F27,G27,H27,I27,J27,K27,L27,M27,N27,Q27)</f>
+        <f>SUM(B27:M27)</f>
         <v/>
       </c>
       <c r="P27" s="1" t="inlineStr">
@@ -3223,7 +3199,7 @@
       <c r="M28" s="2" t="n"/>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2">
-        <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,J28,K28,L28,M28,N28,Q28)</f>
+        <f>SUM(B28:M28)</f>
         <v/>
       </c>
       <c r="P28" s="1" t="inlineStr">
@@ -3252,7 +3228,7 @@
       <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2">
-        <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29,N29,Q29)</f>
+        <f>SUM(B29:M29)</f>
         <v/>
       </c>
       <c r="P29" s="1" t="inlineStr">
@@ -3281,7 +3257,7 @@
       <c r="M30" s="2" t="n"/>
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2">
-        <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30,N30,Q30)</f>
+        <f>SUM(B30:M30)</f>
         <v/>
       </c>
       <c r="P30" s="1" t="inlineStr">
@@ -3310,7 +3286,7 @@
       <c r="M31" s="2" t="n"/>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2">
-        <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31,N31,Q31)</f>
+        <f>SUM(B31:M31)</f>
         <v/>
       </c>
       <c r="P31" s="1" t="inlineStr">
@@ -3339,7 +3315,7 @@
       <c r="M32" s="2" t="n"/>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2">
-        <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32,N32,Q32)</f>
+        <f>SUM(B32:M32)</f>
         <v/>
       </c>
       <c r="P32" s="1" t="inlineStr">
@@ -3368,7 +3344,7 @@
       <c r="M33" s="2" t="n"/>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2">
-        <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33,N33,Q33)</f>
+        <f>SUM(B33:M33)</f>
         <v/>
       </c>
       <c r="P33" s="1" t="inlineStr">
@@ -3397,7 +3373,7 @@
       <c r="M34" s="2" t="n"/>
       <c r="N34" s="2" t="n"/>
       <c r="O34" s="2">
-        <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,J34,K34,L34,M34,N34,Q34)</f>
+        <f>SUM(B34:M34)</f>
         <v/>
       </c>
       <c r="P34" s="1" t="inlineStr">
@@ -3426,7 +3402,7 @@
       <c r="M35" s="2" t="n"/>
       <c r="N35" s="2" t="n"/>
       <c r="O35" s="2">
-        <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,J35,K35,L35,M35,N35,Q35)</f>
+        <f>SUM(B35:M35)</f>
         <v/>
       </c>
       <c r="P35" s="1" t="inlineStr">
@@ -3455,7 +3431,7 @@
       <c r="M36" s="2" t="n"/>
       <c r="N36" s="2" t="n"/>
       <c r="O36" s="2">
-        <f>SUM(B36,C36,D36,E36,F36,G36,H36,I36,J36,K36,L36,M36,N36,Q36)</f>
+        <f>SUM(B36:M36)</f>
         <v/>
       </c>
       <c r="P36" s="1" t="inlineStr">
@@ -3484,7 +3460,7 @@
       <c r="M37" s="2" t="n"/>
       <c r="N37" s="2" t="n"/>
       <c r="O37" s="2">
-        <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,J37,K37,L37,M37,N37,Q37)</f>
+        <f>SUM(B37:M37)</f>
         <v/>
       </c>
       <c r="P37" s="1" t="inlineStr">
@@ -3513,7 +3489,7 @@
       <c r="M38" s="2" t="n"/>
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2">
-        <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38,N38,Q38)</f>
+        <f>SUM(B38:M38)</f>
         <v/>
       </c>
       <c r="P38" s="1" t="inlineStr">
@@ -3542,7 +3518,7 @@
       <c r="M39" s="2" t="n"/>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2">
-        <f>SUM(B39,C39,D39,E39,F39,G39,H39,I39,J39,K39,L39,M39,N39,Q39)</f>
+        <f>SUM(B39:M39)</f>
         <v/>
       </c>
       <c r="P39" s="1" t="inlineStr">
@@ -3571,7 +3547,7 @@
       <c r="M40" s="2" t="n"/>
       <c r="N40" s="2" t="n"/>
       <c r="O40" s="2">
-        <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,J40,K40,L40,M40,N40,Q40)</f>
+        <f>SUM(B40:M40)</f>
         <v/>
       </c>
       <c r="P40" s="1" t="inlineStr">
@@ -3634,21 +3610,13 @@
         <f>SUM(M2:M40)</f>
         <v/>
       </c>
-      <c r="N41" s="2">
-        <f>SUM(N2:N40)</f>
-        <v/>
-      </c>
+      <c r="N41" s="2" t="n"/>
       <c r="O41" s="2">
-        <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41,N41,Q41)</f>
+        <f>SUM(B41:M41)</f>
         <v/>
       </c>
       <c r="P41" s="1" t="n"/>
-      <c r="Q41" s="3">
-        <f>SUM(Q2:Q40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42"/>
+    </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -3846,9 +3814,7 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1"/>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/credit_monthly_summary.xlsx
+++ b/credit_monthly_summary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="2" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="CHASE #3444" sheetId="1" state="visible" r:id="rId1"/>
@@ -115,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -125,6 +125,14 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -133,12 +141,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -504,168 +506,236 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:AG17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="19"/>
+    <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="8.140625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8.140625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="5" bestFit="1" customWidth="1" min="5" max="8"/>
+    <col width="7.140625" bestFit="1" customWidth="1" min="9" max="10"/>
+    <col width="8.140625" bestFit="1" customWidth="1" min="11" max="12"/>
+    <col width="6" bestFit="1" customWidth="1" min="13" max="15"/>
+    <col width="7.140625" bestFit="1" customWidth="1" min="16" max="17"/>
+    <col width="6" bestFit="1" customWidth="1" min="18" max="18"/>
+    <col width="8.140625" bestFit="1" customWidth="1" min="19" max="19"/>
+    <col width="7.140625" bestFit="1" customWidth="1" min="20" max="23"/>
+    <col width="6" bestFit="1" customWidth="1" min="24" max="25"/>
+    <col width="7.140625" bestFit="1" customWidth="1" min="26" max="26"/>
+    <col width="6" bestFit="1" customWidth="1" min="27" max="28"/>
+    <col width="7.140625" bestFit="1" customWidth="1" min="29" max="29"/>
+    <col width="6" bestFit="1" customWidth="1" min="30" max="30"/>
+    <col width="13.85546875" bestFit="1" customWidth="1" min="31" max="31"/>
+    <col width="9.28515625" bestFit="1" customWidth="1" min="32" max="32"/>
+    <col width="17.42578125" bestFit="1" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>CHASE #3444</t>
         </is>
       </c>
-      <c r="B1" s="7" t="n"/>
-      <c r="C1" s="7" t="n"/>
-      <c r="D1" s="7" t="n"/>
-      <c r="E1" s="7" t="n"/>
-      <c r="F1" s="7" t="n"/>
-      <c r="G1" s="7" t="n"/>
-      <c r="H1" s="7" t="n"/>
-      <c r="I1" s="7" t="n"/>
-      <c r="J1" s="7" t="n"/>
-      <c r="K1" s="7" t="n"/>
-      <c r="L1" s="7" t="n"/>
-      <c r="M1" s="7" t="n"/>
-      <c r="N1" s="7" t="n"/>
-      <c r="O1" s="7" t="n"/>
-      <c r="P1" s="7" t="n"/>
-      <c r="Q1" s="7" t="n"/>
-      <c r="R1" s="7" t="n"/>
-      <c r="S1" s="8" t="n"/>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+      <c r="G1" s="11" t="n"/>
+      <c r="H1" s="11" t="n"/>
+      <c r="I1" s="11" t="n"/>
+      <c r="J1" s="11" t="n"/>
+      <c r="K1" s="11" t="n"/>
+      <c r="L1" s="11" t="n"/>
+      <c r="M1" s="11" t="n"/>
+      <c r="N1" s="11" t="n"/>
+      <c r="O1" s="11" t="n"/>
+      <c r="P1" s="11" t="n"/>
+      <c r="Q1" s="11" t="n"/>
+      <c r="R1" s="11" t="n"/>
+      <c r="S1" s="12" t="n"/>
+      <c r="T1" s="11" t="n"/>
+      <c r="U1" s="11" t="n"/>
+      <c r="V1" s="11" t="n"/>
+      <c r="W1" s="11" t="n"/>
+      <c r="X1" s="11" t="n"/>
+      <c r="Y1" s="11" t="n"/>
+      <c r="Z1" s="11" t="n"/>
+      <c r="AA1" s="11" t="n"/>
+      <c r="AB1" s="11" t="n"/>
+      <c r="AC1" s="11" t="n"/>
+      <c r="AD1" s="11" t="n"/>
+      <c r="AE1" s="11" t="n"/>
+      <c r="AF1" s="11" t="n"/>
+      <c r="AG1" s="12" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>MONTH</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>BEGIN BALANCE</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>CASH / CHECK DEPOSIT</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>NO1 SUSHI 88 CORKBBO ACH</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>VEOLIA WATER</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>ORANGE &amp; ROCKLAND</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>WITHDRAWAL BRANCH 0964</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>AMAZON</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>BILL PAY:VEOLIA WATER NEW Y 200045 6BU1T6KR</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>BILL PAY:ORANGE &amp; ROCKLAND 136130 6BQ1P6KR</t>
-        </is>
-      </c>
-      <c r="K2" s="6" t="inlineStr">
-        <is>
-          <t>INTERNET TRF TO CLIENT-ADDED TRANSFER ACCOUNT</t>
-        </is>
-      </c>
-      <c r="L2" s="6" t="inlineStr">
-        <is>
-          <t>WITHDRAWAL BRANCH 0964 NEW YORK</t>
-        </is>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
-          <t>POS MAC AMAZON.COM*NX6 SEATTLE WA</t>
-        </is>
-      </c>
-      <c r="N2" s="6" t="inlineStr">
-        <is>
-          <t>POS MAC AMAZON.COM*9O5 SEATTLE WA</t>
-        </is>
-      </c>
-      <c r="O2" s="6" t="inlineStr">
-        <is>
-          <t>POS MAC AMAZON.COM*SB8 SEATTLE WA</t>
-        </is>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>NYS DTF PIT TAX PAYMNT</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL CREDIT</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="A2" s="10" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="10" t="n"/>
+      <c r="AE2" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="AF2" s="10" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="S2" s="6" t="inlineStr">
-        <is>
-          <t>ENDING BALANCE</t>
+      <c r="AG2" s="10" t="inlineStr">
+        <is>
+          <t>ENDING</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="7" t="n">
         <v>45383</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
+      <c r="D3" s="2">
+        <f>4000</f>
+        <v/>
+      </c>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
+      <c r="I3" s="2">
+        <f>300</f>
+        <v/>
+      </c>
+      <c r="J3" s="2">
+        <f>350</f>
+        <v/>
+      </c>
+      <c r="K3" s="2">
+        <f>385.77+740</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>1000+3200</f>
+        <v/>
+      </c>
+      <c r="M3" s="2">
+        <f>75.4</f>
+        <v/>
+      </c>
+      <c r="N3" s="2">
+        <f>26.57</f>
+        <v/>
+      </c>
+      <c r="O3" s="2">
+        <f>18.75</f>
+        <v/>
+      </c>
+      <c r="P3" s="2">
+        <f>200+200</f>
+        <v/>
+      </c>
       <c r="Q3" s="2">
-        <f>SUM(C3:P3)</f>
-        <v/>
-      </c>
-      <c r="R3" s="2" t="n"/>
+        <f>490+120</f>
+        <v/>
+      </c>
+      <c r="R3" s="2">
+        <f>16.25</f>
+        <v/>
+      </c>
       <c r="S3" s="2">
-        <f>B3+Q3-R3</f>
+        <f>800+800</f>
+        <v/>
+      </c>
+      <c r="T3" s="2">
+        <f>817.29</f>
+        <v/>
+      </c>
+      <c r="U3" s="2">
+        <f>930.52</f>
+        <v/>
+      </c>
+      <c r="V3" s="2">
+        <f>975</f>
+        <v/>
+      </c>
+      <c r="W3" s="2">
+        <f>117.76</f>
+        <v/>
+      </c>
+      <c r="X3" s="2">
+        <f>50.03</f>
+        <v/>
+      </c>
+      <c r="Y3" s="2">
+        <f>71.79</f>
+        <v/>
+      </c>
+      <c r="Z3" s="2">
+        <f>152.14</f>
+        <v/>
+      </c>
+      <c r="AA3" s="2">
+        <f>20.8</f>
+        <v/>
+      </c>
+      <c r="AB3" s="2">
+        <f>40.33</f>
+        <v/>
+      </c>
+      <c r="AC3" s="2">
+        <f>343.93</f>
+        <v/>
+      </c>
+      <c r="AD3" s="2">
+        <f>17.59</f>
+        <v/>
+      </c>
+      <c r="AE3" s="2">
+        <f>SUM(C3:AD3)</f>
+        <v/>
+      </c>
+      <c r="AF3" s="2">
+        <f>'CHASE DETIAL#3444'!B42</f>
+        <v/>
+      </c>
+      <c r="AG3" s="2">
+        <f>B3+AE3-AF3</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n">
+      <c r="A4" s="7" t="n">
         <v>45413</v>
       </c>
       <c r="B4" s="2">
@@ -686,18 +756,32 @@
       <c r="N4" s="2" t="n"/>
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="n"/>
-      <c r="Q4" s="2">
-        <f>SUM(C4:P4)</f>
-        <v/>
-      </c>
+      <c r="Q4" s="2" t="n"/>
       <c r="R4" s="2" t="n"/>
-      <c r="S4" s="2">
-        <f>B4+Q4-R4</f>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="n"/>
+      <c r="X4" s="2" t="n"/>
+      <c r="Y4" s="2" t="n"/>
+      <c r="Z4" s="2" t="n"/>
+      <c r="AA4" s="2" t="n"/>
+      <c r="AB4" s="2" t="n"/>
+      <c r="AC4" s="2" t="n"/>
+      <c r="AD4" s="2" t="n"/>
+      <c r="AE4" s="2">
+        <f>SUM(C4:AD4)</f>
+        <v/>
+      </c>
+      <c r="AF4" s="2" t="n"/>
+      <c r="AG4" s="2">
+        <f>B4+AE4-AF4</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="7" t="n">
         <v>45444</v>
       </c>
       <c r="B5" s="2">
@@ -718,18 +802,32 @@
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="n"/>
-      <c r="Q5" s="2">
-        <f>SUM(C5:P5)</f>
-        <v/>
-      </c>
+      <c r="Q5" s="2" t="n"/>
       <c r="R5" s="2" t="n"/>
-      <c r="S5" s="2">
-        <f>B5+Q5-R5</f>
+      <c r="S5" s="2" t="n"/>
+      <c r="T5" s="2" t="n"/>
+      <c r="U5" s="2" t="n"/>
+      <c r="V5" s="2" t="n"/>
+      <c r="W5" s="2" t="n"/>
+      <c r="X5" s="2" t="n"/>
+      <c r="Y5" s="2" t="n"/>
+      <c r="Z5" s="2" t="n"/>
+      <c r="AA5" s="2" t="n"/>
+      <c r="AB5" s="2" t="n"/>
+      <c r="AC5" s="2" t="n"/>
+      <c r="AD5" s="2" t="n"/>
+      <c r="AE5" s="2">
+        <f>SUM(C5:AD5)</f>
+        <v/>
+      </c>
+      <c r="AF5" s="2" t="n"/>
+      <c r="AG5" s="2">
+        <f>B5+AE5-AF5</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="7" t="n">
         <v>45474</v>
       </c>
       <c r="B6" s="2">
@@ -750,18 +848,32 @@
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2">
-        <f>SUM(C6:P6)</f>
-        <v/>
-      </c>
+      <c r="Q6" s="2" t="n"/>
       <c r="R6" s="2" t="n"/>
-      <c r="S6" s="2">
-        <f>B6+Q6-R6</f>
+      <c r="S6" s="2" t="n"/>
+      <c r="T6" s="2" t="n"/>
+      <c r="U6" s="2" t="n"/>
+      <c r="V6" s="2" t="n"/>
+      <c r="W6" s="2" t="n"/>
+      <c r="X6" s="2" t="n"/>
+      <c r="Y6" s="2" t="n"/>
+      <c r="Z6" s="2" t="n"/>
+      <c r="AA6" s="2" t="n"/>
+      <c r="AB6" s="2" t="n"/>
+      <c r="AC6" s="2" t="n"/>
+      <c r="AD6" s="2" t="n"/>
+      <c r="AE6" s="2">
+        <f>SUM(C6:AD6)</f>
+        <v/>
+      </c>
+      <c r="AF6" s="2" t="n"/>
+      <c r="AG6" s="2">
+        <f>B6+AE6-AF6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="7" t="n">
         <v>45505</v>
       </c>
       <c r="B7" s="2">
@@ -782,18 +894,32 @@
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="n"/>
-      <c r="Q7" s="2">
-        <f>SUM(C7:P7)</f>
-        <v/>
-      </c>
+      <c r="Q7" s="2" t="n"/>
       <c r="R7" s="2" t="n"/>
-      <c r="S7" s="2">
-        <f>B7+Q7-R7</f>
+      <c r="S7" s="2" t="n"/>
+      <c r="T7" s="2" t="n"/>
+      <c r="U7" s="2" t="n"/>
+      <c r="V7" s="2" t="n"/>
+      <c r="W7" s="2" t="n"/>
+      <c r="X7" s="2" t="n"/>
+      <c r="Y7" s="2" t="n"/>
+      <c r="Z7" s="2" t="n"/>
+      <c r="AA7" s="2" t="n"/>
+      <c r="AB7" s="2" t="n"/>
+      <c r="AC7" s="2" t="n"/>
+      <c r="AD7" s="2" t="n"/>
+      <c r="AE7" s="2">
+        <f>SUM(C7:AD7)</f>
+        <v/>
+      </c>
+      <c r="AF7" s="2" t="n"/>
+      <c r="AG7" s="2">
+        <f>B7+AE7-AF7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="7" t="n">
         <v>45536</v>
       </c>
       <c r="B8" s="2">
@@ -814,18 +940,32 @@
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="n"/>
-      <c r="Q8" s="2">
-        <f>SUM(C8:P8)</f>
-        <v/>
-      </c>
+      <c r="Q8" s="2" t="n"/>
       <c r="R8" s="2" t="n"/>
-      <c r="S8" s="2">
-        <f>B8+Q8-R8</f>
+      <c r="S8" s="2" t="n"/>
+      <c r="T8" s="2" t="n"/>
+      <c r="U8" s="2" t="n"/>
+      <c r="V8" s="2" t="n"/>
+      <c r="W8" s="2" t="n"/>
+      <c r="X8" s="2" t="n"/>
+      <c r="Y8" s="2" t="n"/>
+      <c r="Z8" s="2" t="n"/>
+      <c r="AA8" s="2" t="n"/>
+      <c r="AB8" s="2" t="n"/>
+      <c r="AC8" s="2" t="n"/>
+      <c r="AD8" s="2" t="n"/>
+      <c r="AE8" s="2">
+        <f>SUM(C8:AD8)</f>
+        <v/>
+      </c>
+      <c r="AF8" s="2" t="n"/>
+      <c r="AG8" s="2">
+        <f>B8+AE8-AF8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="7" t="n">
         <v>45566</v>
       </c>
       <c r="B9" s="2">
@@ -846,18 +986,32 @@
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="n"/>
-      <c r="Q9" s="2">
-        <f>SUM(C9:P9)</f>
-        <v/>
-      </c>
+      <c r="Q9" s="2" t="n"/>
       <c r="R9" s="2" t="n"/>
-      <c r="S9" s="2">
-        <f>B9+Q9-R9</f>
+      <c r="S9" s="2" t="n"/>
+      <c r="T9" s="2" t="n"/>
+      <c r="U9" s="2" t="n"/>
+      <c r="V9" s="2" t="n"/>
+      <c r="W9" s="2" t="n"/>
+      <c r="X9" s="2" t="n"/>
+      <c r="Y9" s="2" t="n"/>
+      <c r="Z9" s="2" t="n"/>
+      <c r="AA9" s="2" t="n"/>
+      <c r="AB9" s="2" t="n"/>
+      <c r="AC9" s="2" t="n"/>
+      <c r="AD9" s="2" t="n"/>
+      <c r="AE9" s="2">
+        <f>SUM(C9:AD9)</f>
+        <v/>
+      </c>
+      <c r="AF9" s="2" t="n"/>
+      <c r="AG9" s="2">
+        <f>B9+AE9-AF9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n">
+      <c r="A10" s="7" t="n">
         <v>45597</v>
       </c>
       <c r="B10" s="2">
@@ -878,18 +1032,32 @@
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2">
-        <f>SUM(C10:P10)</f>
-        <v/>
-      </c>
+      <c r="Q10" s="2" t="n"/>
       <c r="R10" s="2" t="n"/>
-      <c r="S10" s="2">
-        <f>B10+Q10-R10</f>
+      <c r="S10" s="2" t="n"/>
+      <c r="T10" s="2" t="n"/>
+      <c r="U10" s="2" t="n"/>
+      <c r="V10" s="2" t="n"/>
+      <c r="W10" s="2" t="n"/>
+      <c r="X10" s="2" t="n"/>
+      <c r="Y10" s="2" t="n"/>
+      <c r="Z10" s="2" t="n"/>
+      <c r="AA10" s="2" t="n"/>
+      <c r="AB10" s="2" t="n"/>
+      <c r="AC10" s="2" t="n"/>
+      <c r="AD10" s="2" t="n"/>
+      <c r="AE10" s="2">
+        <f>SUM(C10:AD10)</f>
+        <v/>
+      </c>
+      <c r="AF10" s="2" t="n"/>
+      <c r="AG10" s="2">
+        <f>B10+AE10-AF10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n">
+      <c r="A11" s="7" t="n">
         <v>45627</v>
       </c>
       <c r="B11" s="2">
@@ -910,18 +1078,32 @@
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2">
-        <f>SUM(C11:P11)</f>
-        <v/>
-      </c>
+      <c r="Q11" s="2" t="n"/>
       <c r="R11" s="2" t="n"/>
-      <c r="S11" s="2">
-        <f>B11+Q11-R11</f>
+      <c r="S11" s="2" t="n"/>
+      <c r="T11" s="2" t="n"/>
+      <c r="U11" s="2" t="n"/>
+      <c r="V11" s="2" t="n"/>
+      <c r="W11" s="2" t="n"/>
+      <c r="X11" s="2" t="n"/>
+      <c r="Y11" s="2" t="n"/>
+      <c r="Z11" s="2" t="n"/>
+      <c r="AA11" s="2" t="n"/>
+      <c r="AB11" s="2" t="n"/>
+      <c r="AC11" s="2" t="n"/>
+      <c r="AD11" s="2" t="n"/>
+      <c r="AE11" s="2">
+        <f>SUM(C11:AD11)</f>
+        <v/>
+      </c>
+      <c r="AF11" s="2" t="n"/>
+      <c r="AG11" s="2">
+        <f>B11+AE11-AF11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n">
+      <c r="A12" s="7" t="n">
         <v>45658</v>
       </c>
       <c r="B12" s="2">
@@ -942,18 +1124,32 @@
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="n"/>
-      <c r="Q12" s="2">
-        <f>SUM(C12:P12)</f>
-        <v/>
-      </c>
+      <c r="Q12" s="2" t="n"/>
       <c r="R12" s="2" t="n"/>
-      <c r="S12" s="2">
-        <f>B12+Q12-R12</f>
+      <c r="S12" s="2" t="n"/>
+      <c r="T12" s="2" t="n"/>
+      <c r="U12" s="2" t="n"/>
+      <c r="V12" s="2" t="n"/>
+      <c r="W12" s="2" t="n"/>
+      <c r="X12" s="2" t="n"/>
+      <c r="Y12" s="2" t="n"/>
+      <c r="Z12" s="2" t="n"/>
+      <c r="AA12" s="2" t="n"/>
+      <c r="AB12" s="2" t="n"/>
+      <c r="AC12" s="2" t="n"/>
+      <c r="AD12" s="2" t="n"/>
+      <c r="AE12" s="2">
+        <f>SUM(C12:AD12)</f>
+        <v/>
+      </c>
+      <c r="AF12" s="2" t="n"/>
+      <c r="AG12" s="2">
+        <f>B12+AE12-AF12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n">
+      <c r="A13" s="7" t="n">
         <v>45689</v>
       </c>
       <c r="B13" s="2">
@@ -974,18 +1170,32 @@
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="n"/>
-      <c r="Q13" s="2">
-        <f>SUM(C13:P13)</f>
-        <v/>
-      </c>
+      <c r="Q13" s="2" t="n"/>
       <c r="R13" s="2" t="n"/>
-      <c r="S13" s="2">
-        <f>B13+Q13-R13</f>
+      <c r="S13" s="2" t="n"/>
+      <c r="T13" s="2" t="n"/>
+      <c r="U13" s="2" t="n"/>
+      <c r="V13" s="2" t="n"/>
+      <c r="W13" s="2" t="n"/>
+      <c r="X13" s="2" t="n"/>
+      <c r="Y13" s="2" t="n"/>
+      <c r="Z13" s="2" t="n"/>
+      <c r="AA13" s="2" t="n"/>
+      <c r="AB13" s="2" t="n"/>
+      <c r="AC13" s="2" t="n"/>
+      <c r="AD13" s="2" t="n"/>
+      <c r="AE13" s="2">
+        <f>SUM(C13:AD13)</f>
+        <v/>
+      </c>
+      <c r="AF13" s="2" t="n"/>
+      <c r="AG13" s="2">
+        <f>B13+AE13-AF13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n">
+      <c r="A14" s="7" t="n">
         <v>45717</v>
       </c>
       <c r="B14" s="2">
@@ -1006,13 +1216,27 @@
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2">
-        <f>SUM(C14:P14)</f>
-        <v/>
-      </c>
+      <c r="Q14" s="2" t="n"/>
       <c r="R14" s="2" t="n"/>
-      <c r="S14" s="2">
-        <f>B14+Q14-R14</f>
+      <c r="S14" s="2" t="n"/>
+      <c r="T14" s="2" t="n"/>
+      <c r="U14" s="2" t="n"/>
+      <c r="V14" s="2" t="n"/>
+      <c r="W14" s="2" t="n"/>
+      <c r="X14" s="2" t="n"/>
+      <c r="Y14" s="2" t="n"/>
+      <c r="Z14" s="2" t="n"/>
+      <c r="AA14" s="2" t="n"/>
+      <c r="AB14" s="2" t="n"/>
+      <c r="AC14" s="2" t="n"/>
+      <c r="AD14" s="2" t="n"/>
+      <c r="AE14" s="2">
+        <f>SUM(C14:AD14)</f>
+        <v/>
+      </c>
+      <c r="AF14" s="2" t="n"/>
+      <c r="AG14" s="2">
+        <f>B14+AE14-AF14</f>
         <v/>
       </c>
     </row>
@@ -1088,8 +1312,72 @@
         <v/>
       </c>
       <c r="S15" s="2">
-        <f>S14</f>
-        <v/>
+        <f>SUM(S3:S14)</f>
+        <v/>
+      </c>
+      <c r="T15" s="2">
+        <f>SUM(T3:T14)</f>
+        <v/>
+      </c>
+      <c r="U15" s="2">
+        <f>SUM(U3:U14)</f>
+        <v/>
+      </c>
+      <c r="V15" s="2">
+        <f>SUM(V3:V14)</f>
+        <v/>
+      </c>
+      <c r="W15" s="2">
+        <f>SUM(W3:W14)</f>
+        <v/>
+      </c>
+      <c r="X15" s="2">
+        <f>SUM(X3:X14)</f>
+        <v/>
+      </c>
+      <c r="Y15" s="2">
+        <f>SUM(Y3:Y14)</f>
+        <v/>
+      </c>
+      <c r="Z15" s="2">
+        <f>SUM(Z3:Z14)</f>
+        <v/>
+      </c>
+      <c r="AA15" s="2">
+        <f>SUM(AA3:AA14)</f>
+        <v/>
+      </c>
+      <c r="AB15" s="2">
+        <f>SUM(AB3:AB14)</f>
+        <v/>
+      </c>
+      <c r="AC15" s="2">
+        <f>SUM(AC3:AC14)</f>
+        <v/>
+      </c>
+      <c r="AD15" s="2">
+        <f>SUM(AD3:AD14)</f>
+        <v/>
+      </c>
+      <c r="AE15" s="2">
+        <f>SUM(AE3:AE14)</f>
+        <v/>
+      </c>
+      <c r="AF15" s="2">
+        <f>SUM(AF3:AF14)</f>
+        <v/>
+      </c>
+      <c r="AG15" s="2">
+        <f>AG14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eric </t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1107,75 +1395,75 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="50.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Merchant</t>
         </is>
       </c>
-      <c r="B1" s="10">
+      <c r="B1" s="8">
         <f>'CHASE #3444'!A3</f>
         <v/>
       </c>
-      <c r="C1" s="10">
+      <c r="C1" s="8">
         <f>'CHASE #3444'!A4</f>
         <v/>
       </c>
-      <c r="D1" s="10">
+      <c r="D1" s="8">
         <f>'CHASE #3444'!A5</f>
         <v/>
       </c>
-      <c r="E1" s="10">
+      <c r="E1" s="8">
         <f>'CHASE #3444'!A6</f>
         <v/>
       </c>
-      <c r="F1" s="10">
+      <c r="F1" s="8">
         <f>'CHASE #3444'!A7</f>
         <v/>
       </c>
-      <c r="G1" s="10">
+      <c r="G1" s="8">
         <f>'CHASE #3444'!A8</f>
         <v/>
       </c>
-      <c r="H1" s="10">
+      <c r="H1" s="8">
         <f>'CHASE #3444'!A9</f>
         <v/>
       </c>
-      <c r="I1" s="10">
+      <c r="I1" s="8">
         <f>'CHASE #3444'!A10</f>
         <v/>
       </c>
-      <c r="J1" s="10">
+      <c r="J1" s="8">
         <f>'CHASE #3444'!A11</f>
         <v/>
       </c>
-      <c r="K1" s="10">
+      <c r="K1" s="8">
         <f>'CHASE #3444'!A12</f>
         <v/>
       </c>
-      <c r="L1" s="10">
+      <c r="L1" s="8">
         <f>'CHASE #3444'!A13</f>
         <v/>
       </c>
-      <c r="M1" s="10">
+      <c r="M1" s="8">
         <f>'CHASE #3444'!A14</f>
         <v/>
       </c>
-      <c r="N1" s="6" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="O1" s="6" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
@@ -2274,61 +2562,85 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>discover Bank Net/Mobile</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2">
+        <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41)</f>
+        <v/>
+      </c>
+      <c r="O41" s="1" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B41" s="3">
-        <f>SUM(B2:B40)</f>
-        <v/>
-      </c>
-      <c r="C41" s="3">
-        <f>SUM(C2:C40)</f>
-        <v/>
-      </c>
-      <c r="D41" s="3">
-        <f>SUM(D2:D40)</f>
-        <v/>
-      </c>
-      <c r="E41" s="3">
-        <f>SUM(E2:E40)</f>
-        <v/>
-      </c>
-      <c r="F41" s="3">
-        <f>SUM(F2:F40)</f>
-        <v/>
-      </c>
-      <c r="G41" s="3">
-        <f>SUM(G2:G40)</f>
-        <v/>
-      </c>
-      <c r="H41" s="3">
-        <f>SUM(H2:H40)</f>
-        <v/>
-      </c>
-      <c r="I41" s="3">
-        <f>SUM(I2:I40)</f>
-        <v/>
-      </c>
-      <c r="J41" s="3">
-        <f>SUM(J2:J40)</f>
-        <v/>
-      </c>
-      <c r="K41" s="3">
-        <f>SUM(K2:K40)</f>
-        <v/>
-      </c>
-      <c r="L41" s="3">
-        <f>SUM(L2:L40)</f>
-        <v/>
-      </c>
-      <c r="M41" s="3">
-        <f>SUM(M2:M40)</f>
-        <v/>
-      </c>
-      <c r="N41" s="3">
-        <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41)</f>
+      <c r="B42" s="3">
+        <f>SUM(B2:B41)</f>
+        <v/>
+      </c>
+      <c r="C42" s="3">
+        <f>SUM(C2:C41)</f>
+        <v/>
+      </c>
+      <c r="D42" s="3">
+        <f>SUM(D2:D41)</f>
+        <v/>
+      </c>
+      <c r="E42" s="3">
+        <f>SUM(E2:E41)</f>
+        <v/>
+      </c>
+      <c r="F42" s="3">
+        <f>SUM(F2:F41)</f>
+        <v/>
+      </c>
+      <c r="G42" s="3">
+        <f>SUM(G2:G41)</f>
+        <v/>
+      </c>
+      <c r="H42" s="3">
+        <f>SUM(H2:H41)</f>
+        <v/>
+      </c>
+      <c r="I42" s="3">
+        <f>SUM(I2:I41)</f>
+        <v/>
+      </c>
+      <c r="J42" s="3">
+        <f>SUM(J2:J41)</f>
+        <v/>
+      </c>
+      <c r="K42" s="3">
+        <f>SUM(K2:K41)</f>
+        <v/>
+      </c>
+      <c r="L42" s="3">
+        <f>SUM(L2:L41)</f>
+        <v/>
+      </c>
+      <c r="M42" s="3">
+        <f>SUM(M2:M41)</f>
+        <v/>
+      </c>
+      <c r="N42" s="3">
+        <f>SUM(B42,C42,D42,E42,F42,G42,H42,I42,J42,K42,L42,M42)</f>
         <v/>
       </c>
     </row>
@@ -2367,56 +2679,56 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Merchant</t>
         </is>
       </c>
-      <c r="B1" s="10" t="n">
+      <c r="B1" s="8" t="n">
         <v>45748</v>
       </c>
-      <c r="C1" s="10" t="n">
+      <c r="C1" s="8" t="n">
         <v>45778</v>
       </c>
-      <c r="D1" s="10" t="n">
+      <c r="D1" s="8" t="n">
         <v>45809</v>
       </c>
-      <c r="E1" s="10" t="n">
+      <c r="E1" s="8" t="n">
         <v>45839</v>
       </c>
-      <c r="F1" s="10" t="n">
+      <c r="F1" s="8" t="n">
         <v>45870</v>
       </c>
-      <c r="G1" s="10" t="n">
+      <c r="G1" s="8" t="n">
         <v>45901</v>
       </c>
-      <c r="H1" s="10" t="n">
+      <c r="H1" s="8" t="n">
         <v>45931</v>
       </c>
-      <c r="I1" s="10" t="n">
+      <c r="I1" s="8" t="n">
         <v>45962</v>
       </c>
-      <c r="J1" s="10" t="n">
+      <c r="J1" s="8" t="n">
         <v>45992</v>
       </c>
-      <c r="K1" s="10" t="n">
+      <c r="K1" s="8" t="n">
         <v>46023</v>
       </c>
-      <c r="L1" s="10" t="n">
+      <c r="L1" s="8" t="n">
         <v>46054</v>
       </c>
-      <c r="M1" s="10" t="n">
+      <c r="M1" s="8" t="n">
         <v>46082</v>
       </c>
-      <c r="N1" s="10" t="n">
+      <c r="N1" s="8" t="n">
         <v>46113</v>
       </c>
-      <c r="O1" s="6" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="P1" s="6" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
@@ -2445,7 +2757,7 @@
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2">
-        <f>SUM(B2:M2)</f>
+        <f>SUM(B2,C2,D2,E2,F2,G2,H2,I2,J2,K2,L2,M2,N2,Q2)</f>
         <v/>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -2474,7 +2786,7 @@
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2">
-        <f>SUM(B3:M3)</f>
+        <f>SUM(B3,C3,D3,E3,F3,G3,H3,I3,J3,K3,L3,M3,N3,Q3)</f>
         <v/>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -2503,7 +2815,7 @@
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
       <c r="O4" s="2">
-        <f>SUM(B4:M4)</f>
+        <f>SUM(B4,C4,D4,E4,F4,G4,H4,I4,J4,K4,L4,M4,N4,Q4)</f>
         <v/>
       </c>
       <c r="P4" s="1" t="inlineStr">
@@ -2532,7 +2844,7 @@
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="2">
-        <f>SUM(B5:M5)</f>
+        <f>SUM(B5,C5,D5,E5,F5,G5,H5,I5,J5,K5,L5,M5,N5,Q5)</f>
         <v/>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -2561,7 +2873,7 @@
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2">
-        <f>SUM(B6:M6)</f>
+        <f>SUM(B6,C6,D6,E6,F6,G6,H6,I6,J6,K6,L6,M6,N6,Q6)</f>
         <v/>
       </c>
       <c r="P6" s="1" t="inlineStr">
@@ -2590,7 +2902,7 @@
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2">
-        <f>SUM(B7:M7)</f>
+        <f>SUM(B7,C7,D7,E7,F7,G7,H7,I7,J7,K7,L7,M7,N7,Q7)</f>
         <v/>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -2619,7 +2931,7 @@
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2">
-        <f>SUM(B8:M8)</f>
+        <f>SUM(B8,C8,D8,E8,F8,G8,H8,I8,J8,K8,L8,M8,N8,Q8)</f>
         <v/>
       </c>
       <c r="P8" s="1" t="inlineStr">
@@ -2648,7 +2960,7 @@
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2">
-        <f>SUM(B9:M9)</f>
+        <f>SUM(B9,C9,D9,E9,F9,G9,H9,I9,J9,K9,L9,M9,N9,Q9)</f>
         <v/>
       </c>
       <c r="P9" s="1" t="inlineStr">
@@ -2677,7 +2989,7 @@
       <c r="M10" s="2" t="n"/>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2">
-        <f>SUM(B10:M10)</f>
+        <f>SUM(B10,C10,D10,E10,F10,G10,H10,I10,J10,K10,L10,M10,N10,Q10)</f>
         <v/>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -2706,7 +3018,7 @@
       <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2">
-        <f>SUM(B11:M11)</f>
+        <f>SUM(B11,C11,D11,E11,F11,G11,H11,I11,J11,K11,L11,M11,N11,Q11)</f>
         <v/>
       </c>
       <c r="P11" s="1" t="inlineStr">
@@ -2735,7 +3047,7 @@
       <c r="M12" s="2" t="n"/>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2">
-        <f>SUM(B12:M12)</f>
+        <f>SUM(B12,C12,D12,E12,F12,G12,H12,I12,J12,K12,L12,M12,N12,Q12)</f>
         <v/>
       </c>
       <c r="P12" s="1" t="inlineStr">
@@ -2764,7 +3076,7 @@
       <c r="M13" s="2" t="n"/>
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2">
-        <f>SUM(B13:M13)</f>
+        <f>SUM(B13,C13,D13,E13,F13,G13,H13,I13,J13,K13,L13,M13,N13,Q13)</f>
         <v/>
       </c>
       <c r="P13" s="1" t="inlineStr">
@@ -2793,7 +3105,7 @@
       <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2">
-        <f>SUM(B14:M14)</f>
+        <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,J14,K14,L14,M14,N14,Q14)</f>
         <v/>
       </c>
       <c r="P14" s="1" t="inlineStr">
@@ -2822,7 +3134,7 @@
       <c r="M15" s="2" t="n"/>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2">
-        <f>SUM(B15:M15)</f>
+        <f>SUM(B15,C15,D15,E15,F15,G15,H15,I15,J15,K15,L15,M15,N15,Q15)</f>
         <v/>
       </c>
       <c r="P15" s="1" t="inlineStr">
@@ -2851,7 +3163,7 @@
       <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2">
-        <f>SUM(B16:M16)</f>
+        <f>SUM(B16,C16,D16,E16,F16,G16,H16,I16,J16,K16,L16,M16,N16,Q16)</f>
         <v/>
       </c>
       <c r="P16" s="1" t="inlineStr">
@@ -2880,7 +3192,7 @@
       <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="2">
-        <f>SUM(B17:M17)</f>
+        <f>SUM(B17,C17,D17,E17,F17,G17,H17,I17,J17,K17,L17,M17,N17,Q17)</f>
         <v/>
       </c>
       <c r="P17" s="1" t="inlineStr">
@@ -2909,7 +3221,7 @@
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2">
-        <f>SUM(B18:M18)</f>
+        <f>SUM(B18,C18,D18,E18,F18,G18,H18,I18,J18,K18,L18,M18,N18,Q18)</f>
         <v/>
       </c>
       <c r="P18" s="1" t="inlineStr">
@@ -2938,7 +3250,7 @@
       <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2">
-        <f>SUM(B19:M19)</f>
+        <f>SUM(B19,C19,D19,E19,F19,G19,H19,I19,J19,K19,L19,M19,N19,Q19)</f>
         <v/>
       </c>
       <c r="P19" s="1" t="inlineStr">
@@ -2967,7 +3279,7 @@
       <c r="M20" s="2" t="n"/>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2">
-        <f>SUM(B20:M20)</f>
+        <f>SUM(B20,C20,D20,E20,F20,G20,H20,I20,J20,K20,L20,M20,N20,Q20)</f>
         <v/>
       </c>
       <c r="P20" s="1" t="inlineStr">
@@ -2996,7 +3308,7 @@
       <c r="M21" s="2" t="n"/>
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2">
-        <f>SUM(B21:M21)</f>
+        <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,J21,K21,L21,M21,N21,Q21)</f>
         <v/>
       </c>
       <c r="P21" s="1" t="inlineStr">
@@ -3025,7 +3337,7 @@
       <c r="M22" s="2" t="n"/>
       <c r="N22" s="2" t="n"/>
       <c r="O22" s="2">
-        <f>SUM(B22:M22)</f>
+        <f>SUM(B22,C22,D22,E22,F22,G22,H22,I22,J22,K22,L22,M22,N22,Q22)</f>
         <v/>
       </c>
       <c r="P22" s="1" t="inlineStr">
@@ -3054,7 +3366,7 @@
       <c r="M23" s="2" t="n"/>
       <c r="N23" s="2" t="n"/>
       <c r="O23" s="2">
-        <f>SUM(B23:M23)</f>
+        <f>SUM(B23,C23,D23,E23,F23,G23,H23,I23,J23,K23,L23,M23,N23,Q23)</f>
         <v/>
       </c>
       <c r="P23" s="1" t="inlineStr">
@@ -3083,7 +3395,7 @@
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2">
-        <f>SUM(B24:M24)</f>
+        <f>SUM(B24,C24,D24,E24,F24,G24,H24,I24,J24,K24,L24,M24,N24,Q24)</f>
         <v/>
       </c>
       <c r="P24" s="1" t="inlineStr">
@@ -3112,7 +3424,7 @@
       <c r="M25" s="2" t="n"/>
       <c r="N25" s="2" t="n"/>
       <c r="O25" s="2">
-        <f>SUM(B25:M25)</f>
+        <f>SUM(B25,C25,D25,E25,F25,G25,H25,I25,J25,K25,L25,M25,N25,Q25)</f>
         <v/>
       </c>
       <c r="P25" s="1" t="inlineStr">
@@ -3141,7 +3453,7 @@
       <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="n"/>
       <c r="O26" s="2">
-        <f>SUM(B26:M26)</f>
+        <f>SUM(B26,C26,D26,E26,F26,G26,H26,I26,J26,K26,L26,M26,N26,Q26)</f>
         <v/>
       </c>
       <c r="P26" s="1" t="inlineStr">
@@ -3170,7 +3482,7 @@
       <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2">
-        <f>SUM(B27:M27)</f>
+        <f>SUM(B27,C27,D27,E27,F27,G27,H27,I27,J27,K27,L27,M27,N27,Q27)</f>
         <v/>
       </c>
       <c r="P27" s="1" t="inlineStr">
@@ -3199,7 +3511,7 @@
       <c r="M28" s="2" t="n"/>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2">
-        <f>SUM(B28:M28)</f>
+        <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,J28,K28,L28,M28,N28,Q28)</f>
         <v/>
       </c>
       <c r="P28" s="1" t="inlineStr">
@@ -3228,7 +3540,7 @@
       <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2">
-        <f>SUM(B29:M29)</f>
+        <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29,N29,Q29)</f>
         <v/>
       </c>
       <c r="P29" s="1" t="inlineStr">
@@ -3257,7 +3569,7 @@
       <c r="M30" s="2" t="n"/>
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2">
-        <f>SUM(B30:M30)</f>
+        <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30,N30,Q30)</f>
         <v/>
       </c>
       <c r="P30" s="1" t="inlineStr">
@@ -3286,7 +3598,7 @@
       <c r="M31" s="2" t="n"/>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2">
-        <f>SUM(B31:M31)</f>
+        <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31,N31,Q31)</f>
         <v/>
       </c>
       <c r="P31" s="1" t="inlineStr">
@@ -3315,7 +3627,7 @@
       <c r="M32" s="2" t="n"/>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2">
-        <f>SUM(B32:M32)</f>
+        <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32,N32,Q32)</f>
         <v/>
       </c>
       <c r="P32" s="1" t="inlineStr">
@@ -3344,7 +3656,7 @@
       <c r="M33" s="2" t="n"/>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2">
-        <f>SUM(B33:M33)</f>
+        <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33,N33,Q33)</f>
         <v/>
       </c>
       <c r="P33" s="1" t="inlineStr">
@@ -3373,7 +3685,7 @@
       <c r="M34" s="2" t="n"/>
       <c r="N34" s="2" t="n"/>
       <c r="O34" s="2">
-        <f>SUM(B34:M34)</f>
+        <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,J34,K34,L34,M34,N34,Q34)</f>
         <v/>
       </c>
       <c r="P34" s="1" t="inlineStr">
@@ -3402,7 +3714,7 @@
       <c r="M35" s="2" t="n"/>
       <c r="N35" s="2" t="n"/>
       <c r="O35" s="2">
-        <f>SUM(B35:M35)</f>
+        <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,J35,K35,L35,M35,N35,Q35)</f>
         <v/>
       </c>
       <c r="P35" s="1" t="inlineStr">
@@ -3431,7 +3743,7 @@
       <c r="M36" s="2" t="n"/>
       <c r="N36" s="2" t="n"/>
       <c r="O36" s="2">
-        <f>SUM(B36:M36)</f>
+        <f>SUM(B36,C36,D36,E36,F36,G36,H36,I36,J36,K36,L36,M36,N36,Q36)</f>
         <v/>
       </c>
       <c r="P36" s="1" t="inlineStr">
@@ -3460,7 +3772,7 @@
       <c r="M37" s="2" t="n"/>
       <c r="N37" s="2" t="n"/>
       <c r="O37" s="2">
-        <f>SUM(B37:M37)</f>
+        <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,J37,K37,L37,M37,N37,Q37)</f>
         <v/>
       </c>
       <c r="P37" s="1" t="inlineStr">
@@ -3489,7 +3801,7 @@
       <c r="M38" s="2" t="n"/>
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2">
-        <f>SUM(B38:M38)</f>
+        <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38,N38,Q38)</f>
         <v/>
       </c>
       <c r="P38" s="1" t="inlineStr">
@@ -3518,7 +3830,7 @@
       <c r="M39" s="2" t="n"/>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2">
-        <f>SUM(B39:M39)</f>
+        <f>SUM(B39,C39,D39,E39,F39,G39,H39,I39,J39,K39,L39,M39,N39,Q39)</f>
         <v/>
       </c>
       <c r="P39" s="1" t="inlineStr">
@@ -3547,7 +3859,7 @@
       <c r="M40" s="2" t="n"/>
       <c r="N40" s="2" t="n"/>
       <c r="O40" s="2">
-        <f>SUM(B40:M40)</f>
+        <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,J40,K40,L40,M40,N40,Q40)</f>
         <v/>
       </c>
       <c r="P40" s="1" t="inlineStr">
@@ -3610,13 +3922,21 @@
         <f>SUM(M2:M40)</f>
         <v/>
       </c>
-      <c r="N41" s="2" t="n"/>
+      <c r="N41" s="2">
+        <f>SUM(N2:N40)</f>
+        <v/>
+      </c>
       <c r="O41" s="2">
-        <f>SUM(B41:M41)</f>
+        <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41,N41,Q41)</f>
         <v/>
       </c>
       <c r="P41" s="1" t="n"/>
-    </row>
+      <c r="Q41" s="3">
+        <f>SUM(Q2:Q40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -3814,7 +4134,9 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1"/>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/credit_monthly_summary.xlsx
+++ b/credit_monthly_summary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="2" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="CHASE #3444" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHASE #3444'!$A$2:$S$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CHASE DETIAL#3444'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CHASE DETIAL#3444'!$A$1:$P$44</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
@@ -125,8 +125,6 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -136,6 +134,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG17"/>
+  <dimension ref="A1:BD17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -526,9 +526,29 @@
     <col width="6" bestFit="1" customWidth="1" min="27" max="28"/>
     <col width="7.140625" bestFit="1" customWidth="1" min="29" max="29"/>
     <col width="6" bestFit="1" customWidth="1" min="30" max="30"/>
-    <col width="13.85546875" bestFit="1" customWidth="1" min="31" max="31"/>
-    <col width="9.28515625" bestFit="1" customWidth="1" min="32" max="32"/>
-    <col width="17.42578125" bestFit="1" customWidth="1" min="33" max="33"/>
+    <col width="6" bestFit="1" customWidth="1" min="31" max="31"/>
+    <col width="6" bestFit="1" customWidth="1" min="32" max="32"/>
+    <col width="6" bestFit="1" customWidth="1" min="33" max="33"/>
+    <col width="6" customWidth="1" min="34" max="34"/>
+    <col width="6" customWidth="1" min="35" max="35"/>
+    <col width="6" customWidth="1" min="36" max="36"/>
+    <col width="6" customWidth="1" min="37" max="37"/>
+    <col width="6" customWidth="1" min="38" max="38"/>
+    <col width="6" customWidth="1" min="39" max="39"/>
+    <col width="6" customWidth="1" min="40" max="40"/>
+    <col width="6" customWidth="1" min="41" max="41"/>
+    <col width="6" customWidth="1" min="42" max="42"/>
+    <col width="6" customWidth="1" min="43" max="43"/>
+    <col width="6" customWidth="1" min="44" max="44"/>
+    <col width="6" customWidth="1" min="45" max="45"/>
+    <col width="6" customWidth="1" min="46" max="46"/>
+    <col width="6" customWidth="1" min="47" max="47"/>
+    <col width="6" customWidth="1" min="48" max="48"/>
+    <col width="6" customWidth="1" min="49" max="49"/>
+    <col width="6" customWidth="1" min="50" max="50"/>
+    <col width="6" customWidth="1" min="51" max="51"/>
+    <col width="6" customWidth="1" min="52" max="52"/>
+    <col width="6" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -568,11 +588,42 @@
       <c r="AD1" s="11" t="n"/>
       <c r="AE1" s="11" t="n"/>
       <c r="AF1" s="11" t="n"/>
-      <c r="AG1" s="12" t="n"/>
+      <c r="AG1" s="11" t="n"/>
+      <c r="AH1" s="11" t="n"/>
+      <c r="AI1" s="11" t="n"/>
+      <c r="AJ1" s="11" t="n"/>
+      <c r="AK1" s="11" t="n"/>
+      <c r="AL1" s="11" t="n"/>
+      <c r="AM1" s="11" t="n"/>
+      <c r="AN1" s="11" t="n"/>
+      <c r="AO1" s="11" t="n"/>
+      <c r="AP1" s="11" t="n"/>
+      <c r="AQ1" s="11" t="n"/>
+      <c r="AR1" s="11" t="n"/>
+      <c r="AS1" s="11" t="n"/>
+      <c r="AT1" s="11" t="n"/>
+      <c r="AU1" s="11" t="n"/>
+      <c r="AV1" s="11" t="n"/>
+      <c r="AW1" s="11" t="n"/>
+      <c r="AX1" s="11" t="n"/>
+      <c r="AY1" s="11" t="n"/>
+      <c r="AZ1" s="11" t="n"/>
+      <c r="BA1" s="11" t="n"/>
+      <c r="BB1" s="11" t="n"/>
+      <c r="BC1" s="11" t="n"/>
+      <c r="BD1" s="12" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="10" t="n"/>
-      <c r="B2" s="10" t="n"/>
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Begin</t>
+        </is>
+      </c>
       <c r="C2" s="10" t="n"/>
       <c r="D2" s="10" t="n"/>
       <c r="E2" s="10" t="n"/>
@@ -603,143 +654,278 @@
       <c r="AD2" s="10" t="n"/>
       <c r="AE2" s="10" t="inlineStr">
         <is>
+          <t>NO1 SUSHI 88 CORKBBO ACH</t>
+        </is>
+      </c>
+      <c r="AF2" s="10" t="inlineStr">
+        <is>
+          <t>INTERNET TRF TO CLIENT-ADDED TRANSFER ACCOUNT</t>
+        </is>
+      </c>
+      <c r="AG2" s="10" t="inlineStr">
+        <is>
+          <t>BILL PAY:VEOLIA WATER NEW Y 200045 6BU1T6KR</t>
+        </is>
+      </c>
+      <c r="AH2" s="10" t="inlineStr">
+        <is>
+          <t>BILL PAY:ORANGE &amp; ROCKLAND 136130 6BQ1P6KR</t>
+        </is>
+      </c>
+      <c r="AI2" s="10" t="inlineStr">
+        <is>
+          <t>WITHDRAWAL BRANCH 0964 NEW YORK</t>
+        </is>
+      </c>
+      <c r="AJ2" s="10" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*NX6 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="AK2" s="10" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*9O5 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="AL2" s="10" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*SB8 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="AM2" s="10" t="inlineStr">
+        <is>
+          <t>NYS DTF PIT TAX PAYMNT</t>
+        </is>
+      </c>
+      <c r="AN2" s="10" t="inlineStr">
+        <is>
+          <t>KINDERCARE PORTLAND OR</t>
+        </is>
+      </c>
+      <c r="AO2" s="10" t="inlineStr">
+        <is>
+          <t>AMAZON PRIME*ZH8618UZ3 AMZN.COM/BILL WA</t>
+        </is>
+      </c>
+      <c r="AP2" s="10" t="inlineStr">
+        <is>
+          <t>IRS USATAXPYMT</t>
+        </is>
+      </c>
+      <c r="AQ2" s="10" t="inlineStr">
+        <is>
+          <t>CREDIT ONE BANK PAYMENT</t>
+        </is>
+      </c>
+      <c r="AR2" s="10" t="inlineStr">
+        <is>
+          <t>PROG CASUALTY INS PREM</t>
+        </is>
+      </c>
+      <c r="AS2" s="10" t="inlineStr">
+        <is>
+          <t>CITI CARD ONLINEPAYMENT</t>
+        </is>
+      </c>
+      <c r="AT2" s="10" t="inlineStr">
+        <is>
+          <t>AMAZON.COMSEATTLEWA US</t>
+        </is>
+      </c>
+      <c r="AU2" s="10" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*TN0 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="AV2" s="10" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*MZ5 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="AW2" s="10" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*GE2 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="AX2" s="10" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*V25 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="AY2" s="10" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*ZA2 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="AZ2" s="10" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*AU5 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="BA2" s="10" t="inlineStr">
+        <is>
+          <t>POS MAC AMAZON.COM*BQ9 SEATTLE WA</t>
+        </is>
+      </c>
+      <c r="BB2" s="10" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="AF2" s="10" t="inlineStr">
+      <c r="BC2" s="10" t="inlineStr">
         <is>
           <t>DEBIT</t>
         </is>
       </c>
-      <c r="AG2" s="10" t="inlineStr">
+      <c r="BD2" s="10" t="inlineStr">
         <is>
           <t>ENDING</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2">
-        <f>4000</f>
-        <v/>
-      </c>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2">
-        <f>300</f>
-        <v/>
-      </c>
-      <c r="J3" s="2">
-        <f>350</f>
-        <v/>
-      </c>
-      <c r="K3" s="2">
-        <f>385.77+740</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>1000+3200</f>
-        <v/>
-      </c>
-      <c r="M3" s="2">
-        <f>75.4</f>
-        <v/>
-      </c>
-      <c r="N3" s="2">
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
+      <c r="X3" s="2" t="n"/>
+      <c r="Y3" s="2" t="n"/>
+      <c r="Z3" s="2" t="n"/>
+      <c r="AA3" s="2" t="n"/>
+      <c r="AB3" s="2" t="n"/>
+      <c r="AC3" s="2" t="n"/>
+      <c r="AD3" s="2" t="n"/>
+      <c r="AE3" s="2">
+        <f>4000.00</f>
+        <v/>
+      </c>
+      <c r="AF3" s="2">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
+      <c r="AG3" s="2">
+        <f>300.00</f>
+        <v/>
+      </c>
+      <c r="AH3" s="2">
+        <f>350.00</f>
+        <v/>
+      </c>
+      <c r="AI3" s="2">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
+      <c r="AJ3" s="2">
+        <f>75.40</f>
+        <v/>
+      </c>
+      <c r="AK3" s="2">
         <f>26.57</f>
         <v/>
       </c>
-      <c r="O3" s="2">
+      <c r="AL3" s="2">
         <f>18.75</f>
         <v/>
       </c>
-      <c r="P3" s="2">
-        <f>200+200</f>
-        <v/>
-      </c>
-      <c r="Q3" s="2">
-        <f>490+120</f>
-        <v/>
-      </c>
-      <c r="R3" s="2">
+      <c r="AM3" s="2">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
+      <c r="AN3" s="2">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
+      <c r="AO3" s="2">
         <f>16.25</f>
         <v/>
       </c>
-      <c r="S3" s="2">
-        <f>800+800</f>
-        <v/>
-      </c>
-      <c r="T3" s="2">
+      <c r="AP3" s="2">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
+      <c r="AQ3" s="2">
         <f>817.29</f>
         <v/>
       </c>
-      <c r="U3" s="2">
+      <c r="AR3" s="2">
         <f>930.52</f>
         <v/>
       </c>
-      <c r="V3" s="2">
-        <f>975</f>
-        <v/>
-      </c>
-      <c r="W3" s="2">
+      <c r="AS3" s="2">
+        <f>975.00+364.75+1400.00</f>
+        <v/>
+      </c>
+      <c r="AT3" s="2">
         <f>117.76</f>
         <v/>
       </c>
-      <c r="X3" s="2">
+      <c r="AU3" s="2">
         <f>50.03</f>
         <v/>
       </c>
-      <c r="Y3" s="2">
+      <c r="AV3" s="2">
         <f>71.79</f>
         <v/>
       </c>
-      <c r="Z3" s="2">
+      <c r="AW3" s="2">
         <f>152.14</f>
         <v/>
       </c>
-      <c r="AA3" s="2">
-        <f>20.8</f>
-        <v/>
-      </c>
-      <c r="AB3" s="2">
+      <c r="AX3" s="2">
+        <f>20.80</f>
+        <v/>
+      </c>
+      <c r="AY3" s="2">
         <f>40.33</f>
         <v/>
       </c>
-      <c r="AC3" s="2">
+      <c r="AZ3" s="2">
         <f>343.93</f>
         <v/>
       </c>
-      <c r="AD3" s="2">
+      <c r="BA3" s="2">
         <f>17.59</f>
         <v/>
       </c>
-      <c r="AE3" s="2">
-        <f>SUM(C3:AD3)</f>
-        <v/>
-      </c>
-      <c r="AF3" s="2">
-        <f>'CHASE DETIAL#3444'!B42</f>
-        <v/>
-      </c>
-      <c r="AG3" s="2">
-        <f>B3+AE3-AF3</f>
+      <c r="BB3" s="2">
+        <f>SUM(C3:BA3)</f>
+        <v/>
+      </c>
+      <c r="BC3" s="2" t="n"/>
+      <c r="BD3" s="2">
+        <f>B3+BB3-BC3</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B4" s="2">
-        <f>S3</f>
+        <f>AG3</f>
         <v/>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -770,22 +956,45 @@
       <c r="AB4" s="2" t="n"/>
       <c r="AC4" s="2" t="n"/>
       <c r="AD4" s="2" t="n"/>
-      <c r="AE4" s="2">
-        <f>SUM(C4:AD4)</f>
-        <v/>
-      </c>
+      <c r="AE4" s="2" t="n"/>
       <c r="AF4" s="2" t="n"/>
-      <c r="AG4" s="2">
-        <f>B4+AE4-AF4</f>
+      <c r="AG4" s="2" t="n"/>
+      <c r="AH4" s="2" t="n"/>
+      <c r="AI4" s="2" t="n"/>
+      <c r="AJ4" s="2" t="n"/>
+      <c r="AK4" s="2" t="n"/>
+      <c r="AL4" s="2" t="n"/>
+      <c r="AM4" s="2" t="n"/>
+      <c r="AN4" s="2" t="n"/>
+      <c r="AO4" s="2" t="n"/>
+      <c r="AP4" s="2" t="n"/>
+      <c r="AQ4" s="2" t="n"/>
+      <c r="AR4" s="2" t="n"/>
+      <c r="AS4" s="2" t="n"/>
+      <c r="AT4" s="2" t="n"/>
+      <c r="AU4" s="2" t="n"/>
+      <c r="AV4" s="2" t="n"/>
+      <c r="AW4" s="2" t="n"/>
+      <c r="AX4" s="2" t="n"/>
+      <c r="AY4" s="2" t="n"/>
+      <c r="AZ4" s="2" t="n"/>
+      <c r="BA4" s="2" t="n"/>
+      <c r="BB4" s="2">
+        <f>SUM(C4:BA4)</f>
+        <v/>
+      </c>
+      <c r="BC4" s="2" t="n"/>
+      <c r="BD4" s="2">
+        <f>B4+BB4-BC4</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B5" s="2">
-        <f>S4</f>
+        <f>AG4</f>
         <v/>
       </c>
       <c r="C5" s="2" t="n"/>
@@ -817,21 +1026,113 @@
       <c r="AC5" s="2" t="n"/>
       <c r="AD5" s="2" t="n"/>
       <c r="AE5" s="2">
-        <f>SUM(C5:AD5)</f>
-        <v/>
-      </c>
-      <c r="AF5" s="2" t="n"/>
+        <f>4000.00</f>
+        <v/>
+      </c>
+      <c r="AF5" s="2">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
       <c r="AG5" s="2">
-        <f>B5+AE5-AF5</f>
+        <f>300.00</f>
+        <v/>
+      </c>
+      <c r="AH5" s="2">
+        <f>350.00</f>
+        <v/>
+      </c>
+      <c r="AI5" s="2">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="2">
+        <f>75.40</f>
+        <v/>
+      </c>
+      <c r="AK5" s="2">
+        <f>26.57</f>
+        <v/>
+      </c>
+      <c r="AL5" s="2">
+        <f>18.75</f>
+        <v/>
+      </c>
+      <c r="AM5" s="2">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
+      <c r="AN5" s="2">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
+      <c r="AO5" s="2">
+        <f>16.25</f>
+        <v/>
+      </c>
+      <c r="AP5" s="2">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
+      <c r="AQ5" s="2">
+        <f>817.29</f>
+        <v/>
+      </c>
+      <c r="AR5" s="2">
+        <f>930.52</f>
+        <v/>
+      </c>
+      <c r="AS5" s="2">
+        <f>975.00+364.75+1400.00</f>
+        <v/>
+      </c>
+      <c r="AT5" s="2">
+        <f>117.76</f>
+        <v/>
+      </c>
+      <c r="AU5" s="2">
+        <f>50.03</f>
+        <v/>
+      </c>
+      <c r="AV5" s="2">
+        <f>71.79</f>
+        <v/>
+      </c>
+      <c r="AW5" s="2">
+        <f>152.14</f>
+        <v/>
+      </c>
+      <c r="AX5" s="2">
+        <f>20.80</f>
+        <v/>
+      </c>
+      <c r="AY5" s="2">
+        <f>40.33</f>
+        <v/>
+      </c>
+      <c r="AZ5" s="2">
+        <f>343.93</f>
+        <v/>
+      </c>
+      <c r="BA5" s="2">
+        <f>17.59</f>
+        <v/>
+      </c>
+      <c r="BB5" s="2">
+        <f>SUM(C5:BA5)</f>
+        <v/>
+      </c>
+      <c r="BC5" s="2" t="n"/>
+      <c r="BD5" s="2">
+        <f>B5+BB5-BC5</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B6" s="2">
-        <f>S5</f>
+        <f>AG5</f>
         <v/>
       </c>
       <c r="C6" s="2" t="n"/>
@@ -862,22 +1163,45 @@
       <c r="AB6" s="2" t="n"/>
       <c r="AC6" s="2" t="n"/>
       <c r="AD6" s="2" t="n"/>
-      <c r="AE6" s="2">
-        <f>SUM(C6:AD6)</f>
-        <v/>
-      </c>
+      <c r="AE6" s="2" t="n"/>
       <c r="AF6" s="2" t="n"/>
-      <c r="AG6" s="2">
-        <f>B6+AE6-AF6</f>
+      <c r="AG6" s="2" t="n"/>
+      <c r="AH6" s="2" t="n"/>
+      <c r="AI6" s="2" t="n"/>
+      <c r="AJ6" s="2" t="n"/>
+      <c r="AK6" s="2" t="n"/>
+      <c r="AL6" s="2" t="n"/>
+      <c r="AM6" s="2" t="n"/>
+      <c r="AN6" s="2" t="n"/>
+      <c r="AO6" s="2" t="n"/>
+      <c r="AP6" s="2" t="n"/>
+      <c r="AQ6" s="2" t="n"/>
+      <c r="AR6" s="2" t="n"/>
+      <c r="AS6" s="2" t="n"/>
+      <c r="AT6" s="2" t="n"/>
+      <c r="AU6" s="2" t="n"/>
+      <c r="AV6" s="2" t="n"/>
+      <c r="AW6" s="2" t="n"/>
+      <c r="AX6" s="2" t="n"/>
+      <c r="AY6" s="2" t="n"/>
+      <c r="AZ6" s="2" t="n"/>
+      <c r="BA6" s="2" t="n"/>
+      <c r="BB6" s="2">
+        <f>SUM(C6:BA6)</f>
+        <v/>
+      </c>
+      <c r="BC6" s="2" t="n"/>
+      <c r="BD6" s="2">
+        <f>B6+BB6-BC6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B7" s="2">
-        <f>S6</f>
+        <f>AG6</f>
         <v/>
       </c>
       <c r="C7" s="2" t="n"/>
@@ -908,22 +1232,45 @@
       <c r="AB7" s="2" t="n"/>
       <c r="AC7" s="2" t="n"/>
       <c r="AD7" s="2" t="n"/>
-      <c r="AE7" s="2">
-        <f>SUM(C7:AD7)</f>
-        <v/>
-      </c>
+      <c r="AE7" s="2" t="n"/>
       <c r="AF7" s="2" t="n"/>
-      <c r="AG7" s="2">
-        <f>B7+AE7-AF7</f>
+      <c r="AG7" s="2" t="n"/>
+      <c r="AH7" s="2" t="n"/>
+      <c r="AI7" s="2" t="n"/>
+      <c r="AJ7" s="2" t="n"/>
+      <c r="AK7" s="2" t="n"/>
+      <c r="AL7" s="2" t="n"/>
+      <c r="AM7" s="2" t="n"/>
+      <c r="AN7" s="2" t="n"/>
+      <c r="AO7" s="2" t="n"/>
+      <c r="AP7" s="2" t="n"/>
+      <c r="AQ7" s="2" t="n"/>
+      <c r="AR7" s="2" t="n"/>
+      <c r="AS7" s="2" t="n"/>
+      <c r="AT7" s="2" t="n"/>
+      <c r="AU7" s="2" t="n"/>
+      <c r="AV7" s="2" t="n"/>
+      <c r="AW7" s="2" t="n"/>
+      <c r="AX7" s="2" t="n"/>
+      <c r="AY7" s="2" t="n"/>
+      <c r="AZ7" s="2" t="n"/>
+      <c r="BA7" s="2" t="n"/>
+      <c r="BB7" s="2">
+        <f>SUM(C7:BA7)</f>
+        <v/>
+      </c>
+      <c r="BC7" s="2" t="n"/>
+      <c r="BD7" s="2">
+        <f>B7+BB7-BC7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B8" s="2">
-        <f>S7</f>
+        <f>AG7</f>
         <v/>
       </c>
       <c r="C8" s="2" t="n"/>
@@ -955,21 +1302,113 @@
       <c r="AC8" s="2" t="n"/>
       <c r="AD8" s="2" t="n"/>
       <c r="AE8" s="2">
-        <f>SUM(C8:AD8)</f>
-        <v/>
-      </c>
-      <c r="AF8" s="2" t="n"/>
+        <f>4000.00</f>
+        <v/>
+      </c>
+      <c r="AF8" s="2">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
       <c r="AG8" s="2">
-        <f>B8+AE8-AF8</f>
+        <f>300.00</f>
+        <v/>
+      </c>
+      <c r="AH8" s="2">
+        <f>350.00</f>
+        <v/>
+      </c>
+      <c r="AI8" s="2">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="2">
+        <f>75.40</f>
+        <v/>
+      </c>
+      <c r="AK8" s="2">
+        <f>26.57</f>
+        <v/>
+      </c>
+      <c r="AL8" s="2">
+        <f>18.75</f>
+        <v/>
+      </c>
+      <c r="AM8" s="2">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
+      <c r="AN8" s="2">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
+      <c r="AO8" s="2">
+        <f>16.25</f>
+        <v/>
+      </c>
+      <c r="AP8" s="2">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
+      <c r="AQ8" s="2">
+        <f>817.29</f>
+        <v/>
+      </c>
+      <c r="AR8" s="2">
+        <f>930.52</f>
+        <v/>
+      </c>
+      <c r="AS8" s="2">
+        <f>975.00+364.75+1400.00</f>
+        <v/>
+      </c>
+      <c r="AT8" s="2">
+        <f>117.76</f>
+        <v/>
+      </c>
+      <c r="AU8" s="2">
+        <f>50.03</f>
+        <v/>
+      </c>
+      <c r="AV8" s="2">
+        <f>71.79</f>
+        <v/>
+      </c>
+      <c r="AW8" s="2">
+        <f>152.14</f>
+        <v/>
+      </c>
+      <c r="AX8" s="2">
+        <f>20.80</f>
+        <v/>
+      </c>
+      <c r="AY8" s="2">
+        <f>40.33</f>
+        <v/>
+      </c>
+      <c r="AZ8" s="2">
+        <f>343.93</f>
+        <v/>
+      </c>
+      <c r="BA8" s="2">
+        <f>17.59</f>
+        <v/>
+      </c>
+      <c r="BB8" s="2">
+        <f>SUM(C8:BA8)</f>
+        <v/>
+      </c>
+      <c r="BC8" s="2" t="n"/>
+      <c r="BD8" s="2">
+        <f>B8+BB8-BC8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B9" s="2">
-        <f>S8</f>
+        <f>AG8</f>
         <v/>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -1000,22 +1439,45 @@
       <c r="AB9" s="2" t="n"/>
       <c r="AC9" s="2" t="n"/>
       <c r="AD9" s="2" t="n"/>
-      <c r="AE9" s="2">
-        <f>SUM(C9:AD9)</f>
-        <v/>
-      </c>
+      <c r="AE9" s="2" t="n"/>
       <c r="AF9" s="2" t="n"/>
-      <c r="AG9" s="2">
-        <f>B9+AE9-AF9</f>
+      <c r="AG9" s="2" t="n"/>
+      <c r="AH9" s="2" t="n"/>
+      <c r="AI9" s="2" t="n"/>
+      <c r="AJ9" s="2" t="n"/>
+      <c r="AK9" s="2" t="n"/>
+      <c r="AL9" s="2" t="n"/>
+      <c r="AM9" s="2" t="n"/>
+      <c r="AN9" s="2" t="n"/>
+      <c r="AO9" s="2" t="n"/>
+      <c r="AP9" s="2" t="n"/>
+      <c r="AQ9" s="2" t="n"/>
+      <c r="AR9" s="2" t="n"/>
+      <c r="AS9" s="2" t="n"/>
+      <c r="AT9" s="2" t="n"/>
+      <c r="AU9" s="2" t="n"/>
+      <c r="AV9" s="2" t="n"/>
+      <c r="AW9" s="2" t="n"/>
+      <c r="AX9" s="2" t="n"/>
+      <c r="AY9" s="2" t="n"/>
+      <c r="AZ9" s="2" t="n"/>
+      <c r="BA9" s="2" t="n"/>
+      <c r="BB9" s="2">
+        <f>SUM(C9:BA9)</f>
+        <v/>
+      </c>
+      <c r="BC9" s="2" t="n"/>
+      <c r="BD9" s="2">
+        <f>B9+BB9-BC9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B10" s="2">
-        <f>S9</f>
+        <f>AG9</f>
         <v/>
       </c>
       <c r="C10" s="2" t="n"/>
@@ -1046,22 +1508,45 @@
       <c r="AB10" s="2" t="n"/>
       <c r="AC10" s="2" t="n"/>
       <c r="AD10" s="2" t="n"/>
-      <c r="AE10" s="2">
-        <f>SUM(C10:AD10)</f>
-        <v/>
-      </c>
+      <c r="AE10" s="2" t="n"/>
       <c r="AF10" s="2" t="n"/>
-      <c r="AG10" s="2">
-        <f>B10+AE10-AF10</f>
+      <c r="AG10" s="2" t="n"/>
+      <c r="AH10" s="2" t="n"/>
+      <c r="AI10" s="2" t="n"/>
+      <c r="AJ10" s="2" t="n"/>
+      <c r="AK10" s="2" t="n"/>
+      <c r="AL10" s="2" t="n"/>
+      <c r="AM10" s="2" t="n"/>
+      <c r="AN10" s="2" t="n"/>
+      <c r="AO10" s="2" t="n"/>
+      <c r="AP10" s="2" t="n"/>
+      <c r="AQ10" s="2" t="n"/>
+      <c r="AR10" s="2" t="n"/>
+      <c r="AS10" s="2" t="n"/>
+      <c r="AT10" s="2" t="n"/>
+      <c r="AU10" s="2" t="n"/>
+      <c r="AV10" s="2" t="n"/>
+      <c r="AW10" s="2" t="n"/>
+      <c r="AX10" s="2" t="n"/>
+      <c r="AY10" s="2" t="n"/>
+      <c r="AZ10" s="2" t="n"/>
+      <c r="BA10" s="2" t="n"/>
+      <c r="BB10" s="2">
+        <f>SUM(C10:BA10)</f>
+        <v/>
+      </c>
+      <c r="BC10" s="2" t="n"/>
+      <c r="BD10" s="2">
+        <f>B10+BB10-BC10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B11" s="2">
-        <f>S10</f>
+        <f>AG10</f>
         <v/>
       </c>
       <c r="C11" s="2" t="n"/>
@@ -1092,22 +1577,45 @@
       <c r="AB11" s="2" t="n"/>
       <c r="AC11" s="2" t="n"/>
       <c r="AD11" s="2" t="n"/>
-      <c r="AE11" s="2">
-        <f>SUM(C11:AD11)</f>
-        <v/>
-      </c>
+      <c r="AE11" s="2" t="n"/>
       <c r="AF11" s="2" t="n"/>
-      <c r="AG11" s="2">
-        <f>B11+AE11-AF11</f>
+      <c r="AG11" s="2" t="n"/>
+      <c r="AH11" s="2" t="n"/>
+      <c r="AI11" s="2" t="n"/>
+      <c r="AJ11" s="2" t="n"/>
+      <c r="AK11" s="2" t="n"/>
+      <c r="AL11" s="2" t="n"/>
+      <c r="AM11" s="2" t="n"/>
+      <c r="AN11" s="2" t="n"/>
+      <c r="AO11" s="2" t="n"/>
+      <c r="AP11" s="2" t="n"/>
+      <c r="AQ11" s="2" t="n"/>
+      <c r="AR11" s="2" t="n"/>
+      <c r="AS11" s="2" t="n"/>
+      <c r="AT11" s="2" t="n"/>
+      <c r="AU11" s="2" t="n"/>
+      <c r="AV11" s="2" t="n"/>
+      <c r="AW11" s="2" t="n"/>
+      <c r="AX11" s="2" t="n"/>
+      <c r="AY11" s="2" t="n"/>
+      <c r="AZ11" s="2" t="n"/>
+      <c r="BA11" s="2" t="n"/>
+      <c r="BB11" s="2">
+        <f>SUM(C11:BA11)</f>
+        <v/>
+      </c>
+      <c r="BC11" s="2" t="n"/>
+      <c r="BD11" s="2">
+        <f>B11+BB11-BC11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B12" s="2">
-        <f>S11</f>
+        <f>AG11</f>
         <v/>
       </c>
       <c r="C12" s="2" t="n"/>
@@ -1138,22 +1646,45 @@
       <c r="AB12" s="2" t="n"/>
       <c r="AC12" s="2" t="n"/>
       <c r="AD12" s="2" t="n"/>
-      <c r="AE12" s="2">
-        <f>SUM(C12:AD12)</f>
-        <v/>
-      </c>
+      <c r="AE12" s="2" t="n"/>
       <c r="AF12" s="2" t="n"/>
-      <c r="AG12" s="2">
-        <f>B12+AE12-AF12</f>
+      <c r="AG12" s="2" t="n"/>
+      <c r="AH12" s="2" t="n"/>
+      <c r="AI12" s="2" t="n"/>
+      <c r="AJ12" s="2" t="n"/>
+      <c r="AK12" s="2" t="n"/>
+      <c r="AL12" s="2" t="n"/>
+      <c r="AM12" s="2" t="n"/>
+      <c r="AN12" s="2" t="n"/>
+      <c r="AO12" s="2" t="n"/>
+      <c r="AP12" s="2" t="n"/>
+      <c r="AQ12" s="2" t="n"/>
+      <c r="AR12" s="2" t="n"/>
+      <c r="AS12" s="2" t="n"/>
+      <c r="AT12" s="2" t="n"/>
+      <c r="AU12" s="2" t="n"/>
+      <c r="AV12" s="2" t="n"/>
+      <c r="AW12" s="2" t="n"/>
+      <c r="AX12" s="2" t="n"/>
+      <c r="AY12" s="2" t="n"/>
+      <c r="AZ12" s="2" t="n"/>
+      <c r="BA12" s="2" t="n"/>
+      <c r="BB12" s="2">
+        <f>SUM(C12:BA12)</f>
+        <v/>
+      </c>
+      <c r="BC12" s="2" t="n"/>
+      <c r="BD12" s="2">
+        <f>B12+BB12-BC12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B13" s="2">
-        <f>S12</f>
+        <f>AG12</f>
         <v/>
       </c>
       <c r="C13" s="2" t="n"/>
@@ -1184,22 +1715,45 @@
       <c r="AB13" s="2" t="n"/>
       <c r="AC13" s="2" t="n"/>
       <c r="AD13" s="2" t="n"/>
-      <c r="AE13" s="2">
-        <f>SUM(C13:AD13)</f>
-        <v/>
-      </c>
+      <c r="AE13" s="2" t="n"/>
       <c r="AF13" s="2" t="n"/>
-      <c r="AG13" s="2">
-        <f>B13+AE13-AF13</f>
+      <c r="AG13" s="2" t="n"/>
+      <c r="AH13" s="2" t="n"/>
+      <c r="AI13" s="2" t="n"/>
+      <c r="AJ13" s="2" t="n"/>
+      <c r="AK13" s="2" t="n"/>
+      <c r="AL13" s="2" t="n"/>
+      <c r="AM13" s="2" t="n"/>
+      <c r="AN13" s="2" t="n"/>
+      <c r="AO13" s="2" t="n"/>
+      <c r="AP13" s="2" t="n"/>
+      <c r="AQ13" s="2" t="n"/>
+      <c r="AR13" s="2" t="n"/>
+      <c r="AS13" s="2" t="n"/>
+      <c r="AT13" s="2" t="n"/>
+      <c r="AU13" s="2" t="n"/>
+      <c r="AV13" s="2" t="n"/>
+      <c r="AW13" s="2" t="n"/>
+      <c r="AX13" s="2" t="n"/>
+      <c r="AY13" s="2" t="n"/>
+      <c r="AZ13" s="2" t="n"/>
+      <c r="BA13" s="2" t="n"/>
+      <c r="BB13" s="2">
+        <f>SUM(C13:BA13)</f>
+        <v/>
+      </c>
+      <c r="BC13" s="2" t="n"/>
+      <c r="BD13" s="2">
+        <f>B13+BB13-BC13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B14" s="2">
-        <f>S13</f>
+        <f>AG13</f>
         <v/>
       </c>
       <c r="C14" s="2" t="n"/>
@@ -1230,13 +1784,36 @@
       <c r="AB14" s="2" t="n"/>
       <c r="AC14" s="2" t="n"/>
       <c r="AD14" s="2" t="n"/>
-      <c r="AE14" s="2">
-        <f>SUM(C14:AD14)</f>
-        <v/>
-      </c>
+      <c r="AE14" s="2" t="n"/>
       <c r="AF14" s="2" t="n"/>
-      <c r="AG14" s="2">
-        <f>B14+AE14-AF14</f>
+      <c r="AG14" s="2" t="n"/>
+      <c r="AH14" s="2" t="n"/>
+      <c r="AI14" s="2" t="n"/>
+      <c r="AJ14" s="2" t="n"/>
+      <c r="AK14" s="2" t="n"/>
+      <c r="AL14" s="2" t="n"/>
+      <c r="AM14" s="2" t="n"/>
+      <c r="AN14" s="2" t="n"/>
+      <c r="AO14" s="2" t="n"/>
+      <c r="AP14" s="2" t="n"/>
+      <c r="AQ14" s="2" t="n"/>
+      <c r="AR14" s="2" t="n"/>
+      <c r="AS14" s="2" t="n"/>
+      <c r="AT14" s="2" t="n"/>
+      <c r="AU14" s="2" t="n"/>
+      <c r="AV14" s="2" t="n"/>
+      <c r="AW14" s="2" t="n"/>
+      <c r="AX14" s="2" t="n"/>
+      <c r="AY14" s="2" t="n"/>
+      <c r="AZ14" s="2" t="n"/>
+      <c r="BA14" s="2" t="n"/>
+      <c r="BB14" s="2">
+        <f>SUM(C14:BA14)</f>
+        <v/>
+      </c>
+      <c r="BC14" s="2" t="n"/>
+      <c r="BD14" s="2">
+        <f>B14+BB14-BC14</f>
         <v/>
       </c>
     </row>
@@ -1368,11 +1945,102 @@
         <v/>
       </c>
       <c r="AG15" s="2">
-        <f>AG14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16"/>
+        <f>SUM(AG3:AG14)</f>
+        <v/>
+      </c>
+      <c r="AH15" s="2">
+        <f>SUM(AH3:AH14)</f>
+        <v/>
+      </c>
+      <c r="AI15" s="2">
+        <f>SUM(AI3:AI14)</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="2">
+        <f>SUM(AJ3:AJ14)</f>
+        <v/>
+      </c>
+      <c r="AK15" s="2">
+        <f>SUM(AK3:AK14)</f>
+        <v/>
+      </c>
+      <c r="AL15" s="2">
+        <f>SUM(AL3:AL14)</f>
+        <v/>
+      </c>
+      <c r="AM15" s="2">
+        <f>SUM(AM3:AM14)</f>
+        <v/>
+      </c>
+      <c r="AN15" s="2">
+        <f>SUM(AN3:AN14)</f>
+        <v/>
+      </c>
+      <c r="AO15" s="2">
+        <f>SUM(AO3:AO14)</f>
+        <v/>
+      </c>
+      <c r="AP15" s="2">
+        <f>SUM(AP3:AP14)</f>
+        <v/>
+      </c>
+      <c r="AQ15" s="2">
+        <f>SUM(AQ3:AQ14)</f>
+        <v/>
+      </c>
+      <c r="AR15" s="2">
+        <f>SUM(AR3:AR14)</f>
+        <v/>
+      </c>
+      <c r="AS15" s="2">
+        <f>SUM(AS3:AS14)</f>
+        <v/>
+      </c>
+      <c r="AT15" s="2">
+        <f>SUM(AT3:AT14)</f>
+        <v/>
+      </c>
+      <c r="AU15" s="2">
+        <f>SUM(AU3:AU14)</f>
+        <v/>
+      </c>
+      <c r="AV15" s="2">
+        <f>SUM(AV3:AV14)</f>
+        <v/>
+      </c>
+      <c r="AW15" s="2">
+        <f>SUM(AW3:AW14)</f>
+        <v/>
+      </c>
+      <c r="AX15" s="2">
+        <f>SUM(AX3:AX14)</f>
+        <v/>
+      </c>
+      <c r="AY15" s="2">
+        <f>SUM(AY3:AY14)</f>
+        <v/>
+      </c>
+      <c r="AZ15" s="2">
+        <f>SUM(AZ3:AZ14)</f>
+        <v/>
+      </c>
+      <c r="BA15" s="2">
+        <f>SUM(BA3:BA14)</f>
+        <v/>
+      </c>
+      <c r="BB15" s="2">
+        <f>SUM(BB3:BB14)</f>
+        <v/>
+      </c>
+      <c r="BC15" s="2">
+        <f>SUM(BC3:BC14)</f>
+        <v/>
+      </c>
+      <c r="BD15" s="2">
+        <f>BD14</f>
+        <v/>
+      </c>
+    </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -1395,13 +2063,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="2" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1410,60 +2078,61 @@
           <t>Merchant</t>
         </is>
       </c>
-      <c r="B1" s="8">
+      <c r="B1" s="6">
         <f>'CHASE #3444'!A3</f>
         <v/>
       </c>
-      <c r="C1" s="8">
+      <c r="C1" s="6">
         <f>'CHASE #3444'!A4</f>
         <v/>
       </c>
-      <c r="D1" s="8">
+      <c r="D1" s="6">
         <f>'CHASE #3444'!A5</f>
         <v/>
       </c>
-      <c r="E1" s="8">
+      <c r="E1" s="6">
         <f>'CHASE #3444'!A6</f>
         <v/>
       </c>
-      <c r="F1" s="8">
+      <c r="F1" s="6">
         <f>'CHASE #3444'!A7</f>
         <v/>
       </c>
-      <c r="G1" s="8">
+      <c r="G1" s="6">
         <f>'CHASE #3444'!A8</f>
         <v/>
       </c>
-      <c r="H1" s="8">
+      <c r="H1" s="6">
         <f>'CHASE #3444'!A9</f>
         <v/>
       </c>
-      <c r="I1" s="8">
+      <c r="I1" s="6">
         <f>'CHASE #3444'!A10</f>
         <v/>
       </c>
-      <c r="J1" s="8">
+      <c r="J1" s="6" t="n"/>
+      <c r="K1" s="6">
         <f>'CHASE #3444'!A11</f>
         <v/>
       </c>
-      <c r="K1" s="8">
+      <c r="L1" s="6">
         <f>'CHASE #3444'!A12</f>
         <v/>
       </c>
-      <c r="L1" s="8">
+      <c r="M1" s="6">
         <f>'CHASE #3444'!A13</f>
         <v/>
       </c>
-      <c r="M1" s="8">
+      <c r="N1" s="6">
         <f>'CHASE #3444'!A14</f>
         <v/>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
@@ -1487,11 +2156,12 @@
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2">
-        <f>SUM(B2,C2,D2,E2,F2,G2,H2,I2,J2,K2,L2,M2)</f>
-        <v/>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2">
+        <f>SUM(B2,C2,D2,E2,F2,G2,H2,I2,J2,K2,L2,M2,N2)</f>
+        <v/>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -1505,21 +2175,31 @@
       </c>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
+      <c r="D3" s="2">
+        <f>16.25+16.25</f>
+        <v/>
+      </c>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
+      <c r="H3" s="2">
+        <f>16.25</f>
+        <v/>
+      </c>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2">
-        <f>SUM(B3,C3,D3,E3,F3,G3,H3,I3,J3,K3,L3,M3)</f>
-        <v/>
-      </c>
-      <c r="O3" s="1" t="inlineStr">
+        <f>16.25</f>
+        <v/>
+      </c>
+      <c r="O3" s="2">
+        <f>SUM(B3,C3,D3,E3,F3,G3,H3,I3,J3,K3,L3,M3,N3)</f>
+        <v/>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -1543,11 +2223,12 @@
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2">
-        <f>SUM(B4,C4,D4,E4,F4,G4,H4,I4,J4,K4,L4,M4)</f>
-        <v/>
-      </c>
-      <c r="O4" s="1" t="inlineStr">
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2">
+        <f>SUM(B4,C4,D4,E4,F4,G4,H4,I4,J4,K4,L4,M4,N4)</f>
+        <v/>
+      </c>
+      <c r="P4" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -1561,21 +2242,31 @@
       </c>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
+      <c r="D5" s="2">
+        <f>117.76+117.76</f>
+        <v/>
+      </c>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="H5" s="2">
+        <f>117.76</f>
+        <v/>
+      </c>
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2">
-        <f>SUM(B5,C5,D5,E5,F5,G5,H5,I5,J5,K5,L5,M5)</f>
-        <v/>
-      </c>
-      <c r="O5" s="1" t="inlineStr">
+        <f>117.76</f>
+        <v/>
+      </c>
+      <c r="O5" s="2">
+        <f>SUM(B5,C5,D5,E5,F5,G5,H5,I5,J5,K5,L5,M5,N5)</f>
+        <v/>
+      </c>
+      <c r="P5" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -1599,11 +2290,12 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2">
-        <f>SUM(B6,C6,D6,E6,F6,G6,H6,I6,J6,K6,L6,M6)</f>
-        <v/>
-      </c>
-      <c r="O6" s="1" t="inlineStr">
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2">
+        <f>SUM(B6,C6,D6,E6,F6,G6,H6,I6,J6,K6,L6,M6,N6)</f>
+        <v/>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -1627,11 +2319,12 @@
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
-      <c r="N7" s="2">
-        <f>SUM(B7,C7,D7,E7,F7,G7,H7,I7,J7,K7,L7,M7)</f>
-        <v/>
-      </c>
-      <c r="O7" s="1" t="inlineStr">
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2">
+        <f>SUM(B7,C7,D7,E7,F7,G7,H7,I7,J7,K7,L7,M7,N7)</f>
+        <v/>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -1655,22 +2348,19 @@
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2">
-        <f>SUM(B8,C8,D8,E8,F8,G8,H8,I8,J8,K8,L8,M8)</f>
-        <v/>
-      </c>
-      <c r="O8" s="1" t="inlineStr">
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2">
+        <f>SUM(B8,C8,D8,E8,F8,G8,H8,I8,J8,K8,L8,M8,N8)</f>
+        <v/>
+      </c>
+      <c r="P8" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
-        </is>
-      </c>
+      <c r="A9" s="1" t="n"/>
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
@@ -1683,22 +2373,15 @@
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2">
-        <f>SUM(B9,C9,D9,E9,F9,G9,H9,I9,J9,K9,L9,M9)</f>
-        <v/>
-      </c>
-      <c r="O9" s="1" t="inlineStr">
-        <is>
-          <t>OFFICE EXPENSE</t>
-        </is>
-      </c>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2">
+        <f>SUM(B9,C9,D9,E9,F9,G9,H9,I9,J9,K9,L9,M9,N9)</f>
+        <v/>
+      </c>
+      <c r="P9" s="1" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
-        </is>
-      </c>
+      <c r="A10" s="1" t="n"/>
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
@@ -1711,22 +2394,15 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2">
-        <f>SUM(B10,C10,D10,E10,F10,G10,H10,I10,J10,K10,L10,M10)</f>
-        <v/>
-      </c>
-      <c r="O10" s="1" t="inlineStr">
-        <is>
-          <t>OFFICE EXPENSE</t>
-        </is>
-      </c>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2">
+        <f>SUM(B10,C10,D10,E10,F10,G10,H10,I10,J10,K10,L10,M10,N10)</f>
+        <v/>
+      </c>
+      <c r="P10" s="1" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Bill Pay:Orange &amp; Rockland 879293 5Bq1P6Kr</t>
-        </is>
-      </c>
+      <c r="A11" s="1" t="n"/>
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
@@ -1739,20 +2415,17 @@
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2">
-        <f>SUM(B11,C11,D11,E11,F11,G11,H11,I11,J11,K11,L11,M11)</f>
-        <v/>
-      </c>
-      <c r="O11" s="1" t="inlineStr">
-        <is>
-          <t>OFFICE EXPENSE</t>
-        </is>
-      </c>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2">
+        <f>SUM(B11,C11,D11,E11,F11,G11,H11,I11,J11,K11,L11,M11,N11)</f>
+        <v/>
+      </c>
+      <c r="P11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
+          <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -1767,11 +2440,12 @@
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2">
-        <f>SUM(B12,C12,D12,E12,F12,G12,H12,I12,J12,K12,L12,M12)</f>
-        <v/>
-      </c>
-      <c r="O12" s="1" t="inlineStr">
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2">
+        <f>SUM(B12,C12,D12,E12,F12,G12,H12,I12,J12,K12,L12,M12,N12)</f>
+        <v/>
+      </c>
+      <c r="P12" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -1780,26 +2454,36 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Bill Pay:Veolia Water New Y 200054 Hbu1T6Kr</t>
+          <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
+      <c r="D13" s="2">
+        <f>350.00+350.00</f>
+        <v/>
+      </c>
       <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
+      <c r="H13" s="2">
+        <f>350.00</f>
+        <v/>
+      </c>
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n"/>
       <c r="N13" s="2">
-        <f>SUM(B13,C13,D13,E13,F13,G13,H13,I13,J13,K13,L13,M13)</f>
-        <v/>
-      </c>
-      <c r="O13" s="1" t="inlineStr">
+        <f>350.00</f>
+        <v/>
+      </c>
+      <c r="O13" s="2">
+        <f>SUM(B13,C13,D13,E13,F13,G13,H13,I13,J13,K13,L13,M13,N13)</f>
+        <v/>
+      </c>
+      <c r="P13" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -1808,7 +2492,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Citi Card Onlinepayment</t>
+          <t>Bill Pay:Orange &amp; Rockland 879293 5Bq1P6Kr</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -1823,11 +2507,12 @@
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2">
-        <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,J14,K14,L14,M14)</f>
-        <v/>
-      </c>
-      <c r="O14" s="1" t="inlineStr">
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2">
+        <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,J14,K14,L14,M14,N14)</f>
+        <v/>
+      </c>
+      <c r="P14" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -1836,26 +2521,36 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Credit One Bank Payment</t>
+          <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
+      <c r="D15" s="2">
+        <f>300.00+300.00</f>
+        <v/>
+      </c>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
+      <c r="H15" s="2">
+        <f>300.00</f>
+        <v/>
+      </c>
       <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
       <c r="N15" s="2">
-        <f>SUM(B15,C15,D15,E15,F15,G15,H15,I15,J15,K15,L15,M15)</f>
-        <v/>
-      </c>
-      <c r="O15" s="1" t="inlineStr">
+        <f>300.00</f>
+        <v/>
+      </c>
+      <c r="O15" s="2">
+        <f>SUM(B15,C15,D15,E15,F15,G15,H15,I15,J15,K15,L15,M15,N15)</f>
+        <v/>
+      </c>
+      <c r="P15" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -1864,7 +2559,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Discover Bank Net/Mobile</t>
+          <t>Bill Pay:Veolia Water New Y 200054 Hbu1T6Kr</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -1879,11 +2574,12 @@
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2">
-        <f>SUM(B16,C16,D16,E16,F16,G16,H16,I16,J16,K16,L16,M16)</f>
-        <v/>
-      </c>
-      <c r="O16" s="1" t="inlineStr">
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2">
+        <f>SUM(B16,C16,D16,E16,F16,G16,H16,I16,J16,K16,L16,M16,N16)</f>
+        <v/>
+      </c>
+      <c r="P16" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -1892,26 +2588,36 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
+          <t>Citi Card Onlinepayment</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
+      <c r="D17" s="2">
+        <f>975.00+364.75+1400.00+975.00+364.75+1400.00</f>
+        <v/>
+      </c>
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
+      <c r="H17" s="2">
+        <f>975.00+364.75+1400.00</f>
+        <v/>
+      </c>
       <c r="I17" s="2" t="n"/>
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
       <c r="N17" s="2">
-        <f>SUM(B17,C17,D17,E17,F17,G17,H17,I17,J17,K17,L17,M17)</f>
-        <v/>
-      </c>
-      <c r="O17" s="1" t="inlineStr">
+        <f>975.00+364.75+1400.00</f>
+        <v/>
+      </c>
+      <c r="O17" s="2">
+        <f>SUM(B17,C17,D17,E17,F17,G17,H17,I17,J17,K17,L17,M17,N17)</f>
+        <v/>
+      </c>
+      <c r="P17" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -1920,35 +2626,45 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Huntington Banksil Payment</t>
+          <t>Credit One Bank Payment</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
+      <c r="D18" s="2">
+        <f>817.29+817.29</f>
+        <v/>
+      </c>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
+      <c r="H18" s="2">
+        <f>817.29</f>
+        <v/>
+      </c>
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2">
-        <f>SUM(B18,C18,D18,E18,F18,G18,H18,I18,J18,K18,L18,M18)</f>
-        <v/>
-      </c>
-      <c r="O18" s="1" t="inlineStr">
-        <is>
-          <t>MEALS</t>
+        <f>817.29</f>
+        <v/>
+      </c>
+      <c r="O18" s="2">
+        <f>SUM(B18,C18,D18,E18,F18,G18,H18,I18,J18,K18,L18,M18,N18)</f>
+        <v/>
+      </c>
+      <c r="P18" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Internet Trf To Client-Added Transfer Account</t>
+          <t>Discover Bank Net/Mobile</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
@@ -1963,20 +2679,21 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2">
-        <f>SUM(B19,C19,D19,E19,F19,G19,H19,I19,J19,K19,L19,M19)</f>
-        <v/>
-      </c>
-      <c r="O19" s="1" t="inlineStr">
-        <is>
-          <t>MEALS</t>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2">
+        <f>SUM(B19,C19,D19,E19,F19,G19,H19,I19,J19,K19,L19,M19,N19)</f>
+        <v/>
+      </c>
+      <c r="P19" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Irs Usataxpymt</t>
+          <t>FIVE GUYS 1522 QSR 000001522 TULSA OK</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
@@ -1991,20 +2708,21 @@
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2">
-        <f>SUM(B20,C20,D20,E20,F20,G20,H20,I20,J20,K20,L20,M20)</f>
-        <v/>
-      </c>
-      <c r="O20" s="1" t="inlineStr">
-        <is>
-          <t>MEALS</t>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2">
+        <f>SUM(B20,C20,D20,E20,F20,G20,H20,I20,J20,K20,L20,M20,N20)</f>
+        <v/>
+      </c>
+      <c r="P20" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Kindercare Portland OR</t>
+          <t>Huntington Banksil Payment</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
@@ -2019,11 +2737,12 @@
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n"/>
-      <c r="N21" s="2">
-        <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,J21,K21,L21,M21)</f>
-        <v/>
-      </c>
-      <c r="O21" s="1" t="inlineStr">
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2">
+        <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,J21,K21,L21,M21,N21)</f>
+        <v/>
+      </c>
+      <c r="P21" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2032,26 +2751,36 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>No1 Sushi 88 Corkbbo ACH</t>
+          <t>Internet Trf To Client-Added Transfer Account</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
+      <c r="D22" s="2">
+        <f>385.77+740.00+385.77+740.00</f>
+        <v/>
+      </c>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
+      <c r="H22" s="2">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
       <c r="M22" s="2" t="n"/>
       <c r="N22" s="2">
-        <f>SUM(B22,C22,D22,E22,F22,G22,H22,I22,J22,K22,L22,M22)</f>
-        <v/>
-      </c>
-      <c r="O22" s="1" t="inlineStr">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
+      <c r="O22" s="2">
+        <f>SUM(B22,C22,D22,E22,F22,G22,H22,I22,J22,K22,L22,M22,N22)</f>
+        <v/>
+      </c>
+      <c r="P22" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2060,26 +2789,36 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
+          <t>Irs Usataxpymt</t>
         </is>
       </c>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
+      <c r="D23" s="2">
+        <f>800.00+800.00+800.00+800.00</f>
+        <v/>
+      </c>
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
+      <c r="H23" s="2">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
       <c r="I23" s="2" t="n"/>
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n"/>
       <c r="N23" s="2">
-        <f>SUM(B23,C23,D23,E23,F23,G23,H23,I23,J23,K23,L23,M23)</f>
-        <v/>
-      </c>
-      <c r="O23" s="1" t="inlineStr">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
+      <c r="O23" s="2">
+        <f>SUM(B23,C23,D23,E23,F23,G23,H23,I23,J23,K23,L23,M23,N23)</f>
+        <v/>
+      </c>
+      <c r="P23" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2088,26 +2827,36 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Nys Dtf Pit Tax Paymnt</t>
+          <t>Kindercare Portland OR</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
+      <c r="D24" s="2">
+        <f>490.00+120.00+490.00+120.00</f>
+        <v/>
+      </c>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
+      <c r="H24" s="2">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2">
-        <f>SUM(B24,C24,D24,E24,F24,G24,H24,I24,J24,K24,L24,M24)</f>
-        <v/>
-      </c>
-      <c r="O24" s="1" t="inlineStr">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
+      <c r="O24" s="2">
+        <f>SUM(B24,C24,D24,E24,F24,G24,H24,I24,J24,K24,L24,M24,N24)</f>
+        <v/>
+      </c>
+      <c r="P24" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2116,26 +2865,36 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>PANDA EXPRESS TACOMA WA</t>
+          <t>No1 Sushi 88 Corkbbo ACH</t>
         </is>
       </c>
       <c r="B25" s="2" t="n"/>
       <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
+      <c r="D25" s="2">
+        <f>4000.00+4000.00</f>
+        <v/>
+      </c>
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
+      <c r="H25" s="2">
+        <f>4000.00</f>
+        <v/>
+      </c>
       <c r="I25" s="2" t="n"/>
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="n"/>
       <c r="N25" s="2">
-        <f>SUM(B25,C25,D25,E25,F25,G25,H25,I25,J25,K25,L25,M25)</f>
-        <v/>
-      </c>
-      <c r="O25" s="1" t="inlineStr">
+        <f>4000.00</f>
+        <v/>
+      </c>
+      <c r="O25" s="2">
+        <f>SUM(B25,C25,D25,E25,F25,G25,H25,I25,J25,K25,L25,M25,N25)</f>
+        <v/>
+      </c>
+      <c r="P25" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2144,7 +2903,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Paypal Inst Xfer</t>
+          <t>NORDSTROM DIRECT http://shop.nordstrom WA</t>
         </is>
       </c>
       <c r="B26" s="2" t="n"/>
@@ -2159,11 +2918,12 @@
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n"/>
-      <c r="N26" s="2">
-        <f>SUM(B26,C26,D26,E26,F26,G26,H26,I26,J26,K26,L26,M26)</f>
-        <v/>
-      </c>
-      <c r="O26" s="1" t="inlineStr">
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2">
+        <f>SUM(B26,C26,D26,E26,F26,G26,H26,I26,J26,K26,L26,M26,N26)</f>
+        <v/>
+      </c>
+      <c r="P26" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2172,26 +2932,36 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*9O5 Seattle WA</t>
+          <t>Nys Dtf Pit Tax Paymnt</t>
         </is>
       </c>
       <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
+      <c r="D27" s="2">
+        <f>200.00+200.00+200.00+200.00</f>
+        <v/>
+      </c>
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
+      <c r="H27" s="2">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
       <c r="N27" s="2">
-        <f>SUM(B27,C27,D27,E27,F27,G27,H27,I27,J27,K27,L27,M27)</f>
-        <v/>
-      </c>
-      <c r="O27" s="1" t="inlineStr">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
+      <c r="O27" s="2">
+        <f>SUM(B27,C27,D27,E27,F27,G27,H27,I27,J27,K27,L27,M27,N27)</f>
+        <v/>
+      </c>
+      <c r="P27" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2200,7 +2970,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
+          <t>PANDA EXPRESS TACOMA WA</t>
         </is>
       </c>
       <c r="B28" s="2" t="n"/>
@@ -2215,11 +2985,12 @@
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n"/>
-      <c r="N28" s="2">
-        <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,J28,K28,L28,M28)</f>
-        <v/>
-      </c>
-      <c r="O28" s="1" t="inlineStr">
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2">
+        <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,J28,K28,L28,M28,N28)</f>
+        <v/>
+      </c>
+      <c r="P28" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2228,7 +2999,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
+          <t>Paypal Inst Xfer</t>
         </is>
       </c>
       <c r="B29" s="2" t="n"/>
@@ -2243,95 +3014,126 @@
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
-      <c r="N29" s="2">
-        <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29)</f>
-        <v/>
-      </c>
-      <c r="O29" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2">
+        <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29,N29)</f>
+        <v/>
+      </c>
+      <c r="P29" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
+          <t>POS Mac Amazon.Com*9O5 Seattle WA</t>
         </is>
       </c>
       <c r="B30" s="2" t="n"/>
       <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
+      <c r="D30" s="2">
+        <f>26.57+26.57</f>
+        <v/>
+      </c>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
+      <c r="H30" s="2">
+        <f>26.57</f>
+        <v/>
+      </c>
       <c r="I30" s="2" t="n"/>
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n"/>
       <c r="N30" s="2">
-        <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30)</f>
-        <v/>
-      </c>
-      <c r="O30" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
+        <f>26.57</f>
+        <v/>
+      </c>
+      <c r="O30" s="2">
+        <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30,N30)</f>
+        <v/>
+      </c>
+      <c r="P30" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
+          <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
         </is>
       </c>
       <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
+      <c r="D31" s="2">
+        <f>343.93+343.93</f>
+        <v/>
+      </c>
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
+      <c r="H31" s="2">
+        <f>343.93</f>
+        <v/>
+      </c>
       <c r="I31" s="2" t="n"/>
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
       <c r="N31" s="2">
-        <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31)</f>
-        <v/>
-      </c>
-      <c r="O31" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY</t>
+        <f>343.93</f>
+        <v/>
+      </c>
+      <c r="O31" s="2">
+        <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31,N31)</f>
+        <v/>
+      </c>
+      <c r="P31" s="1" t="inlineStr">
+        <is>
+          <t>MEALS</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Nx6 Seattle WA</t>
+          <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
         </is>
       </c>
       <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
+      <c r="D32" s="2">
+        <f>17.59+17.59</f>
+        <v/>
+      </c>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
+      <c r="H32" s="2">
+        <f>17.59</f>
+        <v/>
+      </c>
       <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
       <c r="M32" s="2" t="n"/>
       <c r="N32" s="2">
-        <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32)</f>
-        <v/>
-      </c>
-      <c r="O32" s="1" t="inlineStr">
+        <f>17.59</f>
+        <v/>
+      </c>
+      <c r="O32" s="2">
+        <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32,N32)</f>
+        <v/>
+      </c>
+      <c r="P32" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -2340,26 +3142,36 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
+          <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
         </is>
       </c>
       <c r="B33" s="2" t="n"/>
       <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
+      <c r="D33" s="2">
+        <f>152.14+152.14</f>
+        <v/>
+      </c>
       <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
+      <c r="H33" s="2">
+        <f>152.14</f>
+        <v/>
+      </c>
       <c r="I33" s="2" t="n"/>
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n"/>
       <c r="N33" s="2">
-        <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33)</f>
-        <v/>
-      </c>
-      <c r="O33" s="1" t="inlineStr">
+        <f>152.14</f>
+        <v/>
+      </c>
+      <c r="O33" s="2">
+        <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33,N33)</f>
+        <v/>
+      </c>
+      <c r="P33" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -2368,26 +3180,36 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
+          <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
         </is>
       </c>
       <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
+      <c r="D34" s="2">
+        <f>71.79+71.79</f>
+        <v/>
+      </c>
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
+      <c r="H34" s="2">
+        <f>71.79</f>
+        <v/>
+      </c>
       <c r="I34" s="2" t="n"/>
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
       <c r="M34" s="2" t="n"/>
       <c r="N34" s="2">
-        <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,J34,K34,L34,M34)</f>
-        <v/>
-      </c>
-      <c r="O34" s="1" t="inlineStr">
+        <f>71.79</f>
+        <v/>
+      </c>
+      <c r="O34" s="2">
+        <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,J34,K34,L34,M34,N34)</f>
+        <v/>
+      </c>
+      <c r="P34" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -2396,26 +3218,36 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*V25 Seattle WA</t>
+          <t>POS Mac Amazon.Com*Nx6 Seattle WA</t>
         </is>
       </c>
       <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
+      <c r="D35" s="2">
+        <f>75.40+75.40</f>
+        <v/>
+      </c>
       <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
+      <c r="H35" s="2">
+        <f>75.40</f>
+        <v/>
+      </c>
       <c r="I35" s="2" t="n"/>
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n"/>
       <c r="N35" s="2">
-        <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,J35,K35,L35,M35)</f>
-        <v/>
-      </c>
-      <c r="O35" s="1" t="inlineStr">
+        <f>75.40</f>
+        <v/>
+      </c>
+      <c r="O35" s="2">
+        <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,J35,K35,L35,M35,N35)</f>
+        <v/>
+      </c>
+      <c r="P35" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -2424,26 +3256,36 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Yr6 Seattle WA</t>
+          <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
         </is>
       </c>
       <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
+      <c r="D36" s="2">
+        <f>18.75+18.75</f>
+        <v/>
+      </c>
       <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
+      <c r="H36" s="2">
+        <f>18.75</f>
+        <v/>
+      </c>
       <c r="I36" s="2" t="n"/>
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n"/>
       <c r="N36" s="2">
-        <f>SUM(B36,C36,D36,E36,F36,G36,H36,I36,J36,K36,L36,M36)</f>
-        <v/>
-      </c>
-      <c r="O36" s="1" t="inlineStr">
+        <f>18.75</f>
+        <v/>
+      </c>
+      <c r="O36" s="2">
+        <f>SUM(B36,C36,D36,E36,F36,G36,H36,I36,J36,K36,L36,M36,N36)</f>
+        <v/>
+      </c>
+      <c r="P36" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -2452,26 +3294,36 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
+          <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
         </is>
       </c>
       <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
+      <c r="D37" s="2">
+        <f>50.03+50.03</f>
+        <v/>
+      </c>
       <c r="E37" s="2" t="n"/>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
+      <c r="H37" s="2">
+        <f>50.03</f>
+        <v/>
+      </c>
       <c r="I37" s="2" t="n"/>
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
       <c r="M37" s="2" t="n"/>
       <c r="N37" s="2">
-        <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,J37,K37,L37,M37)</f>
-        <v/>
-      </c>
-      <c r="O37" s="1" t="inlineStr">
+        <f>50.03</f>
+        <v/>
+      </c>
+      <c r="O37" s="2">
+        <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,J37,K37,L37,M37,N37)</f>
+        <v/>
+      </c>
+      <c r="P37" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -2480,26 +3332,36 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Prog Casualty Ins Prem</t>
+          <t>POS Mac Amazon.Com*V25 Seattle WA</t>
         </is>
       </c>
       <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
+      <c r="D38" s="2">
+        <f>20.80+20.80</f>
+        <v/>
+      </c>
       <c r="E38" s="2" t="n"/>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
+      <c r="H38" s="2">
+        <f>20.80</f>
+        <v/>
+      </c>
       <c r="I38" s="2" t="n"/>
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n"/>
       <c r="N38" s="2">
-        <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38)</f>
-        <v/>
-      </c>
-      <c r="O38" s="1" t="inlineStr">
+        <f>20.80</f>
+        <v/>
+      </c>
+      <c r="O38" s="2">
+        <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38,N38)</f>
+        <v/>
+      </c>
+      <c r="P38" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -2508,7 +3370,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
+          <t>POS Mac Amazon.Com*Yr6 Seattle WA</t>
         </is>
       </c>
       <c r="B39" s="2" t="n"/>
@@ -2523,11 +3385,12 @@
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n"/>
-      <c r="N39" s="2">
-        <f>SUM(B39,C39,D39,E39,F39,G39,H39,I39,J39,K39,L39,M39)</f>
-        <v/>
-      </c>
-      <c r="O39" s="1" t="inlineStr">
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2">
+        <f>SUM(B39,C39,D39,E39,F39,G39,H39,I39,J39,K39,L39,M39,N39)</f>
+        <v/>
+      </c>
+      <c r="P39" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -2536,26 +3399,36 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Withdrawal Branch 0964 New York</t>
+          <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
         </is>
       </c>
       <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
+      <c r="D40" s="2">
+        <f>40.33+40.33</f>
+        <v/>
+      </c>
       <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
+      <c r="H40" s="2">
+        <f>40.33</f>
+        <v/>
+      </c>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
       <c r="M40" s="2" t="n"/>
       <c r="N40" s="2">
-        <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,J40,K40,L40,M40)</f>
-        <v/>
-      </c>
-      <c r="O40" s="1" t="inlineStr">
+        <f>40.33</f>
+        <v/>
+      </c>
+      <c r="O40" s="2">
+        <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,J40,K40,L40,M40,N40)</f>
+        <v/>
+      </c>
+      <c r="P40" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -2564,88 +3437,173 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>discover Bank Net/Mobile</t>
+          <t>Prog Casualty Ins Prem</t>
         </is>
       </c>
       <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
+      <c r="D41" s="2">
+        <f>930.52+930.52</f>
+        <v/>
+      </c>
       <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
+      <c r="H41" s="2">
+        <f>930.52</f>
+        <v/>
+      </c>
       <c r="I41" s="2" t="n"/>
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
       <c r="M41" s="2" t="n"/>
       <c r="N41" s="2">
-        <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41)</f>
-        <v/>
-      </c>
-      <c r="O41" s="1" t="n"/>
+        <f>930.52</f>
+        <v/>
+      </c>
+      <c r="O41" s="2">
+        <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41,N41)</f>
+        <v/>
+      </c>
+      <c r="P41" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>WHOLEFDS CHB #10588 000010588 UNIVERSITY PL WA</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2">
+        <f>SUM(B42,C42,D42,E42,F42,G42,H42,I42,J42,K42,L42,M42,N42)</f>
+        <v/>
+      </c>
+      <c r="P42" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Withdrawal Branch 0964 New York</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2">
+        <f>1000.00+3200.00+1000.00+3200.00</f>
+        <v/>
+      </c>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
+      <c r="O43" s="2">
+        <f>SUM(B43,C43,D43,E43,F43,G43,H43,I43,J43,K43,L43,M43,N43)</f>
+        <v/>
+      </c>
+      <c r="P43" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B42" s="3">
-        <f>SUM(B2:B41)</f>
-        <v/>
-      </c>
-      <c r="C42" s="3">
-        <f>SUM(C2:C41)</f>
-        <v/>
-      </c>
-      <c r="D42" s="3">
-        <f>SUM(D2:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="3">
-        <f>SUM(E2:E41)</f>
-        <v/>
-      </c>
-      <c r="F42" s="3">
-        <f>SUM(F2:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="3">
-        <f>SUM(G2:G41)</f>
-        <v/>
-      </c>
-      <c r="H42" s="3">
-        <f>SUM(H2:H41)</f>
-        <v/>
-      </c>
-      <c r="I42" s="3">
-        <f>SUM(I2:I41)</f>
-        <v/>
-      </c>
-      <c r="J42" s="3">
-        <f>SUM(J2:J41)</f>
-        <v/>
-      </c>
-      <c r="K42" s="3">
-        <f>SUM(K2:K41)</f>
-        <v/>
-      </c>
-      <c r="L42" s="3">
-        <f>SUM(L2:L41)</f>
-        <v/>
-      </c>
-      <c r="M42" s="3">
-        <f>SUM(M2:M41)</f>
-        <v/>
-      </c>
-      <c r="N42" s="3">
-        <f>SUM(B42,C42,D42,E42,F42,G42,H42,I42,J42,K42,L42,M42)</f>
+      <c r="B44" s="3">
+        <f>SUM(B2:B43)</f>
+        <v/>
+      </c>
+      <c r="C44" s="3">
+        <f>SUM(C2:C43)</f>
+        <v/>
+      </c>
+      <c r="D44" s="3">
+        <f>SUM(D2:D43)</f>
+        <v/>
+      </c>
+      <c r="E44" s="3">
+        <f>SUM(E2:E43)</f>
+        <v/>
+      </c>
+      <c r="F44" s="3">
+        <f>SUM(F2:F43)</f>
+        <v/>
+      </c>
+      <c r="G44" s="3">
+        <f>SUM(G2:G43)</f>
+        <v/>
+      </c>
+      <c r="H44" s="3">
+        <f>SUM(H2:H43)</f>
+        <v/>
+      </c>
+      <c r="I44" s="3">
+        <f>SUM(I2:I43)</f>
+        <v/>
+      </c>
+      <c r="J44" s="3">
+        <f>SUM(J2:J43)</f>
+        <v/>
+      </c>
+      <c r="K44" s="3">
+        <f>SUM(K2:K43)</f>
+        <v/>
+      </c>
+      <c r="L44" s="3">
+        <f>SUM(L2:L43)</f>
+        <v/>
+      </c>
+      <c r="M44" s="3">
+        <f>SUM(M2:M43)</f>
+        <v/>
+      </c>
+      <c r="N44" s="3">
+        <f>SUM(N2:N43)</f>
+        <v/>
+      </c>
+      <c r="O44" s="3">
+        <f>SUM(B44,C44,D44,E44,F44,G44,H44,I44,J44,K44,L44,M44,N44)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O41"/>
+  <autoFilter ref="A1:P44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2664,9 +3622,9 @@
     <col width="7.85546875" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="7" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="6.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="7.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="9.28515625" bestFit="1" customWidth="1" min="6" max="6"/>
     <col width="7.140625" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="7" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="9.28515625" bestFit="1" customWidth="1" min="8" max="8"/>
     <col width="7.5703125" bestFit="1" customWidth="1" min="9" max="9"/>
     <col width="7.28515625" bestFit="1" customWidth="1" min="10" max="10"/>
     <col width="6.85546875" bestFit="1" customWidth="1" min="11" max="11"/>
@@ -2681,46 +3639,46 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>Merchant</t>
-        </is>
-      </c>
-      <c r="B1" s="8" t="n">
+          <t>banewofhjsofih</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="n">
         <v>45748</v>
       </c>
-      <c r="C1" s="8" t="n">
+      <c r="C1" s="6" t="n">
         <v>45778</v>
       </c>
-      <c r="D1" s="8" t="n">
+      <c r="D1" s="6" t="n">
         <v>45809</v>
       </c>
-      <c r="E1" s="8" t="n">
+      <c r="E1" s="6" t="n">
         <v>45839</v>
       </c>
-      <c r="F1" s="8" t="n">
+      <c r="F1" s="6" t="n">
         <v>45870</v>
       </c>
-      <c r="G1" s="8" t="n">
+      <c r="G1" s="6" t="n">
         <v>45901</v>
       </c>
-      <c r="H1" s="8" t="n">
+      <c r="H1" s="6" t="n">
         <v>45931</v>
       </c>
-      <c r="I1" s="8" t="n">
+      <c r="I1" s="6" t="n">
         <v>45962</v>
       </c>
-      <c r="J1" s="8" t="n">
+      <c r="J1" s="6" t="n">
         <v>45992</v>
       </c>
-      <c r="K1" s="8" t="n">
+      <c r="K1" s="6" t="n">
         <v>46023</v>
       </c>
-      <c r="L1" s="8" t="n">
+      <c r="L1" s="6" t="n">
         <v>46054</v>
       </c>
-      <c r="M1" s="8" t="n">
+      <c r="M1" s="6" t="n">
         <v>46082</v>
       </c>
-      <c r="N1" s="8" t="n">
+      <c r="N1" s="6" t="n">
         <v>46113</v>
       </c>
       <c r="O1" s="10" t="inlineStr">
@@ -2772,18 +3730,27 @@
           <t>Amazon Prime*Zh8618Uz3 Amzn.Com/Bill WA</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
+      <c r="B3" s="2">
+        <f>16.25</f>
+        <v/>
+      </c>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
+      <c r="H3" s="2">
+        <f>16.25</f>
+        <v/>
+      </c>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
+      <c r="M3" s="2">
+        <f>16.25</f>
+        <v/>
+      </c>
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2">
         <f>SUM(B3,C3,D3,E3,F3,G3,H3,I3,J3,K3,L3,M3,N3,Q3)</f>
@@ -2830,18 +3797,27 @@
           <t>Amazon.Comseattlewa US</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="2">
+        <f>117.76</f>
+        <v/>
+      </c>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="H5" s="2">
+        <f>117.76</f>
+        <v/>
+      </c>
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
+      <c r="M5" s="2">
+        <f>117.76</f>
+        <v/>
+      </c>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="2">
         <f>SUM(B5,C5,D5,E5,F5,G5,H5,I5,J5,K5,L5,M5,N5,Q5)</f>
@@ -2975,18 +3951,27 @@
           <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
+      <c r="B10" s="2">
+        <f>350.00</f>
+        <v/>
+      </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
+      <c r="H10" s="2">
+        <f>350.00</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="n"/>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
+      <c r="M10" s="2">
+        <f>350.00</f>
+        <v/>
+      </c>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2">
         <f>SUM(B10,C10,D10,E10,F10,G10,H10,I10,J10,K10,L10,M10,N10,Q10)</f>
@@ -3033,18 +4018,27 @@
           <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n"/>
+      <c r="B12" s="2">
+        <f>300.00</f>
+        <v/>
+      </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
+      <c r="H12" s="2">
+        <f>300.00</f>
+        <v/>
+      </c>
       <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
+      <c r="M12" s="2">
+        <f>300.00</f>
+        <v/>
+      </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2">
         <f>SUM(B12,C12,D12,E12,F12,G12,H12,I12,J12,K12,L12,M12,N12,Q12)</f>
@@ -3091,18 +4085,27 @@
           <t>Citi Card Onlinepayment</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
+      <c r="B14" s="2">
+        <f>975.00+364.75+1400.00</f>
+        <v/>
+      </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="H14" s="2">
+        <f>975.00+364.75+1400.00</f>
+        <v/>
+      </c>
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
+      <c r="M14" s="2">
+        <f>975.00+364.75+1400.00</f>
+        <v/>
+      </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2">
         <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,J14,K14,L14,M14,N14,Q14)</f>
@@ -3120,18 +4123,27 @@
           <t>Credit One Bank Payment</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2">
+        <f>817.29</f>
+        <v/>
+      </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
+      <c r="H15" s="2">
+        <f>817.29</f>
+        <v/>
+      </c>
       <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="n"/>
+      <c r="M15" s="2">
+        <f>817.29</f>
+        <v/>
+      </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2">
         <f>SUM(B15,C15,D15,E15,F15,G15,H15,I15,J15,K15,L15,M15,N15,Q15)</f>
@@ -3236,18 +4248,27 @@
           <t>Internet Trf To Client-Added Transfer Account</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n"/>
+      <c r="B19" s="2">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
+      <c r="H19" s="2">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
       <c r="I19" s="2" t="n"/>
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
+      <c r="M19" s="2">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2">
         <f>SUM(B19,C19,D19,E19,F19,G19,H19,I19,J19,K19,L19,M19,N19,Q19)</f>
@@ -3265,18 +4286,27 @@
           <t>Irs Usataxpymt</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
+      <c r="B20" s="2">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
+      <c r="H20" s="2">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
+      <c r="M20" s="2">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2">
         <f>SUM(B20,C20,D20,E20,F20,G20,H20,I20,J20,K20,L20,M20,N20,Q20)</f>
@@ -3294,18 +4324,27 @@
           <t>Kindercare Portland OR</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n"/>
+      <c r="B21" s="2">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
+      <c r="H21" s="2">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
       <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="n"/>
+      <c r="M21" s="2">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2">
         <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,J21,K21,L21,M21,N21,Q21)</f>
@@ -3323,18 +4362,27 @@
           <t>No1 Sushi 88 Corkbbo ACH</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2">
+        <f>4000.00</f>
+        <v/>
+      </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
+      <c r="H22" s="2">
+        <f>4000.00</f>
+        <v/>
+      </c>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
+      <c r="M22" s="2">
+        <f>4000.00</f>
+        <v/>
+      </c>
       <c r="N22" s="2" t="n"/>
       <c r="O22" s="2">
         <f>SUM(B22,C22,D22,E22,F22,G22,H22,I22,J22,K22,L22,M22,N22,Q22)</f>
@@ -3381,18 +4429,27 @@
           <t>Nys Dtf Pit Tax Paymnt</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n"/>
+      <c r="B24" s="2">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
+      <c r="H24" s="2">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="n"/>
+      <c r="M24" s="2">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2">
         <f>SUM(B24,C24,D24,E24,F24,G24,H24,I24,J24,K24,L24,M24,N24,Q24)</f>
@@ -3468,18 +4525,27 @@
           <t>POS Mac Amazon.Com*9O5 Seattle WA</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n"/>
+      <c r="B27" s="2">
+        <f>26.57</f>
+        <v/>
+      </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
+      <c r="H27" s="2">
+        <f>26.57</f>
+        <v/>
+      </c>
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
-      <c r="M27" s="2" t="n"/>
+      <c r="M27" s="2">
+        <f>26.57</f>
+        <v/>
+      </c>
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2">
         <f>SUM(B27,C27,D27,E27,F27,G27,H27,I27,J27,K27,L27,M27,N27,Q27)</f>
@@ -3497,18 +4563,27 @@
           <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n"/>
+      <c r="B28" s="2">
+        <f>343.93</f>
+        <v/>
+      </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
+      <c r="H28" s="2">
+        <f>343.93</f>
+        <v/>
+      </c>
       <c r="I28" s="2" t="n"/>
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="n"/>
+      <c r="M28" s="2">
+        <f>343.93</f>
+        <v/>
+      </c>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2">
         <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,J28,K28,L28,M28,N28,Q28)</f>
@@ -3526,18 +4601,27 @@
           <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n"/>
+      <c r="B29" s="2">
+        <f>17.59</f>
+        <v/>
+      </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
+      <c r="H29" s="2">
+        <f>17.59</f>
+        <v/>
+      </c>
       <c r="I29" s="2" t="n"/>
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="n"/>
+      <c r="M29" s="2">
+        <f>17.59</f>
+        <v/>
+      </c>
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2">
         <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29,N29,Q29)</f>
@@ -3555,18 +4639,27 @@
           <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n"/>
+      <c r="B30" s="2">
+        <f>152.14</f>
+        <v/>
+      </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
+      <c r="H30" s="2">
+        <f>152.14</f>
+        <v/>
+      </c>
       <c r="I30" s="2" t="n"/>
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="n"/>
+      <c r="M30" s="2">
+        <f>152.14</f>
+        <v/>
+      </c>
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2">
         <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30,N30,Q30)</f>
@@ -3584,18 +4677,27 @@
           <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n"/>
+      <c r="B31" s="2">
+        <f>71.79</f>
+        <v/>
+      </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
+      <c r="H31" s="2">
+        <f>71.79</f>
+        <v/>
+      </c>
       <c r="I31" s="2" t="n"/>
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
+      <c r="M31" s="2">
+        <f>71.79</f>
+        <v/>
+      </c>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2">
         <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31,N31,Q31)</f>
@@ -3613,18 +4715,27 @@
           <t>POS Mac Amazon.Com*Nx6 Seattle WA</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n"/>
+      <c r="B32" s="2">
+        <f>75.40</f>
+        <v/>
+      </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
+      <c r="H32" s="2">
+        <f>75.40</f>
+        <v/>
+      </c>
       <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
+      <c r="M32" s="2">
+        <f>75.40</f>
+        <v/>
+      </c>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2">
         <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32,N32,Q32)</f>
@@ -3642,18 +4753,27 @@
           <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n"/>
+      <c r="B33" s="2">
+        <f>18.75</f>
+        <v/>
+      </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
+      <c r="H33" s="2">
+        <f>18.75</f>
+        <v/>
+      </c>
       <c r="I33" s="2" t="n"/>
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
+      <c r="M33" s="2">
+        <f>18.75</f>
+        <v/>
+      </c>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2">
         <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33,N33,Q33)</f>
@@ -3671,18 +4791,27 @@
           <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n"/>
+      <c r="B34" s="2">
+        <f>50.03</f>
+        <v/>
+      </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
+      <c r="H34" s="2">
+        <f>50.03</f>
+        <v/>
+      </c>
       <c r="I34" s="2" t="n"/>
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
+      <c r="M34" s="2">
+        <f>50.03</f>
+        <v/>
+      </c>
       <c r="N34" s="2" t="n"/>
       <c r="O34" s="2">
         <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,J34,K34,L34,M34,N34,Q34)</f>
@@ -3700,18 +4829,27 @@
           <t>POS Mac Amazon.Com*V25 Seattle WA</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n"/>
+      <c r="B35" s="2">
+        <f>20.80</f>
+        <v/>
+      </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n"/>
       <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
+      <c r="H35" s="2">
+        <f>20.80</f>
+        <v/>
+      </c>
       <c r="I35" s="2" t="n"/>
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
+      <c r="M35" s="2">
+        <f>20.80</f>
+        <v/>
+      </c>
       <c r="N35" s="2" t="n"/>
       <c r="O35" s="2">
         <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,J35,K35,L35,M35,N35,Q35)</f>
@@ -3758,18 +4896,27 @@
           <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n"/>
+      <c r="B37" s="2">
+        <f>40.33</f>
+        <v/>
+      </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n"/>
       <c r="E37" s="2" t="n"/>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
+      <c r="H37" s="2">
+        <f>40.33</f>
+        <v/>
+      </c>
       <c r="I37" s="2" t="n"/>
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="n"/>
+      <c r="M37" s="2">
+        <f>40.33</f>
+        <v/>
+      </c>
       <c r="N37" s="2" t="n"/>
       <c r="O37" s="2">
         <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,J37,K37,L37,M37,N37,Q37)</f>
@@ -3787,18 +4934,27 @@
           <t>Prog Casualty Ins Prem</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n"/>
+      <c r="B38" s="2">
+        <f>930.52</f>
+        <v/>
+      </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="n"/>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
+      <c r="H38" s="2">
+        <f>930.52</f>
+        <v/>
+      </c>
       <c r="I38" s="2" t="n"/>
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n"/>
+      <c r="M38" s="2">
+        <f>930.52</f>
+        <v/>
+      </c>
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2">
         <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38,N38,Q38)</f>
@@ -3845,18 +5001,27 @@
           <t>Withdrawal Branch 0964 New York</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n"/>
+      <c r="B40" s="2">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
+      <c r="H40" s="2">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="n"/>
+      <c r="M40" s="2">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
       <c r="N40" s="2" t="n"/>
       <c r="O40" s="2">
         <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,J40,K40,L40,M40,N40,Q40)</f>
@@ -3936,7 +5101,6 @@
         <v/>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -4134,9 +5298,7 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1"/>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/credit_monthly_summary.xlsx
+++ b/credit_monthly_summary.xlsx
@@ -1025,98 +1025,29 @@
       <c r="AB5" s="2" t="n"/>
       <c r="AC5" s="2" t="n"/>
       <c r="AD5" s="2" t="n"/>
-      <c r="AE5" s="2">
-        <f>4000.00</f>
-        <v/>
-      </c>
-      <c r="AF5" s="2">
-        <f>385.77+740.00</f>
-        <v/>
-      </c>
-      <c r="AG5" s="2">
-        <f>300.00</f>
-        <v/>
-      </c>
-      <c r="AH5" s="2">
-        <f>350.00</f>
-        <v/>
-      </c>
-      <c r="AI5" s="2">
-        <f>1000.00+3200.00</f>
-        <v/>
-      </c>
-      <c r="AJ5" s="2">
-        <f>75.40</f>
-        <v/>
-      </c>
-      <c r="AK5" s="2">
-        <f>26.57</f>
-        <v/>
-      </c>
-      <c r="AL5" s="2">
-        <f>18.75</f>
-        <v/>
-      </c>
-      <c r="AM5" s="2">
-        <f>200.00+200.00</f>
-        <v/>
-      </c>
-      <c r="AN5" s="2">
-        <f>490.00+120.00</f>
-        <v/>
-      </c>
-      <c r="AO5" s="2">
-        <f>16.25</f>
-        <v/>
-      </c>
-      <c r="AP5" s="2">
-        <f>800.00+800.00</f>
-        <v/>
-      </c>
-      <c r="AQ5" s="2">
-        <f>817.29</f>
-        <v/>
-      </c>
-      <c r="AR5" s="2">
-        <f>930.52</f>
-        <v/>
-      </c>
-      <c r="AS5" s="2">
-        <f>975.00+364.75+1400.00</f>
-        <v/>
-      </c>
-      <c r="AT5" s="2">
-        <f>117.76</f>
-        <v/>
-      </c>
-      <c r="AU5" s="2">
-        <f>50.03</f>
-        <v/>
-      </c>
-      <c r="AV5" s="2">
-        <f>71.79</f>
-        <v/>
-      </c>
-      <c r="AW5" s="2">
-        <f>152.14</f>
-        <v/>
-      </c>
-      <c r="AX5" s="2">
-        <f>20.80</f>
-        <v/>
-      </c>
-      <c r="AY5" s="2">
-        <f>40.33</f>
-        <v/>
-      </c>
-      <c r="AZ5" s="2">
-        <f>343.93</f>
-        <v/>
-      </c>
-      <c r="BA5" s="2">
-        <f>17.59</f>
-        <v/>
-      </c>
+      <c r="AE5" s="2" t="n"/>
+      <c r="AF5" s="2" t="n"/>
+      <c r="AG5" s="2" t="n"/>
+      <c r="AH5" s="2" t="n"/>
+      <c r="AI5" s="2" t="n"/>
+      <c r="AJ5" s="2" t="n"/>
+      <c r="AK5" s="2" t="n"/>
+      <c r="AL5" s="2" t="n"/>
+      <c r="AM5" s="2" t="n"/>
+      <c r="AN5" s="2" t="n"/>
+      <c r="AO5" s="2" t="n"/>
+      <c r="AP5" s="2" t="n"/>
+      <c r="AQ5" s="2" t="n"/>
+      <c r="AR5" s="2" t="n"/>
+      <c r="AS5" s="2" t="n"/>
+      <c r="AT5" s="2" t="n"/>
+      <c r="AU5" s="2" t="n"/>
+      <c r="AV5" s="2" t="n"/>
+      <c r="AW5" s="2" t="n"/>
+      <c r="AX5" s="2" t="n"/>
+      <c r="AY5" s="2" t="n"/>
+      <c r="AZ5" s="2" t="n"/>
+      <c r="BA5" s="2" t="n"/>
       <c r="BB5" s="2">
         <f>SUM(C5:BA5)</f>
         <v/>
@@ -1163,29 +1094,98 @@
       <c r="AB6" s="2" t="n"/>
       <c r="AC6" s="2" t="n"/>
       <c r="AD6" s="2" t="n"/>
-      <c r="AE6" s="2" t="n"/>
-      <c r="AF6" s="2" t="n"/>
-      <c r="AG6" s="2" t="n"/>
-      <c r="AH6" s="2" t="n"/>
-      <c r="AI6" s="2" t="n"/>
-      <c r="AJ6" s="2" t="n"/>
-      <c r="AK6" s="2" t="n"/>
-      <c r="AL6" s="2" t="n"/>
-      <c r="AM6" s="2" t="n"/>
-      <c r="AN6" s="2" t="n"/>
-      <c r="AO6" s="2" t="n"/>
-      <c r="AP6" s="2" t="n"/>
-      <c r="AQ6" s="2" t="n"/>
-      <c r="AR6" s="2" t="n"/>
-      <c r="AS6" s="2" t="n"/>
-      <c r="AT6" s="2" t="n"/>
-      <c r="AU6" s="2" t="n"/>
-      <c r="AV6" s="2" t="n"/>
-      <c r="AW6" s="2" t="n"/>
-      <c r="AX6" s="2" t="n"/>
-      <c r="AY6" s="2" t="n"/>
-      <c r="AZ6" s="2" t="n"/>
-      <c r="BA6" s="2" t="n"/>
+      <c r="AE6" s="2">
+        <f>4000.00</f>
+        <v/>
+      </c>
+      <c r="AF6" s="2">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
+      <c r="AG6" s="2">
+        <f>300.00</f>
+        <v/>
+      </c>
+      <c r="AH6" s="2">
+        <f>350.00</f>
+        <v/>
+      </c>
+      <c r="AI6" s="2">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="2">
+        <f>75.40</f>
+        <v/>
+      </c>
+      <c r="AK6" s="2">
+        <f>26.57</f>
+        <v/>
+      </c>
+      <c r="AL6" s="2">
+        <f>18.75</f>
+        <v/>
+      </c>
+      <c r="AM6" s="2">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
+      <c r="AN6" s="2">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
+      <c r="AO6" s="2">
+        <f>16.25</f>
+        <v/>
+      </c>
+      <c r="AP6" s="2">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
+      <c r="AQ6" s="2">
+        <f>817.29</f>
+        <v/>
+      </c>
+      <c r="AR6" s="2">
+        <f>930.52</f>
+        <v/>
+      </c>
+      <c r="AS6" s="2">
+        <f>975.00+364.75+1400.00</f>
+        <v/>
+      </c>
+      <c r="AT6" s="2">
+        <f>117.76</f>
+        <v/>
+      </c>
+      <c r="AU6" s="2">
+        <f>50.03</f>
+        <v/>
+      </c>
+      <c r="AV6" s="2">
+        <f>71.79</f>
+        <v/>
+      </c>
+      <c r="AW6" s="2">
+        <f>152.14</f>
+        <v/>
+      </c>
+      <c r="AX6" s="2">
+        <f>20.80</f>
+        <v/>
+      </c>
+      <c r="AY6" s="2">
+        <f>40.33</f>
+        <v/>
+      </c>
+      <c r="AZ6" s="2">
+        <f>343.93</f>
+        <v/>
+      </c>
+      <c r="BA6" s="2">
+        <f>17.59</f>
+        <v/>
+      </c>
       <c r="BB6" s="2">
         <f>SUM(C6:BA6)</f>
         <v/>
@@ -1301,98 +1301,29 @@
       <c r="AB8" s="2" t="n"/>
       <c r="AC8" s="2" t="n"/>
       <c r="AD8" s="2" t="n"/>
-      <c r="AE8" s="2">
-        <f>4000.00</f>
-        <v/>
-      </c>
-      <c r="AF8" s="2">
-        <f>385.77+740.00</f>
-        <v/>
-      </c>
-      <c r="AG8" s="2">
-        <f>300.00</f>
-        <v/>
-      </c>
-      <c r="AH8" s="2">
-        <f>350.00</f>
-        <v/>
-      </c>
-      <c r="AI8" s="2">
-        <f>1000.00+3200.00</f>
-        <v/>
-      </c>
-      <c r="AJ8" s="2">
-        <f>75.40</f>
-        <v/>
-      </c>
-      <c r="AK8" s="2">
-        <f>26.57</f>
-        <v/>
-      </c>
-      <c r="AL8" s="2">
-        <f>18.75</f>
-        <v/>
-      </c>
-      <c r="AM8" s="2">
-        <f>200.00+200.00</f>
-        <v/>
-      </c>
-      <c r="AN8" s="2">
-        <f>490.00+120.00</f>
-        <v/>
-      </c>
-      <c r="AO8" s="2">
-        <f>16.25</f>
-        <v/>
-      </c>
-      <c r="AP8" s="2">
-        <f>800.00+800.00</f>
-        <v/>
-      </c>
-      <c r="AQ8" s="2">
-        <f>817.29</f>
-        <v/>
-      </c>
-      <c r="AR8" s="2">
-        <f>930.52</f>
-        <v/>
-      </c>
-      <c r="AS8" s="2">
-        <f>975.00+364.75+1400.00</f>
-        <v/>
-      </c>
-      <c r="AT8" s="2">
-        <f>117.76</f>
-        <v/>
-      </c>
-      <c r="AU8" s="2">
-        <f>50.03</f>
-        <v/>
-      </c>
-      <c r="AV8" s="2">
-        <f>71.79</f>
-        <v/>
-      </c>
-      <c r="AW8" s="2">
-        <f>152.14</f>
-        <v/>
-      </c>
-      <c r="AX8" s="2">
-        <f>20.80</f>
-        <v/>
-      </c>
-      <c r="AY8" s="2">
-        <f>40.33</f>
-        <v/>
-      </c>
-      <c r="AZ8" s="2">
-        <f>343.93</f>
-        <v/>
-      </c>
-      <c r="BA8" s="2">
-        <f>17.59</f>
-        <v/>
-      </c>
+      <c r="AE8" s="2" t="n"/>
+      <c r="AF8" s="2" t="n"/>
+      <c r="AG8" s="2" t="n"/>
+      <c r="AH8" s="2" t="n"/>
+      <c r="AI8" s="2" t="n"/>
+      <c r="AJ8" s="2" t="n"/>
+      <c r="AK8" s="2" t="n"/>
+      <c r="AL8" s="2" t="n"/>
+      <c r="AM8" s="2" t="n"/>
+      <c r="AN8" s="2" t="n"/>
+      <c r="AO8" s="2" t="n"/>
+      <c r="AP8" s="2" t="n"/>
+      <c r="AQ8" s="2" t="n"/>
+      <c r="AR8" s="2" t="n"/>
+      <c r="AS8" s="2" t="n"/>
+      <c r="AT8" s="2" t="n"/>
+      <c r="AU8" s="2" t="n"/>
+      <c r="AV8" s="2" t="n"/>
+      <c r="AW8" s="2" t="n"/>
+      <c r="AX8" s="2" t="n"/>
+      <c r="AY8" s="2" t="n"/>
+      <c r="AZ8" s="2" t="n"/>
+      <c r="BA8" s="2" t="n"/>
       <c r="BB8" s="2">
         <f>SUM(C8:BA8)</f>
         <v/>
@@ -2041,6 +1972,7 @@
         <v/>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -2063,7 +1995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2158,7 +2090,7 @@
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2">
-        <f>SUM(B2,C2,D2,E2,F2,G2,H2,I2,J2,K2,L2,M2,N2)</f>
+        <f>SUM(B2,C2,D2,E2,F2,G2,H2,I2,K2,L2,M2,N2)</f>
         <v/>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -2175,28 +2107,25 @@
       </c>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2">
-        <f>16.25+16.25</f>
-        <v/>
-      </c>
-      <c r="E3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2">
+        <f>16.25</f>
+        <v/>
+      </c>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2">
-        <f>16.25</f>
-        <v/>
-      </c>
+      <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
+      <c r="L3" s="2">
+        <f>16.25</f>
+        <v/>
+      </c>
       <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2">
-        <f>16.25</f>
-        <v/>
-      </c>
+      <c r="N3" s="2" t="n"/>
       <c r="O3" s="2">
-        <f>SUM(B3,C3,D3,E3,F3,G3,H3,I3,J3,K3,L3,M3,N3)</f>
+        <f>SUM(B3,C3,D3,E3,F3,G3,H3,I3,K3,L3,M3,N3)</f>
         <v/>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -2225,7 +2154,7 @@
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
       <c r="O4" s="2">
-        <f>SUM(B4,C4,D4,E4,F4,G4,H4,I4,J4,K4,L4,M4,N4)</f>
+        <f>SUM(B4,C4,D4,E4,F4,G4,H4,I4,K4,L4,M4,N4)</f>
         <v/>
       </c>
       <c r="P4" s="1" t="inlineStr">
@@ -2242,28 +2171,25 @@
       </c>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2">
-        <f>117.76+117.76</f>
-        <v/>
-      </c>
-      <c r="E5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2">
+        <f>117.76</f>
+        <v/>
+      </c>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2">
-        <f>117.76</f>
-        <v/>
-      </c>
+      <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
+      <c r="L5" s="2">
+        <f>117.76</f>
+        <v/>
+      </c>
       <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2">
-        <f>117.76</f>
-        <v/>
-      </c>
+      <c r="N5" s="2" t="n"/>
       <c r="O5" s="2">
-        <f>SUM(B5,C5,D5,E5,F5,G5,H5,I5,J5,K5,L5,M5,N5)</f>
+        <f>SUM(B5,C5,D5,E5,F5,G5,H5,I5,K5,L5,M5,N5)</f>
         <v/>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -2292,7 +2218,7 @@
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2">
-        <f>SUM(B6,C6,D6,E6,F6,G6,H6,I6,J6,K6,L6,M6,N6)</f>
+        <f>SUM(B6,C6,D6,E6,F6,G6,H6,I6,K6,L6,M6,N6)</f>
         <v/>
       </c>
       <c r="P6" s="1" t="inlineStr">
@@ -2321,7 +2247,7 @@
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2">
-        <f>SUM(B7,C7,D7,E7,F7,G7,H7,I7,J7,K7,L7,M7,N7)</f>
+        <f>SUM(B7,C7,D7,E7,F7,G7,H7,I7,K7,L7,M7,N7)</f>
         <v/>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -2350,7 +2276,7 @@
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2">
-        <f>SUM(B8,C8,D8,E8,F8,G8,H8,I8,J8,K8,L8,M8,N8)</f>
+        <f>SUM(B8,C8,D8,E8,F8,G8,H8,I8,K8,L8,M8,N8)</f>
         <v/>
       </c>
       <c r="P8" s="1" t="inlineStr">
@@ -2374,10 +2300,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2">
-        <f>SUM(B9,C9,D9,E9,F9,G9,H9,I9,J9,K9,L9,M9,N9)</f>
-        <v/>
-      </c>
+      <c r="O9" s="2" t="n"/>
       <c r="P9" s="1" t="n"/>
     </row>
     <row r="10">
@@ -2395,10 +2318,7 @@
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
       <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2">
-        <f>SUM(B10,C10,D10,E10,F10,G10,H10,I10,J10,K10,L10,M10,N10)</f>
-        <v/>
-      </c>
+      <c r="O10" s="2" t="n"/>
       <c r="P10" s="1" t="n"/>
     </row>
     <row r="11">
@@ -2416,10 +2336,7 @@
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2">
-        <f>SUM(B11,C11,D11,E11,F11,G11,H11,I11,J11,K11,L11,M11,N11)</f>
-        <v/>
-      </c>
+      <c r="O11" s="2" t="n"/>
       <c r="P11" s="1" t="n"/>
     </row>
     <row r="12">
@@ -2442,7 +2359,7 @@
       <c r="M12" s="2" t="n"/>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2">
-        <f>SUM(B12,C12,D12,E12,F12,G12,H12,I12,J12,K12,L12,M12,N12)</f>
+        <f>SUM(B12,C12,D12,E12,F12,G12,H12,I12,K12,L12,M12,N12)</f>
         <v/>
       </c>
       <c r="P12" s="1" t="inlineStr">
@@ -2459,28 +2376,25 @@
       </c>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2">
-        <f>350.00+350.00</f>
-        <v/>
-      </c>
-      <c r="E13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2">
+        <f>350.00</f>
+        <v/>
+      </c>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2">
-        <f>350.00</f>
-        <v/>
-      </c>
+      <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
+      <c r="L13" s="2">
+        <f>350.00</f>
+        <v/>
+      </c>
       <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2">
-        <f>350.00</f>
-        <v/>
-      </c>
+      <c r="N13" s="2" t="n"/>
       <c r="O13" s="2">
-        <f>SUM(B13,C13,D13,E13,F13,G13,H13,I13,J13,K13,L13,M13,N13)</f>
+        <f>SUM(B13,C13,D13,E13,F13,G13,H13,I13,K13,L13,M13,N13)</f>
         <v/>
       </c>
       <c r="P13" s="1" t="inlineStr">
@@ -2509,7 +2423,7 @@
       <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2">
-        <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,J14,K14,L14,M14,N14)</f>
+        <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,K14,L14,M14,N14)</f>
         <v/>
       </c>
       <c r="P14" s="1" t="inlineStr">
@@ -2526,28 +2440,25 @@
       </c>
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2">
-        <f>300.00+300.00</f>
-        <v/>
-      </c>
-      <c r="E15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2">
+        <f>300.00</f>
+        <v/>
+      </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2">
-        <f>300.00</f>
-        <v/>
-      </c>
+      <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n"/>
+      <c r="L15" s="2">
+        <f>300.00</f>
+        <v/>
+      </c>
       <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2">
-        <f>300.00</f>
-        <v/>
-      </c>
+      <c r="N15" s="2" t="n"/>
       <c r="O15" s="2">
-        <f>SUM(B15,C15,D15,E15,F15,G15,H15,I15,J15,K15,L15,M15,N15)</f>
+        <f>SUM(B15,C15,D15,E15,F15,G15,H15,I15,K15,L15,M15,N15)</f>
         <v/>
       </c>
       <c r="P15" s="1" t="inlineStr">
@@ -2576,7 +2487,7 @@
       <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2">
-        <f>SUM(B16,C16,D16,E16,F16,G16,H16,I16,J16,K16,L16,M16,N16)</f>
+        <f>SUM(B16,C16,D16,E16,F16,G16,H16,I16,K16,L16,M16,N16)</f>
         <v/>
       </c>
       <c r="P16" s="1" t="inlineStr">
@@ -2593,28 +2504,25 @@
       </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2">
-        <f>975.00+364.75+1400.00+975.00+364.75+1400.00</f>
-        <v/>
-      </c>
-      <c r="E17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2">
+        <f>975.00+364.75+1400.00</f>
+        <v/>
+      </c>
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2">
-        <f>975.00+364.75+1400.00</f>
-        <v/>
-      </c>
+      <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
+      <c r="L17" s="2">
+        <f>975.00+364.75+1400.00</f>
+        <v/>
+      </c>
       <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2">
-        <f>975.00+364.75+1400.00</f>
-        <v/>
-      </c>
+      <c r="N17" s="2" t="n"/>
       <c r="O17" s="2">
-        <f>SUM(B17,C17,D17,E17,F17,G17,H17,I17,J17,K17,L17,M17,N17)</f>
+        <f>SUM(B17,C17,D17,E17,F17,G17,H17,I17,K17,L17,M17,N17)</f>
         <v/>
       </c>
       <c r="P17" s="1" t="inlineStr">
@@ -2631,28 +2539,25 @@
       </c>
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2">
-        <f>817.29+817.29</f>
-        <v/>
-      </c>
-      <c r="E18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2">
+        <f>817.29</f>
+        <v/>
+      </c>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2">
-        <f>817.29</f>
-        <v/>
-      </c>
+      <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
+      <c r="L18" s="2">
+        <f>817.29</f>
+        <v/>
+      </c>
       <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2">
-        <f>817.29</f>
-        <v/>
-      </c>
+      <c r="N18" s="2" t="n"/>
       <c r="O18" s="2">
-        <f>SUM(B18,C18,D18,E18,F18,G18,H18,I18,J18,K18,L18,M18,N18)</f>
+        <f>SUM(B18,C18,D18,E18,F18,G18,H18,I18,K18,L18,M18,N18)</f>
         <v/>
       </c>
       <c r="P18" s="1" t="inlineStr">
@@ -2681,7 +2586,7 @@
       <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2">
-        <f>SUM(B19,C19,D19,E19,F19,G19,H19,I19,J19,K19,L19,M19,N19)</f>
+        <f>SUM(B19,C19,D19,E19,F19,G19,H19,I19,K19,L19,M19,N19)</f>
         <v/>
       </c>
       <c r="P19" s="1" t="inlineStr">
@@ -2710,7 +2615,7 @@
       <c r="M20" s="2" t="n"/>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2">
-        <f>SUM(B20,C20,D20,E20,F20,G20,H20,I20,J20,K20,L20,M20,N20)</f>
+        <f>SUM(B20,C20,D20,E20,F20,G20,H20,I20,K20,L20,M20,N20)</f>
         <v/>
       </c>
       <c r="P20" s="1" t="inlineStr">
@@ -2739,7 +2644,7 @@
       <c r="M21" s="2" t="n"/>
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2">
-        <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,J21,K21,L21,M21,N21)</f>
+        <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,K21,L21,M21,N21)</f>
         <v/>
       </c>
       <c r="P21" s="1" t="inlineStr">
@@ -2756,28 +2661,25 @@
       </c>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2">
-        <f>385.77+740.00+385.77+740.00</f>
-        <v/>
-      </c>
-      <c r="E22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2">
-        <f>385.77+740.00</f>
-        <v/>
-      </c>
+      <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="n"/>
+      <c r="L22" s="2">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
       <c r="M22" s="2" t="n"/>
-      <c r="N22" s="2">
-        <f>385.77+740.00</f>
-        <v/>
-      </c>
+      <c r="N22" s="2" t="n"/>
       <c r="O22" s="2">
-        <f>SUM(B22,C22,D22,E22,F22,G22,H22,I22,J22,K22,L22,M22,N22)</f>
+        <f>SUM(B22,C22,D22,E22,F22,G22,H22,I22,K22,L22,M22,N22)</f>
         <v/>
       </c>
       <c r="P22" s="1" t="inlineStr">
@@ -2794,28 +2696,25 @@
       </c>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2">
-        <f>800.00+800.00+800.00+800.00</f>
-        <v/>
-      </c>
-      <c r="E23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2">
-        <f>800.00+800.00</f>
-        <v/>
-      </c>
+      <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="n"/>
+      <c r="L23" s="2">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
       <c r="M23" s="2" t="n"/>
-      <c r="N23" s="2">
-        <f>800.00+800.00</f>
-        <v/>
-      </c>
+      <c r="N23" s="2" t="n"/>
       <c r="O23" s="2">
-        <f>SUM(B23,C23,D23,E23,F23,G23,H23,I23,J23,K23,L23,M23,N23)</f>
+        <f>SUM(B23,C23,D23,E23,F23,G23,H23,I23,K23,L23,M23,N23)</f>
         <v/>
       </c>
       <c r="P23" s="1" t="inlineStr">
@@ -2832,28 +2731,25 @@
       </c>
       <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2">
-        <f>490.00+120.00+490.00+120.00</f>
-        <v/>
-      </c>
-      <c r="E24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2">
-        <f>490.00+120.00</f>
-        <v/>
-      </c>
+      <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="n"/>
+      <c r="L24" s="2">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
       <c r="M24" s="2" t="n"/>
-      <c r="N24" s="2">
-        <f>490.00+120.00</f>
-        <v/>
-      </c>
+      <c r="N24" s="2" t="n"/>
       <c r="O24" s="2">
-        <f>SUM(B24,C24,D24,E24,F24,G24,H24,I24,J24,K24,L24,M24,N24)</f>
+        <f>SUM(B24,C24,D24,E24,F24,G24,H24,I24,K24,L24,M24,N24)</f>
         <v/>
       </c>
       <c r="P24" s="1" t="inlineStr">
@@ -2870,28 +2766,25 @@
       </c>
       <c r="B25" s="2" t="n"/>
       <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2">
-        <f>4000.00+4000.00</f>
-        <v/>
-      </c>
-      <c r="E25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2">
+        <f>4000.00</f>
+        <v/>
+      </c>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2">
-        <f>4000.00</f>
-        <v/>
-      </c>
+      <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="n"/>
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2" t="n"/>
+      <c r="L25" s="2">
+        <f>4000.00</f>
+        <v/>
+      </c>
       <c r="M25" s="2" t="n"/>
-      <c r="N25" s="2">
-        <f>4000.00</f>
-        <v/>
-      </c>
+      <c r="N25" s="2" t="n"/>
       <c r="O25" s="2">
-        <f>SUM(B25,C25,D25,E25,F25,G25,H25,I25,J25,K25,L25,M25,N25)</f>
+        <f>SUM(B25,C25,D25,E25,F25,G25,H25,I25,K25,L25,M25,N25)</f>
         <v/>
       </c>
       <c r="P25" s="1" t="inlineStr">
@@ -2920,7 +2813,7 @@
       <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="n"/>
       <c r="O26" s="2">
-        <f>SUM(B26,C26,D26,E26,F26,G26,H26,I26,J26,K26,L26,M26,N26)</f>
+        <f>SUM(B26,C26,D26,E26,F26,G26,H26,I26,K26,L26,M26,N26)</f>
         <v/>
       </c>
       <c r="P26" s="1" t="inlineStr">
@@ -2937,28 +2830,25 @@
       </c>
       <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2">
-        <f>200.00+200.00+200.00+200.00</f>
-        <v/>
-      </c>
-      <c r="E27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2">
-        <f>200.00+200.00</f>
-        <v/>
-      </c>
+      <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2" t="n"/>
+      <c r="L27" s="2">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
       <c r="M27" s="2" t="n"/>
-      <c r="N27" s="2">
-        <f>200.00+200.00</f>
-        <v/>
-      </c>
+      <c r="N27" s="2" t="n"/>
       <c r="O27" s="2">
-        <f>SUM(B27,C27,D27,E27,F27,G27,H27,I27,J27,K27,L27,M27,N27)</f>
+        <f>SUM(B27,C27,D27,E27,F27,G27,H27,I27,K27,L27,M27,N27)</f>
         <v/>
       </c>
       <c r="P27" s="1" t="inlineStr">
@@ -2987,7 +2877,7 @@
       <c r="M28" s="2" t="n"/>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2">
-        <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,J28,K28,L28,M28,N28)</f>
+        <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,K28,L28,M28,N28)</f>
         <v/>
       </c>
       <c r="P28" s="1" t="inlineStr">
@@ -3016,7 +2906,7 @@
       <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2">
-        <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29,N29)</f>
+        <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,K29,L29,M29,N29)</f>
         <v/>
       </c>
       <c r="P29" s="1" t="inlineStr">
@@ -3033,28 +2923,25 @@
       </c>
       <c r="B30" s="2" t="n"/>
       <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2">
-        <f>26.57+26.57</f>
-        <v/>
-      </c>
-      <c r="E30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2">
+        <f>26.57</f>
+        <v/>
+      </c>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2">
-        <f>26.57</f>
-        <v/>
-      </c>
+      <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
+      <c r="L30" s="2">
+        <f>26.57</f>
+        <v/>
+      </c>
       <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2">
-        <f>26.57</f>
-        <v/>
-      </c>
+      <c r="N30" s="2" t="n"/>
       <c r="O30" s="2">
-        <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30,N30)</f>
+        <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,K30,L30,M30,N30)</f>
         <v/>
       </c>
       <c r="P30" s="1" t="inlineStr">
@@ -3071,28 +2958,25 @@
       </c>
       <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2">
-        <f>343.93+343.93</f>
-        <v/>
-      </c>
-      <c r="E31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2">
+        <f>343.93</f>
+        <v/>
+      </c>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2">
-        <f>343.93</f>
-        <v/>
-      </c>
+      <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
+      <c r="L31" s="2">
+        <f>343.93</f>
+        <v/>
+      </c>
       <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2">
-        <f>343.93</f>
-        <v/>
-      </c>
+      <c r="N31" s="2" t="n"/>
       <c r="O31" s="2">
-        <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31,N31)</f>
+        <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,K31,L31,M31,N31)</f>
         <v/>
       </c>
       <c r="P31" s="1" t="inlineStr">
@@ -3109,28 +2993,25 @@
       </c>
       <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2">
-        <f>17.59+17.59</f>
-        <v/>
-      </c>
-      <c r="E32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2">
+        <f>17.59</f>
+        <v/>
+      </c>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2">
-        <f>17.59</f>
-        <v/>
-      </c>
+      <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
+      <c r="L32" s="2">
+        <f>17.59</f>
+        <v/>
+      </c>
       <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2">
-        <f>17.59</f>
-        <v/>
-      </c>
+      <c r="N32" s="2" t="n"/>
       <c r="O32" s="2">
-        <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32,N32)</f>
+        <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,K32,L32,M32,N32)</f>
         <v/>
       </c>
       <c r="P32" s="1" t="inlineStr">
@@ -3147,28 +3028,25 @@
       </c>
       <c r="B33" s="2" t="n"/>
       <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2">
-        <f>152.14+152.14</f>
-        <v/>
-      </c>
-      <c r="E33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2">
+        <f>152.14</f>
+        <v/>
+      </c>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2">
-        <f>152.14</f>
-        <v/>
-      </c>
+      <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="n"/>
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="n"/>
+      <c r="L33" s="2">
+        <f>152.14</f>
+        <v/>
+      </c>
       <c r="M33" s="2" t="n"/>
-      <c r="N33" s="2">
-        <f>152.14</f>
-        <v/>
-      </c>
+      <c r="N33" s="2" t="n"/>
       <c r="O33" s="2">
-        <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33,N33)</f>
+        <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,K33,L33,M33,N33)</f>
         <v/>
       </c>
       <c r="P33" s="1" t="inlineStr">
@@ -3185,28 +3063,25 @@
       </c>
       <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2">
-        <f>71.79+71.79</f>
-        <v/>
-      </c>
-      <c r="E34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2">
+        <f>71.79</f>
+        <v/>
+      </c>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2">
-        <f>71.79</f>
-        <v/>
-      </c>
+      <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="n"/>
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
+      <c r="L34" s="2">
+        <f>71.79</f>
+        <v/>
+      </c>
       <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2">
-        <f>71.79</f>
-        <v/>
-      </c>
+      <c r="N34" s="2" t="n"/>
       <c r="O34" s="2">
-        <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,J34,K34,L34,M34,N34)</f>
+        <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,K34,L34,M34,N34)</f>
         <v/>
       </c>
       <c r="P34" s="1" t="inlineStr">
@@ -3223,28 +3098,25 @@
       </c>
       <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2">
-        <f>75.40+75.40</f>
-        <v/>
-      </c>
-      <c r="E35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2">
+        <f>75.40</f>
+        <v/>
+      </c>
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2">
-        <f>75.40</f>
-        <v/>
-      </c>
+      <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
+      <c r="L35" s="2">
+        <f>75.40</f>
+        <v/>
+      </c>
       <c r="M35" s="2" t="n"/>
-      <c r="N35" s="2">
-        <f>75.40</f>
-        <v/>
-      </c>
+      <c r="N35" s="2" t="n"/>
       <c r="O35" s="2">
-        <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,J35,K35,L35,M35,N35)</f>
+        <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,K35,L35,M35,N35)</f>
         <v/>
       </c>
       <c r="P35" s="1" t="inlineStr">
@@ -3261,28 +3133,25 @@
       </c>
       <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2">
-        <f>18.75+18.75</f>
-        <v/>
-      </c>
-      <c r="E36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2">
+        <f>18.75</f>
+        <v/>
+      </c>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2">
-        <f>18.75</f>
-        <v/>
-      </c>
+      <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="n"/>
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
+      <c r="L36" s="2">
+        <f>18.75</f>
+        <v/>
+      </c>
       <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2">
-        <f>18.75</f>
-        <v/>
-      </c>
+      <c r="N36" s="2" t="n"/>
       <c r="O36" s="2">
-        <f>SUM(B36,C36,D36,E36,F36,G36,H36,I36,J36,K36,L36,M36,N36)</f>
+        <f>SUM(B36,C36,D36,E36,F36,G36,H36,I36,K36,L36,M36,N36)</f>
         <v/>
       </c>
       <c r="P36" s="1" t="inlineStr">
@@ -3299,28 +3168,25 @@
       </c>
       <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2">
-        <f>50.03+50.03</f>
-        <v/>
-      </c>
-      <c r="E37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2">
+        <f>50.03</f>
+        <v/>
+      </c>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2">
-        <f>50.03</f>
-        <v/>
-      </c>
+      <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="n"/>
+      <c r="L37" s="2">
+        <f>50.03</f>
+        <v/>
+      </c>
       <c r="M37" s="2" t="n"/>
-      <c r="N37" s="2">
-        <f>50.03</f>
-        <v/>
-      </c>
+      <c r="N37" s="2" t="n"/>
       <c r="O37" s="2">
-        <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,J37,K37,L37,M37,N37)</f>
+        <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,K37,L37,M37,N37)</f>
         <v/>
       </c>
       <c r="P37" s="1" t="inlineStr">
@@ -3337,28 +3203,25 @@
       </c>
       <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2">
-        <f>20.80+20.80</f>
-        <v/>
-      </c>
-      <c r="E38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2">
+        <f>20.80</f>
+        <v/>
+      </c>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2">
-        <f>20.80</f>
-        <v/>
-      </c>
+      <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="n"/>
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
+      <c r="L38" s="2">
+        <f>20.80</f>
+        <v/>
+      </c>
       <c r="M38" s="2" t="n"/>
-      <c r="N38" s="2">
-        <f>20.80</f>
-        <v/>
-      </c>
+      <c r="N38" s="2" t="n"/>
       <c r="O38" s="2">
-        <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38,N38)</f>
+        <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,K38,L38,M38,N38)</f>
         <v/>
       </c>
       <c r="P38" s="1" t="inlineStr">
@@ -3387,7 +3250,7 @@
       <c r="M39" s="2" t="n"/>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2">
-        <f>SUM(B39,C39,D39,E39,F39,G39,H39,I39,J39,K39,L39,M39,N39)</f>
+        <f>SUM(B39,C39,D39,E39,F39,G39,H39,I39,K39,L39,M39,N39)</f>
         <v/>
       </c>
       <c r="P39" s="1" t="inlineStr">
@@ -3404,28 +3267,25 @@
       </c>
       <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2">
-        <f>40.33+40.33</f>
-        <v/>
-      </c>
-      <c r="E40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2">
+        <f>40.33</f>
+        <v/>
+      </c>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2">
-        <f>40.33</f>
-        <v/>
-      </c>
+      <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
+      <c r="L40" s="2">
+        <f>40.33</f>
+        <v/>
+      </c>
       <c r="M40" s="2" t="n"/>
-      <c r="N40" s="2">
-        <f>40.33</f>
-        <v/>
-      </c>
+      <c r="N40" s="2" t="n"/>
       <c r="O40" s="2">
-        <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,J40,K40,L40,M40,N40)</f>
+        <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,K40,L40,M40,N40)</f>
         <v/>
       </c>
       <c r="P40" s="1" t="inlineStr">
@@ -3442,28 +3302,25 @@
       </c>
       <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2">
-        <f>930.52+930.52</f>
-        <v/>
-      </c>
-      <c r="E41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2">
+        <f>930.52</f>
+        <v/>
+      </c>
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2">
-        <f>930.52</f>
-        <v/>
-      </c>
+      <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
+      <c r="L41" s="2">
+        <f>930.52</f>
+        <v/>
+      </c>
       <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2">
-        <f>930.52</f>
-        <v/>
-      </c>
+      <c r="N41" s="2" t="n"/>
       <c r="O41" s="2">
-        <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41,N41)</f>
+        <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,K41,L41,M41,N41)</f>
         <v/>
       </c>
       <c r="P41" s="1" t="inlineStr">
@@ -3492,7 +3349,7 @@
       <c r="M42" s="2" t="n"/>
       <c r="N42" s="2" t="n"/>
       <c r="O42" s="2">
-        <f>SUM(B42,C42,D42,E42,F42,G42,H42,I42,J42,K42,L42,M42,N42)</f>
+        <f>SUM(B42,C42,D42,E42,F42,G42,H42,I42,K42,L42,M42,N42)</f>
         <v/>
       </c>
       <c r="P42" s="1" t="inlineStr">
@@ -3509,28 +3366,25 @@
       </c>
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2">
-        <f>1000.00+3200.00+1000.00+3200.00</f>
-        <v/>
-      </c>
-      <c r="E43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2">
-        <f>1000.00+3200.00</f>
-        <v/>
-      </c>
+      <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="n"/>
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
-      <c r="L43" s="2" t="n"/>
+      <c r="L43" s="2">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
       <c r="M43" s="2" t="n"/>
-      <c r="N43" s="2">
-        <f>1000.00+3200.00</f>
-        <v/>
-      </c>
+      <c r="N43" s="2" t="n"/>
       <c r="O43" s="2">
-        <f>SUM(B43,C43,D43,E43,F43,G43,H43,I43,J43,K43,L43,M43,N43)</f>
+        <f>SUM(B43,C43,D43,E43,F43,G43,H43,I43,K43,L43,M43,N43)</f>
         <v/>
       </c>
       <c r="P43" s="1" t="inlineStr">
@@ -3540,65 +3394,94 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>discover Bank Net/Mobile</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2">
+        <f>SUM(B44,C44,D44,E44,F44,G44,H44,I44,K44,L44,M44,N44)</f>
+        <v/>
+      </c>
+      <c r="P44" s="1" t="inlineStr">
+        <is>
+          <t>OFFICE EXPENSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B44" s="3">
-        <f>SUM(B2:B43)</f>
-        <v/>
-      </c>
-      <c r="C44" s="3">
-        <f>SUM(C2:C43)</f>
-        <v/>
-      </c>
-      <c r="D44" s="3">
-        <f>SUM(D2:D43)</f>
-        <v/>
-      </c>
-      <c r="E44" s="3">
-        <f>SUM(E2:E43)</f>
-        <v/>
-      </c>
-      <c r="F44" s="3">
-        <f>SUM(F2:F43)</f>
-        <v/>
-      </c>
-      <c r="G44" s="3">
-        <f>SUM(G2:G43)</f>
-        <v/>
-      </c>
-      <c r="H44" s="3">
-        <f>SUM(H2:H43)</f>
-        <v/>
-      </c>
-      <c r="I44" s="3">
-        <f>SUM(I2:I43)</f>
-        <v/>
-      </c>
-      <c r="J44" s="3">
-        <f>SUM(J2:J43)</f>
-        <v/>
-      </c>
-      <c r="K44" s="3">
-        <f>SUM(K2:K43)</f>
-        <v/>
-      </c>
-      <c r="L44" s="3">
-        <f>SUM(L2:L43)</f>
-        <v/>
-      </c>
-      <c r="M44" s="3">
-        <f>SUM(M2:M43)</f>
-        <v/>
-      </c>
-      <c r="N44" s="3">
-        <f>SUM(N2:N43)</f>
-        <v/>
-      </c>
-      <c r="O44" s="3">
-        <f>SUM(B44,C44,D44,E44,F44,G44,H44,I44,J44,K44,L44,M44,N44)</f>
+      <c r="B45" s="3">
+        <f>SUM(B2:B44)</f>
+        <v/>
+      </c>
+      <c r="C45" s="3">
+        <f>SUM(C2:C44)</f>
+        <v/>
+      </c>
+      <c r="D45" s="3">
+        <f>SUM(D2:D44)</f>
+        <v/>
+      </c>
+      <c r="E45" s="3">
+        <f>SUM(E2:E44)</f>
+        <v/>
+      </c>
+      <c r="F45" s="3">
+        <f>SUM(F2:F44)</f>
+        <v/>
+      </c>
+      <c r="G45" s="3">
+        <f>SUM(G2:G44)</f>
+        <v/>
+      </c>
+      <c r="H45" s="3">
+        <f>SUM(H2:H44)</f>
+        <v/>
+      </c>
+      <c r="I45" s="3">
+        <f>SUM(I2:I44)</f>
+        <v/>
+      </c>
+      <c r="J45" s="3">
+        <f>SUM(J2:J44)</f>
+        <v/>
+      </c>
+      <c r="K45" s="3">
+        <f>SUM(K2:K44)</f>
+        <v/>
+      </c>
+      <c r="L45" s="3">
+        <f>SUM(L2:L44)</f>
+        <v/>
+      </c>
+      <c r="M45" s="3">
+        <f>SUM(M2:M44)</f>
+        <v/>
+      </c>
+      <c r="N45" s="3">
+        <f>SUM(N2:N44)</f>
+        <v/>
+      </c>
+      <c r="O45" s="3">
+        <f>SUM(B45,C45,D45,E45,F45,G45,H45,I45,K45,L45,M45,N45)</f>
         <v/>
       </c>
     </row>
@@ -3739,10 +3622,7 @@
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2">
-        <f>16.25</f>
-        <v/>
-      </c>
+      <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
@@ -3806,10 +3686,7 @@
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2">
-        <f>117.76</f>
-        <v/>
-      </c>
+      <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
@@ -3960,10 +3837,7 @@
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2">
-        <f>350.00</f>
-        <v/>
-      </c>
+      <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
@@ -4027,10 +3901,7 @@
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2">
-        <f>300.00</f>
-        <v/>
-      </c>
+      <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
@@ -4094,10 +3965,7 @@
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2">
-        <f>975.00+364.75+1400.00</f>
-        <v/>
-      </c>
+      <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
@@ -4132,10 +4000,7 @@
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2">
-        <f>817.29</f>
-        <v/>
-      </c>
+      <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n"/>
@@ -4257,10 +4122,7 @@
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2">
-        <f>385.77+740.00</f>
-        <v/>
-      </c>
+      <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
@@ -4295,10 +4157,7 @@
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2">
-        <f>800.00+800.00</f>
-        <v/>
-      </c>
+      <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
@@ -4333,10 +4192,7 @@
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2">
-        <f>490.00+120.00</f>
-        <v/>
-      </c>
+      <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
@@ -4371,10 +4227,7 @@
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2">
-        <f>4000.00</f>
-        <v/>
-      </c>
+      <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
@@ -4438,10 +4291,7 @@
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2">
-        <f>200.00+200.00</f>
-        <v/>
-      </c>
+      <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
@@ -4534,10 +4384,7 @@
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2">
-        <f>26.57</f>
-        <v/>
-      </c>
+      <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
@@ -4572,10 +4419,7 @@
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2">
-        <f>343.93</f>
-        <v/>
-      </c>
+      <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
@@ -4610,10 +4454,7 @@
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2">
-        <f>17.59</f>
-        <v/>
-      </c>
+      <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="n"/>
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="n"/>
@@ -4648,10 +4489,7 @@
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2">
-        <f>152.14</f>
-        <v/>
-      </c>
+      <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="n"/>
@@ -4686,10 +4524,7 @@
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2">
-        <f>71.79</f>
-        <v/>
-      </c>
+      <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
@@ -4724,10 +4559,7 @@
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2">
-        <f>75.40</f>
-        <v/>
-      </c>
+      <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
@@ -4762,10 +4594,7 @@
       <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2">
-        <f>18.75</f>
-        <v/>
-      </c>
+      <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="n"/>
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="n"/>
@@ -4800,10 +4629,7 @@
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2">
-        <f>50.03</f>
-        <v/>
-      </c>
+      <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="n"/>
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="n"/>
@@ -4838,10 +4664,7 @@
       <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2">
-        <f>20.80</f>
-        <v/>
-      </c>
+      <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="n"/>
@@ -4905,10 +4728,7 @@
       <c r="E37" s="2" t="n"/>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2">
-        <f>40.33</f>
-        <v/>
-      </c>
+      <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="n"/>
@@ -4943,10 +4763,7 @@
       <c r="E38" s="2" t="n"/>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2">
-        <f>930.52</f>
-        <v/>
-      </c>
+      <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="n"/>
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="n"/>
@@ -5010,10 +4827,7 @@
       <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2">
-        <f>1000.00+3200.00</f>
-        <v/>
-      </c>
+      <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
@@ -5101,6 +4915,7 @@
         <v/>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>

--- a/credit_monthly_summary.xlsx
+++ b/credit_monthly_summary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="2" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="CHASE #3444" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CHASE #3444'!$A$2:$S$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CHASE DETIAL#3444'!$A$1:$P$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CHASE DETIAL#3444'!$A$1:$O$44</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
@@ -131,11 +131,11 @@
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -526,29 +526,9 @@
     <col width="6" bestFit="1" customWidth="1" min="27" max="28"/>
     <col width="7.140625" bestFit="1" customWidth="1" min="29" max="29"/>
     <col width="6" bestFit="1" customWidth="1" min="30" max="30"/>
-    <col width="6" bestFit="1" customWidth="1" min="31" max="31"/>
-    <col width="6" bestFit="1" customWidth="1" min="32" max="32"/>
-    <col width="6" bestFit="1" customWidth="1" min="33" max="33"/>
-    <col width="6" customWidth="1" min="34" max="34"/>
-    <col width="6" customWidth="1" min="35" max="35"/>
-    <col width="6" customWidth="1" min="36" max="36"/>
-    <col width="6" customWidth="1" min="37" max="37"/>
-    <col width="6" customWidth="1" min="38" max="38"/>
-    <col width="6" customWidth="1" min="39" max="39"/>
-    <col width="6" customWidth="1" min="40" max="40"/>
-    <col width="6" customWidth="1" min="41" max="41"/>
-    <col width="6" customWidth="1" min="42" max="42"/>
-    <col width="6" customWidth="1" min="43" max="43"/>
-    <col width="6" customWidth="1" min="44" max="44"/>
-    <col width="6" customWidth="1" min="45" max="45"/>
-    <col width="6" customWidth="1" min="46" max="46"/>
-    <col width="6" customWidth="1" min="47" max="47"/>
-    <col width="6" customWidth="1" min="48" max="48"/>
-    <col width="6" customWidth="1" min="49" max="49"/>
-    <col width="6" customWidth="1" min="50" max="50"/>
-    <col width="6" customWidth="1" min="51" max="51"/>
-    <col width="6" customWidth="1" min="52" max="52"/>
-    <col width="6" customWidth="1" min="53" max="53"/>
+    <col width="13.85546875" bestFit="1" customWidth="1" min="31" max="31"/>
+    <col width="9.28515625" bestFit="1" customWidth="1" min="32" max="32"/>
+    <col width="17.42578125" bestFit="1" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -575,12 +555,6 @@
       <c r="Q1" s="11" t="n"/>
       <c r="R1" s="11" t="n"/>
       <c r="S1" s="12" t="n"/>
-      <c r="T1" s="11" t="n"/>
-      <c r="U1" s="11" t="n"/>
-      <c r="V1" s="11" t="n"/>
-      <c r="W1" s="11" t="n"/>
-      <c r="X1" s="11" t="n"/>
-      <c r="Y1" s="11" t="n"/>
       <c r="Z1" s="11" t="n"/>
       <c r="AA1" s="11" t="n"/>
       <c r="AB1" s="11" t="n"/>
@@ -597,7 +571,7 @@
       <c r="AM1" s="11" t="n"/>
       <c r="AN1" s="11" t="n"/>
       <c r="AO1" s="11" t="n"/>
-      <c r="AP1" s="11" t="n"/>
+      <c r="AP1" s="12" t="n"/>
       <c r="AQ1" s="11" t="n"/>
       <c r="AR1" s="11" t="n"/>
       <c r="AS1" s="11" t="n"/>
@@ -614,159 +588,151 @@
       <c r="BD1" s="12" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>Begin</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
+      <c r="A2" s="10" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*V25 Seattle WA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Amazon.Comseattlewa US</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Citi Card Onlinepayment</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Prog Casualty Ins Prem</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Credit One Bank Payment</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Irs Usataxpymt</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Amazon Prime*Zh8618Uz3 Amzn.Com/Bill WA</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Kindercare Portland OR</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Nys Dtf Pit Tax Paymnt</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*9O5 Seattle WA</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>POS Mac Amazon.Com*Nx6 Seattle WA</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Withdrawal Branch 0964 New York</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Internet Trf To Client-Added Transfer Account</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>No1 Sushi 88 Corkbbo ACH</t>
+        </is>
+      </c>
       <c r="Z2" s="10" t="n"/>
       <c r="AA2" s="10" t="n"/>
       <c r="AB2" s="10" t="n"/>
       <c r="AC2" s="10" t="n"/>
       <c r="AD2" s="10" t="n"/>
-      <c r="AE2" s="10" t="inlineStr">
-        <is>
-          <t>NO1 SUSHI 88 CORKBBO ACH</t>
-        </is>
-      </c>
-      <c r="AF2" s="10" t="inlineStr">
-        <is>
-          <t>INTERNET TRF TO CLIENT-ADDED TRANSFER ACCOUNT</t>
-        </is>
-      </c>
-      <c r="AG2" s="10" t="inlineStr">
-        <is>
-          <t>BILL PAY:VEOLIA WATER NEW Y 200045 6BU1T6KR</t>
-        </is>
-      </c>
-      <c r="AH2" s="10" t="inlineStr">
-        <is>
-          <t>BILL PAY:ORANGE &amp; ROCKLAND 136130 6BQ1P6KR</t>
-        </is>
-      </c>
-      <c r="AI2" s="10" t="inlineStr">
-        <is>
-          <t>WITHDRAWAL BRANCH 0964 NEW YORK</t>
-        </is>
-      </c>
-      <c r="AJ2" s="10" t="inlineStr">
-        <is>
-          <t>POS MAC AMAZON.COM*NX6 SEATTLE WA</t>
-        </is>
-      </c>
-      <c r="AK2" s="10" t="inlineStr">
-        <is>
-          <t>POS MAC AMAZON.COM*9O5 SEATTLE WA</t>
-        </is>
-      </c>
-      <c r="AL2" s="10" t="inlineStr">
-        <is>
-          <t>POS MAC AMAZON.COM*SB8 SEATTLE WA</t>
-        </is>
-      </c>
-      <c r="AM2" s="10" t="inlineStr">
-        <is>
-          <t>NYS DTF PIT TAX PAYMNT</t>
-        </is>
-      </c>
-      <c r="AN2" s="10" t="inlineStr">
-        <is>
-          <t>KINDERCARE PORTLAND OR</t>
-        </is>
-      </c>
-      <c r="AO2" s="10" t="inlineStr">
-        <is>
-          <t>AMAZON PRIME*ZH8618UZ3 AMZN.COM/BILL WA</t>
-        </is>
-      </c>
-      <c r="AP2" s="10" t="inlineStr">
-        <is>
-          <t>IRS USATAXPYMT</t>
-        </is>
-      </c>
-      <c r="AQ2" s="10" t="inlineStr">
-        <is>
-          <t>CREDIT ONE BANK PAYMENT</t>
-        </is>
-      </c>
-      <c r="AR2" s="10" t="inlineStr">
-        <is>
-          <t>PROG CASUALTY INS PREM</t>
-        </is>
-      </c>
-      <c r="AS2" s="10" t="inlineStr">
-        <is>
-          <t>CITI CARD ONLINEPAYMENT</t>
-        </is>
-      </c>
-      <c r="AT2" s="10" t="inlineStr">
-        <is>
-          <t>AMAZON.COMSEATTLEWA US</t>
-        </is>
-      </c>
-      <c r="AU2" s="10" t="inlineStr">
-        <is>
-          <t>POS MAC AMAZON.COM*TN0 SEATTLE WA</t>
-        </is>
-      </c>
-      <c r="AV2" s="10" t="inlineStr">
-        <is>
-          <t>POS MAC AMAZON.COM*MZ5 SEATTLE WA</t>
-        </is>
-      </c>
-      <c r="AW2" s="10" t="inlineStr">
-        <is>
-          <t>POS MAC AMAZON.COM*GE2 SEATTLE WA</t>
-        </is>
-      </c>
-      <c r="AX2" s="10" t="inlineStr">
-        <is>
-          <t>POS MAC AMAZON.COM*V25 SEATTLE WA</t>
-        </is>
-      </c>
-      <c r="AY2" s="10" t="inlineStr">
-        <is>
-          <t>POS MAC AMAZON.COM*ZA2 SEATTLE WA</t>
-        </is>
-      </c>
-      <c r="AZ2" s="10" t="inlineStr">
-        <is>
-          <t>POS MAC AMAZON.COM*AU5 SEATTLE WA</t>
-        </is>
-      </c>
-      <c r="BA2" s="10" t="inlineStr">
-        <is>
-          <t>POS MAC AMAZON.COM*BQ9 SEATTLE WA</t>
-        </is>
-      </c>
+      <c r="AE2" s="10" t="n"/>
+      <c r="AF2" s="10" t="n"/>
+      <c r="AG2" s="10" t="n"/>
+      <c r="AH2" s="10" t="n"/>
+      <c r="AI2" s="10" t="n"/>
+      <c r="AJ2" s="10" t="n"/>
+      <c r="AK2" s="10" t="n"/>
+      <c r="AL2" s="10" t="n"/>
+      <c r="AM2" s="10" t="n"/>
+      <c r="AN2" s="10" t="n"/>
+      <c r="AO2" s="10" t="n"/>
+      <c r="AP2" s="10" t="n"/>
+      <c r="AQ2" s="10" t="n"/>
+      <c r="AR2" s="10" t="n"/>
+      <c r="AS2" s="10" t="n"/>
+      <c r="AT2" s="10" t="n"/>
+      <c r="AU2" s="10" t="n"/>
+      <c r="AV2" s="10" t="n"/>
+      <c r="AW2" s="10" t="n"/>
+      <c r="AX2" s="10" t="n"/>
+      <c r="AY2" s="10" t="n"/>
+      <c r="AZ2" s="10" t="n"/>
+      <c r="BA2" s="10" t="n"/>
       <c r="BB2" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -790,56 +756,102 @@
       <c r="B3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
-      <c r="X3" s="2" t="n"/>
-      <c r="Y3" s="2" t="n"/>
+      <c r="C3" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="D3" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="E3" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>152.14</v>
+      </c>
+      <c r="H3" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="J3" t="n">
+        <v>117.76</v>
+      </c>
+      <c r="K3" t="n">
+        <v>975</v>
+      </c>
+      <c r="L3" t="n">
+        <v>930.52</v>
+      </c>
+      <c r="M3" t="n">
+        <v>817.29</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="O3" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="P3" t="n">
+        <v>610</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>400</v>
+      </c>
+      <c r="R3" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="S3" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="T3" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4200</v>
+      </c>
+      <c r="V3" t="n">
+        <v>350</v>
+      </c>
+      <c r="W3" t="n">
+        <v>300</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1125.77</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4000</v>
+      </c>
       <c r="Z3" s="2" t="n"/>
-      <c r="AA3" s="2" t="n"/>
+      <c r="AA3" s="2">
+        <f>4000</f>
+        <v/>
+      </c>
       <c r="AB3" s="2" t="n"/>
       <c r="AC3" s="2" t="n"/>
       <c r="AD3" s="2" t="n"/>
-      <c r="AE3" s="2">
-        <f>4000.00</f>
-        <v/>
-      </c>
+      <c r="AE3" s="2" t="n"/>
       <c r="AF3" s="2">
-        <f>385.77+740.00</f>
+        <f>300</f>
         <v/>
       </c>
       <c r="AG3" s="2">
-        <f>300.00</f>
+        <f>350</f>
         <v/>
       </c>
       <c r="AH3" s="2">
-        <f>350.00</f>
+        <f>385.77+740</f>
         <v/>
       </c>
       <c r="AI3" s="2">
-        <f>1000.00+3200.00</f>
+        <f>1000+3200</f>
         <v/>
       </c>
       <c r="AJ3" s="2">
-        <f>75.40</f>
+        <f>75.4</f>
         <v/>
       </c>
       <c r="AK3" s="2">
@@ -851,11 +863,11 @@
         <v/>
       </c>
       <c r="AM3" s="2">
-        <f>200.00+200.00</f>
+        <f>200+200</f>
         <v/>
       </c>
       <c r="AN3" s="2">
-        <f>490.00+120.00</f>
+        <f>490+120</f>
         <v/>
       </c>
       <c r="AO3" s="2">
@@ -863,7 +875,7 @@
         <v/>
       </c>
       <c r="AP3" s="2">
-        <f>800.00+800.00</f>
+        <f>800+800</f>
         <v/>
       </c>
       <c r="AQ3" s="2">
@@ -875,7 +887,7 @@
         <v/>
       </c>
       <c r="AS3" s="2">
-        <f>975.00+364.75+1400.00</f>
+        <f>975</f>
         <v/>
       </c>
       <c r="AT3" s="2">
@@ -895,7 +907,7 @@
         <v/>
       </c>
       <c r="AX3" s="2">
-        <f>20.80</f>
+        <f>20.8</f>
         <v/>
       </c>
       <c r="AY3" s="2">
@@ -911,12 +923,15 @@
         <v/>
       </c>
       <c r="BB3" s="2">
-        <f>SUM(C3:BA3)</f>
-        <v/>
-      </c>
-      <c r="BC3" s="2" t="n"/>
+        <f>SUM(C3:AD3)</f>
+        <v/>
+      </c>
+      <c r="BC3" s="2">
+        <f>'CHASE DETIAL#3444'!B45</f>
+        <v/>
+      </c>
       <c r="BD3" s="2">
-        <f>B3+BB3-BC3</f>
+        <f>B3+AE3-AF3</f>
         <v/>
       </c>
     </row>
@@ -925,32 +940,9 @@
         <v>45413</v>
       </c>
       <c r="B4" s="2">
-        <f>AG3</f>
-        <v/>
-      </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
-      <c r="P4" s="2" t="n"/>
-      <c r="Q4" s="2" t="n"/>
-      <c r="R4" s="2" t="n"/>
-      <c r="S4" s="2" t="n"/>
-      <c r="T4" s="2" t="n"/>
-      <c r="U4" s="2" t="n"/>
-      <c r="V4" s="2" t="n"/>
-      <c r="W4" s="2" t="n"/>
-      <c r="X4" s="2" t="n"/>
-      <c r="Y4" s="2" t="n"/>
+        <f>S3</f>
+        <v/>
+      </c>
       <c r="Z4" s="2" t="n"/>
       <c r="AA4" s="2" t="n"/>
       <c r="AB4" s="2" t="n"/>
@@ -980,12 +972,12 @@
       <c r="AZ4" s="2" t="n"/>
       <c r="BA4" s="2" t="n"/>
       <c r="BB4" s="2">
-        <f>SUM(C4:BA4)</f>
+        <f>SUM(C4:AD4)</f>
         <v/>
       </c>
       <c r="BC4" s="2" t="n"/>
       <c r="BD4" s="2">
-        <f>B4+BB4-BC4</f>
+        <f>B4+AE4-AF4</f>
         <v/>
       </c>
     </row>
@@ -994,32 +986,9 @@
         <v>45444</v>
       </c>
       <c r="B5" s="2">
-        <f>AG4</f>
-        <v/>
-      </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n"/>
-      <c r="Q5" s="2" t="n"/>
-      <c r="R5" s="2" t="n"/>
-      <c r="S5" s="2" t="n"/>
-      <c r="T5" s="2" t="n"/>
-      <c r="U5" s="2" t="n"/>
-      <c r="V5" s="2" t="n"/>
-      <c r="W5" s="2" t="n"/>
-      <c r="X5" s="2" t="n"/>
-      <c r="Y5" s="2" t="n"/>
+        <f>S4</f>
+        <v/>
+      </c>
       <c r="Z5" s="2" t="n"/>
       <c r="AA5" s="2" t="n"/>
       <c r="AB5" s="2" t="n"/>
@@ -1049,12 +1018,12 @@
       <c r="AZ5" s="2" t="n"/>
       <c r="BA5" s="2" t="n"/>
       <c r="BB5" s="2">
-        <f>SUM(C5:BA5)</f>
+        <f>SUM(C5:AD5)</f>
         <v/>
       </c>
       <c r="BC5" s="2" t="n"/>
       <c r="BD5" s="2">
-        <f>B5+BB5-BC5</f>
+        <f>B5+AE5-AF5</f>
         <v/>
       </c>
     </row>
@@ -1063,136 +1032,44 @@
         <v>45474</v>
       </c>
       <c r="B6" s="2">
-        <f>AG5</f>
-        <v/>
-      </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
-      <c r="R6" s="2" t="n"/>
-      <c r="S6" s="2" t="n"/>
-      <c r="T6" s="2" t="n"/>
-      <c r="U6" s="2" t="n"/>
-      <c r="V6" s="2" t="n"/>
-      <c r="W6" s="2" t="n"/>
-      <c r="X6" s="2" t="n"/>
-      <c r="Y6" s="2" t="n"/>
+        <f>S5</f>
+        <v/>
+      </c>
       <c r="Z6" s="2" t="n"/>
       <c r="AA6" s="2" t="n"/>
       <c r="AB6" s="2" t="n"/>
       <c r="AC6" s="2" t="n"/>
       <c r="AD6" s="2" t="n"/>
-      <c r="AE6" s="2">
-        <f>4000.00</f>
-        <v/>
-      </c>
-      <c r="AF6" s="2">
-        <f>385.77+740.00</f>
-        <v/>
-      </c>
-      <c r="AG6" s="2">
-        <f>300.00</f>
-        <v/>
-      </c>
-      <c r="AH6" s="2">
-        <f>350.00</f>
-        <v/>
-      </c>
-      <c r="AI6" s="2">
-        <f>1000.00+3200.00</f>
-        <v/>
-      </c>
-      <c r="AJ6" s="2">
-        <f>75.40</f>
-        <v/>
-      </c>
-      <c r="AK6" s="2">
-        <f>26.57</f>
-        <v/>
-      </c>
-      <c r="AL6" s="2">
-        <f>18.75</f>
-        <v/>
-      </c>
-      <c r="AM6" s="2">
-        <f>200.00+200.00</f>
-        <v/>
-      </c>
-      <c r="AN6" s="2">
-        <f>490.00+120.00</f>
-        <v/>
-      </c>
-      <c r="AO6" s="2">
-        <f>16.25</f>
-        <v/>
-      </c>
-      <c r="AP6" s="2">
-        <f>800.00+800.00</f>
-        <v/>
-      </c>
-      <c r="AQ6" s="2">
-        <f>817.29</f>
-        <v/>
-      </c>
-      <c r="AR6" s="2">
-        <f>930.52</f>
-        <v/>
-      </c>
-      <c r="AS6" s="2">
-        <f>975.00+364.75+1400.00</f>
-        <v/>
-      </c>
-      <c r="AT6" s="2">
-        <f>117.76</f>
-        <v/>
-      </c>
-      <c r="AU6" s="2">
-        <f>50.03</f>
-        <v/>
-      </c>
-      <c r="AV6" s="2">
-        <f>71.79</f>
-        <v/>
-      </c>
-      <c r="AW6" s="2">
-        <f>152.14</f>
-        <v/>
-      </c>
-      <c r="AX6" s="2">
-        <f>20.80</f>
-        <v/>
-      </c>
-      <c r="AY6" s="2">
-        <f>40.33</f>
-        <v/>
-      </c>
-      <c r="AZ6" s="2">
-        <f>343.93</f>
-        <v/>
-      </c>
-      <c r="BA6" s="2">
-        <f>17.59</f>
-        <v/>
-      </c>
+      <c r="AE6" s="2" t="n"/>
+      <c r="AF6" s="2" t="n"/>
+      <c r="AG6" s="2" t="n"/>
+      <c r="AH6" s="2" t="n"/>
+      <c r="AI6" s="2" t="n"/>
+      <c r="AJ6" s="2" t="n"/>
+      <c r="AK6" s="2" t="n"/>
+      <c r="AL6" s="2" t="n"/>
+      <c r="AM6" s="2" t="n"/>
+      <c r="AN6" s="2" t="n"/>
+      <c r="AO6" s="2" t="n"/>
+      <c r="AP6" s="2" t="n"/>
+      <c r="AQ6" s="2" t="n"/>
+      <c r="AR6" s="2" t="n"/>
+      <c r="AS6" s="2" t="n"/>
+      <c r="AT6" s="2" t="n"/>
+      <c r="AU6" s="2" t="n"/>
+      <c r="AV6" s="2" t="n"/>
+      <c r="AW6" s="2" t="n"/>
+      <c r="AX6" s="2" t="n"/>
+      <c r="AY6" s="2" t="n"/>
+      <c r="AZ6" s="2" t="n"/>
+      <c r="BA6" s="2" t="n"/>
       <c r="BB6" s="2">
-        <f>SUM(C6:BA6)</f>
+        <f>SUM(C6:AD6)</f>
         <v/>
       </c>
       <c r="BC6" s="2" t="n"/>
       <c r="BD6" s="2">
-        <f>B6+BB6-BC6</f>
+        <f>B6+AE6-AF6</f>
         <v/>
       </c>
     </row>
@@ -1201,32 +1078,78 @@
         <v>45505</v>
       </c>
       <c r="B7" s="2">
-        <f>AG6</f>
-        <v/>
-      </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="n"/>
-      <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2" t="n"/>
-      <c r="P7" s="2" t="n"/>
-      <c r="Q7" s="2" t="n"/>
-      <c r="R7" s="2" t="n"/>
-      <c r="S7" s="2" t="n"/>
-      <c r="T7" s="2" t="n"/>
-      <c r="U7" s="2" t="n"/>
-      <c r="V7" s="2" t="n"/>
-      <c r="W7" s="2" t="n"/>
-      <c r="X7" s="2" t="n"/>
-      <c r="Y7" s="2" t="n"/>
+        <f>S6</f>
+        <v/>
+      </c>
+      <c r="C7" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="D7" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="E7" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="F7" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>152.14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="J7" t="n">
+        <v>117.76</v>
+      </c>
+      <c r="K7" t="n">
+        <v>975</v>
+      </c>
+      <c r="L7" t="n">
+        <v>930.52</v>
+      </c>
+      <c r="M7" t="n">
+        <v>817.29</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1600</v>
+      </c>
+      <c r="O7" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="P7" t="n">
+        <v>610</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>400</v>
+      </c>
+      <c r="R7" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="S7" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="T7" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4200</v>
+      </c>
+      <c r="V7" t="n">
+        <v>350</v>
+      </c>
+      <c r="W7" t="n">
+        <v>300</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1125.77</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4000</v>
+      </c>
       <c r="Z7" s="2" t="n"/>
       <c r="AA7" s="2" t="n"/>
       <c r="AB7" s="2" t="n"/>
@@ -1256,12 +1179,12 @@
       <c r="AZ7" s="2" t="n"/>
       <c r="BA7" s="2" t="n"/>
       <c r="BB7" s="2">
-        <f>SUM(C7:BA7)</f>
+        <f>SUM(C7:AD7)</f>
         <v/>
       </c>
       <c r="BC7" s="2" t="n"/>
       <c r="BD7" s="2">
-        <f>B7+BB7-BC7</f>
+        <f>B7+AE7-AF7</f>
         <v/>
       </c>
     </row>
@@ -1270,32 +1193,9 @@
         <v>45536</v>
       </c>
       <c r="B8" s="2">
-        <f>AG7</f>
-        <v/>
-      </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
-      <c r="P8" s="2" t="n"/>
-      <c r="Q8" s="2" t="n"/>
-      <c r="R8" s="2" t="n"/>
-      <c r="S8" s="2" t="n"/>
-      <c r="T8" s="2" t="n"/>
-      <c r="U8" s="2" t="n"/>
-      <c r="V8" s="2" t="n"/>
-      <c r="W8" s="2" t="n"/>
-      <c r="X8" s="2" t="n"/>
-      <c r="Y8" s="2" t="n"/>
+        <f>S7</f>
+        <v/>
+      </c>
       <c r="Z8" s="2" t="n"/>
       <c r="AA8" s="2" t="n"/>
       <c r="AB8" s="2" t="n"/>
@@ -1325,12 +1225,12 @@
       <c r="AZ8" s="2" t="n"/>
       <c r="BA8" s="2" t="n"/>
       <c r="BB8" s="2">
-        <f>SUM(C8:BA8)</f>
+        <f>SUM(C8:AD8)</f>
         <v/>
       </c>
       <c r="BC8" s="2" t="n"/>
       <c r="BD8" s="2">
-        <f>B8+BB8-BC8</f>
+        <f>B8+AE8-AF8</f>
         <v/>
       </c>
     </row>
@@ -1339,32 +1239,9 @@
         <v>45566</v>
       </c>
       <c r="B9" s="2">
-        <f>AG8</f>
-        <v/>
-      </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
-      <c r="P9" s="2" t="n"/>
-      <c r="Q9" s="2" t="n"/>
-      <c r="R9" s="2" t="n"/>
-      <c r="S9" s="2" t="n"/>
-      <c r="T9" s="2" t="n"/>
-      <c r="U9" s="2" t="n"/>
-      <c r="V9" s="2" t="n"/>
-      <c r="W9" s="2" t="n"/>
-      <c r="X9" s="2" t="n"/>
-      <c r="Y9" s="2" t="n"/>
+        <f>S8</f>
+        <v/>
+      </c>
       <c r="Z9" s="2" t="n"/>
       <c r="AA9" s="2" t="n"/>
       <c r="AB9" s="2" t="n"/>
@@ -1394,12 +1271,12 @@
       <c r="AZ9" s="2" t="n"/>
       <c r="BA9" s="2" t="n"/>
       <c r="BB9" s="2">
-        <f>SUM(C9:BA9)</f>
+        <f>SUM(C9:AD9)</f>
         <v/>
       </c>
       <c r="BC9" s="2" t="n"/>
       <c r="BD9" s="2">
-        <f>B9+BB9-BC9</f>
+        <f>B9+AE9-AF9</f>
         <v/>
       </c>
     </row>
@@ -1408,32 +1285,78 @@
         <v>45597</v>
       </c>
       <c r="B10" s="2">
-        <f>AG9</f>
-        <v/>
-      </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
-      <c r="R10" s="2" t="n"/>
-      <c r="S10" s="2" t="n"/>
-      <c r="T10" s="2" t="n"/>
-      <c r="U10" s="2" t="n"/>
-      <c r="V10" s="2" t="n"/>
-      <c r="W10" s="2" t="n"/>
-      <c r="X10" s="2" t="n"/>
-      <c r="Y10" s="2" t="n"/>
+        <f>S9</f>
+        <v/>
+      </c>
+      <c r="C10" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="D10" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="E10" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="F10" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>152.14</v>
+      </c>
+      <c r="H10" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="I10" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="J10" t="n">
+        <v>117.76</v>
+      </c>
+      <c r="K10" t="n">
+        <v>975</v>
+      </c>
+      <c r="L10" t="n">
+        <v>930.52</v>
+      </c>
+      <c r="M10" t="n">
+        <v>817.29</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1600</v>
+      </c>
+      <c r="O10" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="P10" t="n">
+        <v>610</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>400</v>
+      </c>
+      <c r="R10" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="S10" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="T10" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4200</v>
+      </c>
+      <c r="V10" t="n">
+        <v>350</v>
+      </c>
+      <c r="W10" t="n">
+        <v>300</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1125.77</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4000</v>
+      </c>
       <c r="Z10" s="2" t="n"/>
       <c r="AA10" s="2" t="n"/>
       <c r="AB10" s="2" t="n"/>
@@ -1463,12 +1386,12 @@
       <c r="AZ10" s="2" t="n"/>
       <c r="BA10" s="2" t="n"/>
       <c r="BB10" s="2">
-        <f>SUM(C10:BA10)</f>
+        <f>SUM(C10:AD10)</f>
         <v/>
       </c>
       <c r="BC10" s="2" t="n"/>
       <c r="BD10" s="2">
-        <f>B10+BB10-BC10</f>
+        <f>B10+AE10-AF10</f>
         <v/>
       </c>
     </row>
@@ -1477,32 +1400,9 @@
         <v>45627</v>
       </c>
       <c r="B11" s="2">
-        <f>AG10</f>
-        <v/>
-      </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n"/>
-      <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2" t="n"/>
-      <c r="R11" s="2" t="n"/>
-      <c r="S11" s="2" t="n"/>
-      <c r="T11" s="2" t="n"/>
-      <c r="U11" s="2" t="n"/>
-      <c r="V11" s="2" t="n"/>
-      <c r="W11" s="2" t="n"/>
-      <c r="X11" s="2" t="n"/>
-      <c r="Y11" s="2" t="n"/>
+        <f>S10</f>
+        <v/>
+      </c>
       <c r="Z11" s="2" t="n"/>
       <c r="AA11" s="2" t="n"/>
       <c r="AB11" s="2" t="n"/>
@@ -1532,12 +1432,12 @@
       <c r="AZ11" s="2" t="n"/>
       <c r="BA11" s="2" t="n"/>
       <c r="BB11" s="2">
-        <f>SUM(C11:BA11)</f>
+        <f>SUM(C11:AD11)</f>
         <v/>
       </c>
       <c r="BC11" s="2" t="n"/>
       <c r="BD11" s="2">
-        <f>B11+BB11-BC11</f>
+        <f>B11+AE11-AF11</f>
         <v/>
       </c>
     </row>
@@ -1546,32 +1446,9 @@
         <v>45658</v>
       </c>
       <c r="B12" s="2">
-        <f>AG11</f>
-        <v/>
-      </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
-      <c r="P12" s="2" t="n"/>
-      <c r="Q12" s="2" t="n"/>
-      <c r="R12" s="2" t="n"/>
-      <c r="S12" s="2" t="n"/>
-      <c r="T12" s="2" t="n"/>
-      <c r="U12" s="2" t="n"/>
-      <c r="V12" s="2" t="n"/>
-      <c r="W12" s="2" t="n"/>
-      <c r="X12" s="2" t="n"/>
-      <c r="Y12" s="2" t="n"/>
+        <f>S11</f>
+        <v/>
+      </c>
       <c r="Z12" s="2" t="n"/>
       <c r="AA12" s="2" t="n"/>
       <c r="AB12" s="2" t="n"/>
@@ -1601,12 +1478,12 @@
       <c r="AZ12" s="2" t="n"/>
       <c r="BA12" s="2" t="n"/>
       <c r="BB12" s="2">
-        <f>SUM(C12:BA12)</f>
+        <f>SUM(C12:AD12)</f>
         <v/>
       </c>
       <c r="BC12" s="2" t="n"/>
       <c r="BD12" s="2">
-        <f>B12+BB12-BC12</f>
+        <f>B12+AE12-AF12</f>
         <v/>
       </c>
     </row>
@@ -1615,32 +1492,9 @@
         <v>45689</v>
       </c>
       <c r="B13" s="2">
-        <f>AG12</f>
-        <v/>
-      </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="n"/>
-      <c r="Q13" s="2" t="n"/>
-      <c r="R13" s="2" t="n"/>
-      <c r="S13" s="2" t="n"/>
-      <c r="T13" s="2" t="n"/>
-      <c r="U13" s="2" t="n"/>
-      <c r="V13" s="2" t="n"/>
-      <c r="W13" s="2" t="n"/>
-      <c r="X13" s="2" t="n"/>
-      <c r="Y13" s="2" t="n"/>
+        <f>S12</f>
+        <v/>
+      </c>
       <c r="Z13" s="2" t="n"/>
       <c r="AA13" s="2" t="n"/>
       <c r="AB13" s="2" t="n"/>
@@ -1670,12 +1524,12 @@
       <c r="AZ13" s="2" t="n"/>
       <c r="BA13" s="2" t="n"/>
       <c r="BB13" s="2">
-        <f>SUM(C13:BA13)</f>
+        <f>SUM(C13:AD13)</f>
         <v/>
       </c>
       <c r="BC13" s="2" t="n"/>
       <c r="BD13" s="2">
-        <f>B13+BB13-BC13</f>
+        <f>B13+AE13-AF13</f>
         <v/>
       </c>
     </row>
@@ -1684,32 +1538,9 @@
         <v>45717</v>
       </c>
       <c r="B14" s="2">
-        <f>AG13</f>
-        <v/>
-      </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n"/>
-      <c r="R14" s="2" t="n"/>
-      <c r="S14" s="2" t="n"/>
-      <c r="T14" s="2" t="n"/>
-      <c r="U14" s="2" t="n"/>
-      <c r="V14" s="2" t="n"/>
-      <c r="W14" s="2" t="n"/>
-      <c r="X14" s="2" t="n"/>
-      <c r="Y14" s="2" t="n"/>
+        <f>S13</f>
+        <v/>
+      </c>
       <c r="Z14" s="2" t="n"/>
       <c r="AA14" s="2" t="n"/>
       <c r="AB14" s="2" t="n"/>
@@ -1739,12 +1570,12 @@
       <c r="AZ14" s="2" t="n"/>
       <c r="BA14" s="2" t="n"/>
       <c r="BB14" s="2">
-        <f>SUM(C14:BA14)</f>
+        <f>SUM(C14:AD14)</f>
         <v/>
       </c>
       <c r="BC14" s="2" t="n"/>
       <c r="BD14" s="2">
-        <f>B14+BB14-BC14</f>
+        <f>B14+AE14-AF14</f>
         <v/>
       </c>
     </row>
@@ -1755,95 +1586,95 @@
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <f>SUM(C3:C14)</f>
         <v/>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="3">
         <f>SUM(D3:D14)</f>
         <v/>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="3">
         <f>SUM(E3:E14)</f>
         <v/>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="3">
         <f>SUM(F3:F14)</f>
         <v/>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="3">
         <f>SUM(G3:G14)</f>
         <v/>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="3">
         <f>SUM(H3:H14)</f>
         <v/>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="3">
         <f>SUM(I3:I14)</f>
         <v/>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="3">
         <f>SUM(J3:J14)</f>
         <v/>
       </c>
-      <c r="K15" s="2">
+      <c r="K15" s="3">
         <f>SUM(K3:K14)</f>
         <v/>
       </c>
-      <c r="L15" s="2">
+      <c r="L15" s="3">
         <f>SUM(L3:L14)</f>
         <v/>
       </c>
-      <c r="M15" s="2">
+      <c r="M15" s="3">
         <f>SUM(M3:M14)</f>
         <v/>
       </c>
-      <c r="N15" s="2">
+      <c r="N15" s="3">
         <f>SUM(N3:N14)</f>
         <v/>
       </c>
-      <c r="O15" s="2">
+      <c r="O15" s="3">
         <f>SUM(O3:O14)</f>
         <v/>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="3">
         <f>SUM(P3:P14)</f>
         <v/>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15" s="3">
         <f>SUM(Q3:Q14)</f>
         <v/>
       </c>
-      <c r="R15" s="2">
+      <c r="R15" s="3">
         <f>SUM(R3:R14)</f>
         <v/>
       </c>
-      <c r="S15" s="2">
+      <c r="S15" s="3">
         <f>SUM(S3:S14)</f>
         <v/>
       </c>
-      <c r="T15" s="2">
+      <c r="T15" s="3">
         <f>SUM(T3:T14)</f>
         <v/>
       </c>
-      <c r="U15" s="2">
+      <c r="U15" s="3">
         <f>SUM(U3:U14)</f>
         <v/>
       </c>
-      <c r="V15" s="2">
+      <c r="V15" s="3">
         <f>SUM(V3:V14)</f>
         <v/>
       </c>
-      <c r="W15" s="2">
+      <c r="W15" s="3">
         <f>SUM(W3:W14)</f>
         <v/>
       </c>
-      <c r="X15" s="2">
+      <c r="X15" s="3">
         <f>SUM(X3:X14)</f>
         <v/>
       </c>
-      <c r="Y15" s="2">
+      <c r="Y15" s="3">
         <f>SUM(Y3:Y14)</f>
         <v/>
       </c>
@@ -1968,7 +1799,7 @@
         <v/>
       </c>
       <c r="BD15" s="2">
-        <f>BD14</f>
+        <f>SUM(BD3:BD14)</f>
         <v/>
       </c>
     </row>
@@ -1995,20 +1826,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="2" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
+      <c r="A1" s="10">
+        <f>'CHASE #3444'!A1</f>
+        <v/>
       </c>
       <c r="B1" s="6">
         <f>'CHASE #3444'!A3</f>
@@ -2042,29 +1872,28 @@
         <f>'CHASE #3444'!A10</f>
         <v/>
       </c>
-      <c r="J1" s="6" t="n"/>
+      <c r="J1" s="6">
+        <f>'CHASE #3444'!A11</f>
+        <v/>
+      </c>
       <c r="K1" s="6">
-        <f>'CHASE #3444'!A11</f>
+        <f>'CHASE #3444'!A12</f>
         <v/>
       </c>
       <c r="L1" s="6">
-        <f>'CHASE #3444'!A12</f>
+        <f>'CHASE #3444'!A13</f>
         <v/>
       </c>
       <c r="M1" s="6">
-        <f>'CHASE #3444'!A13</f>
-        <v/>
-      </c>
-      <c r="N1" s="6">
         <f>'CHASE #3444'!A14</f>
         <v/>
       </c>
+      <c r="N1" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="O1" s="10" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
@@ -2088,12 +1917,11 @@
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2">
-        <f>SUM(B2,C2,D2,E2,F2,G2,H2,I2,K2,L2,M2,N2)</f>
-        <v/>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="N2" s="2">
+        <f>SUM(B2,C2,D2,E2,F2,G2,H2,I2,J2,K2,L2,M2)</f>
+        <v/>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -2105,7 +1933,10 @@
           <t>Amazon Prime*Zh8618Uz3 Amzn.Com/Bill WA</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
+      <c r="B3" s="2">
+        <f>16.25</f>
+        <v/>
+      </c>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2">
@@ -2114,21 +1945,20 @@
       </c>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
+      <c r="H3" s="2">
+        <f>16.25</f>
+        <v/>
+      </c>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2">
-        <f>16.25</f>
-        <v/>
-      </c>
+      <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2">
-        <f>SUM(B3,C3,D3,E3,F3,G3,H3,I3,K3,L3,M3,N3)</f>
-        <v/>
-      </c>
-      <c r="P3" s="1" t="inlineStr">
+      <c r="N3" s="2">
+        <f>SUM(B3,C3,D3,E3,F3,G3,H3,I3,J3,K3,L3,M3)</f>
+        <v/>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -2152,12 +1982,11 @@
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2">
-        <f>SUM(B4,C4,D4,E4,F4,G4,H4,I4,K4,L4,M4,N4)</f>
-        <v/>
-      </c>
-      <c r="P4" s="1" t="inlineStr">
+      <c r="N4" s="2">
+        <f>SUM(B4,C4,D4,E4,F4,G4,H4,I4,J4,K4,L4,M4)</f>
+        <v/>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -2169,7 +1998,10 @@
           <t>Amazon.Comseattlewa US</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="2">
+        <f>117.76</f>
+        <v/>
+      </c>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2">
@@ -2178,21 +2010,20 @@
       </c>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="H5" s="2">
+        <f>117.76</f>
+        <v/>
+      </c>
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2">
-        <f>117.76</f>
-        <v/>
-      </c>
+      <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2">
-        <f>SUM(B5,C5,D5,E5,F5,G5,H5,I5,K5,L5,M5,N5)</f>
-        <v/>
-      </c>
-      <c r="P5" s="1" t="inlineStr">
+      <c r="N5" s="2">
+        <f>SUM(B5,C5,D5,E5,F5,G5,H5,I5,J5,K5,L5,M5)</f>
+        <v/>
+      </c>
+      <c r="O5" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -2216,12 +2047,11 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2">
-        <f>SUM(B6,C6,D6,E6,F6,G6,H6,I6,K6,L6,M6,N6)</f>
-        <v/>
-      </c>
-      <c r="P6" s="1" t="inlineStr">
+      <c r="N6" s="2">
+        <f>SUM(B6,C6,D6,E6,F6,G6,H6,I6,J6,K6,L6,M6)</f>
+        <v/>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -2245,12 +2075,11 @@
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
-      <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2">
-        <f>SUM(B7,C7,D7,E7,F7,G7,H7,I7,K7,L7,M7,N7)</f>
-        <v/>
-      </c>
-      <c r="P7" s="1" t="inlineStr">
+      <c r="N7" s="2">
+        <f>SUM(B7,C7,D7,E7,F7,G7,H7,I7,J7,K7,L7,M7)</f>
+        <v/>
+      </c>
+      <c r="O7" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -2274,12 +2103,11 @@
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2">
-        <f>SUM(B8,C8,D8,E8,F8,G8,H8,I8,K8,L8,M8,N8)</f>
-        <v/>
-      </c>
-      <c r="P8" s="1" t="inlineStr">
+      <c r="N8" s="2">
+        <f>SUM(B8,C8,D8,E8,F8,G8,H8,I8,J8,K8,L8,M8)</f>
+        <v/>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
         <is>
           <t>GERCORY</t>
         </is>
@@ -2300,8 +2128,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
-      <c r="P9" s="1" t="n"/>
+      <c r="O9" s="1" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
@@ -2318,8 +2145,7 @@
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
       <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="1" t="n"/>
+      <c r="O10" s="1" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -2336,8 +2162,7 @@
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n"/>
-      <c r="P11" s="1" t="n"/>
+      <c r="O11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -2357,12 +2182,11 @@
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2">
-        <f>SUM(B12,C12,D12,E12,F12,G12,H12,I12,K12,L12,M12,N12)</f>
-        <v/>
-      </c>
-      <c r="P12" s="1" t="inlineStr">
+      <c r="N12" s="2">
+        <f>SUM(B12,C12,D12,E12,F12,G12,H12,I12,J12,K12,L12,M12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -2374,7 +2198,10 @@
           <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
+      <c r="B13" s="2">
+        <f>350.00</f>
+        <v/>
+      </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2">
@@ -2383,21 +2210,20 @@
       </c>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
+      <c r="H13" s="2">
+        <f>350.00</f>
+        <v/>
+      </c>
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2">
-        <f>350.00</f>
-        <v/>
-      </c>
+      <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2">
-        <f>SUM(B13,C13,D13,E13,F13,G13,H13,I13,K13,L13,M13,N13)</f>
-        <v/>
-      </c>
-      <c r="P13" s="1" t="inlineStr">
+      <c r="N13" s="2">
+        <f>SUM(B13,C13,D13,E13,F13,G13,H13,I13,J13,K13,L13,M13)</f>
+        <v/>
+      </c>
+      <c r="O13" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -2421,12 +2247,11 @@
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2">
-        <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,K14,L14,M14,N14)</f>
-        <v/>
-      </c>
-      <c r="P14" s="1" t="inlineStr">
+      <c r="N14" s="2">
+        <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,J14,K14,L14,M14)</f>
+        <v/>
+      </c>
+      <c r="O14" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -2438,7 +2263,10 @@
           <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2">
+        <f>300.00</f>
+        <v/>
+      </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2">
@@ -2447,21 +2275,20 @@
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
+      <c r="H15" s="2">
+        <f>300.00</f>
+        <v/>
+      </c>
       <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2">
-        <f>300.00</f>
-        <v/>
-      </c>
+      <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2">
-        <f>SUM(B15,C15,D15,E15,F15,G15,H15,I15,K15,L15,M15,N15)</f>
-        <v/>
-      </c>
-      <c r="P15" s="1" t="inlineStr">
+      <c r="N15" s="2">
+        <f>SUM(B15,C15,D15,E15,F15,G15,H15,I15,J15,K15,L15,M15)</f>
+        <v/>
+      </c>
+      <c r="O15" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -2485,12 +2312,11 @@
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2">
-        <f>SUM(B16,C16,D16,E16,F16,G16,H16,I16,K16,L16,M16,N16)</f>
-        <v/>
-      </c>
-      <c r="P16" s="1" t="inlineStr">
+      <c r="N16" s="2">
+        <f>SUM(B16,C16,D16,E16,F16,G16,H16,I16,J16,K16,L16,M16)</f>
+        <v/>
+      </c>
+      <c r="O16" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -2502,30 +2328,32 @@
           <t>Citi Card Onlinepayment</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n"/>
+      <c r="B17" s="2">
+        <f>975.00</f>
+        <v/>
+      </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2">
-        <f>975.00+364.75+1400.00</f>
+        <f>975.00</f>
         <v/>
       </c>
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
+      <c r="H17" s="2">
+        <f>975.00</f>
+        <v/>
+      </c>
       <c r="I17" s="2" t="n"/>
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2">
-        <f>975.00+364.75+1400.00</f>
-        <v/>
-      </c>
+      <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2">
-        <f>SUM(B17,C17,D17,E17,F17,G17,H17,I17,K17,L17,M17,N17)</f>
-        <v/>
-      </c>
-      <c r="P17" s="1" t="inlineStr">
+      <c r="N17" s="2">
+        <f>SUM(B17,C17,D17,E17,F17,G17,H17,I17,J17,K17,L17,M17)</f>
+        <v/>
+      </c>
+      <c r="O17" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -2537,7 +2365,10 @@
           <t>Credit One Bank Payment</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
+      <c r="B18" s="2">
+        <f>817.29</f>
+        <v/>
+      </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2">
@@ -2546,21 +2377,20 @@
       </c>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
+      <c r="H18" s="2">
+        <f>817.29</f>
+        <v/>
+      </c>
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2">
-        <f>817.29</f>
-        <v/>
-      </c>
+      <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2">
-        <f>SUM(B18,C18,D18,E18,F18,G18,H18,I18,K18,L18,M18,N18)</f>
-        <v/>
-      </c>
-      <c r="P18" s="1" t="inlineStr">
+      <c r="N18" s="2">
+        <f>SUM(B18,C18,D18,E18,F18,G18,H18,I18,J18,K18,L18,M18)</f>
+        <v/>
+      </c>
+      <c r="O18" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -2584,12 +2414,11 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2">
-        <f>SUM(B19,C19,D19,E19,F19,G19,H19,I19,K19,L19,M19,N19)</f>
-        <v/>
-      </c>
-      <c r="P19" s="1" t="inlineStr">
+      <c r="N19" s="2">
+        <f>SUM(B19,C19,D19,E19,F19,G19,H19,I19,J19,K19,L19,M19)</f>
+        <v/>
+      </c>
+      <c r="O19" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -2613,12 +2442,11 @@
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2">
-        <f>SUM(B20,C20,D20,E20,F20,G20,H20,I20,K20,L20,M20,N20)</f>
-        <v/>
-      </c>
-      <c r="P20" s="1" t="inlineStr">
+      <c r="N20" s="2">
+        <f>SUM(B20,C20,D20,E20,F20,G20,H20,I20,J20,K20,L20,M20)</f>
+        <v/>
+      </c>
+      <c r="O20" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -2642,12 +2470,11 @@
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n"/>
-      <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2">
-        <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,K21,L21,M21,N21)</f>
-        <v/>
-      </c>
-      <c r="P21" s="1" t="inlineStr">
+      <c r="N21" s="2">
+        <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,J21,K21,L21,M21)</f>
+        <v/>
+      </c>
+      <c r="O21" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2659,7 +2486,10 @@
           <t>Internet Trf To Client-Added Transfer Account</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2">
@@ -2668,21 +2498,20 @@
       </c>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
+      <c r="H22" s="2">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2">
-        <f>385.77+740.00</f>
-        <v/>
-      </c>
+      <c r="L22" s="2" t="n"/>
       <c r="M22" s="2" t="n"/>
-      <c r="N22" s="2" t="n"/>
-      <c r="O22" s="2">
-        <f>SUM(B22,C22,D22,E22,F22,G22,H22,I22,K22,L22,M22,N22)</f>
-        <v/>
-      </c>
-      <c r="P22" s="1" t="inlineStr">
+      <c r="N22" s="2">
+        <f>SUM(B22,C22,D22,E22,F22,G22,H22,I22,J22,K22,L22,M22)</f>
+        <v/>
+      </c>
+      <c r="O22" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2694,7 +2523,10 @@
           <t>Irs Usataxpymt</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n"/>
+      <c r="B23" s="2">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="2">
@@ -2703,21 +2535,20 @@
       </c>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
+      <c r="H23" s="2">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
       <c r="I23" s="2" t="n"/>
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2">
-        <f>800.00+800.00</f>
-        <v/>
-      </c>
+      <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n"/>
-      <c r="N23" s="2" t="n"/>
-      <c r="O23" s="2">
-        <f>SUM(B23,C23,D23,E23,F23,G23,H23,I23,K23,L23,M23,N23)</f>
-        <v/>
-      </c>
-      <c r="P23" s="1" t="inlineStr">
+      <c r="N23" s="2">
+        <f>SUM(B23,C23,D23,E23,F23,G23,H23,I23,J23,K23,L23,M23)</f>
+        <v/>
+      </c>
+      <c r="O23" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2729,7 +2560,10 @@
           <t>Kindercare Portland OR</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n"/>
+      <c r="B24" s="2">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2">
@@ -2738,21 +2572,20 @@
       </c>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
+      <c r="H24" s="2">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2">
-        <f>490.00+120.00</f>
-        <v/>
-      </c>
+      <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2">
-        <f>SUM(B24,C24,D24,E24,F24,G24,H24,I24,K24,L24,M24,N24)</f>
-        <v/>
-      </c>
-      <c r="P24" s="1" t="inlineStr">
+      <c r="N24" s="2">
+        <f>SUM(B24,C24,D24,E24,F24,G24,H24,I24,J24,K24,L24,M24)</f>
+        <v/>
+      </c>
+      <c r="O24" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2764,7 +2597,10 @@
           <t>No1 Sushi 88 Corkbbo ACH</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n"/>
+      <c r="B25" s="2">
+        <f>4000.00</f>
+        <v/>
+      </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2">
@@ -2773,21 +2609,20 @@
       </c>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
+      <c r="H25" s="2">
+        <f>4000.00</f>
+        <v/>
+      </c>
       <c r="I25" s="2" t="n"/>
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2">
-        <f>4000.00</f>
-        <v/>
-      </c>
+      <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="n"/>
-      <c r="N25" s="2" t="n"/>
-      <c r="O25" s="2">
-        <f>SUM(B25,C25,D25,E25,F25,G25,H25,I25,K25,L25,M25,N25)</f>
-        <v/>
-      </c>
-      <c r="P25" s="1" t="inlineStr">
+      <c r="N25" s="2">
+        <f>SUM(B25,C25,D25,E25,F25,G25,H25,I25,J25,K25,L25,M25)</f>
+        <v/>
+      </c>
+      <c r="O25" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2811,12 +2646,11 @@
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n"/>
-      <c r="N26" s="2" t="n"/>
-      <c r="O26" s="2">
-        <f>SUM(B26,C26,D26,E26,F26,G26,H26,I26,K26,L26,M26,N26)</f>
-        <v/>
-      </c>
-      <c r="P26" s="1" t="inlineStr">
+      <c r="N26" s="2">
+        <f>SUM(B26,C26,D26,E26,F26,G26,H26,I26,J26,K26,L26,M26)</f>
+        <v/>
+      </c>
+      <c r="O26" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2828,7 +2662,10 @@
           <t>Nys Dtf Pit Tax Paymnt</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n"/>
+      <c r="B27" s="2">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2">
@@ -2837,21 +2674,20 @@
       </c>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
+      <c r="H27" s="2">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2">
-        <f>200.00+200.00</f>
-        <v/>
-      </c>
+      <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
-      <c r="N27" s="2" t="n"/>
-      <c r="O27" s="2">
-        <f>SUM(B27,C27,D27,E27,F27,G27,H27,I27,K27,L27,M27,N27)</f>
-        <v/>
-      </c>
-      <c r="P27" s="1" t="inlineStr">
+      <c r="N27" s="2">
+        <f>SUM(B27,C27,D27,E27,F27,G27,H27,I27,J27,K27,L27,M27)</f>
+        <v/>
+      </c>
+      <c r="O27" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2875,12 +2711,11 @@
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n"/>
-      <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2">
-        <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,K28,L28,M28,N28)</f>
-        <v/>
-      </c>
-      <c r="P28" s="1" t="inlineStr">
+      <c r="N28" s="2">
+        <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,J28,K28,L28,M28)</f>
+        <v/>
+      </c>
+      <c r="O28" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2904,12 +2739,11 @@
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
-      <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2">
-        <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,K29,L29,M29,N29)</f>
-        <v/>
-      </c>
-      <c r="P29" s="1" t="inlineStr">
+      <c r="N29" s="2">
+        <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29)</f>
+        <v/>
+      </c>
+      <c r="O29" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2921,7 +2755,10 @@
           <t>POS Mac Amazon.Com*9O5 Seattle WA</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n"/>
+      <c r="B30" s="2">
+        <f>26.57</f>
+        <v/>
+      </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2">
@@ -2930,21 +2767,20 @@
       </c>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
+      <c r="H30" s="2">
+        <f>26.57</f>
+        <v/>
+      </c>
       <c r="I30" s="2" t="n"/>
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2">
-        <f>26.57</f>
-        <v/>
-      </c>
+      <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2">
-        <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,K30,L30,M30,N30)</f>
-        <v/>
-      </c>
-      <c r="P30" s="1" t="inlineStr">
+      <c r="N30" s="2">
+        <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30)</f>
+        <v/>
+      </c>
+      <c r="O30" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2956,7 +2792,10 @@
           <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n"/>
+      <c r="B31" s="2">
+        <f>343.93</f>
+        <v/>
+      </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2">
@@ -2965,21 +2804,20 @@
       </c>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
+      <c r="H31" s="2">
+        <f>343.93</f>
+        <v/>
+      </c>
       <c r="I31" s="2" t="n"/>
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2">
-        <f>343.93</f>
-        <v/>
-      </c>
+      <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2">
-        <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,K31,L31,M31,N31)</f>
-        <v/>
-      </c>
-      <c r="P31" s="1" t="inlineStr">
+      <c r="N31" s="2">
+        <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31)</f>
+        <v/>
+      </c>
+      <c r="O31" s="1" t="inlineStr">
         <is>
           <t>MEALS</t>
         </is>
@@ -2991,7 +2829,10 @@
           <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n"/>
+      <c r="B32" s="2">
+        <f>17.59</f>
+        <v/>
+      </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2">
@@ -3000,21 +2841,20 @@
       </c>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
+      <c r="H32" s="2">
+        <f>17.59</f>
+        <v/>
+      </c>
       <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2">
-        <f>17.59</f>
-        <v/>
-      </c>
+      <c r="L32" s="2" t="n"/>
       <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2">
-        <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,K32,L32,M32,N32)</f>
-        <v/>
-      </c>
-      <c r="P32" s="1" t="inlineStr">
+      <c r="N32" s="2">
+        <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32)</f>
+        <v/>
+      </c>
+      <c r="O32" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -3026,7 +2866,10 @@
           <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n"/>
+      <c r="B33" s="2">
+        <f>152.14</f>
+        <v/>
+      </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n"/>
       <c r="E33" s="2">
@@ -3035,21 +2878,20 @@
       </c>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
+      <c r="H33" s="2">
+        <f>152.14</f>
+        <v/>
+      </c>
       <c r="I33" s="2" t="n"/>
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2">
-        <f>152.14</f>
-        <v/>
-      </c>
+      <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n"/>
-      <c r="N33" s="2" t="n"/>
-      <c r="O33" s="2">
-        <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,K33,L33,M33,N33)</f>
-        <v/>
-      </c>
-      <c r="P33" s="1" t="inlineStr">
+      <c r="N33" s="2">
+        <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33)</f>
+        <v/>
+      </c>
+      <c r="O33" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -3061,7 +2903,10 @@
           <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n"/>
+      <c r="B34" s="2">
+        <f>71.79</f>
+        <v/>
+      </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2">
@@ -3070,21 +2915,20 @@
       </c>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
+      <c r="H34" s="2">
+        <f>71.79</f>
+        <v/>
+      </c>
       <c r="I34" s="2" t="n"/>
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2">
-        <f>71.79</f>
-        <v/>
-      </c>
+      <c r="L34" s="2" t="n"/>
       <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2">
-        <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,K34,L34,M34,N34)</f>
-        <v/>
-      </c>
-      <c r="P34" s="1" t="inlineStr">
+      <c r="N34" s="2">
+        <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,J34,K34,L34,M34)</f>
+        <v/>
+      </c>
+      <c r="O34" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -3096,7 +2940,10 @@
           <t>POS Mac Amazon.Com*Nx6 Seattle WA</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n"/>
+      <c r="B35" s="2">
+        <f>75.40</f>
+        <v/>
+      </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n"/>
       <c r="E35" s="2">
@@ -3105,21 +2952,20 @@
       </c>
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
+      <c r="H35" s="2">
+        <f>75.40</f>
+        <v/>
+      </c>
       <c r="I35" s="2" t="n"/>
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2">
-        <f>75.40</f>
-        <v/>
-      </c>
+      <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n"/>
-      <c r="N35" s="2" t="n"/>
-      <c r="O35" s="2">
-        <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,K35,L35,M35,N35)</f>
-        <v/>
-      </c>
-      <c r="P35" s="1" t="inlineStr">
+      <c r="N35" s="2">
+        <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,J35,K35,L35,M35)</f>
+        <v/>
+      </c>
+      <c r="O35" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -3131,7 +2977,10 @@
           <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n"/>
+      <c r="B36" s="2">
+        <f>18.75</f>
+        <v/>
+      </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2">
@@ -3140,21 +2989,20 @@
       </c>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
+      <c r="H36" s="2">
+        <f>18.75</f>
+        <v/>
+      </c>
       <c r="I36" s="2" t="n"/>
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2">
-        <f>18.75</f>
-        <v/>
-      </c>
+      <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="n"/>
-      <c r="O36" s="2">
-        <f>SUM(B36,C36,D36,E36,F36,G36,H36,I36,K36,L36,M36,N36)</f>
-        <v/>
-      </c>
-      <c r="P36" s="1" t="inlineStr">
+      <c r="N36" s="2">
+        <f>SUM(B36,C36,D36,E36,F36,G36,H36,I36,J36,K36,L36,M36)</f>
+        <v/>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -3166,7 +3014,10 @@
           <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n"/>
+      <c r="B37" s="2">
+        <f>50.03</f>
+        <v/>
+      </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n"/>
       <c r="E37" s="2">
@@ -3175,21 +3026,20 @@
       </c>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
+      <c r="H37" s="2">
+        <f>50.03</f>
+        <v/>
+      </c>
       <c r="I37" s="2" t="n"/>
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2">
-        <f>50.03</f>
-        <v/>
-      </c>
+      <c r="L37" s="2" t="n"/>
       <c r="M37" s="2" t="n"/>
-      <c r="N37" s="2" t="n"/>
-      <c r="O37" s="2">
-        <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,K37,L37,M37,N37)</f>
-        <v/>
-      </c>
-      <c r="P37" s="1" t="inlineStr">
+      <c r="N37" s="2">
+        <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,J37,K37,L37,M37)</f>
+        <v/>
+      </c>
+      <c r="O37" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -3201,7 +3051,10 @@
           <t>POS Mac Amazon.Com*V25 Seattle WA</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n"/>
+      <c r="B38" s="2">
+        <f>20.80</f>
+        <v/>
+      </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2">
@@ -3210,21 +3063,20 @@
       </c>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
+      <c r="H38" s="2">
+        <f>20.80</f>
+        <v/>
+      </c>
       <c r="I38" s="2" t="n"/>
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2">
-        <f>20.80</f>
-        <v/>
-      </c>
+      <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n"/>
-      <c r="N38" s="2" t="n"/>
-      <c r="O38" s="2">
-        <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,K38,L38,M38,N38)</f>
-        <v/>
-      </c>
-      <c r="P38" s="1" t="inlineStr">
+      <c r="N38" s="2">
+        <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38)</f>
+        <v/>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -3248,12 +3100,11 @@
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n"/>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2">
-        <f>SUM(B39,C39,D39,E39,F39,G39,H39,I39,K39,L39,M39,N39)</f>
-        <v/>
-      </c>
-      <c r="P39" s="1" t="inlineStr">
+      <c r="N39" s="2">
+        <f>SUM(B39,C39,D39,E39,F39,G39,H39,I39,J39,K39,L39,M39)</f>
+        <v/>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -3265,7 +3116,10 @@
           <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n"/>
+      <c r="B40" s="2">
+        <f>40.33</f>
+        <v/>
+      </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2">
@@ -3274,21 +3128,20 @@
       </c>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
+      <c r="H40" s="2">
+        <f>40.33</f>
+        <v/>
+      </c>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2">
-        <f>40.33</f>
-        <v/>
-      </c>
+      <c r="L40" s="2" t="n"/>
       <c r="M40" s="2" t="n"/>
-      <c r="N40" s="2" t="n"/>
-      <c r="O40" s="2">
-        <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,K40,L40,M40,N40)</f>
-        <v/>
-      </c>
-      <c r="P40" s="1" t="inlineStr">
+      <c r="N40" s="2">
+        <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,J40,K40,L40,M40)</f>
+        <v/>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -3300,7 +3153,10 @@
           <t>Prog Casualty Ins Prem</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n"/>
+      <c r="B41" s="2">
+        <f>930.52</f>
+        <v/>
+      </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n"/>
       <c r="E41" s="2">
@@ -3309,21 +3165,20 @@
       </c>
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
+      <c r="H41" s="2">
+        <f>930.52</f>
+        <v/>
+      </c>
       <c r="I41" s="2" t="n"/>
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2">
-        <f>930.52</f>
-        <v/>
-      </c>
+      <c r="L41" s="2" t="n"/>
       <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2" t="n"/>
-      <c r="O41" s="2">
-        <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,K41,L41,M41,N41)</f>
-        <v/>
-      </c>
-      <c r="P41" s="1" t="inlineStr">
+      <c r="N41" s="2">
+        <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41)</f>
+        <v/>
+      </c>
+      <c r="O41" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -3347,12 +3202,11 @@
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
       <c r="M42" s="2" t="n"/>
-      <c r="N42" s="2" t="n"/>
-      <c r="O42" s="2">
-        <f>SUM(B42,C42,D42,E42,F42,G42,H42,I42,K42,L42,M42,N42)</f>
-        <v/>
-      </c>
-      <c r="P42" s="1" t="inlineStr">
+      <c r="N42" s="2">
+        <f>SUM(B42,C42,D42,E42,F42,G42,H42,I42,J42,K42,L42,M42)</f>
+        <v/>
+      </c>
+      <c r="O42" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -3364,7 +3218,10 @@
           <t>Withdrawal Branch 0964 New York</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n"/>
+      <c r="B43" s="2">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n"/>
       <c r="E43" s="2">
@@ -3373,21 +3230,20 @@
       </c>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
+      <c r="H43" s="2">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
       <c r="I43" s="2" t="n"/>
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
-      <c r="L43" s="2">
-        <f>1000.00+3200.00</f>
-        <v/>
-      </c>
+      <c r="L43" s="2" t="n"/>
       <c r="M43" s="2" t="n"/>
-      <c r="N43" s="2" t="n"/>
-      <c r="O43" s="2">
-        <f>SUM(B43,C43,D43,E43,F43,G43,H43,I43,K43,L43,M43,N43)</f>
-        <v/>
-      </c>
-      <c r="P43" s="1" t="inlineStr">
+      <c r="N43" s="2">
+        <f>SUM(B43,C43,D43,E43,F43,G43,H43,I43,J43,K43,L43,M43)</f>
+        <v/>
+      </c>
+      <c r="O43" s="1" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
@@ -3411,12 +3267,11 @@
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
       <c r="M44" s="2" t="n"/>
-      <c r="N44" s="2" t="n"/>
-      <c r="O44" s="2">
-        <f>SUM(B44,C44,D44,E44,F44,G44,H44,I44,K44,L44,M44,N44)</f>
-        <v/>
-      </c>
-      <c r="P44" s="1" t="inlineStr">
+      <c r="N44" s="2">
+        <f>SUM(B44,C44,D44,E44,F44,G44,H44,I44,J44,K44,L44,M44)</f>
+        <v/>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
@@ -3477,16 +3332,12 @@
         <v/>
       </c>
       <c r="N45" s="3">
-        <f>SUM(N2:N44)</f>
-        <v/>
-      </c>
-      <c r="O45" s="3">
-        <f>SUM(B45,C45,D45,E45,F45,G45,H45,I45,K45,L45,M45,N45)</f>
+        <f>SUM(B45,C45,D45,E45,F45,G45,H45,I45,J45,K45,L45,M45)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P44"/>
+  <autoFilter ref="A1:O44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3505,9 +3356,9 @@
     <col width="7.85546875" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="7" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="6.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="9.28515625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="7.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
     <col width="7.140625" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="9.28515625" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="7" bestFit="1" customWidth="1" min="8" max="8"/>
     <col width="7.5703125" bestFit="1" customWidth="1" min="9" max="9"/>
     <col width="7.28515625" bestFit="1" customWidth="1" min="10" max="10"/>
     <col width="6.85546875" bestFit="1" customWidth="1" min="11" max="11"/>
@@ -3522,7 +3373,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>banewofhjsofih</t>
+          <t>Merchant</t>
         </is>
       </c>
       <c r="B1" s="6" t="n">
@@ -3613,24 +3464,21 @@
           <t>Amazon Prime*Zh8618Uz3 Amzn.Com/Bill WA</t>
         </is>
       </c>
-      <c r="B3" s="2">
-        <f>16.25</f>
-        <v/>
-      </c>
+      <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
+      <c r="H3" s="2">
+        <f>16.25</f>
+        <v/>
+      </c>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2">
-        <f>16.25</f>
-        <v/>
-      </c>
+      <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2">
         <f>SUM(B3,C3,D3,E3,F3,G3,H3,I3,J3,K3,L3,M3,N3,Q3)</f>
@@ -3640,6 +3488,10 @@
         <is>
           <t>GERCORY</t>
         </is>
+      </c>
+      <c r="Q3" s="3">
+        <f>16.25</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -3677,24 +3529,21 @@
           <t>Amazon.Comseattlewa US</t>
         </is>
       </c>
-      <c r="B5" s="2">
-        <f>117.76</f>
-        <v/>
-      </c>
+      <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="H5" s="2">
+        <f>117.76</f>
+        <v/>
+      </c>
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2">
-        <f>117.76</f>
-        <v/>
-      </c>
+      <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="2">
         <f>SUM(B5,C5,D5,E5,F5,G5,H5,I5,J5,K5,L5,M5,N5,Q5)</f>
@@ -3704,6 +3553,10 @@
         <is>
           <t>GERCORY</t>
         </is>
+      </c>
+      <c r="Q5" s="3">
+        <f>117.76</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -3828,24 +3681,21 @@
           <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <f>350.00</f>
-        <v/>
-      </c>
+      <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
+      <c r="H10" s="2">
+        <f>350.00</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="n"/>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2">
-        <f>350.00</f>
-        <v/>
-      </c>
+      <c r="M10" s="2" t="n"/>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2">
         <f>SUM(B10,C10,D10,E10,F10,G10,H10,I10,J10,K10,L10,M10,N10,Q10)</f>
@@ -3855,6 +3705,10 @@
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
+      </c>
+      <c r="Q10" s="3">
+        <f>350.00</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -3892,24 +3746,21 @@
           <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
         </is>
       </c>
-      <c r="B12" s="2">
-        <f>300.00</f>
-        <v/>
-      </c>
+      <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
+      <c r="H12" s="2">
+        <f>300.00</f>
+        <v/>
+      </c>
       <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2">
-        <f>300.00</f>
-        <v/>
-      </c>
+      <c r="M12" s="2" t="n"/>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2">
         <f>SUM(B12,C12,D12,E12,F12,G12,H12,I12,J12,K12,L12,M12,N12,Q12)</f>
@@ -3919,6 +3770,10 @@
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
+      </c>
+      <c r="Q12" s="3">
+        <f>300.00</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -3956,24 +3811,21 @@
           <t>Citi Card Onlinepayment</t>
         </is>
       </c>
-      <c r="B14" s="2">
-        <f>975.00+364.75+1400.00</f>
-        <v/>
-      </c>
+      <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="H14" s="2">
+        <f>975.00</f>
+        <v/>
+      </c>
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2">
-        <f>975.00+364.75+1400.00</f>
-        <v/>
-      </c>
+      <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2">
         <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,J14,K14,L14,M14,N14,Q14)</f>
@@ -3984,6 +3836,10 @@
           <t>OFFICE EXPENSE</t>
         </is>
       </c>
+      <c r="Q14" s="3">
+        <f>975.00</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -3991,24 +3847,21 @@
           <t>Credit One Bank Payment</t>
         </is>
       </c>
-      <c r="B15" s="2">
-        <f>817.29</f>
-        <v/>
-      </c>
+      <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
+      <c r="H15" s="2">
+        <f>817.29</f>
+        <v/>
+      </c>
       <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2">
-        <f>817.29</f>
-        <v/>
-      </c>
+      <c r="M15" s="2" t="n"/>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2">
         <f>SUM(B15,C15,D15,E15,F15,G15,H15,I15,J15,K15,L15,M15,N15,Q15)</f>
@@ -4018,6 +3871,10 @@
         <is>
           <t>OFFICE EXPENSE</t>
         </is>
+      </c>
+      <c r="Q15" s="3">
+        <f>817.29</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -4113,24 +3970,21 @@
           <t>Internet Trf To Client-Added Transfer Account</t>
         </is>
       </c>
-      <c r="B19" s="2">
-        <f>385.77+740.00</f>
-        <v/>
-      </c>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
+      <c r="H19" s="2">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
       <c r="I19" s="2" t="n"/>
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2">
-        <f>385.77+740.00</f>
-        <v/>
-      </c>
+      <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2">
         <f>SUM(B19,C19,D19,E19,F19,G19,H19,I19,J19,K19,L19,M19,N19,Q19)</f>
@@ -4141,6 +3995,10 @@
           <t>MEALS</t>
         </is>
       </c>
+      <c r="Q19" s="3">
+        <f>385.77+740.00</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -4148,24 +4006,21 @@
           <t>Irs Usataxpymt</t>
         </is>
       </c>
-      <c r="B20" s="2">
-        <f>800.00+800.00</f>
-        <v/>
-      </c>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
+      <c r="H20" s="2">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2">
-        <f>800.00+800.00</f>
-        <v/>
-      </c>
+      <c r="M20" s="2" t="n"/>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2">
         <f>SUM(B20,C20,D20,E20,F20,G20,H20,I20,J20,K20,L20,M20,N20,Q20)</f>
@@ -4176,6 +4031,10 @@
           <t>MEALS</t>
         </is>
       </c>
+      <c r="Q20" s="3">
+        <f>800.00+800.00</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -4183,24 +4042,21 @@
           <t>Kindercare Portland OR</t>
         </is>
       </c>
-      <c r="B21" s="2">
-        <f>490.00+120.00</f>
-        <v/>
-      </c>
+      <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
+      <c r="H21" s="2">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
       <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2">
-        <f>490.00+120.00</f>
-        <v/>
-      </c>
+      <c r="M21" s="2" t="n"/>
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2">
         <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,J21,K21,L21,M21,N21,Q21)</f>
@@ -4211,6 +4067,10 @@
           <t>MEALS</t>
         </is>
       </c>
+      <c r="Q21" s="3">
+        <f>490.00+120.00</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -4218,24 +4078,21 @@
           <t>No1 Sushi 88 Corkbbo ACH</t>
         </is>
       </c>
-      <c r="B22" s="2">
-        <f>4000.00</f>
-        <v/>
-      </c>
+      <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
+      <c r="H22" s="2">
+        <f>4000.00</f>
+        <v/>
+      </c>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2">
-        <f>4000.00</f>
-        <v/>
-      </c>
+      <c r="M22" s="2" t="n"/>
       <c r="N22" s="2" t="n"/>
       <c r="O22" s="2">
         <f>SUM(B22,C22,D22,E22,F22,G22,H22,I22,J22,K22,L22,M22,N22,Q22)</f>
@@ -4245,6 +4102,10 @@
         <is>
           <t>MEALS</t>
         </is>
+      </c>
+      <c r="Q22" s="3">
+        <f>4000.00</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -4282,24 +4143,21 @@
           <t>Nys Dtf Pit Tax Paymnt</t>
         </is>
       </c>
-      <c r="B24" s="2">
-        <f>200.00+200.00</f>
-        <v/>
-      </c>
+      <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
+      <c r="H24" s="2">
+        <f>200.00+200.00</f>
+        <v/>
+      </c>
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2">
-        <f>200.00+200.00</f>
-        <v/>
-      </c>
+      <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2">
         <f>SUM(B24,C24,D24,E24,F24,G24,H24,I24,J24,K24,L24,M24,N24,Q24)</f>
@@ -4309,6 +4167,10 @@
         <is>
           <t>MEALS</t>
         </is>
+      </c>
+      <c r="Q24" s="3">
+        <f>200.00+200.00</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -4375,24 +4237,21 @@
           <t>POS Mac Amazon.Com*9O5 Seattle WA</t>
         </is>
       </c>
-      <c r="B27" s="2">
-        <f>26.57</f>
-        <v/>
-      </c>
+      <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
+      <c r="H27" s="2">
+        <f>26.57</f>
+        <v/>
+      </c>
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
-      <c r="M27" s="2">
-        <f>26.57</f>
-        <v/>
-      </c>
+      <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2">
         <f>SUM(B27,C27,D27,E27,F27,G27,H27,I27,J27,K27,L27,M27,N27,Q27)</f>
@@ -4403,6 +4262,10 @@
           <t>MEALS</t>
         </is>
       </c>
+      <c r="Q27" s="3">
+        <f>26.57</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -4410,24 +4273,21 @@
           <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
         </is>
       </c>
-      <c r="B28" s="2">
-        <f>343.93</f>
-        <v/>
-      </c>
+      <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
+      <c r="H28" s="2">
+        <f>343.93</f>
+        <v/>
+      </c>
       <c r="I28" s="2" t="n"/>
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2">
-        <f>343.93</f>
-        <v/>
-      </c>
+      <c r="M28" s="2" t="n"/>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2">
         <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,J28,K28,L28,M28,N28,Q28)</f>
@@ -4438,6 +4298,10 @@
           <t>MEALS</t>
         </is>
       </c>
+      <c r="Q28" s="3">
+        <f>343.93</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -4445,24 +4309,21 @@
           <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
         </is>
       </c>
-      <c r="B29" s="2">
-        <f>17.59</f>
-        <v/>
-      </c>
+      <c r="B29" s="2" t="n"/>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
+      <c r="H29" s="2">
+        <f>17.59</f>
+        <v/>
+      </c>
       <c r="I29" s="2" t="n"/>
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2">
-        <f>17.59</f>
-        <v/>
-      </c>
+      <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2">
         <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29,N29,Q29)</f>
@@ -4473,6 +4334,10 @@
           <t>SUPPLY</t>
         </is>
       </c>
+      <c r="Q29" s="3">
+        <f>17.59</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -4480,24 +4345,21 @@
           <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
         </is>
       </c>
-      <c r="B30" s="2">
-        <f>152.14</f>
-        <v/>
-      </c>
+      <c r="B30" s="2" t="n"/>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
+      <c r="H30" s="2">
+        <f>152.14</f>
+        <v/>
+      </c>
       <c r="I30" s="2" t="n"/>
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2">
-        <f>152.14</f>
-        <v/>
-      </c>
+      <c r="M30" s="2" t="n"/>
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2">
         <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30,N30,Q30)</f>
@@ -4508,6 +4370,10 @@
           <t>SUPPLY</t>
         </is>
       </c>
+      <c r="Q30" s="3">
+        <f>152.14</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -4515,24 +4381,21 @@
           <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
         </is>
       </c>
-      <c r="B31" s="2">
-        <f>71.79</f>
-        <v/>
-      </c>
+      <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
+      <c r="H31" s="2">
+        <f>71.79</f>
+        <v/>
+      </c>
       <c r="I31" s="2" t="n"/>
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2">
-        <f>71.79</f>
-        <v/>
-      </c>
+      <c r="M31" s="2" t="n"/>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2">
         <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31,N31,Q31)</f>
@@ -4543,6 +4406,10 @@
           <t>SUPPLY</t>
         </is>
       </c>
+      <c r="Q31" s="3">
+        <f>71.79</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -4550,24 +4417,21 @@
           <t>POS Mac Amazon.Com*Nx6 Seattle WA</t>
         </is>
       </c>
-      <c r="B32" s="2">
-        <f>75.40</f>
-        <v/>
-      </c>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
+      <c r="H32" s="2">
+        <f>75.40</f>
+        <v/>
+      </c>
       <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2">
-        <f>75.40</f>
-        <v/>
-      </c>
+      <c r="M32" s="2" t="n"/>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2">
         <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32,N32,Q32)</f>
@@ -4578,6 +4442,10 @@
           <t>SUPPLY</t>
         </is>
       </c>
+      <c r="Q32" s="3">
+        <f>75.40</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -4585,24 +4453,21 @@
           <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
         </is>
       </c>
-      <c r="B33" s="2">
-        <f>18.75</f>
-        <v/>
-      </c>
+      <c r="B33" s="2" t="n"/>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
+      <c r="H33" s="2">
+        <f>18.75</f>
+        <v/>
+      </c>
       <c r="I33" s="2" t="n"/>
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2">
-        <f>18.75</f>
-        <v/>
-      </c>
+      <c r="M33" s="2" t="n"/>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2">
         <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33,N33,Q33)</f>
@@ -4613,6 +4478,10 @@
           <t>SUPPLY</t>
         </is>
       </c>
+      <c r="Q33" s="3">
+        <f>18.75</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -4620,24 +4489,21 @@
           <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
         </is>
       </c>
-      <c r="B34" s="2">
-        <f>50.03</f>
-        <v/>
-      </c>
+      <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
+      <c r="H34" s="2">
+        <f>50.03</f>
+        <v/>
+      </c>
       <c r="I34" s="2" t="n"/>
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2">
-        <f>50.03</f>
-        <v/>
-      </c>
+      <c r="M34" s="2" t="n"/>
       <c r="N34" s="2" t="n"/>
       <c r="O34" s="2">
         <f>SUM(B34,C34,D34,E34,F34,G34,H34,I34,J34,K34,L34,M34,N34,Q34)</f>
@@ -4648,6 +4514,10 @@
           <t>SUPPLY</t>
         </is>
       </c>
+      <c r="Q34" s="3">
+        <f>50.03</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -4655,24 +4525,21 @@
           <t>POS Mac Amazon.Com*V25 Seattle WA</t>
         </is>
       </c>
-      <c r="B35" s="2">
-        <f>20.80</f>
-        <v/>
-      </c>
+      <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n"/>
       <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
+      <c r="H35" s="2">
+        <f>20.80</f>
+        <v/>
+      </c>
       <c r="I35" s="2" t="n"/>
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2">
-        <f>20.80</f>
-        <v/>
-      </c>
+      <c r="M35" s="2" t="n"/>
       <c r="N35" s="2" t="n"/>
       <c r="O35" s="2">
         <f>SUM(B35,C35,D35,E35,F35,G35,H35,I35,J35,K35,L35,M35,N35,Q35)</f>
@@ -4682,6 +4549,10 @@
         <is>
           <t>SUPPLY</t>
         </is>
+      </c>
+      <c r="Q35" s="3">
+        <f>20.80</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -4719,24 +4590,21 @@
           <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
         </is>
       </c>
-      <c r="B37" s="2">
-        <f>40.33</f>
-        <v/>
-      </c>
+      <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n"/>
       <c r="E37" s="2" t="n"/>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
+      <c r="H37" s="2">
+        <f>40.33</f>
+        <v/>
+      </c>
       <c r="I37" s="2" t="n"/>
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2">
-        <f>40.33</f>
-        <v/>
-      </c>
+      <c r="M37" s="2" t="n"/>
       <c r="N37" s="2" t="n"/>
       <c r="O37" s="2">
         <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,J37,K37,L37,M37,N37,Q37)</f>
@@ -4747,6 +4615,10 @@
           <t>SUPPLY</t>
         </is>
       </c>
+      <c r="Q37" s="3">
+        <f>40.33</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -4754,24 +4626,21 @@
           <t>Prog Casualty Ins Prem</t>
         </is>
       </c>
-      <c r="B38" s="2">
-        <f>930.52</f>
-        <v/>
-      </c>
+      <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="n"/>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
+      <c r="H38" s="2">
+        <f>930.52</f>
+        <v/>
+      </c>
       <c r="I38" s="2" t="n"/>
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2">
-        <f>930.52</f>
-        <v/>
-      </c>
+      <c r="M38" s="2" t="n"/>
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2">
         <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38,N38,Q38)</f>
@@ -4781,6 +4650,10 @@
         <is>
           <t>SUPPLY</t>
         </is>
+      </c>
+      <c r="Q38" s="3">
+        <f>930.52</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -4818,24 +4691,21 @@
           <t>Withdrawal Branch 0964 New York</t>
         </is>
       </c>
-      <c r="B40" s="2">
-        <f>1000.00+3200.00</f>
-        <v/>
-      </c>
+      <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
+      <c r="H40" s="2">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2">
-        <f>1000.00+3200.00</f>
-        <v/>
-      </c>
+      <c r="M40" s="2" t="n"/>
       <c r="N40" s="2" t="n"/>
       <c r="O40" s="2">
         <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,J40,K40,L40,M40,N40,Q40)</f>
@@ -4846,6 +4716,10 @@
           <t>SUPPLY</t>
         </is>
       </c>
+      <c r="Q40" s="3">
+        <f>1000.00+3200.00</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -4915,7 +4789,6 @@
         <v/>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>

--- a/credit_monthly_summary.xlsx
+++ b/credit_monthly_summary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Chase #156" sheetId="1" state="visible" r:id="rId1"/>
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK17"/>
+  <dimension ref="A1:AG17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.85546875" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
@@ -524,12 +524,12 @@
       <c r="F1" s="10" t="n"/>
       <c r="G1" s="10" t="n"/>
       <c r="H1" s="11" t="n"/>
+      <c r="Z1" s="10" t="n"/>
+      <c r="AA1" s="10" t="n"/>
+      <c r="AB1" s="10" t="n"/>
+      <c r="AC1" s="10" t="n"/>
       <c r="AD1" s="10" t="n"/>
-      <c r="AE1" s="10" t="n"/>
-      <c r="AF1" s="10" t="n"/>
-      <c r="AG1" s="10" t="n"/>
-      <c r="AH1" s="10" t="n"/>
-      <c r="AI1" s="11" t="n"/>
+      <c r="AE1" s="11" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -537,168 +537,156 @@
           <t>Month</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n"/>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Begin</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Arrow Bank Na Web Pmt</t>
+          <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Yr6 Seattle WA</t>
+          <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Amazon.Com*N22Fjseattlewa US</t>
+          <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
+          <t>POS Mac Amazon.Com*V25 Seattle WA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
+          <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
+          <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
+          <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*V25 Seattle WA</t>
+          <t>Amazon.Comseattlewa US</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
+          <t>Citi Card Onlinepayment</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
+          <t>Prog Casualty Ins Prem</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
+          <t>Credit One Bank Payment</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Amazon.Comseattlewa US</t>
+          <t>Irs Usataxpymt</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Citi Card Onlinepayment</t>
+          <t>Amazon Prime*Zh8618Uz3 Amzn.Com/Bill WA</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Prog Casualty Ins Prem</t>
+          <t>Kindercare Portland OR</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Credit One Bank Payment</t>
+          <t>Nys Dtf Pit Tax Paymnt</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Irs Usataxpymt</t>
+          <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Amazon Prime*Zh8618Uz3 Amzn.Com/Bill WA</t>
+          <t>POS Mac Amazon.Com*9O5 Seattle WA</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Kindercare Portland OR</t>
+          <t>POS Mac Amazon.Com*Nx6 Seattle WA</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Nys Dtf Pit Tax Paymnt</t>
+          <t>Withdrawal Branch 0964 New York</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Sb8 Seattle WA</t>
+          <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*9O5 Seattle WA</t>
+          <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>POS Mac Amazon.Com*Nx6 Seattle WA</t>
+          <t>Internet Trf To Client-Added Transfer Account</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Withdrawal Branch 0964 New York</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Bill Pay:Orange &amp; Rockland 136130 6Bq1P6Kr</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Bill Pay:Veolia Water New Y 200045 6Bu1T6Kr</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Internet Trf To Client-Added Transfer Account</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
           <t>No1 Sushi 88 Corkbbo ACH</t>
         </is>
       </c>
+      <c r="Z2" s="1" t="inlineStr">
+        <is>
+          <t>Atm Deposit</t>
+        </is>
+      </c>
+      <c r="AA2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amazon </t>
+        </is>
+      </c>
+      <c r="AB2" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AC2" s="1" t="inlineStr">
+        <is>
+          <t>total Credit</t>
+        </is>
+      </c>
       <c r="AD2" s="1" t="inlineStr">
         <is>
-          <t>Atm Deposit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="AE2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amazon </t>
-        </is>
-      </c>
-      <c r="AF2" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="AG2" s="1" t="inlineStr">
-        <is>
-          <t>total Credit</t>
-        </is>
-      </c>
-      <c r="AH2" s="1" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="AI2" s="1" t="n"/>
+          <t>Ending</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -707,28 +695,25 @@
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" s="1" t="n"/>
-      <c r="AE3" s="1" t="n"/>
-      <c r="AF3" s="1">
-        <f>SUM(C3:AE3)</f>
-        <v/>
-      </c>
-      <c r="AG3" s="1">
-        <f>SUM(C3:E3)</f>
-        <v/>
-      </c>
-      <c r="AH3" s="1">
-        <f>B3+AF3-AG3</f>
-        <v/>
-      </c>
-      <c r="AI3" s="3">
+      <c r="Z3" s="1" t="n"/>
+      <c r="AA3" s="1" t="n"/>
+      <c r="AB3" s="1" t="n"/>
+      <c r="AC3" s="3">
+        <f>SUM(C3:AB3)</f>
+        <v/>
+      </c>
+      <c r="AD3" s="1">
+        <f>'Chase detial #1256'!B21</f>
+        <v/>
+      </c>
+      <c r="AE3" s="3">
         <f>B3+F3-G3</f>
         <v/>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AF3" t="n">
         <v>413048</v>
       </c>
-      <c r="AK3" s="6">
+      <c r="AG3" s="6">
         <f>I3-H3</f>
         <v/>
       </c>
@@ -738,31 +723,97 @@
         <v>45778</v>
       </c>
       <c r="B4" s="3">
-        <f>AH3</f>
-        <v/>
-      </c>
-      <c r="AD4" s="1" t="n"/>
-      <c r="AE4" s="1" t="n"/>
-      <c r="AF4" s="1">
-        <f>SUM(C4:AE4)</f>
-        <v/>
-      </c>
-      <c r="AG4" s="1">
-        <f>SUM(C4:E4)</f>
-        <v/>
-      </c>
-      <c r="AH4" s="1">
-        <f>B4+AF4-AG4</f>
-        <v/>
-      </c>
-      <c r="AI4" s="3">
+        <f>H3</f>
+        <v/>
+      </c>
+      <c r="C4" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="D4" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="E4" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="F4" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>152.14</v>
+      </c>
+      <c r="H4" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="I4" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="J4" t="n">
+        <v>117.76</v>
+      </c>
+      <c r="K4" t="n">
+        <v>975</v>
+      </c>
+      <c r="L4" t="n">
+        <v>930.52</v>
+      </c>
+      <c r="M4" t="n">
+        <v>817.29</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="O4" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="P4" t="n">
+        <v>610</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>400</v>
+      </c>
+      <c r="R4" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="S4" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="T4" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4200</v>
+      </c>
+      <c r="V4" t="n">
+        <v>350</v>
+      </c>
+      <c r="W4" t="n">
+        <v>300</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1125.77</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Z4" s="1" t="n"/>
+      <c r="AA4" s="1" t="n"/>
+      <c r="AB4" s="1" t="n"/>
+      <c r="AC4" s="3">
+        <f>SUM(C4:AB4)</f>
+        <v/>
+      </c>
+      <c r="AD4" s="1">
+        <f>'Chase detial #1256'!C21</f>
+        <v/>
+      </c>
+      <c r="AE4" s="3">
         <f>B4+F4-G4</f>
         <v/>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AF4" t="n">
         <v>412604</v>
       </c>
-      <c r="AK4" s="6">
+      <c r="AG4" s="6">
         <f>I4-H4</f>
         <v/>
       </c>
@@ -772,31 +823,28 @@
         <v>45809</v>
       </c>
       <c r="B5" s="3">
-        <f>AH4</f>
-        <v/>
-      </c>
-      <c r="AD5" s="1" t="n"/>
-      <c r="AE5" s="1" t="n"/>
-      <c r="AF5" s="1">
-        <f>SUM(C5:AE5)</f>
-        <v/>
-      </c>
-      <c r="AG5" s="1">
-        <f>SUM(C5:E5)</f>
-        <v/>
-      </c>
-      <c r="AH5" s="1">
-        <f>B5+AF5-AG5</f>
-        <v/>
-      </c>
-      <c r="AI5" s="3">
+        <f>H4</f>
+        <v/>
+      </c>
+      <c r="Z5" s="1" t="n"/>
+      <c r="AA5" s="1" t="n"/>
+      <c r="AB5" s="1" t="n"/>
+      <c r="AC5" s="3">
+        <f>SUM(C5:AB5)</f>
+        <v/>
+      </c>
+      <c r="AD5" s="1">
+        <f>'Chase detial #1256'!D21</f>
+        <v/>
+      </c>
+      <c r="AE5" s="3">
         <f>B5+F5-G5</f>
         <v/>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AF5" t="n">
         <v>425005</v>
       </c>
-      <c r="AK5" s="6">
+      <c r="AG5" s="6">
         <f>I5-H5</f>
         <v/>
       </c>
@@ -806,31 +854,28 @@
         <v>45839</v>
       </c>
       <c r="B6" s="3">
-        <f>AH5</f>
-        <v/>
-      </c>
-      <c r="AD6" s="1" t="n"/>
-      <c r="AE6" s="1" t="n"/>
-      <c r="AF6" s="1">
-        <f>SUM(C6:AE6)</f>
-        <v/>
-      </c>
-      <c r="AG6" s="1">
-        <f>SUM(C6:E6)</f>
-        <v/>
-      </c>
-      <c r="AH6" s="1">
-        <f>B6+AF6-AG6</f>
-        <v/>
-      </c>
-      <c r="AI6" s="3">
+        <f>H5</f>
+        <v/>
+      </c>
+      <c r="Z6" s="1" t="n"/>
+      <c r="AA6" s="1" t="n"/>
+      <c r="AB6" s="1" t="n"/>
+      <c r="AC6" s="3">
+        <f>SUM(C6:AB6)</f>
+        <v/>
+      </c>
+      <c r="AD6" s="1">
+        <f>'Chase detial #1256'!E21</f>
+        <v/>
+      </c>
+      <c r="AE6" s="3">
         <f>B6+F6-G6</f>
         <v/>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AF6" t="n">
         <v>437378</v>
       </c>
-      <c r="AK6" s="6">
+      <c r="AG6" s="6">
         <f>I6-H6</f>
         <v/>
       </c>
@@ -840,31 +885,97 @@
         <v>45870</v>
       </c>
       <c r="B7" s="3">
-        <f>AH6</f>
-        <v/>
-      </c>
-      <c r="AD7" s="1" t="n"/>
-      <c r="AE7" s="1" t="n"/>
-      <c r="AF7" s="1">
-        <f>SUM(C7:AE7)</f>
-        <v/>
-      </c>
-      <c r="AG7" s="1">
-        <f>SUM(C7:E7)</f>
-        <v/>
-      </c>
-      <c r="AH7" s="1">
-        <f>B7+AF7-AG7</f>
-        <v/>
-      </c>
-      <c r="AI7" s="3">
+        <f>H6</f>
+        <v/>
+      </c>
+      <c r="C7" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="D7" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="E7" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="F7" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>152.14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="J7" t="n">
+        <v>117.76</v>
+      </c>
+      <c r="K7" t="n">
+        <v>975</v>
+      </c>
+      <c r="L7" t="n">
+        <v>930.52</v>
+      </c>
+      <c r="M7" t="n">
+        <v>817.29</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1600</v>
+      </c>
+      <c r="O7" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="P7" t="n">
+        <v>610</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>400</v>
+      </c>
+      <c r="R7" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="S7" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="T7" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4200</v>
+      </c>
+      <c r="V7" t="n">
+        <v>350</v>
+      </c>
+      <c r="W7" t="n">
+        <v>300</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1125.77</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Z7" s="1" t="n"/>
+      <c r="AA7" s="1" t="n"/>
+      <c r="AB7" s="1" t="n"/>
+      <c r="AC7" s="3">
+        <f>SUM(C7:AB7)</f>
+        <v/>
+      </c>
+      <c r="AD7" s="1">
+        <f>'Chase detial #1256'!F21</f>
+        <v/>
+      </c>
+      <c r="AE7" s="3">
         <f>B7+F7-G7</f>
         <v/>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AF7" t="n">
         <v>438873</v>
       </c>
-      <c r="AK7" s="6">
+      <c r="AG7" s="6">
         <f>I7-H7</f>
         <v/>
       </c>
@@ -874,31 +985,28 @@
         <v>45901</v>
       </c>
       <c r="B8" s="3">
-        <f>AH7</f>
-        <v/>
-      </c>
-      <c r="AD8" s="1" t="n"/>
-      <c r="AE8" s="1" t="n"/>
-      <c r="AF8" s="1">
-        <f>SUM(C8:AE8)</f>
-        <v/>
-      </c>
-      <c r="AG8" s="1">
-        <f>SUM(C8:E8)</f>
-        <v/>
-      </c>
-      <c r="AH8" s="1">
-        <f>B8+AF8-AG8</f>
-        <v/>
-      </c>
-      <c r="AI8" s="3">
+        <f>H7</f>
+        <v/>
+      </c>
+      <c r="Z8" s="1" t="n"/>
+      <c r="AA8" s="1" t="n"/>
+      <c r="AB8" s="1" t="n"/>
+      <c r="AC8" s="3">
+        <f>SUM(C8:AB8)</f>
+        <v/>
+      </c>
+      <c r="AD8" s="1">
+        <f>'Chase detial #1256'!G21</f>
+        <v/>
+      </c>
+      <c r="AE8" s="3">
         <f>B8+F8-G8</f>
         <v/>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AF8" t="n">
         <v>438831</v>
       </c>
-      <c r="AK8" s="6">
+      <c r="AG8" s="6">
         <f>I8-H8</f>
         <v/>
       </c>
@@ -908,31 +1016,28 @@
         <v>45931</v>
       </c>
       <c r="B9" s="3">
-        <f>AH8</f>
-        <v/>
-      </c>
-      <c r="AD9" s="1" t="n"/>
-      <c r="AE9" s="1" t="n"/>
-      <c r="AF9" s="1">
-        <f>SUM(C9:AE9)</f>
-        <v/>
-      </c>
-      <c r="AG9" s="1">
-        <f>SUM(C9:E9)</f>
-        <v/>
-      </c>
-      <c r="AH9" s="1">
-        <f>B9+AF9-AG9</f>
-        <v/>
-      </c>
-      <c r="AI9" s="3">
+        <f>H8</f>
+        <v/>
+      </c>
+      <c r="Z9" s="1" t="n"/>
+      <c r="AA9" s="1" t="n"/>
+      <c r="AB9" s="1" t="n"/>
+      <c r="AC9" s="3">
+        <f>SUM(C9:AB9)</f>
+        <v/>
+      </c>
+      <c r="AD9" s="1">
+        <f>'Chase detial #1256'!H21</f>
+        <v/>
+      </c>
+      <c r="AE9" s="3">
         <f>B9+F9-G9</f>
         <v/>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AF9" t="n">
         <v>592012</v>
       </c>
-      <c r="AK9" s="6">
+      <c r="AG9" s="6">
         <f>I9-H9</f>
         <v/>
       </c>
@@ -942,31 +1047,28 @@
         <v>45962</v>
       </c>
       <c r="B10" s="3">
-        <f>AH9</f>
-        <v/>
-      </c>
-      <c r="AD10" s="1" t="n"/>
-      <c r="AE10" s="1" t="n"/>
-      <c r="AF10" s="1">
-        <f>SUM(C10:AE10)</f>
-        <v/>
-      </c>
-      <c r="AG10" s="1">
-        <f>SUM(C10:E10)</f>
-        <v/>
-      </c>
-      <c r="AH10" s="1">
-        <f>B10+AF10-AG10</f>
-        <v/>
-      </c>
-      <c r="AI10" s="3">
+        <f>H9</f>
+        <v/>
+      </c>
+      <c r="Z10" s="1" t="n"/>
+      <c r="AA10" s="1" t="n"/>
+      <c r="AB10" s="1" t="n"/>
+      <c r="AC10" s="3">
+        <f>SUM(C10:AB10)</f>
+        <v/>
+      </c>
+      <c r="AD10" s="1">
+        <f>'Chase detial #1256'!I21</f>
+        <v/>
+      </c>
+      <c r="AE10" s="3">
         <f>B10+F10-G10</f>
         <v/>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AF10" t="n">
         <v>579559</v>
       </c>
-      <c r="AK10" s="6">
+      <c r="AG10" s="6">
         <f>I10-H10</f>
         <v/>
       </c>
@@ -976,31 +1078,28 @@
         <v>45992</v>
       </c>
       <c r="B11" s="3">
-        <f>AH10</f>
-        <v/>
-      </c>
-      <c r="AD11" s="1" t="n"/>
-      <c r="AE11" s="1" t="n"/>
-      <c r="AF11" s="1">
-        <f>SUM(C11:AE11)</f>
-        <v/>
-      </c>
-      <c r="AG11" s="1">
-        <f>SUM(C11:E11)</f>
-        <v/>
-      </c>
-      <c r="AH11" s="1">
-        <f>B11+AF11-AG11</f>
-        <v/>
-      </c>
-      <c r="AI11" s="3">
+        <f>H10</f>
+        <v/>
+      </c>
+      <c r="Z11" s="1" t="n"/>
+      <c r="AA11" s="1" t="n"/>
+      <c r="AB11" s="1" t="n"/>
+      <c r="AC11" s="3">
+        <f>SUM(C11:AB11)</f>
+        <v/>
+      </c>
+      <c r="AD11" s="1">
+        <f>'Chase detial #1256'!J21</f>
+        <v/>
+      </c>
+      <c r="AE11" s="3">
         <f>B11+F11-G11</f>
         <v/>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AF11" t="n">
         <v>703255</v>
       </c>
-      <c r="AK11" s="6">
+      <c r="AG11" s="6">
         <f>I11-H11</f>
         <v/>
       </c>
@@ -1010,31 +1109,28 @@
         <v>46023</v>
       </c>
       <c r="B12" s="3">
-        <f>AH11</f>
-        <v/>
-      </c>
-      <c r="AD12" s="1" t="n"/>
-      <c r="AE12" s="1" t="n"/>
-      <c r="AF12" s="1">
-        <f>SUM(C12:AE12)</f>
-        <v/>
-      </c>
-      <c r="AG12" s="1">
-        <f>SUM(C12:E12)</f>
-        <v/>
-      </c>
-      <c r="AH12" s="1">
-        <f>B12+AF12-AG12</f>
-        <v/>
-      </c>
-      <c r="AI12" s="3">
+        <f>H11</f>
+        <v/>
+      </c>
+      <c r="Z12" s="1" t="n"/>
+      <c r="AA12" s="1" t="n"/>
+      <c r="AB12" s="1" t="n"/>
+      <c r="AC12" s="3">
+        <f>SUM(C12:AB12)</f>
+        <v/>
+      </c>
+      <c r="AD12" s="1">
+        <f>'Chase detial #1256'!K21</f>
+        <v/>
+      </c>
+      <c r="AE12" s="3">
         <f>B12+F12-G12</f>
         <v/>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AF12" t="n">
         <v>698719</v>
       </c>
-      <c r="AK12" s="6">
+      <c r="AG12" s="6">
         <f>I12-H12</f>
         <v/>
       </c>
@@ -1044,31 +1140,28 @@
         <v>46054</v>
       </c>
       <c r="B13" s="3">
-        <f>AH12</f>
-        <v/>
-      </c>
-      <c r="AD13" s="1" t="n"/>
-      <c r="AE13" s="1" t="n"/>
-      <c r="AF13" s="1">
-        <f>SUM(C13:AE13)</f>
-        <v/>
-      </c>
-      <c r="AG13" s="1">
-        <f>SUM(C13:E13)</f>
-        <v/>
-      </c>
-      <c r="AH13" s="1">
-        <f>B13+AF13-AG13</f>
-        <v/>
-      </c>
-      <c r="AI13" s="3">
+        <f>H12</f>
+        <v/>
+      </c>
+      <c r="Z13" s="1" t="n"/>
+      <c r="AA13" s="1" t="n"/>
+      <c r="AB13" s="1" t="n"/>
+      <c r="AC13" s="3">
+        <f>SUM(C13:AB13)</f>
+        <v/>
+      </c>
+      <c r="AD13" s="1">
+        <f>'Chase detial #1256'!L21</f>
+        <v/>
+      </c>
+      <c r="AE13" s="3">
         <f>B13+F13-G13</f>
         <v/>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AF13" t="n">
         <v>713229</v>
       </c>
-      <c r="AK13" s="6">
+      <c r="AG13" s="6">
         <f>I13-H13</f>
         <v/>
       </c>
@@ -1078,31 +1171,28 @@
         <v>46082</v>
       </c>
       <c r="B14" s="3">
-        <f>AH13</f>
-        <v/>
-      </c>
-      <c r="AD14" s="1" t="n"/>
-      <c r="AE14" s="1" t="n"/>
-      <c r="AF14" s="1">
-        <f>SUM(C14:AE14)</f>
-        <v/>
-      </c>
-      <c r="AG14" s="1">
-        <f>SUM(C14:E14)</f>
-        <v/>
-      </c>
-      <c r="AH14" s="1">
-        <f>B14+AF14-AG14</f>
-        <v/>
-      </c>
-      <c r="AI14" s="3">
+        <f>H13</f>
+        <v/>
+      </c>
+      <c r="Z14" s="1" t="n"/>
+      <c r="AA14" s="1" t="n"/>
+      <c r="AB14" s="1" t="n"/>
+      <c r="AC14" s="3">
+        <f>SUM(C14:AB14)</f>
+        <v/>
+      </c>
+      <c r="AD14" s="1">
+        <f>'Chase detial #1256'!M21</f>
+        <v/>
+      </c>
+      <c r="AE14" s="3">
         <f>B14+F14-G14</f>
         <v/>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AF14" t="n">
         <v>716586</v>
       </c>
-      <c r="AK14" s="6">
+      <c r="AG14" s="6">
         <f>I14-H14</f>
         <v/>
       </c>
@@ -1206,19 +1296,19 @@
         <f>SUM(Y3:Y14)</f>
         <v/>
       </c>
-      <c r="Z15" s="6">
+      <c r="Z15" s="3">
         <f>SUM(Z3:Z14)</f>
         <v/>
       </c>
-      <c r="AA15" s="6">
+      <c r="AA15" s="3">
         <f>SUM(AA3:AA14)</f>
         <v/>
       </c>
-      <c r="AB15" s="6">
+      <c r="AB15" s="3">
         <f>SUM(AB3:AB14)</f>
         <v/>
       </c>
-      <c r="AC15" s="6">
+      <c r="AC15" s="3">
         <f>SUM(AC3:AC14)</f>
         <v/>
       </c>
@@ -1226,26 +1316,7 @@
         <f>SUM(AD3:AD14)</f>
         <v/>
       </c>
-      <c r="AE15" s="3">
-        <f>SUM(AE3:AE14)</f>
-        <v/>
-      </c>
-      <c r="AF15" s="3">
-        <f>SUM(AF3:AF14)</f>
-        <v/>
-      </c>
-      <c r="AG15" s="3">
-        <f>SUM(AG3:AG14)</f>
-        <v/>
-      </c>
-      <c r="AH15" s="3">
-        <f>AH14</f>
-        <v/>
-      </c>
-      <c r="AI15" s="3">
-        <f>AI14</f>
-        <v/>
-      </c>
+      <c r="AE15" s="1" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n"/>
@@ -1272,21 +1343,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42.85546875" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
+    <col width="12.28515625" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
     <col width="7.140625" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
     <col width="7.85546875" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
     <col width="6.85546875" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="9.28515625" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="6.28515625" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
     <col width="7.28515625" bestFit="1" customWidth="1" style="5" min="6" max="6"/>
     <col width="7.140625" bestFit="1" customWidth="1" style="5" min="7" max="7"/>
-    <col width="9.28515625" bestFit="1" customWidth="1" style="5" min="8" max="8"/>
+    <col width="7" bestFit="1" customWidth="1" style="5" min="8" max="8"/>
     <col width="7.42578125" bestFit="1" customWidth="1" style="5" min="9" max="9"/>
-    <col width="9.28515625" bestFit="1" customWidth="1" style="5" min="10" max="12"/>
+    <col width="7.28515625" bestFit="1" customWidth="1" style="5" min="10" max="10"/>
+    <col width="6.85546875" bestFit="1" customWidth="1" style="5" min="11" max="11"/>
+    <col width="7.140625" bestFit="1" customWidth="1" style="5" min="12" max="12"/>
     <col width="7.5703125" bestFit="1" customWidth="1" style="5" min="13" max="13"/>
-    <col width="10.42578125" bestFit="1" customWidth="1" style="5" min="14" max="14"/>
+    <col width="6.85546875" bestFit="1" customWidth="1" style="5" min="14" max="14"/>
     <col width="10.5703125" bestFit="1" customWidth="1" style="5" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -1348,7 +1421,11 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="O1" s="2" t="n"/>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>CATEGORY</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1357,10 +1434,16 @@
         </is>
       </c>
       <c r="B2" s="1" t="n"/>
-      <c r="C2" s="1" t="n"/>
+      <c r="C2" s="1">
+        <f>117.76+50.03+71.79+152.14+20.80+40.33+343.93+17.59</f>
+        <v/>
+      </c>
       <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
+      <c r="F2" s="1">
+        <f>117.76+50.03+71.79+152.14+20.80+40.33+343.93+17.59</f>
+        <v/>
+      </c>
       <c r="G2" s="1" t="n"/>
       <c r="H2" s="1" t="n"/>
       <c r="I2" s="1" t="n"/>
@@ -1469,16 +1552,22 @@
         </is>
       </c>
       <c r="B6" s="1" t="n"/>
-      <c r="C6" s="1" t="n"/>
+      <c r="C6" s="3">
+        <f>4000</f>
+        <v/>
+      </c>
       <c r="D6" s="1" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="1" t="n"/>
+      <c r="E6" s="1" t="n"/>
+      <c r="F6" s="3">
+        <f>4000</f>
+        <v/>
+      </c>
       <c r="G6" s="1" t="n"/>
-      <c r="H6" s="3" t="n"/>
+      <c r="H6" s="1" t="n"/>
       <c r="I6" s="1" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
+      <c r="J6" s="1" t="n"/>
+      <c r="K6" s="1" t="n"/>
+      <c r="L6" s="1" t="n"/>
       <c r="M6" s="1" t="n"/>
       <c r="N6" s="3">
         <f>SUM(B6,C6,D6,E6,F6,G6,H6,I6,J6,K6,L6,M6)</f>
@@ -1497,16 +1586,22 @@
         </is>
       </c>
       <c r="B7" s="1" t="n"/>
-      <c r="C7" s="1" t="n"/>
+      <c r="C7" s="3">
+        <f>385.77+740</f>
+        <v/>
+      </c>
       <c r="D7" s="1" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="1" t="n"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="3">
+        <f>385.77+740</f>
+        <v/>
+      </c>
       <c r="G7" s="1" t="n"/>
-      <c r="H7" s="3" t="n"/>
+      <c r="H7" s="1" t="n"/>
       <c r="I7" s="1" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
+      <c r="J7" s="1" t="n"/>
+      <c r="K7" s="1" t="n"/>
+      <c r="L7" s="1" t="n"/>
       <c r="M7" s="1" t="n"/>
       <c r="N7" s="3">
         <f>SUM(B7,C7,D7,E7,F7,G7,H7,I7,J7,K7,L7,M7)</f>
@@ -1525,16 +1620,22 @@
         </is>
       </c>
       <c r="B8" s="1" t="n"/>
-      <c r="C8" s="1" t="n"/>
+      <c r="C8" s="3">
+        <f>300</f>
+        <v/>
+      </c>
       <c r="D8" s="1" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="3">
+        <f>300</f>
+        <v/>
+      </c>
       <c r="G8" s="1" t="n"/>
-      <c r="H8" s="3" t="n"/>
+      <c r="H8" s="1" t="n"/>
       <c r="I8" s="1" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
+      <c r="J8" s="1" t="n"/>
+      <c r="K8" s="1" t="n"/>
+      <c r="L8" s="1" t="n"/>
       <c r="M8" s="1" t="n"/>
       <c r="N8" s="3">
         <f>SUM(B8,C8,D8,E8,F8,G8,H8,I8,J8,K8,L8,M8)</f>
@@ -1553,16 +1654,22 @@
         </is>
       </c>
       <c r="B9" s="1" t="n"/>
-      <c r="C9" s="1" t="n"/>
+      <c r="C9" s="3">
+        <f>350</f>
+        <v/>
+      </c>
       <c r="D9" s="1" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="1" t="n"/>
+      <c r="E9" s="1" t="n"/>
+      <c r="F9" s="3">
+        <f>350</f>
+        <v/>
+      </c>
       <c r="G9" s="1" t="n"/>
-      <c r="H9" s="3" t="n"/>
+      <c r="H9" s="1" t="n"/>
       <c r="I9" s="1" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
+      <c r="J9" s="1" t="n"/>
+      <c r="K9" s="1" t="n"/>
+      <c r="L9" s="1" t="n"/>
       <c r="M9" s="1" t="n"/>
       <c r="N9" s="3">
         <f>SUM(B9,C9,D9,E9,F9,G9,H9,I9,J9,K9,L9,M9)</f>
@@ -1581,16 +1688,22 @@
         </is>
       </c>
       <c r="B10" s="1" t="n"/>
-      <c r="C10" s="1" t="n"/>
+      <c r="C10" s="3">
+        <f>1000+3200</f>
+        <v/>
+      </c>
       <c r="D10" s="1" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="1" t="n"/>
+      <c r="E10" s="1" t="n"/>
+      <c r="F10" s="3">
+        <f>1000+3200</f>
+        <v/>
+      </c>
       <c r="G10" s="1" t="n"/>
-      <c r="H10" s="3" t="n"/>
+      <c r="H10" s="1" t="n"/>
       <c r="I10" s="1" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
+      <c r="J10" s="1" t="n"/>
+      <c r="K10" s="1" t="n"/>
+      <c r="L10" s="1" t="n"/>
       <c r="M10" s="1" t="n"/>
       <c r="N10" s="3">
         <f>SUM(B10,C10,D10,E10,F10,G10,H10,I10,J10,K10,L10,M10)</f>
@@ -1609,16 +1722,22 @@
         </is>
       </c>
       <c r="B11" s="1" t="n"/>
-      <c r="C11" s="1" t="n"/>
+      <c r="C11" s="3">
+        <f>75.4</f>
+        <v/>
+      </c>
       <c r="D11" s="1" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="1" t="n"/>
+      <c r="E11" s="1" t="n"/>
+      <c r="F11" s="3">
+        <f>75.4</f>
+        <v/>
+      </c>
       <c r="G11" s="1" t="n"/>
-      <c r="H11" s="3" t="n"/>
+      <c r="H11" s="1" t="n"/>
       <c r="I11" s="1" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
+      <c r="J11" s="1" t="n"/>
+      <c r="K11" s="1" t="n"/>
+      <c r="L11" s="1" t="n"/>
       <c r="M11" s="1" t="n"/>
       <c r="N11" s="3">
         <f>SUM(B11,C11,D11,E11,F11,G11,H11,I11,J11,K11,L11,M11)</f>
@@ -1637,16 +1756,22 @@
         </is>
       </c>
       <c r="B12" s="1" t="n"/>
-      <c r="C12" s="1" t="n"/>
+      <c r="C12" s="3">
+        <f>26.57</f>
+        <v/>
+      </c>
       <c r="D12" s="1" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="1" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="3">
+        <f>26.57</f>
+        <v/>
+      </c>
       <c r="G12" s="1" t="n"/>
-      <c r="H12" s="3" t="n"/>
+      <c r="H12" s="1" t="n"/>
       <c r="I12" s="1" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
+      <c r="J12" s="1" t="n"/>
+      <c r="K12" s="1" t="n"/>
+      <c r="L12" s="1" t="n"/>
       <c r="M12" s="1" t="n"/>
       <c r="N12" s="3">
         <f>SUM(B12,C12,D12,E12,F12,G12,H12,I12,J12,K12,L12,M12)</f>
@@ -1665,16 +1790,22 @@
         </is>
       </c>
       <c r="B13" s="1" t="n"/>
-      <c r="C13" s="1" t="n"/>
+      <c r="C13" s="3">
+        <f>18.75</f>
+        <v/>
+      </c>
       <c r="D13" s="1" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="1" t="n"/>
+      <c r="E13" s="1" t="n"/>
+      <c r="F13" s="3">
+        <f>18.75</f>
+        <v/>
+      </c>
       <c r="G13" s="1" t="n"/>
-      <c r="H13" s="3" t="n"/>
+      <c r="H13" s="1" t="n"/>
       <c r="I13" s="1" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
+      <c r="J13" s="1" t="n"/>
+      <c r="K13" s="1" t="n"/>
+      <c r="L13" s="1" t="n"/>
       <c r="M13" s="1" t="n"/>
       <c r="N13" s="3">
         <f>SUM(B13,C13,D13,E13,F13,G13,H13,I13,J13,K13,L13,M13)</f>
@@ -1693,16 +1824,22 @@
         </is>
       </c>
       <c r="B14" s="1" t="n"/>
-      <c r="C14" s="1" t="n"/>
+      <c r="C14" s="3">
+        <f>200+200</f>
+        <v/>
+      </c>
       <c r="D14" s="1" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="1" t="n"/>
+      <c r="E14" s="1" t="n"/>
+      <c r="F14" s="3">
+        <f>200+200</f>
+        <v/>
+      </c>
       <c r="G14" s="1" t="n"/>
-      <c r="H14" s="3" t="n"/>
+      <c r="H14" s="1" t="n"/>
       <c r="I14" s="1" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
+      <c r="J14" s="1" t="n"/>
+      <c r="K14" s="1" t="n"/>
+      <c r="L14" s="1" t="n"/>
       <c r="M14" s="1" t="n"/>
       <c r="N14" s="3">
         <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,J14,K14,L14,M14)</f>
@@ -1721,16 +1858,22 @@
         </is>
       </c>
       <c r="B15" s="1" t="n"/>
-      <c r="C15" s="1" t="n"/>
+      <c r="C15" s="3">
+        <f>490+120</f>
+        <v/>
+      </c>
       <c r="D15" s="1" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="1" t="n"/>
+      <c r="E15" s="1" t="n"/>
+      <c r="F15" s="3">
+        <f>490+120</f>
+        <v/>
+      </c>
       <c r="G15" s="1" t="n"/>
-      <c r="H15" s="3" t="n"/>
+      <c r="H15" s="1" t="n"/>
       <c r="I15" s="1" t="n"/>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
+      <c r="J15" s="1" t="n"/>
+      <c r="K15" s="1" t="n"/>
+      <c r="L15" s="1" t="n"/>
       <c r="M15" s="1" t="n"/>
       <c r="N15" s="3">
         <f>SUM(B15,C15,D15,E15,F15,G15,H15,I15,J15,K15,L15,M15)</f>
@@ -1749,16 +1892,22 @@
         </is>
       </c>
       <c r="B16" s="1" t="n"/>
-      <c r="C16" s="1" t="n"/>
+      <c r="C16" s="3">
+        <f>16.25</f>
+        <v/>
+      </c>
       <c r="D16" s="1" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="1" t="n"/>
+      <c r="E16" s="1" t="n"/>
+      <c r="F16" s="3">
+        <f>16.25</f>
+        <v/>
+      </c>
       <c r="G16" s="1" t="n"/>
-      <c r="H16" s="3" t="n"/>
+      <c r="H16" s="1" t="n"/>
       <c r="I16" s="1" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
+      <c r="J16" s="1" t="n"/>
+      <c r="K16" s="1" t="n"/>
+      <c r="L16" s="1" t="n"/>
       <c r="M16" s="1" t="n"/>
       <c r="N16" s="3">
         <f>SUM(B16,C16,D16,E16,F16,G16,H16,I16,J16,K16,L16,M16)</f>
@@ -1777,16 +1926,22 @@
         </is>
       </c>
       <c r="B17" s="1" t="n"/>
-      <c r="C17" s="1" t="n"/>
+      <c r="C17" s="3">
+        <f>800+800</f>
+        <v/>
+      </c>
       <c r="D17" s="1" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="1" t="n"/>
+      <c r="E17" s="1" t="n"/>
+      <c r="F17" s="3">
+        <f>800+800</f>
+        <v/>
+      </c>
       <c r="G17" s="1" t="n"/>
-      <c r="H17" s="3" t="n"/>
+      <c r="H17" s="1" t="n"/>
       <c r="I17" s="1" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
+      <c r="J17" s="1" t="n"/>
+      <c r="K17" s="1" t="n"/>
+      <c r="L17" s="1" t="n"/>
       <c r="M17" s="1" t="n"/>
       <c r="N17" s="3">
         <f>SUM(B17,C17,D17,E17,F17,G17,H17,I17,J17,K17,L17,M17)</f>
@@ -1805,16 +1960,22 @@
         </is>
       </c>
       <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
+      <c r="C18" s="3">
+        <f>817.29</f>
+        <v/>
+      </c>
       <c r="D18" s="1" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="3">
+        <f>817.29</f>
+        <v/>
+      </c>
       <c r="G18" s="1" t="n"/>
-      <c r="H18" s="3" t="n"/>
+      <c r="H18" s="1" t="n"/>
       <c r="I18" s="1" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="n"/>
+      <c r="J18" s="1" t="n"/>
+      <c r="K18" s="1" t="n"/>
+      <c r="L18" s="1" t="n"/>
       <c r="M18" s="1" t="n"/>
       <c r="N18" s="3">
         <f>SUM(B18,C18,D18,E18,F18,G18,H18,I18,J18,K18,L18,M18)</f>
@@ -1833,16 +1994,22 @@
         </is>
       </c>
       <c r="B19" s="1" t="n"/>
-      <c r="C19" s="1" t="n"/>
+      <c r="C19" s="3">
+        <f>930.52</f>
+        <v/>
+      </c>
       <c r="D19" s="1" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="1" t="n"/>
+      <c r="E19" s="1" t="n"/>
+      <c r="F19" s="3">
+        <f>930.52</f>
+        <v/>
+      </c>
       <c r="G19" s="1" t="n"/>
-      <c r="H19" s="3" t="n"/>
+      <c r="H19" s="1" t="n"/>
       <c r="I19" s="1" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
+      <c r="J19" s="1" t="n"/>
+      <c r="K19" s="1" t="n"/>
+      <c r="L19" s="1" t="n"/>
       <c r="M19" s="1" t="n"/>
       <c r="N19" s="3">
         <f>SUM(B19,C19,D19,E19,F19,G19,H19,I19,J19,K19,L19,M19)</f>
@@ -1861,16 +2028,22 @@
         </is>
       </c>
       <c r="B20" s="1" t="n"/>
-      <c r="C20" s="1" t="n"/>
+      <c r="C20" s="3">
+        <f>975</f>
+        <v/>
+      </c>
       <c r="D20" s="1" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="1" t="n"/>
+      <c r="E20" s="1" t="n"/>
+      <c r="F20" s="3">
+        <f>975</f>
+        <v/>
+      </c>
       <c r="G20" s="1" t="n"/>
-      <c r="H20" s="3" t="n"/>
+      <c r="H20" s="1" t="n"/>
       <c r="I20" s="1" t="n"/>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3" t="n"/>
+      <c r="J20" s="1" t="n"/>
+      <c r="K20" s="1" t="n"/>
+      <c r="L20" s="1" t="n"/>
       <c r="M20" s="1" t="n"/>
       <c r="N20" s="3">
         <f>SUM(B20,C20,D20,E20,F20,G20,H20,I20,J20,K20,L20,M20)</f>
@@ -1885,398 +2058,62 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Amazon.Comseattlewa US</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="n"/>
-      <c r="C21" s="1" t="n"/>
-      <c r="D21" s="1" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="1" t="n"/>
-      <c r="G21" s="1" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="1" t="n"/>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="1" t="n"/>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B21" s="3">
+        <f>SUM(B2:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="3">
+        <f>SUM(C2:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="3">
+        <f>SUM(D2:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="3">
+        <f>SUM(E2:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="3">
+        <f>SUM(F2:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="3">
+        <f>SUM(G2:G20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="3">
+        <f>SUM(H2:H20)</f>
+        <v/>
+      </c>
+      <c r="I21" s="3">
+        <f>SUM(I2:I20)</f>
+        <v/>
+      </c>
+      <c r="J21" s="3">
+        <f>SUM(J2:J20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="3">
+        <f>SUM(K2:K20)</f>
+        <v/>
+      </c>
+      <c r="L21" s="3">
+        <f>SUM(L2:L20)</f>
+        <v/>
+      </c>
+      <c r="M21" s="3">
+        <f>SUM(M2:M20)</f>
+        <v/>
+      </c>
       <c r="N21" s="3">
         <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,J21,K21,L21,M21)</f>
         <v/>
       </c>
-      <c r="O21" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Yr6 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="n"/>
-      <c r="C22" s="1" t="n"/>
-      <c r="D22" s="1" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="1" t="n"/>
-      <c r="G22" s="1" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="1" t="n"/>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="1" t="n"/>
-      <c r="N22" s="3">
-        <f>SUM(B22,C22,D22,E22,F22,G22,H22,I22,J22,K22,L22,M22)</f>
-        <v/>
-      </c>
-      <c r="O22" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>Arrow Bank Na Web Pmt</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="n"/>
-      <c r="C23" s="1" t="n"/>
-      <c r="D23" s="1" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="1" t="n"/>
-      <c r="G23" s="1" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="1" t="n"/>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="1" t="n"/>
-      <c r="N23" s="3">
-        <f>SUM(B23,C23,D23,E23,F23,G23,H23,I23,J23,K23,L23,M23)</f>
-        <v/>
-      </c>
-      <c r="O23" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="n"/>
-      <c r="C24" s="1" t="n"/>
-      <c r="D24" s="1" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="1" t="n"/>
-      <c r="G24" s="1" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="1" t="n"/>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n"/>
-      <c r="M24" s="1" t="n"/>
-      <c r="N24" s="3">
-        <f>SUM(B24,C24,D24,E24,F24,G24,H24,I24,J24,K24,L24,M24)</f>
-        <v/>
-      </c>
-      <c r="O24" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="n"/>
-      <c r="C25" s="1" t="n"/>
-      <c r="D25" s="1" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="1" t="n"/>
-      <c r="G25" s="1" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="1" t="n"/>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="1" t="n"/>
-      <c r="N25" s="3">
-        <f>SUM(B25,C25,D25,E25,F25,G25,H25,I25,J25,K25,L25,M25)</f>
-        <v/>
-      </c>
-      <c r="O25" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="n"/>
-      <c r="C26" s="1" t="n"/>
-      <c r="D26" s="1" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="1" t="n"/>
-      <c r="G26" s="1" t="n"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="1" t="n"/>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
-      <c r="M26" s="1" t="n"/>
-      <c r="N26" s="3">
-        <f>SUM(B26,C26,D26,E26,F26,G26,H26,I26,J26,K26,L26,M26)</f>
-        <v/>
-      </c>
-      <c r="O26" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*V25 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="n"/>
-      <c r="C27" s="1" t="n"/>
-      <c r="D27" s="1" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="1" t="n"/>
-      <c r="G27" s="1" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="1" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="1" t="n"/>
-      <c r="N27" s="3">
-        <f>SUM(B27,C27,D27,E27,F27,G27,H27,I27,J27,K27,L27,M27)</f>
-        <v/>
-      </c>
-      <c r="O27" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="n"/>
-      <c r="C28" s="1" t="n"/>
-      <c r="D28" s="1" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="1" t="n"/>
-      <c r="G28" s="1" t="n"/>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="1" t="n"/>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="n"/>
-      <c r="L28" s="3" t="n"/>
-      <c r="M28" s="1" t="n"/>
-      <c r="N28" s="3">
-        <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,J28,K28,L28,M28)</f>
-        <v/>
-      </c>
-      <c r="O28" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="n"/>
-      <c r="C29" s="1" t="n"/>
-      <c r="D29" s="1" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="1" t="n"/>
-      <c r="G29" s="1" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="1" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="1" t="n"/>
-      <c r="N29" s="3">
-        <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29)</f>
-        <v/>
-      </c>
-      <c r="O29" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="n"/>
-      <c r="C30" s="1" t="n"/>
-      <c r="D30" s="1" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="1" t="n"/>
-      <c r="G30" s="1" t="n"/>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="1" t="n"/>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="1" t="n"/>
-      <c r="N30" s="3">
-        <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30)</f>
-        <v/>
-      </c>
-      <c r="O30" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="n"/>
-      <c r="C31" s="1" t="n"/>
-      <c r="D31" s="1" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="1" t="n"/>
-      <c r="G31" s="1" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="1" t="n"/>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
-      <c r="M31" s="1" t="n"/>
-      <c r="N31" s="3">
-        <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31)</f>
-        <v/>
-      </c>
-      <c r="O31" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Amazon.Com*N22Fjseattlewa US</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="n"/>
-      <c r="C32" s="1" t="n"/>
-      <c r="D32" s="1" t="n"/>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="1" t="n"/>
-      <c r="G32" s="1" t="n"/>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="1" t="n"/>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n"/>
-      <c r="M32" s="1" t="n"/>
-      <c r="N32" s="3">
-        <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32)</f>
-        <v/>
-      </c>
-      <c r="O32" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B33" s="3">
-        <f>SUM(B2:B32)</f>
-        <v/>
-      </c>
-      <c r="C33" s="3">
-        <f>SUM(C2:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="3">
-        <f>SUM(D2:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="3">
-        <f>SUM(E2:E32)</f>
-        <v/>
-      </c>
-      <c r="F33" s="3">
-        <f>SUM(F2:F32)</f>
-        <v/>
-      </c>
-      <c r="G33" s="3">
-        <f>SUM(G2:G32)</f>
-        <v/>
-      </c>
-      <c r="H33" s="3">
-        <f>SUM(H2:H32)</f>
-        <v/>
-      </c>
-      <c r="I33" s="3">
-        <f>SUM(I2:I32)</f>
-        <v/>
-      </c>
-      <c r="J33" s="3">
-        <f>SUM(J2:J32)</f>
-        <v/>
-      </c>
-      <c r="K33" s="3">
-        <f>SUM(K2:K32)</f>
-        <v/>
-      </c>
-      <c r="L33" s="3">
-        <f>SUM(L2:L32)</f>
-        <v/>
-      </c>
-      <c r="M33" s="3">
-        <f>SUM(M2:M32)</f>
-        <v/>
-      </c>
-      <c r="N33" s="3">
-        <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33)</f>
-        <v/>
-      </c>
-      <c r="O33" s="1" t="n"/>
+      <c r="O21" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2289,10 +2126,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42.85546875" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
+    <col width="12.28515625" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
     <col width="7.140625" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
     <col width="7.85546875" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
     <col width="6.85546875" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
@@ -2302,10 +2139,10 @@
     <col width="7" bestFit="1" customWidth="1" style="5" min="8" max="8"/>
     <col width="7.42578125" bestFit="1" customWidth="1" style="5" min="9" max="9"/>
     <col width="7.28515625" bestFit="1" customWidth="1" style="5" min="10" max="10"/>
-    <col width="9.28515625" bestFit="1" customWidth="1" style="5" min="11" max="11"/>
+    <col width="6.85546875" bestFit="1" customWidth="1" style="5" min="11" max="11"/>
     <col width="7.140625" bestFit="1" customWidth="1" style="5" min="12" max="12"/>
     <col width="7.5703125" bestFit="1" customWidth="1" style="5" min="13" max="13"/>
-    <col width="9.28515625" bestFit="1" customWidth="1" style="5" min="14" max="14"/>
+    <col width="6.85546875" bestFit="1" customWidth="1" style="5" min="14" max="14"/>
     <col width="10.5703125" bestFit="1" customWidth="1" style="5" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -2369,7 +2206,7 @@
       </c>
       <c r="O1" s="2" t="inlineStr">
         <is>
-          <t>categories</t>
+          <t>CATEGORY</t>
         </is>
       </c>
       <c r="P1" s="4" t="n">
@@ -2386,11 +2223,17 @@
       <c r="C2" s="1" t="n"/>
       <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
+      <c r="F2" s="1">
+        <f>117.76+50.03+71.79+152.14+20.80+40.33+343.93+17.59</f>
+        <v/>
+      </c>
       <c r="G2" s="1" t="n"/>
       <c r="H2" s="1" t="n"/>
       <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
+      <c r="J2" s="1">
+        <f>117.76+50.03+71.79+152.14+20.80+40.33+343.93+17.59</f>
+        <v/>
+      </c>
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n"/>
       <c r="M2" s="1" t="n"/>
@@ -2403,8 +2246,9 @@
           <t>SUPPLY</t>
         </is>
       </c>
-      <c r="P2" t="n">
-        <v>42</v>
+      <c r="P2">
+        <f>117.76+50.03+71.79+152.14+20.80+40.33+343.93+17.59</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -2434,9 +2278,6 @@
           <t>GASOLINE</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2465,9 +2306,6 @@
           <t>SUPRER</t>
         </is>
       </c>
-      <c r="P4" t="n">
-        <v>234</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -2496,9 +2334,6 @@
           <t>SUPPLY</t>
         </is>
       </c>
-      <c r="P5" t="n">
-        <v>234</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -2507,15 +2342,21 @@
         </is>
       </c>
       <c r="B6" s="1" t="n"/>
-      <c r="C6" s="3" t="n"/>
+      <c r="C6" s="1" t="n"/>
       <c r="D6" s="1" t="n"/>
       <c r="E6" s="1" t="n"/>
-      <c r="F6" s="3" t="n"/>
+      <c r="F6" s="3">
+        <f>4000</f>
+        <v/>
+      </c>
       <c r="G6" s="1" t="n"/>
       <c r="H6" s="1" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="1" t="n"/>
-      <c r="K6" s="3" t="n"/>
+      <c r="I6" s="1" t="n"/>
+      <c r="J6" s="3">
+        <f>4000</f>
+        <v/>
+      </c>
+      <c r="K6" s="1" t="n"/>
       <c r="L6" s="1" t="n"/>
       <c r="M6" s="1" t="n"/>
       <c r="N6" s="3">
@@ -2539,15 +2380,21 @@
         </is>
       </c>
       <c r="B7" s="1" t="n"/>
-      <c r="C7" s="3" t="n"/>
+      <c r="C7" s="1" t="n"/>
       <c r="D7" s="1" t="n"/>
       <c r="E7" s="1" t="n"/>
-      <c r="F7" s="3" t="n"/>
+      <c r="F7" s="3">
+        <f>385.77+740</f>
+        <v/>
+      </c>
       <c r="G7" s="1" t="n"/>
       <c r="H7" s="1" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="1" t="n"/>
-      <c r="K7" s="3" t="n"/>
+      <c r="I7" s="1" t="n"/>
+      <c r="J7" s="3">
+        <f>385.77+740</f>
+        <v/>
+      </c>
+      <c r="K7" s="1" t="n"/>
       <c r="L7" s="1" t="n"/>
       <c r="M7" s="1" t="n"/>
       <c r="N7" s="3">
@@ -2560,7 +2407,7 @@
         </is>
       </c>
       <c r="P7" s="6">
-        <f>385.77+740+453</f>
+        <f>385.77+740</f>
         <v/>
       </c>
     </row>
@@ -2571,15 +2418,21 @@
         </is>
       </c>
       <c r="B8" s="1" t="n"/>
-      <c r="C8" s="3" t="n"/>
+      <c r="C8" s="1" t="n"/>
       <c r="D8" s="1" t="n"/>
       <c r="E8" s="1" t="n"/>
-      <c r="F8" s="3" t="n"/>
+      <c r="F8" s="3">
+        <f>300</f>
+        <v/>
+      </c>
       <c r="G8" s="1" t="n"/>
       <c r="H8" s="1" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="1" t="n"/>
-      <c r="K8" s="3" t="n"/>
+      <c r="I8" s="1" t="n"/>
+      <c r="J8" s="3">
+        <f>300</f>
+        <v/>
+      </c>
+      <c r="K8" s="1" t="n"/>
       <c r="L8" s="1" t="n"/>
       <c r="M8" s="1" t="n"/>
       <c r="N8" s="3">
@@ -2603,15 +2456,21 @@
         </is>
       </c>
       <c r="B9" s="1" t="n"/>
-      <c r="C9" s="3" t="n"/>
+      <c r="C9" s="1" t="n"/>
       <c r="D9" s="1" t="n"/>
       <c r="E9" s="1" t="n"/>
-      <c r="F9" s="3" t="n"/>
+      <c r="F9" s="3">
+        <f>350</f>
+        <v/>
+      </c>
       <c r="G9" s="1" t="n"/>
       <c r="H9" s="1" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="1" t="n"/>
-      <c r="K9" s="3" t="n"/>
+      <c r="I9" s="1" t="n"/>
+      <c r="J9" s="3">
+        <f>350</f>
+        <v/>
+      </c>
+      <c r="K9" s="1" t="n"/>
       <c r="L9" s="1" t="n"/>
       <c r="M9" s="1" t="n"/>
       <c r="N9" s="3">
@@ -2635,15 +2494,21 @@
         </is>
       </c>
       <c r="B10" s="1" t="n"/>
-      <c r="C10" s="3" t="n"/>
+      <c r="C10" s="1" t="n"/>
       <c r="D10" s="1" t="n"/>
       <c r="E10" s="1" t="n"/>
-      <c r="F10" s="3" t="n"/>
+      <c r="F10" s="3">
+        <f>1000+3200</f>
+        <v/>
+      </c>
       <c r="G10" s="1" t="n"/>
       <c r="H10" s="1" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="1" t="n"/>
-      <c r="K10" s="3" t="n"/>
+      <c r="I10" s="1" t="n"/>
+      <c r="J10" s="3">
+        <f>1000+3200</f>
+        <v/>
+      </c>
+      <c r="K10" s="1" t="n"/>
       <c r="L10" s="1" t="n"/>
       <c r="M10" s="1" t="n"/>
       <c r="N10" s="3">
@@ -2656,7 +2521,7 @@
         </is>
       </c>
       <c r="P10" s="6">
-        <f>1000+3200+3800</f>
+        <f>1000+3200</f>
         <v/>
       </c>
     </row>
@@ -2667,15 +2532,21 @@
         </is>
       </c>
       <c r="B11" s="1" t="n"/>
-      <c r="C11" s="3" t="n"/>
+      <c r="C11" s="1" t="n"/>
       <c r="D11" s="1" t="n"/>
       <c r="E11" s="1" t="n"/>
-      <c r="F11" s="3" t="n"/>
+      <c r="F11" s="3">
+        <f>75.4</f>
+        <v/>
+      </c>
       <c r="G11" s="1" t="n"/>
       <c r="H11" s="1" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="1" t="n"/>
-      <c r="K11" s="3" t="n"/>
+      <c r="I11" s="1" t="n"/>
+      <c r="J11" s="3">
+        <f>75.4</f>
+        <v/>
+      </c>
+      <c r="K11" s="1" t="n"/>
       <c r="L11" s="1" t="n"/>
       <c r="M11" s="1" t="n"/>
       <c r="N11" s="3">
@@ -2699,15 +2570,21 @@
         </is>
       </c>
       <c r="B12" s="1" t="n"/>
-      <c r="C12" s="3" t="n"/>
+      <c r="C12" s="1" t="n"/>
       <c r="D12" s="1" t="n"/>
       <c r="E12" s="1" t="n"/>
-      <c r="F12" s="3" t="n"/>
+      <c r="F12" s="3">
+        <f>26.57</f>
+        <v/>
+      </c>
       <c r="G12" s="1" t="n"/>
       <c r="H12" s="1" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="1" t="n"/>
-      <c r="K12" s="3" t="n"/>
+      <c r="I12" s="1" t="n"/>
+      <c r="J12" s="3">
+        <f>26.57</f>
+        <v/>
+      </c>
+      <c r="K12" s="1" t="n"/>
       <c r="L12" s="1" t="n"/>
       <c r="M12" s="1" t="n"/>
       <c r="N12" s="3">
@@ -2731,15 +2608,21 @@
         </is>
       </c>
       <c r="B13" s="1" t="n"/>
-      <c r="C13" s="3" t="n"/>
+      <c r="C13" s="1" t="n"/>
       <c r="D13" s="1" t="n"/>
       <c r="E13" s="1" t="n"/>
-      <c r="F13" s="3" t="n"/>
+      <c r="F13" s="3">
+        <f>18.75</f>
+        <v/>
+      </c>
       <c r="G13" s="1" t="n"/>
       <c r="H13" s="1" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="1" t="n"/>
-      <c r="K13" s="3" t="n"/>
+      <c r="I13" s="1" t="n"/>
+      <c r="J13" s="3">
+        <f>18.75</f>
+        <v/>
+      </c>
+      <c r="K13" s="1" t="n"/>
       <c r="L13" s="1" t="n"/>
       <c r="M13" s="1" t="n"/>
       <c r="N13" s="3">
@@ -2763,15 +2646,21 @@
         </is>
       </c>
       <c r="B14" s="1" t="n"/>
-      <c r="C14" s="3" t="n"/>
+      <c r="C14" s="1" t="n"/>
       <c r="D14" s="1" t="n"/>
       <c r="E14" s="1" t="n"/>
-      <c r="F14" s="3" t="n"/>
+      <c r="F14" s="3">
+        <f>200+200</f>
+        <v/>
+      </c>
       <c r="G14" s="1" t="n"/>
       <c r="H14" s="1" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="1" t="n"/>
-      <c r="K14" s="3" t="n"/>
+      <c r="I14" s="1" t="n"/>
+      <c r="J14" s="3">
+        <f>200+200</f>
+        <v/>
+      </c>
+      <c r="K14" s="1" t="n"/>
       <c r="L14" s="1" t="n"/>
       <c r="M14" s="1" t="n"/>
       <c r="N14" s="3">
@@ -2795,15 +2684,21 @@
         </is>
       </c>
       <c r="B15" s="1" t="n"/>
-      <c r="C15" s="3" t="n"/>
+      <c r="C15" s="1" t="n"/>
       <c r="D15" s="1" t="n"/>
       <c r="E15" s="1" t="n"/>
-      <c r="F15" s="3" t="n"/>
+      <c r="F15" s="3">
+        <f>490+120</f>
+        <v/>
+      </c>
       <c r="G15" s="1" t="n"/>
       <c r="H15" s="1" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="1" t="n"/>
-      <c r="K15" s="3" t="n"/>
+      <c r="I15" s="1" t="n"/>
+      <c r="J15" s="3">
+        <f>490+120</f>
+        <v/>
+      </c>
+      <c r="K15" s="1" t="n"/>
       <c r="L15" s="1" t="n"/>
       <c r="M15" s="1" t="n"/>
       <c r="N15" s="3">
@@ -2827,15 +2722,21 @@
         </is>
       </c>
       <c r="B16" s="1" t="n"/>
-      <c r="C16" s="3" t="n"/>
+      <c r="C16" s="1" t="n"/>
       <c r="D16" s="1" t="n"/>
       <c r="E16" s="1" t="n"/>
-      <c r="F16" s="3" t="n"/>
+      <c r="F16" s="3">
+        <f>16.25</f>
+        <v/>
+      </c>
       <c r="G16" s="1" t="n"/>
       <c r="H16" s="1" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="1" t="n"/>
-      <c r="K16" s="3" t="n"/>
+      <c r="I16" s="1" t="n"/>
+      <c r="J16" s="3">
+        <f>16.25</f>
+        <v/>
+      </c>
+      <c r="K16" s="1" t="n"/>
       <c r="L16" s="1" t="n"/>
       <c r="M16" s="1" t="n"/>
       <c r="N16" s="3">
@@ -2859,15 +2760,21 @@
         </is>
       </c>
       <c r="B17" s="1" t="n"/>
-      <c r="C17" s="3" t="n"/>
+      <c r="C17" s="1" t="n"/>
       <c r="D17" s="1" t="n"/>
       <c r="E17" s="1" t="n"/>
-      <c r="F17" s="3" t="n"/>
+      <c r="F17" s="3">
+        <f>800+800</f>
+        <v/>
+      </c>
       <c r="G17" s="1" t="n"/>
       <c r="H17" s="1" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="1" t="n"/>
-      <c r="K17" s="3" t="n"/>
+      <c r="I17" s="1" t="n"/>
+      <c r="J17" s="3">
+        <f>800+800</f>
+        <v/>
+      </c>
+      <c r="K17" s="1" t="n"/>
       <c r="L17" s="1" t="n"/>
       <c r="M17" s="1" t="n"/>
       <c r="N17" s="3">
@@ -2891,15 +2798,21 @@
         </is>
       </c>
       <c r="B18" s="1" t="n"/>
-      <c r="C18" s="3" t="n"/>
+      <c r="C18" s="1" t="n"/>
       <c r="D18" s="1" t="n"/>
       <c r="E18" s="1" t="n"/>
-      <c r="F18" s="3" t="n"/>
+      <c r="F18" s="3">
+        <f>817.29</f>
+        <v/>
+      </c>
       <c r="G18" s="1" t="n"/>
       <c r="H18" s="1" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="1" t="n"/>
-      <c r="K18" s="3" t="n"/>
+      <c r="I18" s="1" t="n"/>
+      <c r="J18" s="3">
+        <f>817.29</f>
+        <v/>
+      </c>
+      <c r="K18" s="1" t="n"/>
       <c r="L18" s="1" t="n"/>
       <c r="M18" s="1" t="n"/>
       <c r="N18" s="3">
@@ -2923,15 +2836,21 @@
         </is>
       </c>
       <c r="B19" s="1" t="n"/>
-      <c r="C19" s="3" t="n"/>
+      <c r="C19" s="1" t="n"/>
       <c r="D19" s="1" t="n"/>
       <c r="E19" s="1" t="n"/>
-      <c r="F19" s="3" t="n"/>
+      <c r="F19" s="3">
+        <f>930.52</f>
+        <v/>
+      </c>
       <c r="G19" s="1" t="n"/>
       <c r="H19" s="1" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="1" t="n"/>
-      <c r="K19" s="3" t="n"/>
+      <c r="I19" s="1" t="n"/>
+      <c r="J19" s="3">
+        <f>930.52</f>
+        <v/>
+      </c>
+      <c r="K19" s="1" t="n"/>
       <c r="L19" s="1" t="n"/>
       <c r="M19" s="1" t="n"/>
       <c r="N19" s="3">
@@ -2955,15 +2874,21 @@
         </is>
       </c>
       <c r="B20" s="1" t="n"/>
-      <c r="C20" s="3" t="n"/>
+      <c r="C20" s="1" t="n"/>
       <c r="D20" s="1" t="n"/>
       <c r="E20" s="1" t="n"/>
-      <c r="F20" s="3" t="n"/>
+      <c r="F20" s="3">
+        <f>975</f>
+        <v/>
+      </c>
       <c r="G20" s="1" t="n"/>
       <c r="H20" s="1" t="n"/>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="1" t="n"/>
-      <c r="K20" s="3" t="n"/>
+      <c r="I20" s="1" t="n"/>
+      <c r="J20" s="3">
+        <f>975</f>
+        <v/>
+      </c>
+      <c r="K20" s="1" t="n"/>
       <c r="L20" s="1" t="n"/>
       <c r="M20" s="1" t="n"/>
       <c r="N20" s="3">
@@ -2976,503 +2901,146 @@
         </is>
       </c>
       <c r="P20" s="6">
-        <f>975+364.75+1400</f>
+        <f>975</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Amazon.Comseattlewa US</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="1" t="n"/>
-      <c r="E21" s="1" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="1" t="n"/>
-      <c r="H21" s="1" t="n"/>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="1" t="n"/>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="1" t="n"/>
-      <c r="M21" s="1" t="n"/>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B21" s="3">
+        <f>SUM(B2:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="3">
+        <f>SUM(C2:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="3">
+        <f>SUM(D2:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="3">
+        <f>SUM(E2:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="3">
+        <f>SUM(F2:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="3">
+        <f>SUM(G2:G20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="3">
+        <f>SUM(H2:H20)</f>
+        <v/>
+      </c>
+      <c r="I21" s="3">
+        <f>SUM(I2:I20)</f>
+        <v/>
+      </c>
+      <c r="J21" s="3">
+        <f>SUM(J2:J20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="3">
+        <f>SUM(K2:K20)</f>
+        <v/>
+      </c>
+      <c r="L21" s="3">
+        <f>SUM(L2:L20)</f>
+        <v/>
+      </c>
+      <c r="M21" s="3">
+        <f>SUM(M2:M20)</f>
+        <v/>
+      </c>
       <c r="N21" s="3">
         <f>SUM(B21,C21,D21,E21,F21,G21,H21,I21,J21,K21,L21,M21)</f>
         <v/>
       </c>
-      <c r="O21" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="P21" s="6">
-        <f>117.76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Yr6 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="1" t="n"/>
-      <c r="E22" s="1" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="1" t="n"/>
-      <c r="H22" s="1" t="n"/>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="1" t="n"/>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="1" t="n"/>
-      <c r="M22" s="1" t="n"/>
-      <c r="N22" s="3">
-        <f>SUM(B22,C22,D22,E22,F22,G22,H22,I22,J22,K22,L22,M22)</f>
-        <v/>
-      </c>
-      <c r="O22" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="P22" s="6">
-        <f>13.79</f>
-        <v/>
-      </c>
-    </row>
+      <c r="O21" s="1" t="n"/>
+      <c r="P21" s="1">
+        <f>SUM(P2:P13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>Arrow Bank Na Web Pmt</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="1" t="n"/>
-      <c r="E23" s="1" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="1" t="n"/>
-      <c r="H23" s="1" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="1" t="n"/>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="1" t="n"/>
-      <c r="M23" s="1" t="n"/>
-      <c r="N23" s="3">
-        <f>SUM(B23,C23,D23,E23,F23,G23,H23,I23,J23,K23,L23,M23)</f>
-        <v/>
-      </c>
-      <c r="O23" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="P23" s="6">
-        <f>703</f>
-        <v/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BEGIN</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*TN0 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="1" t="n"/>
-      <c r="E24" s="1" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="1" t="n"/>
-      <c r="H24" s="1" t="n"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="1" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="1" t="n"/>
-      <c r="M24" s="1" t="n"/>
-      <c r="N24" s="3">
-        <f>SUM(B24,C24,D24,E24,F24,G24,H24,I24,J24,K24,L24,M24)</f>
-        <v/>
-      </c>
-      <c r="O24" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="P24" s="6" t="n"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="B24">
+        <f>B21</f>
+        <v/>
+      </c>
+      <c r="C24">
+        <f>C21</f>
+        <v/>
+      </c>
+      <c r="D24">
+        <f>D21</f>
+        <v/>
+      </c>
+      <c r="E24">
+        <f>E21</f>
+        <v/>
+      </c>
+      <c r="F24">
+        <f>F21</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>G21</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>H21</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>I21</f>
+        <v/>
+      </c>
+      <c r="J24">
+        <f>J21</f>
+        <v/>
+      </c>
+      <c r="K24">
+        <f>K21</f>
+        <v/>
+      </c>
+      <c r="L24">
+        <f>L21</f>
+        <v/>
+      </c>
+      <c r="M24">
+        <f>M21</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Mz5 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="1" t="n"/>
-      <c r="E25" s="1" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="1" t="n"/>
-      <c r="H25" s="1" t="n"/>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="1" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="1" t="n"/>
-      <c r="M25" s="1" t="n"/>
-      <c r="N25" s="3">
-        <f>SUM(B25,C25,D25,E25,F25,G25,H25,I25,J25,K25,L25,M25)</f>
-        <v/>
-      </c>
-      <c r="O25" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="P25" s="6" t="n"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LESS</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Ge2 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="1" t="n"/>
-      <c r="E26" s="1" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="1" t="n"/>
-      <c r="H26" s="1" t="n"/>
-      <c r="I26" s="3" t="n"/>
-      <c r="J26" s="1" t="n"/>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="1" t="n"/>
-      <c r="M26" s="1" t="n"/>
-      <c r="N26" s="3">
-        <f>SUM(B26,C26,D26,E26,F26,G26,H26,I26,J26,K26,L26,M26)</f>
-        <v/>
-      </c>
-      <c r="O26" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="P26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*V25 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="1" t="n"/>
-      <c r="E27" s="1" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="1" t="n"/>
-      <c r="H27" s="1" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="1" t="n"/>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="1" t="n"/>
-      <c r="M27" s="1" t="n"/>
-      <c r="N27" s="3">
-        <f>SUM(B27,C27,D27,E27,F27,G27,H27,I27,J27,K27,L27,M27)</f>
-        <v/>
-      </c>
-      <c r="O27" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="P27" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Za2 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="1" t="n"/>
-      <c r="E28" s="1" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="1" t="n"/>
-      <c r="H28" s="1" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="1" t="n"/>
-      <c r="K28" s="3" t="n"/>
-      <c r="L28" s="1" t="n"/>
-      <c r="M28" s="1" t="n"/>
-      <c r="N28" s="3">
-        <f>SUM(B28,C28,D28,E28,F28,G28,H28,I28,J28,K28,L28,M28)</f>
-        <v/>
-      </c>
-      <c r="O28" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="P28" s="6" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Au5 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="1" t="n"/>
-      <c r="E29" s="1" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="1" t="n"/>
-      <c r="H29" s="1" t="n"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="1" t="n"/>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="1" t="n"/>
-      <c r="M29" s="1" t="n"/>
-      <c r="N29" s="3">
-        <f>SUM(B29,C29,D29,E29,F29,G29,H29,I29,J29,K29,L29,M29)</f>
-        <v/>
-      </c>
-      <c r="O29" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="P29" s="6" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>POS Mac Amazon.Com*Bq9 Seattle WA</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="1" t="n"/>
-      <c r="E30" s="1" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="1" t="n"/>
-      <c r="H30" s="1" t="n"/>
-      <c r="I30" s="3" t="n"/>
-      <c r="J30" s="1" t="n"/>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="1" t="n"/>
-      <c r="M30" s="1" t="n"/>
-      <c r="N30" s="3">
-        <f>SUM(B30,C30,D30,E30,F30,G30,H30,I30,J30,K30,L30,M30)</f>
-        <v/>
-      </c>
-      <c r="O30" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="P30" s="6" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>Bill Pay:New York State Ins 237224 4Bq1P6Kr</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="1" t="n"/>
-      <c r="E31" s="1" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="1" t="n"/>
-      <c r="H31" s="1" t="n"/>
-      <c r="I31" s="3" t="n"/>
-      <c r="J31" s="1" t="n"/>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="1" t="n"/>
-      <c r="M31" s="1" t="n"/>
-      <c r="N31" s="3">
-        <f>SUM(B31,C31,D31,E31,F31,G31,H31,I31,J31,K31,L31,M31)</f>
-        <v/>
-      </c>
-      <c r="O31" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="P31" s="6" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Amazon.Com*N22Fjseattlewa US</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="1" t="n"/>
-      <c r="E32" s="1" t="n"/>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="1" t="n"/>
-      <c r="H32" s="1" t="n"/>
-      <c r="I32" s="3" t="n"/>
-      <c r="J32" s="1" t="n"/>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="1" t="n"/>
-      <c r="M32" s="1" t="n"/>
-      <c r="N32" s="3">
-        <f>SUM(B32,C32,D32,E32,F32,G32,H32,I32,J32,K32,L32,M32)</f>
-        <v/>
-      </c>
-      <c r="O32" s="1" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="P32" s="6" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B33" s="3">
-        <f>SUM(B2:B32)</f>
-        <v/>
-      </c>
-      <c r="C33" s="3">
-        <f>SUM(C2:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="3">
-        <f>SUM(D2:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="3">
-        <f>SUM(E2:E32)</f>
-        <v/>
-      </c>
-      <c r="F33" s="3">
-        <f>SUM(F2:F32)</f>
-        <v/>
-      </c>
-      <c r="G33" s="3">
-        <f>SUM(G2:G32)</f>
-        <v/>
-      </c>
-      <c r="H33" s="3">
-        <f>SUM(H2:H32)</f>
-        <v/>
-      </c>
-      <c r="I33" s="3">
-        <f>SUM(I2:I32)</f>
-        <v/>
-      </c>
-      <c r="J33" s="3">
-        <f>SUM(J2:J32)</f>
-        <v/>
-      </c>
-      <c r="K33" s="3">
-        <f>SUM(K2:K32)</f>
-        <v/>
-      </c>
-      <c r="L33" s="3">
-        <f>SUM(L2:L32)</f>
-        <v/>
-      </c>
-      <c r="M33" s="3">
-        <f>SUM(M2:M32)</f>
-        <v/>
-      </c>
-      <c r="N33" s="3">
-        <f>SUM(B33,C33,D33,E33,F33,G33,H33,I33,J33,K33,L33,M33)</f>
-        <v/>
-      </c>
-      <c r="O33" s="1" t="n"/>
-      <c r="P33" s="1">
-        <f>SUM(P2:P13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>BEGIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="B36">
-        <f>B14</f>
-        <v/>
-      </c>
-      <c r="C36" s="6">
-        <f>C14</f>
-        <v/>
-      </c>
-      <c r="D36">
-        <f>D14</f>
-        <v/>
-      </c>
-      <c r="E36">
-        <f>E14</f>
-        <v/>
-      </c>
-      <c r="F36">
-        <f>F14</f>
-        <v/>
-      </c>
-      <c r="G36">
-        <f>G14</f>
-        <v/>
-      </c>
-      <c r="H36">
-        <f>H14</f>
-        <v/>
-      </c>
-      <c r="I36">
-        <f>I14</f>
-        <v/>
-      </c>
-      <c r="J36">
-        <f>J14</f>
-        <v/>
-      </c>
-      <c r="K36">
-        <f>K14</f>
-        <v/>
-      </c>
-      <c r="L36">
-        <f>L14</f>
-        <v/>
-      </c>
-      <c r="M36">
-        <f>M14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>LESS</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>END</t>
         </is>

--- a/credit_monthly_summary.xlsx
+++ b/credit_monthly_summary.xlsx
@@ -1438,9 +1438,15 @@
         <v/>
       </c>
       <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
+      <c r="K14" s="4">
+        <f>4000.00</f>
+        <v/>
+      </c>
       <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
+      <c r="M14" s="4">
+        <f>4000.00</f>
+        <v/>
+      </c>
       <c r="N14" s="4">
         <f>SUM(B14,C14,D14,E14,F14,G14,H14,I14,J14,K14,L14,M14)</f>
         <v/>
@@ -1478,9 +1484,15 @@
         <v/>
       </c>
       <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
+      <c r="K15" s="4">
+        <f>385.77</f>
+        <v/>
+      </c>
       <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="n"/>
+      <c r="M15" s="4">
+        <f>385.77</f>
+        <v/>
+      </c>
       <c r="N15" s="4">
         <f>SUM(B15,C15,D15,E15,F15,G15,H15,I15,J15,K15,L15,M15)</f>
         <v/>
@@ -1586,9 +1598,15 @@
         <v/>
       </c>
       <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
+      <c r="K18" s="4">
+        <f>3800.00</f>
+        <v/>
+      </c>
       <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
+      <c r="M18" s="4">
+        <f>3800.00</f>
+        <v/>
+      </c>
       <c r="N18" s="4">
         <f>SUM(B18,C18,D18,E18,F18,G18,H18,I18,J18,K18,L18,M18)</f>
         <v/>
@@ -1762,9 +1780,15 @@
         <v/>
       </c>
       <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
+      <c r="K23" s="4">
+        <f>55.00</f>
+        <v/>
+      </c>
       <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="n"/>
+      <c r="M23" s="4">
+        <f>55.00</f>
+        <v/>
+      </c>
       <c r="N23" s="4">
         <f>SUM(B23,C23,D23,E23,F23,G23,H23,I23,J23,K23,L23,M23)</f>
         <v/>
@@ -2244,9 +2268,15 @@
         <v/>
       </c>
       <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
+      <c r="K37" s="4">
+        <f>578.00</f>
+        <v/>
+      </c>
       <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="n"/>
+      <c r="M37" s="4">
+        <f>578.00</f>
+        <v/>
+      </c>
       <c r="N37" s="4">
         <f>SUM(B37,C37,D37,E37,F37,G37,H37,I37,J37,K37,L37,M37)</f>
         <v/>
@@ -2284,9 +2314,15 @@
         <v/>
       </c>
       <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
+      <c r="K38" s="4">
+        <f>109.43</f>
+        <v/>
+      </c>
       <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n"/>
+      <c r="M38" s="4">
+        <f>109.43</f>
+        <v/>
+      </c>
       <c r="N38" s="4">
         <f>SUM(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38)</f>
         <v/>
@@ -2324,9 +2360,15 @@
         <v/>
       </c>
       <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
+      <c r="K39" s="4">
+        <f>13.79</f>
+        <v/>
+      </c>
       <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="n"/>
+      <c r="M39" s="4">
+        <f>13.79</f>
+        <v/>
+      </c>
       <c r="N39" s="4">
         <f>SUM(B39,C39,D39,E39,F39,G39,H39,I39,J39,K39,L39,M39)</f>
         <v/>
@@ -2364,9 +2406,15 @@
         <v/>
       </c>
       <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="n"/>
+      <c r="K40" s="4">
+        <f>703.00</f>
+        <v/>
+      </c>
       <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="n"/>
+      <c r="M40" s="4">
+        <f>703.00</f>
+        <v/>
+      </c>
       <c r="N40" s="4">
         <f>SUM(B40,C40,D40,E40,F40,G40,H40,I40,J40,K40,L40,M40)</f>
         <v/>
@@ -2404,9 +2452,15 @@
         <v/>
       </c>
       <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
+      <c r="K41" s="4">
+        <f>900.00</f>
+        <v/>
+      </c>
       <c r="L41" s="2" t="n"/>
-      <c r="M41" s="2" t="n"/>
+      <c r="M41" s="4">
+        <f>900.00</f>
+        <v/>
+      </c>
       <c r="N41" s="4">
         <f>SUM(B41,C41,D41,E41,F41,G41,H41,I41,J41,K41,L41,M41)</f>
         <v/>
@@ -2444,9 +2498,15 @@
         <v/>
       </c>
       <c r="J42" s="2" t="n"/>
-      <c r="K42" s="2" t="n"/>
+      <c r="K42" s="4">
+        <f>1000.00</f>
+        <v/>
+      </c>
       <c r="L42" s="2" t="n"/>
-      <c r="M42" s="2" t="n"/>
+      <c r="M42" s="4">
+        <f>1000.00</f>
+        <v/>
+      </c>
       <c r="N42" s="4">
         <f>SUM(B42,C42,D42,E42,F42,G42,H42,I42,J42,K42,L42,M42)</f>
         <v/>
@@ -2484,9 +2544,15 @@
         <v/>
       </c>
       <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="n"/>
+      <c r="K43" s="4">
+        <f>300.00</f>
+        <v/>
+      </c>
       <c r="L43" s="2" t="n"/>
-      <c r="M43" s="2" t="n"/>
+      <c r="M43" s="4">
+        <f>300.00</f>
+        <v/>
+      </c>
       <c r="N43" s="4">
         <f>SUM(B43,C43,D43,E43,F43,G43,H43,I43,J43,K43,L43,M43)</f>
         <v/>
@@ -2524,9 +2590,15 @@
         <v/>
       </c>
       <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="n"/>
+      <c r="K44" s="4">
+        <f>723.00</f>
+        <v/>
+      </c>
       <c r="L44" s="2" t="n"/>
-      <c r="M44" s="2" t="n"/>
+      <c r="M44" s="4">
+        <f>723.00</f>
+        <v/>
+      </c>
       <c r="N44" s="4">
         <f>SUM(B44,C44,D44,E44,F44,G44,H44,I44,J44,K44,L44,M44)</f>
         <v/>
@@ -2564,9 +2636,15 @@
         <v/>
       </c>
       <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="n"/>
+      <c r="K45" s="4">
+        <f>2400.00</f>
+        <v/>
+      </c>
       <c r="L45" s="2" t="n"/>
-      <c r="M45" s="2" t="n"/>
+      <c r="M45" s="4">
+        <f>2400.00</f>
+        <v/>
+      </c>
       <c r="N45" s="4">
         <f>SUM(B45,C45,D45,E45,F45,G45,H45,I45,J45,K45,L45,M45)</f>
         <v/>
@@ -2604,9 +2682,15 @@
         <v/>
       </c>
       <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
+      <c r="K46" s="4">
+        <f>220.00</f>
+        <v/>
+      </c>
       <c r="L46" s="2" t="n"/>
-      <c r="M46" s="2" t="n"/>
+      <c r="M46" s="4">
+        <f>220.00</f>
+        <v/>
+      </c>
       <c r="N46" s="4">
         <f>SUM(B46,C46,D46,E46,F46,G46,H46,I46,J46,K46,L46,M46)</f>
         <v/>
@@ -2644,9 +2728,15 @@
         <v/>
       </c>
       <c r="J47" s="2" t="n"/>
-      <c r="K47" s="2" t="n"/>
+      <c r="K47" s="4">
+        <f>833.81</f>
+        <v/>
+      </c>
       <c r="L47" s="2" t="n"/>
-      <c r="M47" s="2" t="n"/>
+      <c r="M47" s="4">
+        <f>833.81</f>
+        <v/>
+      </c>
       <c r="N47" s="4">
         <f>SUM(B47,C47,D47,E47,F47,G47,H47,I47,J47,K47,L47,M47)</f>
         <v/>
@@ -2684,9 +2774,15 @@
         <v/>
       </c>
       <c r="J48" s="2" t="n"/>
-      <c r="K48" s="2" t="n"/>
+      <c r="K48" s="4">
+        <f>4589.17</f>
+        <v/>
+      </c>
       <c r="L48" s="2" t="n"/>
-      <c r="M48" s="2" t="n"/>
+      <c r="M48" s="4">
+        <f>4589.17</f>
+        <v/>
+      </c>
       <c r="N48" s="4">
         <f>SUM(B48,C48,D48,E48,F48,G48,H48,I48,J48,K48,L48,M48)</f>
         <v/>
